--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>shared_target_count</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>shared_target_count</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -742,15 +742,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>https://www.rofenashim.co.il/faq/faq-fertility/</t>
         </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>6</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
@@ -891,15 +891,15 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>355023</v>
-      </c>
-      <c r="AE3" t="inlineStr">
+        <v>1065069</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>https://www.e-piryon.com/</t>
         </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -1040,15 +1040,15 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>242838</v>
-      </c>
-      <c r="AE4" t="inlineStr">
+        <v>728514</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>https://www.profyinoncohen.com/</t>
         </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>2</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
@@ -1187,15 +1187,15 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE5" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>https://www.leidaraka.co.il/</t>
         </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>3</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1334,15 +1334,15 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE6" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>https://kerenzohar.com/%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>2</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1483,15 +1483,15 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE7" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>https://hmc.co.il/doctor/%D7%A4%D7%A8%D7%95%D7%A4-%D7%93%D7%95%D7%93-%D7%9C%D7%91-%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>19</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -1630,15 +1630,15 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE8" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>https://www.israelidoula.co.il/courses-1/embryo-%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>7</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1779,15 +1779,15 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>236925</v>
-      </c>
-      <c r="AE9" t="inlineStr">
+        <v>710775</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>https://www.dr-paz.co.il/</t>
         </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>2</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
@@ -1926,15 +1926,15 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE10" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>https://www.israelivf.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>17</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
@@ -2065,15 +2065,15 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE11" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>https://www.shvil-haleida.co.il/%D7%A8%D7%99%D7%A9%D7%95%D7%9D-%D7%9C%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%9C%D7%99%D7%93%D7%94/</t>
         </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
@@ -2214,15 +2214,15 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE12" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94-9/</t>
         </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
@@ -2353,15 +2353,15 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE13" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>https://harechem.com/</t>
         </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>3</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
@@ -2496,15 +2496,15 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE14" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF14" t="inlineStr">
         <is>
           <t>http://www.amotatchen.org/</t>
         </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>3</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
@@ -2645,15 +2645,15 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE15" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
@@ -2794,15 +2794,15 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE16" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>https://dinadoula.com/%D7%93%D7%95%D7%9C%D7%94/</t>
         </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>2</v>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2943,15 +2943,15 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE17" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>https://www.surmom.co.il/%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/%D7%A4%D7%A8%D7%95%D7%A4-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F-%D7%90%D7%93%D7%A8%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
@@ -3092,15 +3092,15 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE18" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>https://hfhosp.org/he/%D7%A6%D7%95%D7%95%D7%AA-%D7%94%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/%D7%93%D7%A8-%D7%A0%D7%99%D7%A7%D7%95%D7%9C%D7%90-%D7%A4%D7%A8%D7%97</t>
         </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>5</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
@@ -3231,15 +3231,15 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE19" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>https://midwives.org.il/%D7%9C%D7%99%D7%95%D7%95%D7%99-%D7%9E%D7%A7%D7%A6%D7%95%D7%A2%D7%99-%D7%96%D7%94-%D7%9E%D7%99%D7%99%D7%9C%D7%93%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>9</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
@@ -3378,15 +3378,15 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE20" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>8</v>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
@@ -3525,15 +3525,15 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE21" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF21" t="n">
-        <v>11</v>
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
@@ -3664,15 +3664,15 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE22" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>https://www.israelibaby.co.il/where-to-get-birth</t>
         </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>11</v>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
@@ -3803,15 +3803,15 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE23" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF23" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/</t>
         </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>2</v>
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
@@ -3946,15 +3946,15 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE24" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF24" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/fertility-research/</t>
         </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>3</v>
       </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
@@ -4085,15 +4085,15 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE25" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>https://barakivf.com/</t>
         </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>3</v>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
@@ -4228,15 +4228,15 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE26" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>https://demayo.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94/</t>
         </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>3</v>
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
@@ -4375,15 +4375,15 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE27" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>https://bri.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/</t>
         </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>17</v>
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
@@ -4514,15 +4514,15 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE28" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>4</v>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
@@ -4653,15 +4653,15 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE29" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF29" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>4</v>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
@@ -4792,15 +4792,15 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE30" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF30" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>4</v>
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
@@ -4939,15 +4939,15 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE31" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF31" t="inlineStr">
         <is>
           <t>https://www.laniado.org.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%9C%D7%99%D7%93%D7%94-%D7%98%D7%91%D7%A2%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>2</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
@@ -5078,15 +5078,15 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE32" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=A6B809CAFEA13537A84D783709CF5EBB&amp;RequestId=00000000-0000-0000-0001-000000000325</t>
         </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>2</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
@@ -5217,15 +5217,15 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE33" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF33" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>8</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
@@ -5356,15 +5356,15 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE34" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF34" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%91%D7%9C%D7%94-%D7%A2%D7%91%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF34" t="n">
-        <v>2</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
@@ -5495,15 +5495,15 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE35" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF35" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%92%D7%9E%D7%95/</t>
         </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>2</v>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
@@ -5634,15 +5634,15 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE36" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%99%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>2</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -5773,15 +5773,15 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE37" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF37" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%9F-%D7%90%D7%A8%D7%99-%D7%A6%D7%90%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>2</v>
       </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
@@ -5912,15 +5912,15 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE38" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF38" t="n">
-        <v>2</v>
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
@@ -6051,15 +6051,15 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE39" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF39" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%95%D7%A8%D7%A0%D7%92%D7%95%D7%9C%D7%93-%D7%97%D7%99%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>2</v>
       </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
@@ -6190,15 +6190,15 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE40" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF40" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%9C%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF40" t="n">
-        <v>2</v>
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
@@ -6329,15 +6329,15 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE41" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%9C%D7%A0%D7%93%D7%94-%D7%A1%D7%95%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
@@ -6468,15 +6468,15 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE42" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF42" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%95%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%9C%D7%90/</t>
         </is>
-      </c>
-      <c r="AF42" t="n">
-        <v>2</v>
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
@@ -6607,15 +6607,15 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE43" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF43" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%9C%D7%99%D7%94-%D7%94%D7%95%D7%9C%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>2</v>
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
@@ -6746,15 +6746,15 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE44" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF44" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%9E%D7%99%D7%AA-%D7%93%D7%A0%D7%A1%D7%99%D7%95%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF44" t="n">
-        <v>2</v>
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
@@ -6885,15 +6885,15 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE45" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF45" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%9E%D7%95%D7%96%D7%A1-%D7%90%D7%9C%D7%91%D7%96/</t>
         </is>
-      </c>
-      <c r="AF45" t="n">
-        <v>2</v>
       </c>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
@@ -7024,15 +7024,15 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE46" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%A8%D7%95%D7%9F-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF46" t="n">
-        <v>2</v>
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
@@ -7163,15 +7163,15 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE47" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%99%D7%A2%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF47" t="n">
-        <v>2</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
@@ -7302,15 +7302,15 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE48" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF48" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%98%D7%94-%D7%A0%D7%95%D7%91%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF48" t="n">
-        <v>2</v>
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
@@ -7441,15 +7441,15 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE49" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%94-%D7%A4%D7%95%D7%9C%D7%99%D7%90%D7%A7%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF49" t="n">
-        <v>2</v>
       </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
@@ -7580,15 +7580,15 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE50" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF50" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%94-%D7%93%D7%9E%D7%A0%D7%98%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF50" t="n">
-        <v>2</v>
       </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
@@ -7719,15 +7719,15 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE51" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF51" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
         </is>
-      </c>
-      <c r="AF51" t="n">
-        <v>2</v>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
@@ -7858,15 +7858,15 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE52" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%96%D7%92%D7%95%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF52" t="n">
-        <v>2</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
@@ -7997,15 +7997,15 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE53" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF53" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8-%D7%95%D7%99%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF53" t="n">
-        <v>2</v>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
@@ -8136,15 +8136,15 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE54" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF54" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF54" t="n">
-        <v>2</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
@@ -8275,15 +8275,15 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE55" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF55" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%9C%D7%91%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF55" t="n">
-        <v>2</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
@@ -8414,15 +8414,15 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE56" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF56" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%90%D7%9D-%D7%9E%D7%95%D7%A8%D7%94-%D7%97%D7%9E%D7%90%D7%A8%D7%A9%D7%99/</t>
         </is>
-      </c>
-      <c r="AF56" t="n">
-        <v>2</v>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
@@ -8553,15 +8553,15 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE57" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF57" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%91%D7%A8%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF57" t="n">
-        <v>2</v>
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
@@ -8692,15 +8692,15 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE58" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF58" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%A6%D7%99%D7%91%D7%99%D7%90%D7%A7-%D7%93%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF58" t="n">
-        <v>2</v>
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
@@ -8831,15 +8831,15 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE59" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF59" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%9E%D7%95%D7%91%D7%A9%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF59" t="n">
-        <v>2</v>
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
@@ -8970,15 +8970,15 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE60" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF60" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%94-%D7%90%D7%96%D7%91%D7%A0%D7%93/</t>
         </is>
-      </c>
-      <c r="AF60" t="n">
-        <v>2</v>
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
@@ -9109,15 +9109,15 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE61" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%AA%D7%A9%D7%91%D7%A2-%D7%92%D7%A8%D7%A0%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF61" t="n">
-        <v>2</v>
       </c>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
@@ -9248,15 +9248,15 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE62" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%99%D7%9C%D7%99-%D7%90%D7%95%D7%91%D7%A8%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF62" t="n">
-        <v>2</v>
       </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
@@ -9387,15 +9387,15 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE63" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%9C%D7%99%D7%99%D7%A8-%D7%90%D7%9C%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF63" t="n">
-        <v>2</v>
       </c>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
@@ -9526,15 +9526,15 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE64" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF64" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%94%D7%A9%D7%9B%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF64" t="n">
-        <v>2</v>
       </c>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
@@ -9665,15 +9665,15 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE65" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF65" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%98%D7%9C-%D7%91%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF65" t="n">
-        <v>2</v>
       </c>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
@@ -9804,15 +9804,15 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE66" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF66" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%97%D7%95%D7%98%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF66" t="n">
-        <v>2</v>
       </c>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
@@ -9943,15 +9943,15 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE67" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF67" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%9C%D7%90%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF67" t="n">
-        <v>2</v>
       </c>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
@@ -10082,15 +10082,15 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE68" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF68" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%92%D7%93%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF68" t="n">
-        <v>2</v>
       </c>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
@@ -10221,15 +10221,15 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE69" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF69" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%9E%D7%A8%D7%90%D7%93/</t>
         </is>
-      </c>
-      <c r="AF69" t="n">
-        <v>2</v>
       </c>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
@@ -10360,15 +10360,15 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE70" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF70" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%A9%D7%95%D7%95%D7%A8%D7%A6%D7%91%D7%A8%D7%92/</t>
         </is>
-      </c>
-      <c r="AF70" t="n">
-        <v>2</v>
       </c>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
@@ -10499,15 +10499,15 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE71" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF71" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%99%D7%90%D7%9F-%D7%A9%D7%A4%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF71" t="n">
-        <v>2</v>
       </c>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
@@ -10638,15 +10638,15 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE72" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF72" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8-%D7%91%D7%99%D7%98%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF72" t="n">
-        <v>2</v>
       </c>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
@@ -10777,15 +10777,15 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE73" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF73" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8%D7%99%D7%9F-%D7%90%D7%9C%D7%A2%D7%93/</t>
         </is>
-      </c>
-      <c r="AF73" t="n">
-        <v>2</v>
       </c>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
@@ -10916,15 +10916,15 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE74" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF74" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/332/</t>
         </is>
-      </c>
-      <c r="AF74" t="n">
-        <v>2</v>
       </c>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
@@ -11055,15 +11055,15 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE75" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF75" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%91%D7%9F-%D7%A9%D7%A5-%D7%A4%D7%95%D7%A8%D7%A9%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF75" t="n">
-        <v>2</v>
       </c>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
@@ -11194,15 +11194,15 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE76" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF76" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%95%D7%95%D7%A8%D7%99%D7%99%D7%98/</t>
         </is>
-      </c>
-      <c r="AF76" t="n">
-        <v>2</v>
       </c>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
@@ -11333,15 +11333,15 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE77" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF77" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%99%D7%90%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF77" t="n">
-        <v>2</v>
       </c>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
@@ -11472,15 +11472,15 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE78" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF78" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%91%D7%92%D7%9C%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF78" t="n">
-        <v>2</v>
       </c>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
@@ -11611,15 +11611,15 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE79" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF79" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF79" t="n">
-        <v>2</v>
       </c>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
@@ -11750,15 +11750,15 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE80" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF80" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%9C%D7%A0%D7%94-%D7%A9%D7%99%D7%9C%D7%A7%D7%95/</t>
         </is>
-      </c>
-      <c r="AF80" t="n">
-        <v>2</v>
       </c>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
@@ -11889,15 +11889,15 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE81" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF81" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A2%D7%A0%D7%94-%D7%92%D7%95%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF81" t="n">
-        <v>2</v>
       </c>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
@@ -12028,15 +12028,15 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE82" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF82" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%91%D7%A8%D7%A7%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF82" t="n">
-        <v>2</v>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -12167,15 +12167,15 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE83" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF83" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A8%D7%96-%D7%92%D7%99%D7%9C%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF83" t="n">
-        <v>2</v>
       </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
@@ -12306,15 +12306,15 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE84" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF84" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A9%D7%91%D7%A2-%D7%92%D7%95%D7%A8%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF84" t="n">
-        <v>2</v>
       </c>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
@@ -12445,15 +12445,15 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE85" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF85" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%9C%D7%95%D7%A0%D7%92%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF85" t="n">
-        <v>2</v>
       </c>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
@@ -12584,15 +12584,15 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE86" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF86" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%9F-%D7%A9%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF86" t="n">
-        <v>2</v>
       </c>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
@@ -12723,15 +12723,15 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE87" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF87" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%94-%D7%90%D7%99%D7%AA%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF87" t="n">
-        <v>2</v>
       </c>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
@@ -12862,15 +12862,15 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE88" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF88" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%95%D7%A0%D7%94-%D7%95%D7%92%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF88" t="n">
-        <v>2</v>
       </c>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
@@ -13001,15 +13001,15 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE89" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF89" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%90%D7%9C%D7%94-%D7%99%D7%A8%D7%A7%D7%95%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF89" t="n">
-        <v>2</v>
       </c>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
@@ -13140,15 +13140,15 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE90" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF90" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A1%D7%AA%D7%A8-%D7%A4%D7%9C%D7%99%D7%99%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF90" t="n">
-        <v>2</v>
       </c>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
@@ -13279,15 +13279,15 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE91" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF91" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%AA%D7%99-%D7%A1%D7%93%D7%9F-%D7%A7%D7%A0%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF91" t="n">
-        <v>2</v>
       </c>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
@@ -13418,15 +13418,15 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE92" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF92" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A4%D7%A8%D7%A0%D7%A1%D7%99%D7%A1-%D7%A4%D7%A8%D7%9F-%D7%91%D7%A8%D7%95%D7%A0%D7%A9%D7%98%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF92" t="n">
-        <v>2</v>
       </c>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
@@ -13557,15 +13557,15 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE93" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF93" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%91%D7%99-%D7%A4%D7%99%D7%A9%D7%9E%D7%9F-%D7%A4%D7%95%D7%A1%D7%91%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF93" t="n">
-        <v>2</v>
       </c>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
@@ -13696,15 +13696,15 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE94" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF94" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99-%D7%A7%D7%9E%D7%97%D7%99/</t>
         </is>
-      </c>
-      <c r="AF94" t="n">
-        <v>2</v>
       </c>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
@@ -13835,15 +13835,15 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE95" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF95" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%90%D7%A4%D7%9C%D7%91%D7%95%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF95" t="n">
-        <v>2</v>
       </c>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
@@ -13974,15 +13974,15 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE96" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF96" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%AA-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF96" t="n">
-        <v>2</v>
       </c>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
@@ -14113,15 +14113,15 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE97" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF97" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF97" t="n">
-        <v>2</v>
       </c>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
@@ -14252,15 +14252,15 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE98" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF98" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%90%D7%99%D7%94-%D7%92%D7%95%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF98" t="n">
-        <v>2</v>
       </c>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
@@ -14391,15 +14391,15 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE99" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF99" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%94-%D7%90%D7%95%D7%A0%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF99" t="n">
-        <v>2</v>
       </c>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
@@ -14530,15 +14530,15 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE100" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF100" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%99%D7%94-%D7%93%D7%95%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF100" t="n">
-        <v>2</v>
       </c>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
@@ -14669,15 +14669,15 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE101" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF101" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%AA%D7%99%D7%AA-%D7%A9%D7%A4%D7%A8%D7%9C%D7%99%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF101" t="n">
-        <v>2</v>
       </c>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
@@ -14808,15 +14808,15 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE102" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF102" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%9E%D7%95%D7%99%D7%90%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF102" t="n">
-        <v>2</v>
       </c>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
@@ -14947,15 +14947,15 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE103" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF103" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%98%D7%A1%D7%94/</t>
         </is>
-      </c>
-      <c r="AF103" t="n">
-        <v>2</v>
       </c>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
@@ -15086,15 +15086,15 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE104" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF104" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1%D7%94-%D7%A4%D7%97%D7%9C%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF104" t="n">
-        <v>2</v>
       </c>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
@@ -15225,15 +15225,15 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE105" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF105" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%A0%D7%94-%D7%94%D7%A8%D7%95%D7%A9/</t>
         </is>
-      </c>
-      <c r="AF105" t="n">
-        <v>2</v>
       </c>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
@@ -15364,15 +15364,15 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE106" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF106" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%99-%D7%94%D7%A8%D7%A4%D7%96/</t>
         </is>
-      </c>
-      <c r="AF106" t="n">
-        <v>2</v>
       </c>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
@@ -15503,15 +15503,15 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE107" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF107" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9E%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF107" t="n">
-        <v>2</v>
       </c>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
@@ -15642,15 +15642,15 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE108" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF108" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%99%D7%9C%D7%94-%D7%9C%D7%91-%D7%A8%D7%9F-%D7%97%D7%95%D7%AA%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF108" t="n">
-        <v>2</v>
       </c>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
@@ -15781,15 +15781,15 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE109" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF109" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%95%D7%93%D7%99%D7%94-%D7%90%D7%99%D7%AA%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF109" t="n">
-        <v>2</v>
       </c>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
@@ -15920,15 +15920,15 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE110" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF110" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%9C-%D7%91%D7%95%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF110" t="n">
-        <v>2</v>
       </c>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
@@ -16059,15 +16059,15 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE111" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF111" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%A8-%D7%A7%D7%A8%D7%9F-%D7%A8%D7%98%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF111" t="n">
-        <v>2</v>
       </c>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
@@ -16198,15 +16198,15 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE112" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF112" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%B3%D7%95%D7%9C%D7%99-%D7%90%D7%A1%D7%AA%D7%99-%D7%A9%D7%9E%D7%A2%D7%95%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF112" t="n">
-        <v>2</v>
       </c>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
@@ -16337,15 +16337,15 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE113" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF113" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%95%D7%9C%D7%99-%D7%A7%D7%A8%D7%A7%D7%95/</t>
         </is>
-      </c>
-      <c r="AF113" t="n">
-        <v>2</v>
       </c>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
@@ -16476,15 +16476,15 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE114" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF114" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%92%D7%9C%D7%99%D7%9F-%D7%A1%D7%9C%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF114" t="n">
-        <v>2</v>
       </c>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
@@ -16615,15 +16615,15 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE115" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF115" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%92%D7%99%D7%91%D7%A8-%D7%A9%D7%92%D7%91/</t>
         </is>
-      </c>
-      <c r="AF115" t="n">
-        <v>2</v>
       </c>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
@@ -16754,15 +16754,15 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE116" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF116" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%A1%D7%9C%D7%91%D7%95%D7%93%D7%A0%D7%99%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF116" t="n">
-        <v>2</v>
       </c>
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
@@ -16893,15 +16893,15 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE117" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF117" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%95%D7%99%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF117" t="n">
-        <v>2</v>
       </c>
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
@@ -17032,15 +17032,15 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE118" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF118" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%90%D7%A0%D7%94-%D7%91%D7%A8%D7%99%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF118" t="n">
-        <v>2</v>
       </c>
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
@@ -17171,15 +17171,15 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE119" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF119" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99-%D7%90%D7%95%D7%A8-%D7%9C%D7%91%D7%A0%D7%96%D7%95%D7%9F-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF119" t="n">
-        <v>2</v>
       </c>
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
@@ -17310,15 +17310,15 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE120" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF120" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%A8%D7%95%D7%9F-%D7%A4%D7%99%D7%90%D7%97%D7%95%D7%98%D7%94-%D7%A1%D7%90%D7%9C%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF120" t="n">
-        <v>2</v>
       </c>
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
@@ -17449,15 +17449,15 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE121" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF121" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
         </is>
-      </c>
-      <c r="AF121" t="n">
-        <v>2</v>
       </c>
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
@@ -17588,15 +17588,15 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE122" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF122" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%94-%D7%A7%D7%95%D7%92%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF122" t="n">
-        <v>2</v>
       </c>
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
@@ -17727,15 +17727,15 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE123" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF123" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%90%D7%9F-%D7%A9%D7%95%D7%97%D7%98/</t>
         </is>
-      </c>
-      <c r="AF123" t="n">
-        <v>2</v>
       </c>
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
@@ -17866,15 +17866,15 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE124" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF124" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99-%D7%A2%D7%95%D7%96%D7%99%D7%90%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF124" t="n">
-        <v>2</v>
       </c>
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
@@ -18005,15 +18005,15 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE125" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF125" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF125" t="n">
-        <v>2</v>
       </c>
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
@@ -18144,15 +18144,15 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE126" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF126" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8-%D7%9C%D7%95%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF126" t="n">
-        <v>2</v>
       </c>
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
@@ -18283,15 +18283,15 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE127" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF127" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF127" t="n">
-        <v>2</v>
       </c>
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
@@ -18422,15 +18422,15 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE128" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF128" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%98%D7%95%D7%91-%D7%97%D7%99%D7%94-%D7%90%D7%99%D7%98%D7%94/</t>
         </is>
-      </c>
-      <c r="AF128" t="n">
-        <v>2</v>
       </c>
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
@@ -18561,15 +18561,15 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE129" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF129" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A2%D7%99%D7%99%D7%9F-%D7%90%D7%9C%D7%9E%D7%92%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF129" t="n">
-        <v>2</v>
       </c>
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
@@ -18700,15 +18700,15 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE130" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF130" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99-%D7%93%D7%A8%D7%95%D7%A7%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF130" t="n">
-        <v>2</v>
       </c>
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
@@ -18839,15 +18839,15 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE131" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF131" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%94-%D7%92%D7%95%D7%A8%D7%92%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF131" t="n">
-        <v>2</v>
       </c>
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
@@ -18978,15 +18978,15 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE132" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF132" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%99-%D7%90%D7%95%D7%A4%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF132" t="n">
-        <v>2</v>
       </c>
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
@@ -19117,15 +19117,15 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE133" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF133" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%A9%D7%97%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF133" t="n">
-        <v>2</v>
       </c>
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
@@ -19256,15 +19256,15 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE134" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF134" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%95%D7%A4%D7%A8%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF134" t="n">
-        <v>2</v>
       </c>
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
@@ -19395,15 +19395,15 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE135" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF135" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99-%D7%9C%D7%91-%D7%A7%D7%9C%D7%99%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF135" t="n">
-        <v>2</v>
       </c>
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
@@ -19534,15 +19534,15 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE136" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF136" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99%D7%94-%D7%90%D7%A0%D7%95%D7%9A/</t>
         </is>
-      </c>
-      <c r="AF136" t="n">
-        <v>2</v>
       </c>
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
@@ -19673,15 +19673,15 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE137" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF137" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%94-%D7%90%D7%99%D7%96%D7%A7%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF137" t="n">
-        <v>2</v>
       </c>
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
@@ -19812,15 +19812,15 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE138" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF138" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%91-%D7%A0%D7%97%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF138" t="n">
-        <v>2</v>
       </c>
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
@@ -19951,15 +19951,15 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE139" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF139" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99%D7%A1%D7%94-%D7%91%D7%A8-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF139" t="n">
-        <v>2</v>
       </c>
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
@@ -20090,15 +20090,15 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE140" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF140" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%9B%D7%9C-%D7%96%D7%99%D7%9C%D7%91%D7%A8%D7%9E%D7%9F-%D7%A8%D7%99%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF140" t="n">
-        <v>2</v>
       </c>
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
@@ -20229,15 +20229,15 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE141" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF141" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A7%D7%94-%D7%9B%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF141" t="n">
-        <v>2</v>
       </c>
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
@@ -20368,15 +20368,15 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE142" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF142" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99-%D7%A4%D7%91%D7%96%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF142" t="n">
-        <v>2</v>
       </c>
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
@@ -20507,15 +20507,15 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE143" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF143" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99%D7%AA-%D7%A8%D7%95%D7%96%D7%A0%D7%91%D7%90%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF143" t="n">
-        <v>2</v>
       </c>
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
@@ -20646,15 +20646,15 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE144" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF144" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8-%D7%92%D7%95%D7%9C%D7%93%D7%A0%D7%92%D7%95%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF144" t="n">
-        <v>2</v>
       </c>
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
@@ -20785,15 +20785,15 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE145" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF145" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%9E%D7%9C%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF145" t="n">
-        <v>2</v>
       </c>
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
@@ -20924,15 +20924,15 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE146" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF146" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%9C%D7%92%D7%99/</t>
         </is>
-      </c>
-      <c r="AF146" t="n">
-        <v>2</v>
       </c>
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
@@ -21063,15 +21063,15 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE147" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF147" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%95%D7%95%D7%9C%D7%A4%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF147" t="n">
-        <v>2</v>
       </c>
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr"/>
@@ -21202,15 +21202,15 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE148" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF148" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A2%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF148" t="n">
-        <v>2</v>
       </c>
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr"/>
@@ -21341,15 +21341,15 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE149" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF149" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A8%D7%99%D7%91%D7%9C%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF149" t="n">
-        <v>2</v>
       </c>
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
@@ -21480,15 +21480,15 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE150" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF150" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A8%D7%A7%D7%99%D7%A1-%D7%A0%D7%A4%D7%AA%D7%9C%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF150" t="n">
-        <v>2</v>
       </c>
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
@@ -21619,15 +21619,15 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE151" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF151" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%A7%D7%A9%D7%99%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF151" t="n">
-        <v>2</v>
       </c>
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
@@ -21758,15 +21758,15 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE152" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF152" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%91%D7%9F-%D7%A9%D7%A9%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF152" t="n">
-        <v>2</v>
       </c>
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
@@ -21897,15 +21897,15 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE153" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF153" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%A2-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF153" t="n">
-        <v>2</v>
       </c>
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
@@ -22036,15 +22036,15 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE154" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF154" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A0%D7%94-%D7%91%D7%AA%D7%90%D7%A9%D7%95%D7%99%D7%9C%D7%99/</t>
         </is>
-      </c>
-      <c r="AF154" t="n">
-        <v>2</v>
       </c>
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
@@ -22175,15 +22175,15 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE155" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF155" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A8%D7%99%D7%AA-%D7%90%D7%95%D7%9C%D7%99%D7%91%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF155" t="n">
-        <v>2</v>
       </c>
       <c r="AG155" t="inlineStr"/>
       <c r="AH155" t="inlineStr"/>
@@ -22314,15 +22314,15 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE156" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF156" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A6%D7%9F-%D7%99%D7%9E%D7%99%D7%A0%D7%99-%D7%97%D7%99/</t>
         </is>
-      </c>
-      <c r="AF156" t="n">
-        <v>2</v>
       </c>
       <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr"/>
@@ -22453,15 +22453,15 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE157" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF157" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%91%D7%99-%D7%99%D7%A2%D7%A7%D7%91/</t>
         </is>
-      </c>
-      <c r="AF157" t="n">
-        <v>2</v>
       </c>
       <c r="AG157" t="inlineStr"/>
       <c r="AH157" t="inlineStr"/>
@@ -22592,15 +22592,15 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE158" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF158" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A2%D7%94-%D7%95%D7%99%D7%A6%D7%9E%D7%9F-%D7%A8%D7%91%D7%99%D7%91%D7%95/</t>
         </is>
-      </c>
-      <c r="AF158" t="n">
-        <v>2</v>
       </c>
       <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr"/>
@@ -22731,15 +22731,15 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE159" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF159" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%91%D7%95%D7%A8%D7%92-%D7%A1%D7%92%D7%9F-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF159" t="n">
-        <v>2</v>
       </c>
       <c r="AG159" t="inlineStr"/>
       <c r="AH159" t="inlineStr"/>
@@ -22870,15 +22870,15 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE160" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF160" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%92%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF160" t="n">
-        <v>2</v>
       </c>
       <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr"/>
@@ -23009,15 +23009,15 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE161" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF161" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%A4%D7%99%D7%9C%D7%95%D7%A1%D7%95%D7%A3/</t>
         </is>
-      </c>
-      <c r="AF161" t="n">
-        <v>2</v>
       </c>
       <c r="AG161" t="inlineStr"/>
       <c r="AH161" t="inlineStr"/>
@@ -23148,15 +23148,15 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE162" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF162" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%98%D7%95%D7%A9%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF162" t="n">
-        <v>2</v>
       </c>
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr"/>
@@ -23287,15 +23287,15 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE163" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF163" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A8%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF163" t="n">
-        <v>2</v>
       </c>
       <c r="AG163" t="inlineStr"/>
       <c r="AH163" t="inlineStr"/>
@@ -23426,15 +23426,15 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE164" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF164" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%9C%D7%9B%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF164" t="n">
-        <v>2</v>
       </c>
       <c r="AG164" t="inlineStr"/>
       <c r="AH164" t="inlineStr"/>
@@ -23565,15 +23565,15 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE165" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF165" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%9C%D7%92%D7%94-%D7%95%D7%A7%D7%A1%D7%9C%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF165" t="n">
-        <v>2</v>
       </c>
       <c r="AG165" t="inlineStr"/>
       <c r="AH165" t="inlineStr"/>
@@ -23704,15 +23704,15 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE166" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF166" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%97%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF166" t="n">
-        <v>2</v>
       </c>
       <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr"/>
@@ -23843,15 +23843,15 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE167" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF167" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%9E%D7%9C%D7%99-%D7%94%D7%A0%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF167" t="n">
-        <v>2</v>
       </c>
       <c r="AG167" t="inlineStr"/>
       <c r="AH167" t="inlineStr"/>
@@ -23982,15 +23982,15 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE168" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF168" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%93%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF168" t="n">
-        <v>2</v>
       </c>
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr"/>
@@ -24121,15 +24121,15 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE169" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF169" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%99%D7%A2%D7%A7%D7%91%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF169" t="n">
-        <v>2</v>
       </c>
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr"/>
@@ -24260,15 +24260,15 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE170" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF170" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7-%D7%A0%D7%A7%D7%A9/</t>
         </is>
-      </c>
-      <c r="AF170" t="n">
-        <v>2</v>
       </c>
       <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr"/>
@@ -24399,15 +24399,15 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE171" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF171" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF171" t="n">
-        <v>2</v>
       </c>
       <c r="AG171" t="inlineStr"/>
       <c r="AH171" t="inlineStr"/>
@@ -24538,15 +24538,15 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE172" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF172" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A4%D7%96-%D7%A8%D7%99%D7%99%D7%9B%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF172" t="n">
-        <v>2</v>
       </c>
       <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr"/>
@@ -24677,15 +24677,15 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE173" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF173" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%97%D7%9C-%D7%A4%D7%99%D7%A8%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF173" t="n">
-        <v>2</v>
       </c>
       <c r="AG173" t="inlineStr"/>
       <c r="AH173" t="inlineStr"/>
@@ -24816,15 +24816,15 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE174" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF174" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%AA-%D7%9C%D7%91%D7%99%D7%90/</t>
         </is>
-      </c>
-      <c r="AF174" t="n">
-        <v>2</v>
       </c>
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr"/>
@@ -24955,15 +24955,15 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE175" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF175" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%96-%D7%A2%D7%96%D7%A8%D7%90/</t>
         </is>
-      </c>
-      <c r="AF175" t="n">
-        <v>2</v>
       </c>
       <c r="AG175" t="inlineStr"/>
       <c r="AH175" t="inlineStr"/>
@@ -25094,15 +25094,15 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE176" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF176" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A0%D7%A0%D7%94-%D7%95%D7%99%D7%A8%D7%A6%D7%91%D7%95%D7%A8%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF176" t="n">
-        <v>2</v>
       </c>
       <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
@@ -25233,15 +25233,15 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE177" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF177" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A2%D7%95%D7%AA-%D7%94%D7%A8%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF177" t="n">
-        <v>2</v>
       </c>
       <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
@@ -25372,15 +25372,15 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE178" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF178" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%98%D7%9C-%D7%90%D7%99%D7%A9-%D7%A9%D7%9C%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF178" t="n">
-        <v>2</v>
       </c>
       <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
@@ -25511,15 +25511,15 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE179" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF179" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A7%D7%99-%D7%96%D7%9C%D7%9B%D7%94/</t>
         </is>
-      </c>
-      <c r="AF179" t="n">
-        <v>2</v>
       </c>
       <c r="AG179" t="inlineStr"/>
       <c r="AH179" t="inlineStr"/>
@@ -25650,15 +25650,15 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE180" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF180" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A0%D7%AA-%D7%90%D7%9C%D7%93%D7%A8-%D7%92%D7%A8%D7%A9%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF180" t="n">
-        <v>2</v>
       </c>
       <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr"/>
@@ -25789,15 +25789,15 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE181" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF181" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%97%D7%99-%D7%A8%D7%95%D7%96%D7%A0%D7%98%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF181" t="n">
-        <v>2</v>
       </c>
       <c r="AG181" t="inlineStr"/>
       <c r="AH181" t="inlineStr"/>
@@ -25928,15 +25928,15 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE182" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF182" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99-%D7%A4%D7%A8%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF182" t="n">
-        <v>2</v>
       </c>
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr"/>
@@ -26067,15 +26067,15 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE183" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF183" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF183" t="n">
-        <v>2</v>
       </c>
       <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr"/>
@@ -26206,15 +26206,15 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE184" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF184" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%9D-%D7%90%D7%9C%D7%9E%D7%95%D7%92/</t>
         </is>
-      </c>
-      <c r="AF184" t="n">
-        <v>2</v>
       </c>
       <c r="AG184" t="inlineStr"/>
       <c r="AH184" t="inlineStr"/>
@@ -26345,15 +26345,15 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE185" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF185" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%99-%D7%98%D7%9C-%D7%9E%D7%99%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF185" t="n">
-        <v>2</v>
       </c>
       <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr"/>
@@ -26484,15 +26484,15 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE186" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF186" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%92%D7%99%D7%AA-%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF186" t="n">
-        <v>2</v>
       </c>
       <c r="AG186" t="inlineStr"/>
       <c r="AH186" t="inlineStr"/>
@@ -26623,15 +26623,15 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE187" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF187" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF187" t="n">
-        <v>2</v>
       </c>
       <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr"/>
@@ -26762,15 +26762,15 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE188" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF188" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%A9%D7%97%D7%A8-%D7%91%D7%9F-%D7%93%D7%95%D7%93/</t>
         </is>
-      </c>
-      <c r="AF188" t="n">
-        <v>2</v>
       </c>
       <c r="AG188" t="inlineStr"/>
       <c r="AH188" t="inlineStr"/>
@@ -26901,15 +26901,15 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE189" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF189" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A7%D7%93-%D7%9C%D7%99%D7%91%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF189" t="n">
-        <v>2</v>
       </c>
       <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr"/>
@@ -27040,15 +27040,15 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE190" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF190" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%A0%D7%94-%D7%A0%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF190" t="n">
-        <v>2</v>
       </c>
       <c r="AG190" t="inlineStr"/>
       <c r="AH190" t="inlineStr"/>
@@ -27179,15 +27179,15 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE191" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF191" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%9F-%D7%96%D7%9C%D7%9E%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF191" t="n">
-        <v>2</v>
       </c>
       <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr"/>
@@ -27318,15 +27318,15 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE192" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF192" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%99-%D7%97%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF192" t="n">
-        <v>2</v>
       </c>
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
@@ -27457,15 +27457,15 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE193" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF193" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%94-%D7%A1%D7%95%D7%A1%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF193" t="n">
-        <v>2</v>
       </c>
       <c r="AG193" t="inlineStr"/>
       <c r="AH193" t="inlineStr"/>
@@ -27596,15 +27596,15 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE194" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF194" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%90%D7%9C-%D7%A8%D7%91%D7%A7%D7%94-%D7%99%D7%A4%D7%94/</t>
         </is>
-      </c>
-      <c r="AF194" t="n">
-        <v>2</v>
       </c>
       <c r="AG194" t="inlineStr"/>
       <c r="AH194" t="inlineStr"/>
@@ -27735,15 +27735,15 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE195" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF195" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A4%D7%99%D7%99%D7%98%D7%9C%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF195" t="n">
-        <v>2</v>
       </c>
       <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr"/>
@@ -27874,15 +27874,15 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE196" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF196" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%95%D7%98%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF196" t="n">
-        <v>2</v>
       </c>
       <c r="AG196" t="inlineStr"/>
       <c r="AH196" t="inlineStr"/>
@@ -28013,15 +28013,15 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE197" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF197" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%A8%D7%95%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF197" t="n">
-        <v>2</v>
       </c>
       <c r="AG197" t="inlineStr"/>
       <c r="AH197" t="inlineStr"/>
@@ -28152,15 +28152,15 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE198" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF198" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%98-%D7%93%D7%A8%D7%A1%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF198" t="n">
-        <v>2</v>
       </c>
       <c r="AG198" t="inlineStr"/>
       <c r="AH198" t="inlineStr"/>
@@ -28291,15 +28291,15 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE199" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF199" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%92%D7%95%D7%96%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF199" t="n">
-        <v>2</v>
       </c>
       <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr"/>
@@ -28430,15 +28430,15 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE200" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF200" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%94%D7%95%D7%9C%D7%A6%D7%91%D7%A8%D7%92-%D7%97%D7%99%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF200" t="n">
-        <v>2</v>
       </c>
       <c r="AG200" t="inlineStr"/>
       <c r="AH200" t="inlineStr"/>
@@ -28569,15 +28569,15 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE201" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF201" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A0%D7%93%D7%9C%D7%91%D7%90%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF201" t="n">
-        <v>2</v>
       </c>
       <c r="AG201" t="inlineStr"/>
       <c r="AH201" t="inlineStr"/>
@@ -28708,15 +28708,15 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE202" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF202" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A8%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF202" t="n">
-        <v>2</v>
       </c>
       <c r="AG202" t="inlineStr"/>
       <c r="AH202" t="inlineStr"/>
@@ -28847,15 +28847,15 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE203" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF203" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%9E%D7%9C%D7%9B%D7%94-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF203" t="n">
-        <v>2</v>
       </c>
       <c r="AG203" t="inlineStr"/>
       <c r="AH203" t="inlineStr"/>
@@ -28986,15 +28986,15 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE204" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF204" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%94%D7%9C%D7%A4%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF204" t="n">
-        <v>2</v>
       </c>
       <c r="AG204" t="inlineStr"/>
       <c r="AH204" t="inlineStr"/>
@@ -29125,15 +29125,15 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE205" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF205" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%95%D7%A4%D7%99%D7%94-%D7%9E%D7%9C%D7%97%D7%96%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF205" t="n">
-        <v>2</v>
       </c>
       <c r="AG205" t="inlineStr"/>
       <c r="AH205" t="inlineStr"/>
@@ -29264,15 +29264,15 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE206" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF206" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%9E%D7%99%D7%98%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF206" t="n">
-        <v>2</v>
       </c>
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr"/>
@@ -29403,15 +29403,15 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE207" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF207" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%A6%D7%A0%D7%A6%D7%99%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF207" t="n">
-        <v>2</v>
       </c>
       <c r="AG207" t="inlineStr"/>
       <c r="AH207" t="inlineStr"/>
@@ -29542,15 +29542,15 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE208" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF208" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%91%D7%99%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF208" t="n">
-        <v>2</v>
       </c>
       <c r="AG208" t="inlineStr"/>
       <c r="AH208" t="inlineStr"/>
@@ -29681,15 +29681,15 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE209" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF209" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF209" t="n">
-        <v>2</v>
       </c>
       <c r="AG209" t="inlineStr"/>
       <c r="AH209" t="inlineStr"/>
@@ -29820,15 +29820,15 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE210" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF210" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99%D7%94-%D7%91%D7%9F-%D7%9E%D7%96%D7%99%D7%90/</t>
         </is>
-      </c>
-      <c r="AF210" t="n">
-        <v>2</v>
       </c>
       <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr"/>
@@ -29959,15 +29959,15 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE211" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF211" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%A8-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF211" t="n">
-        <v>3</v>
       </c>
       <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr"/>
@@ -30098,15 +30098,15 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE212" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF212" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A9%D7%92%D7%91-%D7%90%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF212" t="n">
-        <v>2</v>
       </c>
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr"/>
@@ -30237,15 +30237,15 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE213" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF213" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A2%D7%95%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF213" t="n">
-        <v>2</v>
       </c>
       <c r="AG213" t="inlineStr"/>
       <c r="AH213" t="inlineStr"/>
@@ -30376,15 +30376,15 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE214" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF214" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99%D7%9E%D7%94-%D7%A9%D7%A2%D7%A9%D7%95%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF214" t="n">
-        <v>2</v>
       </c>
       <c r="AG214" t="inlineStr"/>
       <c r="AH214" t="inlineStr"/>
@@ -30515,15 +30515,15 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE215" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF215" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%A7%D7%95%D7%94-%D7%A6%D7%93%D7%95%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF215" t="n">
-        <v>3</v>
       </c>
       <c r="AG215" t="inlineStr"/>
       <c r="AH215" t="inlineStr"/>
@@ -30654,15 +30654,15 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE216" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF216" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%95%D7%91%D7%94-%D7%99%D7%95%D7%A1%D7%A4%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF216" t="n">
-        <v>2</v>
       </c>
       <c r="AG216" t="inlineStr"/>
       <c r="AH216" t="inlineStr"/>
@@ -30793,15 +30793,15 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE217" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF217" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A6%D7%91%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF217" t="n">
-        <v>2</v>
       </c>
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" t="inlineStr"/>
@@ -30932,15 +30932,15 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE218" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF218" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A6%D7%95%D7%A4%D7%99%D7%AA-%D7%93%D7%99%D7%A1%D7%98%D7%9C%D7%9E%D7%9F-%D7%9E%D7%99%D7%A8%D7%A7%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF218" t="n">
-        <v>2</v>
       </c>
       <c r="AG218" t="inlineStr"/>
       <c r="AH218" t="inlineStr"/>
@@ -31071,15 +31071,15 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE219" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF219" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%9C%D7%A8%D7%99-%D7%9E%D7%99%D7%9C%D7%94%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF219" t="n">
-        <v>2</v>
       </c>
       <c r="AG219" t="inlineStr"/>
       <c r="AH219" t="inlineStr"/>
@@ -31210,15 +31210,15 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE220" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF220" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%91%D7%90%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF220" t="n">
-        <v>2</v>
       </c>
       <c r="AG220" t="inlineStr"/>
       <c r="AH220" t="inlineStr"/>
@@ -31349,15 +31349,15 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE221" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF221" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%99%D7%A7%D7%98%D7%95%D7%A8%D7%99%D7%94-%D7%A7%D7%9E%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF221" t="n">
-        <v>2</v>
       </c>
       <c r="AG221" t="inlineStr"/>
       <c r="AH221" t="inlineStr"/>
@@ -31488,15 +31488,15 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE222" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF222" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A4%D7%90%D7%90-%D7%90%D7%91%D7%95-%D7%90%D7%A1%D7%9E%D7%90%D7%A2%D7%99%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF222" t="n">
-        <v>2</v>
       </c>
       <c r="AG222" t="inlineStr"/>
       <c r="AH222" t="inlineStr"/>
@@ -31627,15 +31627,15 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE223" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF223" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%91%D7%90%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF223" t="n">
-        <v>2</v>
       </c>
       <c r="AG223" t="inlineStr"/>
       <c r="AH223" t="inlineStr"/>
@@ -31766,15 +31766,15 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE224" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF224" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%93%D7%95%D7%91%D7%93%D7%91%D7%9F-%D7%92%D7%9C%D7%95%D7%96%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF224" t="n">
-        <v>2</v>
       </c>
       <c r="AG224" t="inlineStr"/>
       <c r="AH224" t="inlineStr"/>
@@ -31905,15 +31905,15 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE225" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF225" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%90%D7%98%D7%99%D7%90%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF225" t="n">
-        <v>2</v>
       </c>
       <c r="AG225" t="inlineStr"/>
       <c r="AH225" t="inlineStr"/>
@@ -32044,15 +32044,15 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE226" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF226" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%93%D7%95%D7%91%D7%A1%D7%98%D7%A8-%D7%93%D7%95%D7%93/</t>
         </is>
-      </c>
-      <c r="AF226" t="n">
-        <v>2</v>
       </c>
       <c r="AG226" t="inlineStr"/>
       <c r="AH226" t="inlineStr"/>
@@ -32183,15 +32183,15 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE227" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF227" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/291/</t>
         </is>
-      </c>
-      <c r="AF227" t="n">
-        <v>2</v>
       </c>
       <c r="AG227" t="inlineStr"/>
       <c r="AH227" t="inlineStr"/>
@@ -32322,15 +32322,15 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE228" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF228" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%96%D7%99%D7%AA-%D7%97%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF228" t="n">
-        <v>2</v>
       </c>
       <c r="AG228" t="inlineStr"/>
       <c r="AH228" t="inlineStr"/>
@@ -32461,15 +32461,15 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE229" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF229" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%A6%D7%A0%D7%9C%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF229" t="n">
-        <v>2</v>
       </c>
       <c r="AG229" t="inlineStr"/>
       <c r="AH229" t="inlineStr"/>
@@ -32600,15 +32600,15 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE230" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF230" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A4%D7%9C%D7%92/</t>
         </is>
-      </c>
-      <c r="AF230" t="n">
-        <v>2</v>
       </c>
       <c r="AG230" t="inlineStr"/>
       <c r="AH230" t="inlineStr"/>
@@ -32739,15 +32739,15 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE231" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF231" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF231" t="n">
-        <v>2</v>
       </c>
       <c r="AG231" t="inlineStr"/>
       <c r="AH231" t="inlineStr"/>
@@ -32878,15 +32878,15 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE232" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF232" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%90%D7%A0%D7%94-%D7%A4%D7%99%D7%A9%D7%91%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF232" t="n">
-        <v>2</v>
       </c>
       <c r="AG232" t="inlineStr"/>
       <c r="AH232" t="inlineStr"/>
@@ -33017,15 +33017,15 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE233" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF233" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%9E%D7%95%D7%A8%D7%9C%D7%99/</t>
         </is>
-      </c>
-      <c r="AF233" t="n">
-        <v>2</v>
       </c>
       <c r="AG233" t="inlineStr"/>
       <c r="AH233" t="inlineStr"/>
@@ -33156,15 +33156,15 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE234" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF234" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%A8%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF234" t="n">
-        <v>2</v>
       </c>
       <c r="AG234" t="inlineStr"/>
       <c r="AH234" t="inlineStr"/>
@@ -33295,15 +33295,15 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE235" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF235" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%99%D7%AA-%D7%9B%D7%A5-%D7%91%D7%A1%D7%98%D7%A7%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF235" t="n">
-        <v>2</v>
       </c>
       <c r="AG235" t="inlineStr"/>
       <c r="AH235" t="inlineStr"/>
@@ -33434,15 +33434,15 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE236" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF236" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A2%D7%9E%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF236" t="n">
-        <v>2</v>
       </c>
       <c r="AG236" t="inlineStr"/>
       <c r="AH236" t="inlineStr"/>
@@ -33573,15 +33573,15 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE237" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF237" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A8%D7%91%D7%99%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF237" t="n">
-        <v>2</v>
       </c>
       <c r="AG237" t="inlineStr"/>
       <c r="AH237" t="inlineStr"/>
@@ -33712,15 +33712,15 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE238" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF238" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%91%D7%9C-%D7%A7%D7%A1%D7%98%D7%99%D7%9F-%D7%9B%D7%94%D7%A0%D7%90/</t>
         </is>
-      </c>
-      <c r="AF238" t="n">
-        <v>2</v>
       </c>
       <c r="AG238" t="inlineStr"/>
       <c r="AH238" t="inlineStr"/>
@@ -33851,15 +33851,15 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE239" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF239" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF239" t="n">
-        <v>2</v>
       </c>
       <c r="AG239" t="inlineStr"/>
       <c r="AH239" t="inlineStr"/>
@@ -33996,15 +33996,15 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>295248</v>
-      </c>
-      <c r="AE240" t="inlineStr">
+        <v>885744</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF240" t="inlineStr">
         <is>
           <t>https://nefeshachat.co.il/</t>
         </is>
-      </c>
-      <c r="AF240" t="n">
-        <v>2</v>
       </c>
       <c r="AG240" t="inlineStr"/>
       <c r="AH240" t="inlineStr"/>
@@ -34135,15 +34135,15 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE241" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF241" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9B%D7%A4%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF241" t="n">
-        <v>2</v>
       </c>
       <c r="AG241" t="inlineStr"/>
       <c r="AH241" t="inlineStr"/>
@@ -34274,15 +34274,15 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE242" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF242" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A9%D7%9C-%D7%98%D7%95%D7%94%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF242" t="n">
-        <v>2</v>
       </c>
       <c r="AG242" t="inlineStr"/>
       <c r="AH242" t="inlineStr"/>
@@ -34413,15 +34413,15 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE243" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF243" t="inlineStr">
         <is>
           <t>https://tzuna-tova.co.il/</t>
         </is>
-      </c>
-      <c r="AF243" t="n">
-        <v>2</v>
       </c>
       <c r="AG243" t="inlineStr"/>
       <c r="AH243" t="inlineStr"/>
@@ -34552,15 +34552,15 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE244" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF244" t="inlineStr">
         <is>
           <t>https://www.shiri-sleep.co.il/</t>
         </is>
-      </c>
-      <c r="AF244" t="n">
-        <v>2</v>
       </c>
       <c r="AG244" t="inlineStr"/>
       <c r="AH244" t="inlineStr"/>
@@ -34691,15 +34691,15 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE245" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF245" t="inlineStr">
         <is>
           <t>https://tlvmed.co.il/</t>
         </is>
-      </c>
-      <c r="AF245" t="n">
-        <v>2</v>
       </c>
       <c r="AG245" t="inlineStr"/>
       <c r="AH245" t="inlineStr"/>
@@ -34840,15 +34840,15 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>255879</v>
-      </c>
-      <c r="AE246" t="inlineStr">
+        <v>767637</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF246" t="inlineStr">
         <is>
           <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F</t>
         </is>
-      </c>
-      <c r="AF246" t="n">
-        <v>5</v>
       </c>
       <c r="AG246" t="inlineStr"/>
       <c r="AH246" t="inlineStr"/>
@@ -34979,15 +34979,15 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE247" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF247" t="inlineStr">
         <is>
           <t>https://www.mcra.co.il/</t>
         </is>
-      </c>
-      <c r="AF247" t="n">
-        <v>2</v>
       </c>
       <c r="AG247" t="inlineStr"/>
       <c r="AH247" t="inlineStr"/>
@@ -35118,15 +35118,15 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE248" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF248" t="inlineStr">
         <is>
           <t>https://www.leidaschool.co.il/</t>
         </is>
-      </c>
-      <c r="AF248" t="n">
-        <v>2</v>
       </c>
       <c r="AG248" t="inlineStr"/>
       <c r="AH248" t="inlineStr"/>
@@ -35265,15 +35265,15 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE249" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF249" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/</t>
         </is>
-      </c>
-      <c r="AF249" t="n">
-        <v>5</v>
       </c>
       <c r="AG249" t="inlineStr"/>
       <c r="AH249" t="inlineStr"/>
@@ -35412,15 +35412,15 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE250" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>229</v>
+      </c>
+      <c r="AF250" t="inlineStr">
         <is>
           <t>https://ialp.org.il/lllisrael/</t>
         </is>
-      </c>
-      <c r="AF250" t="n">
-        <v>229</v>
       </c>
       <c r="AG250" t="inlineStr"/>
       <c r="AH250" t="inlineStr"/>
@@ -35561,15 +35561,15 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>295488</v>
-      </c>
-      <c r="AE251" t="inlineStr">
+        <v>886464</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF251" t="inlineStr">
         <is>
           <t>https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/</t>
         </is>
-      </c>
-      <c r="AF251" t="n">
-        <v>4</v>
       </c>
       <c r="AG251" t="inlineStr"/>
       <c r="AH251" t="inlineStr"/>
@@ -35700,15 +35700,15 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>236196</v>
-      </c>
-      <c r="AE252" t="inlineStr">
+        <v>708588</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF252" t="inlineStr">
         <is>
           <t>https://balaolam.co.il/</t>
         </is>
-      </c>
-      <c r="AF252" t="n">
-        <v>2</v>
       </c>
       <c r="AG252" t="inlineStr"/>
       <c r="AH252" t="inlineStr"/>
@@ -35843,15 +35843,15 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>295245</v>
-      </c>
-      <c r="AE253" t="inlineStr">
+        <v>885735</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF253" t="inlineStr">
         <is>
           <t>https://babyhub.co.il/tools/pregnancy-tracker</t>
         </is>
-      </c>
-      <c r="AF253" t="n">
-        <v>3</v>
       </c>
       <c r="AG253" t="inlineStr"/>
       <c r="AH253" t="inlineStr"/>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1065069</v>
+        <v>3195207</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>728514</v>
+        <v>2185542</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE5" t="n">
         <v>3</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE7" t="n">
         <v>19</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>710775</v>
+        <v>2132325</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE10" t="n">
         <v>17</v>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE27" t="n">
         <v>17</v>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -7997,7 +7997,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9387,7 +9387,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11055,7 +11055,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -11611,7 +11611,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12306,7 +12306,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -12584,7 +12584,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13001,7 +13001,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13140,7 +13140,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13418,7 +13418,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -13835,7 +13835,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -13974,7 +13974,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14252,7 +14252,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14391,7 +14391,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -14530,7 +14530,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -14669,7 +14669,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -14808,7 +14808,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15086,7 +15086,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15364,7 +15364,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16059,7 +16059,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16198,7 +16198,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -16615,7 +16615,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -16754,7 +16754,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17032,7 +17032,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17310,7 +17310,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -17449,7 +17449,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -17866,7 +17866,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18144,7 +18144,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18283,7 +18283,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -18422,7 +18422,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -18561,7 +18561,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -18839,7 +18839,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -19395,7 +19395,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -19673,7 +19673,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -19951,7 +19951,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20090,7 +20090,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20229,7 +20229,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -20368,7 +20368,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -20785,7 +20785,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -20924,7 +20924,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21063,7 +21063,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21202,7 +21202,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -21341,7 +21341,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -21619,7 +21619,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -21758,7 +21758,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -21897,7 +21897,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22175,7 +22175,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -22314,7 +22314,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -22453,7 +22453,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -22592,7 +22592,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -22731,7 +22731,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -22870,7 +22870,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23148,7 +23148,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -23287,7 +23287,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -23426,7 +23426,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -23565,7 +23565,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -23982,7 +23982,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24121,7 +24121,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -24260,7 +24260,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -24399,7 +24399,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -24538,7 +24538,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -24677,7 +24677,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -24816,7 +24816,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -24955,7 +24955,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25094,7 +25094,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -25233,7 +25233,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -25372,7 +25372,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -25511,7 +25511,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -25650,7 +25650,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -25789,7 +25789,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -25928,7 +25928,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -26206,7 +26206,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -26345,7 +26345,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -26623,7 +26623,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -26762,7 +26762,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -26901,7 +26901,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -27040,7 +27040,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -27179,7 +27179,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -27318,7 +27318,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -27457,7 +27457,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -27874,7 +27874,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -28013,7 +28013,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -28152,7 +28152,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -28291,7 +28291,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -28430,7 +28430,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -28569,7 +28569,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -28708,7 +28708,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -28847,7 +28847,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -28986,7 +28986,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -29125,7 +29125,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -29264,7 +29264,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -29403,7 +29403,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -29542,7 +29542,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -29681,7 +29681,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -29820,7 +29820,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -29959,7 +29959,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -30098,7 +30098,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -30237,7 +30237,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -30376,7 +30376,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -30515,7 +30515,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -30654,7 +30654,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -30793,7 +30793,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -30932,7 +30932,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -31071,7 +31071,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -31210,7 +31210,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -31349,7 +31349,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -31627,7 +31627,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -31766,7 +31766,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -31905,7 +31905,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -32044,7 +32044,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -32183,7 +32183,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -32322,7 +32322,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -32461,7 +32461,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -32600,7 +32600,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -32739,7 +32739,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -32878,7 +32878,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -33017,7 +33017,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -33156,7 +33156,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -33434,7 +33434,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -33573,7 +33573,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -33712,7 +33712,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -33851,7 +33851,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -33996,7 +33996,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>885744</v>
+        <v>2657232</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -34135,7 +34135,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -34274,7 +34274,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -34413,7 +34413,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -34552,7 +34552,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -34691,7 +34691,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -34840,7 +34840,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>767637</v>
+        <v>2302911</v>
       </c>
       <c r="AE246" t="n">
         <v>5</v>
@@ -34979,7 +34979,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -35118,7 +35118,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -35265,7 +35265,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE249" t="n">
         <v>5</v>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE250" t="n">
         <v>229</v>
@@ -35561,7 +35561,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>886464</v>
+        <v>2659392</v>
       </c>
       <c r="AE251" t="n">
         <v>4</v>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>708588</v>
+        <v>2125764</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -35843,7 +35843,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>885735</v>
+        <v>2657205</v>
       </c>
       <c r="AE253" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>3195207</v>
+        <v>9585621</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>2185542</v>
+        <v>6556626</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE5" t="n">
         <v>3</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE7" t="n">
         <v>19</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>2132325</v>
+        <v>6396975</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE10" t="n">
         <v>17</v>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE27" t="n">
         <v>17</v>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -7997,7 +7997,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9387,7 +9387,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11055,7 +11055,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -11611,7 +11611,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12306,7 +12306,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -12584,7 +12584,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13001,7 +13001,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13140,7 +13140,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13418,7 +13418,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -13835,7 +13835,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -13974,7 +13974,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14252,7 +14252,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14391,7 +14391,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -14530,7 +14530,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -14669,7 +14669,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -14808,7 +14808,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15086,7 +15086,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15364,7 +15364,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16059,7 +16059,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16198,7 +16198,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -16615,7 +16615,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -16754,7 +16754,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17032,7 +17032,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17310,7 +17310,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -17449,7 +17449,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -17866,7 +17866,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18144,7 +18144,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18283,7 +18283,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -18422,7 +18422,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -18561,7 +18561,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -18839,7 +18839,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -19395,7 +19395,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -19673,7 +19673,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -19951,7 +19951,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20090,7 +20090,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20229,7 +20229,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -20368,7 +20368,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -20785,7 +20785,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -20924,7 +20924,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21063,7 +21063,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21202,7 +21202,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -21341,7 +21341,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -21619,7 +21619,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -21758,7 +21758,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -21897,7 +21897,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22175,7 +22175,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -22314,7 +22314,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -22453,7 +22453,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -22592,7 +22592,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -22731,7 +22731,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -22870,7 +22870,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23148,7 +23148,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -23287,7 +23287,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -23426,7 +23426,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -23565,7 +23565,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -23982,7 +23982,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24121,7 +24121,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -24260,7 +24260,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -24399,7 +24399,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -24538,7 +24538,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -24677,7 +24677,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -24816,7 +24816,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -24955,7 +24955,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25094,7 +25094,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -25233,7 +25233,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -25372,7 +25372,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -25511,7 +25511,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -25650,7 +25650,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -25789,7 +25789,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -25928,7 +25928,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -26206,7 +26206,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -26345,7 +26345,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -26623,7 +26623,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -26762,7 +26762,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -26901,7 +26901,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -27040,7 +27040,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -27179,7 +27179,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -27318,7 +27318,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -27457,7 +27457,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -27874,7 +27874,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -28013,7 +28013,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -28152,7 +28152,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -28291,7 +28291,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -28430,7 +28430,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -28569,7 +28569,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -28708,7 +28708,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -28847,7 +28847,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -28986,7 +28986,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -29125,7 +29125,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -29264,7 +29264,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -29403,7 +29403,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -29542,7 +29542,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -29681,7 +29681,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -29820,7 +29820,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -29959,7 +29959,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -30098,7 +30098,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -30237,7 +30237,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -30376,7 +30376,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -30515,7 +30515,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -30654,7 +30654,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -30793,7 +30793,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -30932,7 +30932,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -31071,7 +31071,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -31210,7 +31210,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -31349,7 +31349,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -31627,7 +31627,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -31766,7 +31766,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -31905,7 +31905,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -32044,7 +32044,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -32183,7 +32183,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -32322,7 +32322,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -32461,7 +32461,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -32600,7 +32600,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -32739,7 +32739,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -32878,7 +32878,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -33017,7 +33017,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -33156,7 +33156,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -33434,7 +33434,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -33573,7 +33573,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -33712,7 +33712,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -33851,7 +33851,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -33996,7 +33996,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>2657232</v>
+        <v>7971696</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -34135,7 +34135,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -34274,7 +34274,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -34413,7 +34413,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -34552,7 +34552,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -34691,7 +34691,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -34840,7 +34840,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>2302911</v>
+        <v>6908733</v>
       </c>
       <c r="AE246" t="n">
         <v>5</v>
@@ -34979,7 +34979,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -35118,7 +35118,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -35265,7 +35265,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE249" t="n">
         <v>5</v>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE250" t="n">
         <v>229</v>
@@ -35561,7 +35561,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>2659392</v>
+        <v>7978176</v>
       </c>
       <c r="AE251" t="n">
         <v>4</v>
@@ -35700,7 +35700,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>2125764</v>
+        <v>6377292</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -35843,7 +35843,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>2657205</v>
+        <v>7971615</v>
       </c>
       <c r="AE253" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM253"/>
+  <dimension ref="A1:AM254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>identity_url</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>shared_target_count</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>identity_url</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -742,15 +742,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE2" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>https://www.rofenashim.co.il/faq/faq-fertility/</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
         <v>6</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>https://www.rofenashim.co.il/faq/faq-fertility/</t>
-        </is>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
@@ -891,15 +891,15 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>9585621</v>
-      </c>
-      <c r="AE3" t="n">
+        <v>28756863</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>https://www.e-piryon.com/</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>https://www.e-piryon.com/</t>
-        </is>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -1040,15 +1040,15 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>6556626</v>
-      </c>
-      <c r="AE4" t="n">
+        <v>19669878</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>https://www.profyinoncohen.com/</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
         <v>2</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>https://www.profyinoncohen.com/</t>
-        </is>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
@@ -1187,15 +1187,15 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE5" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>https://www.leidaraka.co.il/</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
         <v>3</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>https://www.leidaraka.co.il/</t>
-        </is>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1334,15 +1334,15 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE6" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>https://kerenzohar.com/%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
         <v>2</v>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>https://kerenzohar.com/%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
-        </is>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1483,15 +1483,15 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>6908733</v>
-      </c>
-      <c r="AE7" t="n">
+        <v>20726199</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>https://hmc.co.il/doctor/%D7%A4%D7%A8%D7%95%D7%A4-%D7%93%D7%95%D7%93-%D7%9C%D7%91-%D7%A8%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
         <v>19</v>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>https://hmc.co.il/doctor/%D7%A4%D7%A8%D7%95%D7%A4-%D7%93%D7%95%D7%93-%D7%9C%D7%91-%D7%A8%D7%9F/</t>
-        </is>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -1630,15 +1630,15 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE8" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>https://www.israelidoula.co.il/courses-1/embryo-%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
         <v>7</v>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>https://www.israelidoula.co.il/courses-1/embryo-%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
-        </is>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1779,15 +1779,15 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>6396975</v>
-      </c>
-      <c r="AE9" t="n">
+        <v>19190925</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>https://www.dr-paz.co.il/</t>
+        </is>
+      </c>
+      <c r="AF9" t="n">
         <v>2</v>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>https://www.dr-paz.co.il/</t>
-        </is>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
@@ -1926,15 +1926,15 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE10" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>https://www.israelivf.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
+        </is>
+      </c>
+      <c r="AF10" t="n">
         <v>17</v>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>https://www.israelivf.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
-        </is>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
@@ -2065,15 +2065,15 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE11" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>https://www.shvil-haleida.co.il/%D7%A8%D7%99%D7%A9%D7%95%D7%9D-%D7%9C%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%9C%D7%99%D7%93%D7%94/</t>
+        </is>
+      </c>
+      <c r="AF11" t="n">
         <v>2</v>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>https://www.shvil-haleida.co.il/%D7%A8%D7%99%D7%A9%D7%95%D7%9D-%D7%9C%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%9C%D7%99%D7%93%D7%94/</t>
-        </is>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
@@ -2214,15 +2214,15 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>7978176</v>
-      </c>
-      <c r="AE12" t="n">
+        <v>23934528</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94-9/</t>
+        </is>
+      </c>
+      <c r="AF12" t="n">
         <v>2</v>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94-9/</t>
-        </is>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
@@ -2353,15 +2353,15 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE13" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>https://harechem.com/</t>
+        </is>
+      </c>
+      <c r="AF13" t="n">
         <v>3</v>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>https://harechem.com/</t>
-        </is>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
@@ -2496,15 +2496,15 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE14" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>http://www.amotatchen.org/</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
         <v>3</v>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>http://www.amotatchen.org/</t>
-        </is>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
@@ -2645,15 +2645,15 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>6908733</v>
-      </c>
-      <c r="AE15" t="n">
+        <v>20726199</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF15" t="n">
         <v>2</v>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
-        </is>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
@@ -2794,15 +2794,15 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>7978176</v>
-      </c>
-      <c r="AE16" t="n">
+        <v>23934528</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>https://dinadoula.com/%D7%93%D7%95%D7%9C%D7%94/</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
         <v>2</v>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>https://dinadoula.com/%D7%93%D7%95%D7%9C%D7%94/</t>
-        </is>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2943,15 +2943,15 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>6908733</v>
-      </c>
-      <c r="AE17" t="n">
+        <v>20726199</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>https://www.surmom.co.il/%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/%D7%A4%D7%A8%D7%95%D7%A4-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F-%D7%90%D7%93%D7%A8%D7%99%D7%90%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF17" t="n">
         <v>2</v>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>https://www.surmom.co.il/%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/%D7%A4%D7%A8%D7%95%D7%A4-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F-%D7%90%D7%93%D7%A8%D7%99%D7%90%D7%9F/</t>
-        </is>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
@@ -3092,15 +3092,15 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>6908733</v>
-      </c>
-      <c r="AE18" t="n">
+        <v>20726199</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>https://hfhosp.org/he/%D7%A6%D7%95%D7%95%D7%AA-%D7%94%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/%D7%93%D7%A8-%D7%A0%D7%99%D7%A7%D7%95%D7%9C%D7%90-%D7%A4%D7%A8%D7%97</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
         <v>5</v>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>https://hfhosp.org/he/%D7%A6%D7%95%D7%95%D7%AA-%D7%94%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/%D7%93%D7%A8-%D7%A0%D7%99%D7%A7%D7%95%D7%9C%D7%90-%D7%A4%D7%A8%D7%97</t>
-        </is>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
@@ -3231,15 +3231,15 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE19" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>https://midwives.org.il/%D7%9C%D7%99%D7%95%D7%95%D7%99-%D7%9E%D7%A7%D7%A6%D7%95%D7%A2%D7%99-%D7%96%D7%94-%D7%9E%D7%99%D7%99%D7%9C%D7%93%D7%AA/</t>
+        </is>
+      </c>
+      <c r="AF19" t="n">
         <v>9</v>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>https://midwives.org.il/%D7%9C%D7%99%D7%95%D7%95%D7%99-%D7%9E%D7%A7%D7%A6%D7%95%D7%A2%D7%99-%D7%96%D7%94-%D7%9E%D7%99%D7%99%D7%9C%D7%93%D7%AA/</t>
-        </is>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
@@ -3378,15 +3378,15 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE20" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
         <v>8</v>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
-        </is>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
@@ -3525,15 +3525,15 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE21" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
+        </is>
+      </c>
+      <c r="AF21" t="n">
         <v>11</v>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
-        </is>
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
@@ -3664,15 +3664,15 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE22" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>https://www.israelibaby.co.il/where-to-get-birth</t>
+        </is>
+      </c>
+      <c r="AF22" t="n">
         <v>11</v>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>https://www.israelibaby.co.il/where-to-get-birth</t>
-        </is>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
@@ -3803,15 +3803,15 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE23" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>https://www.tasmc.org.il/lis/</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
         <v>2</v>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>https://www.tasmc.org.il/lis/</t>
-        </is>
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
@@ -3946,15 +3946,15 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE24" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/fertility-research/</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
         <v>3</v>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/fertility-research/</t>
-        </is>
       </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
@@ -4085,15 +4085,15 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE25" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>https://barakivf.com/</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
         <v>3</v>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>https://barakivf.com/</t>
-        </is>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
@@ -4228,15 +4228,15 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE26" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>https://demayo.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94/</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
         <v>3</v>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>https://demayo.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94/</t>
-        </is>
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
@@ -4375,15 +4375,15 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE27" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>https://bri.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
         <v>17</v>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>https://bri.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/</t>
-        </is>
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
@@ -4514,15 +4514,15 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE28" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
+        </is>
+      </c>
+      <c r="AF28" t="n">
         <v>4</v>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
-        </is>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
@@ -4653,15 +4653,15 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE29" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
         <v>4</v>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
-        </is>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
@@ -4792,15 +4792,15 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE30" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
+        </is>
+      </c>
+      <c r="AF30" t="n">
         <v>4</v>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
-        </is>
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
@@ -4939,15 +4939,15 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE31" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>https://www.laniado.org.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%9C%D7%99%D7%93%D7%94-%D7%98%D7%91%D7%A2%D7%99%D7%AA/</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
         <v>2</v>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>https://www.laniado.org.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%9C%D7%99%D7%93%D7%94-%D7%98%D7%91%D7%A2%D7%99%D7%AA/</t>
-        </is>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
@@ -5078,15 +5078,15 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE32" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=A6B809CAFEA13537A84D783709CF5EBB&amp;RequestId=00000000-0000-0000-0001-000000000325</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
         <v>2</v>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=A6B809CAFEA13537A84D783709CF5EBB&amp;RequestId=00000000-0000-0000-0001-000000000325</t>
-        </is>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
@@ -5217,15 +5217,15 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE33" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
+        </is>
+      </c>
+      <c r="AF33" t="n">
         <v>8</v>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
-        </is>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
@@ -5356,15 +5356,15 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE34" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%91%D7%9C%D7%94-%D7%A2%D7%91%D7%93%D7%95/</t>
+        </is>
+      </c>
+      <c r="AF34" t="n">
         <v>2</v>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%91%D7%9C%D7%94-%D7%A2%D7%91%D7%93%D7%95/</t>
-        </is>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
@@ -5495,15 +5495,15 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE35" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%92%D7%9E%D7%95/</t>
+        </is>
+      </c>
+      <c r="AF35" t="n">
         <v>2</v>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%92%D7%9E%D7%95/</t>
-        </is>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
@@ -5634,15 +5634,15 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE36" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%99%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF36" t="n">
         <v>2</v>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%99%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -5773,15 +5773,15 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE37" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%9F-%D7%90%D7%A8%D7%99-%D7%A6%D7%90%D7%A0%D7%94/</t>
+        </is>
+      </c>
+      <c r="AF37" t="n">
         <v>2</v>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%9F-%D7%90%D7%A8%D7%99-%D7%A6%D7%90%D7%A0%D7%94/</t>
-        </is>
       </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
@@ -5912,15 +5912,15 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE38" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%A8%D7%96/</t>
+        </is>
+      </c>
+      <c r="AF38" t="n">
         <v>2</v>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%A8%D7%96/</t>
-        </is>
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
@@ -6051,15 +6051,15 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE39" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%95%D7%A8%D7%A0%D7%92%D7%95%D7%9C%D7%93-%D7%97%D7%99%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF39" t="n">
         <v>2</v>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%95%D7%A8%D7%A0%D7%92%D7%95%D7%9C%D7%93-%D7%97%D7%99%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
@@ -6190,15 +6190,15 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE40" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%9C%D7%A0%D7%92/</t>
+        </is>
+      </c>
+      <c r="AF40" t="n">
         <v>2</v>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%9C%D7%A0%D7%92/</t>
-        </is>
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
@@ -6329,15 +6329,15 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE41" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%9C%D7%A0%D7%93%D7%94-%D7%A1%D7%95%D7%A4%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF41" t="n">
         <v>2</v>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%9C%D7%A0%D7%93%D7%94-%D7%A1%D7%95%D7%A4%D7%A8/</t>
-        </is>
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
@@ -6468,15 +6468,15 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE42" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%95%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%9C%D7%90/</t>
+        </is>
+      </c>
+      <c r="AF42" t="n">
         <v>2</v>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%95%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%9C%D7%90/</t>
-        </is>
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
@@ -6607,15 +6607,15 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE43" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%9C%D7%99%D7%94-%D7%94%D7%95%D7%9C%D7%A6%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF43" t="n">
         <v>2</v>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%9C%D7%99%D7%94-%D7%94%D7%95%D7%9C%D7%A6%D7%A8/</t>
-        </is>
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
@@ -6746,15 +6746,15 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE44" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%9E%D7%99%D7%AA-%D7%93%D7%A0%D7%A1%D7%99%D7%95%D7%A7/</t>
+        </is>
+      </c>
+      <c r="AF44" t="n">
         <v>2</v>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%9E%D7%99%D7%AA-%D7%93%D7%A0%D7%A1%D7%99%D7%95%D7%A7/</t>
-        </is>
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
@@ -6885,15 +6885,15 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE45" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%9E%D7%95%D7%96%D7%A1-%D7%90%D7%9C%D7%91%D7%96/</t>
+        </is>
+      </c>
+      <c r="AF45" t="n">
         <v>2</v>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%9E%D7%95%D7%96%D7%A1-%D7%90%D7%9C%D7%91%D7%96/</t>
-        </is>
       </c>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
@@ -7024,15 +7024,15 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE46" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%A8%D7%95%D7%9F-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF46" t="n">
         <v>2</v>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%A8%D7%95%D7%9F-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
@@ -7163,15 +7163,15 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE47" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%99%D7%A2%D7%A8%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF47" t="n">
         <v>2</v>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%99%D7%A2%D7%A8%D7%99/</t>
-        </is>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
@@ -7302,15 +7302,15 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE48" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%98%D7%94-%D7%A0%D7%95%D7%91%D7%9C/</t>
+        </is>
+      </c>
+      <c r="AF48" t="n">
         <v>2</v>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%98%D7%94-%D7%A0%D7%95%D7%91%D7%9C/</t>
-        </is>
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
@@ -7441,15 +7441,15 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE49" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%94-%D7%A4%D7%95%D7%9C%D7%99%D7%90%D7%A7%D7%95%D7%91/</t>
+        </is>
+      </c>
+      <c r="AF49" t="n">
         <v>2</v>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%94-%D7%A4%D7%95%D7%9C%D7%99%D7%90%D7%A7%D7%95%D7%91/</t>
-        </is>
       </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
@@ -7580,15 +7580,15 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE50" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%94-%D7%93%D7%9E%D7%A0%D7%98%D7%99%D7%99%D7%91/</t>
+        </is>
+      </c>
+      <c r="AF50" t="n">
         <v>2</v>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%94-%D7%93%D7%9E%D7%A0%D7%98%D7%99%D7%99%D7%91/</t>
-        </is>
       </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
@@ -7719,15 +7719,15 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE51" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF51" t="n">
         <v>2</v>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
-        </is>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
@@ -7858,15 +7858,15 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE52" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%96%D7%92%D7%95%D7%A8%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF52" t="n">
         <v>2</v>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%96%D7%92%D7%95%D7%A8%D7%99/</t>
-        </is>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
@@ -7997,15 +7997,15 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE53" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8-%D7%95%D7%99%D7%99%D7%A1/</t>
+        </is>
+      </c>
+      <c r="AF53" t="n">
         <v>2</v>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8-%D7%95%D7%99%D7%99%D7%A1/</t>
-        </is>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
@@ -8136,15 +8136,15 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE54" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF54" t="n">
         <v>2</v>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
@@ -8275,15 +8275,15 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE55" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%9C%D7%91%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF55" t="n">
         <v>2</v>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%9C%D7%91%D7%A8/</t>
-        </is>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
@@ -8414,15 +8414,15 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE56" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%90%D7%9D-%D7%9E%D7%95%D7%A8%D7%94-%D7%97%D7%9E%D7%90%D7%A8%D7%A9%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF56" t="n">
         <v>2</v>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%90%D7%9D-%D7%9E%D7%95%D7%A8%D7%94-%D7%97%D7%9E%D7%90%D7%A8%D7%A9%D7%99/</t>
-        </is>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
@@ -8553,15 +8553,15 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE57" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%91%D7%A8%D7%92%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF57" t="n">
         <v>2</v>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%91%D7%A8%D7%92%D7%A8/</t>
-        </is>
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
@@ -8692,15 +8692,15 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE58" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%A6%D7%99%D7%91%D7%99%D7%90%D7%A7-%D7%93%D7%99%D7%99%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF58" t="n">
         <v>2</v>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%A6%D7%99%D7%91%D7%99%D7%90%D7%A7-%D7%93%D7%99%D7%99%D7%9F/</t>
-        </is>
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
@@ -8831,15 +8831,15 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE59" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%9E%D7%95%D7%91%D7%A9%D7%95%D7%91%D7%99%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF59" t="n">
         <v>2</v>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%9E%D7%95%D7%91%D7%A9%D7%95%D7%91%D7%99%D7%A5/</t>
-        </is>
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
@@ -8970,15 +8970,15 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE60" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%94-%D7%90%D7%96%D7%91%D7%A0%D7%93/</t>
+        </is>
+      </c>
+      <c r="AF60" t="n">
         <v>2</v>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%94-%D7%90%D7%96%D7%91%D7%A0%D7%93/</t>
-        </is>
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
@@ -9109,15 +9109,15 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE61" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%91%D7%AA%D7%A9%D7%91%D7%A2-%D7%92%D7%A8%D7%A0%D7%95%D7%AA/</t>
+        </is>
+      </c>
+      <c r="AF61" t="n">
         <v>2</v>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%91%D7%AA%D7%A9%D7%91%D7%A2-%D7%92%D7%A8%D7%A0%D7%95%D7%AA/</t>
-        </is>
       </c>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
@@ -9248,15 +9248,15 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE62" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%91%D7%99%D7%9C%D7%99-%D7%90%D7%95%D7%91%D7%A8%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF62" t="n">
         <v>2</v>
-      </c>
-      <c r="AF62" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%91%D7%99%D7%9C%D7%99-%D7%90%D7%95%D7%91%D7%A8%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
@@ -9387,15 +9387,15 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE63" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%91%D7%9C%D7%99%D7%99%D7%A8-%D7%90%D7%9C%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF63" t="n">
         <v>2</v>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%91%D7%9C%D7%99%D7%99%D7%A8-%D7%90%D7%9C%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
@@ -9526,15 +9526,15 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE64" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%94%D7%A9%D7%9B%D7%9C/</t>
+        </is>
+      </c>
+      <c r="AF64" t="n">
         <v>2</v>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%94%D7%A9%D7%9B%D7%9C/</t>
-        </is>
       </c>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
@@ -9665,15 +9665,15 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE65" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%98%D7%9C-%D7%91%D7%A7%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF65" t="n">
         <v>2</v>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%98%D7%9C-%D7%91%D7%A7%D7%99/</t>
-        </is>
       </c>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
@@ -9804,15 +9804,15 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE66" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%97%D7%95%D7%98%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF66" t="n">
         <v>2</v>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%97%D7%95%D7%98%D7%A8/</t>
-        </is>
       </c>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
@@ -9943,15 +9943,15 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE67" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%9C%D7%90%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF67" t="n">
         <v>2</v>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%9C%D7%90%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
@@ -10082,15 +10082,15 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE68" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%92%D7%93%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF68" t="n">
         <v>2</v>
-      </c>
-      <c r="AF68" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%92%D7%93%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
@@ -10221,15 +10221,15 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE69" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%9E%D7%A8%D7%90%D7%93/</t>
+        </is>
+      </c>
+      <c r="AF69" t="n">
         <v>2</v>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%9E%D7%A8%D7%90%D7%93/</t>
-        </is>
       </c>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
@@ -10360,15 +10360,15 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE70" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%A9%D7%95%D7%95%D7%A8%D7%A6%D7%91%D7%A8%D7%92/</t>
+        </is>
+      </c>
+      <c r="AF70" t="n">
         <v>2</v>
-      </c>
-      <c r="AF70" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%A9%D7%95%D7%95%D7%A8%D7%A6%D7%91%D7%A8%D7%92/</t>
-        </is>
       </c>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
@@ -10499,15 +10499,15 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE71" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%99%D7%90%D7%9F-%D7%A9%D7%A4%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF71" t="n">
         <v>2</v>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%99%D7%90%D7%9F-%D7%A9%D7%A4%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
@@ -10638,15 +10638,15 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE72" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8-%D7%91%D7%99%D7%98%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF72" t="n">
         <v>2</v>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8-%D7%91%D7%99%D7%98%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
@@ -10777,15 +10777,15 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE73" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8%D7%99%D7%9F-%D7%90%D7%9C%D7%A2%D7%93/</t>
+        </is>
+      </c>
+      <c r="AF73" t="n">
         <v>2</v>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8%D7%99%D7%9F-%D7%90%D7%9C%D7%A2%D7%93/</t>
-        </is>
       </c>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
@@ -10916,15 +10916,15 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE74" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/332/</t>
+        </is>
+      </c>
+      <c r="AF74" t="n">
         <v>2</v>
-      </c>
-      <c r="AF74" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/332/</t>
-        </is>
       </c>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
@@ -11055,15 +11055,15 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE75" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%91%D7%9F-%D7%A9%D7%A5-%D7%A4%D7%95%D7%A8%D7%A9%D7%99%D7%90%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF75" t="n">
         <v>2</v>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%91%D7%9F-%D7%A9%D7%A5-%D7%A4%D7%95%D7%A8%D7%A9%D7%99%D7%90%D7%9F/</t>
-        </is>
       </c>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
@@ -11194,15 +11194,15 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE76" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%95%D7%95%D7%A8%D7%99%D7%99%D7%98/</t>
+        </is>
+      </c>
+      <c r="AF76" t="n">
         <v>2</v>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%95%D7%95%D7%A8%D7%99%D7%99%D7%98/</t>
-        </is>
       </c>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
@@ -11333,15 +11333,15 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE77" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%99%D7%90%D7%A0%D7%92/</t>
+        </is>
+      </c>
+      <c r="AF77" t="n">
         <v>2</v>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%99%D7%90%D7%A0%D7%92/</t>
-        </is>
       </c>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
@@ -11472,15 +11472,15 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE78" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%91%D7%92%D7%9C%D7%A4%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF78" t="n">
         <v>2</v>
-      </c>
-      <c r="AF78" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%91%D7%92%D7%9C%D7%A4%D7%A8/</t>
-        </is>
       </c>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
@@ -11611,15 +11611,15 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE79" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF79" t="n">
         <v>2</v>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
@@ -11750,15 +11750,15 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE80" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%9C%D7%A0%D7%94-%D7%A9%D7%99%D7%9C%D7%A7%D7%95/</t>
+        </is>
+      </c>
+      <c r="AF80" t="n">
         <v>2</v>
-      </c>
-      <c r="AF80" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%9C%D7%A0%D7%94-%D7%A9%D7%99%D7%9C%D7%A7%D7%95/</t>
-        </is>
       </c>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
@@ -11889,15 +11889,15 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE81" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A2%D7%A0%D7%94-%D7%92%D7%95%D7%9C%D7%93%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF81" t="n">
         <v>2</v>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A2%D7%A0%D7%94-%D7%92%D7%95%D7%9C%D7%93%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
@@ -12028,15 +12028,15 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE82" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%91%D7%A8%D7%A7%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF82" t="n">
         <v>2</v>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%91%D7%A8%D7%A7%D7%9F/</t>
-        </is>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -12167,15 +12167,15 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE83" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE83" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A8%D7%96-%D7%92%D7%99%D7%9C%D7%99%D7%A1/</t>
+        </is>
+      </c>
+      <c r="AF83" t="n">
         <v>2</v>
-      </c>
-      <c r="AF83" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A8%D7%96-%D7%92%D7%99%D7%9C%D7%99%D7%A1/</t>
-        </is>
       </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
@@ -12306,15 +12306,15 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE84" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A9%D7%91%D7%A2-%D7%92%D7%95%D7%A8%D7%91%D7%99%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF84" t="n">
         <v>2</v>
-      </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A9%D7%91%D7%A2-%D7%92%D7%95%D7%A8%D7%91%D7%99%D7%A5/</t>
-        </is>
       </c>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
@@ -12445,15 +12445,15 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE85" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%9C%D7%95%D7%A0%D7%92%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF85" t="n">
         <v>2</v>
-      </c>
-      <c r="AF85" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%9C%D7%95%D7%A0%D7%92%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
@@ -12584,15 +12584,15 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE86" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%9F-%D7%A9%D7%99%D7%99%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF86" t="n">
         <v>2</v>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%9F-%D7%A9%D7%99%D7%99%D7%9F/</t>
-        </is>
       </c>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
@@ -12723,15 +12723,15 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE87" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%94-%D7%90%D7%99%D7%AA%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF87" t="n">
         <v>2</v>
-      </c>
-      <c r="AF87" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%94-%D7%90%D7%99%D7%AA%D7%9F/</t>
-        </is>
       </c>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
@@ -12862,15 +12862,15 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE88" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%95%D7%A0%D7%94-%D7%95%D7%92%D7%A0%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF88" t="n">
         <v>2</v>
-      </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%95%D7%A0%D7%94-%D7%95%D7%92%D7%A0%D7%A8/</t>
-        </is>
       </c>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
@@ -13001,15 +13001,15 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE89" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%90%D7%9C%D7%94-%D7%99%D7%A8%D7%A7%D7%95%D7%A0%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF89" t="n">
         <v>2</v>
-      </c>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%90%D7%9C%D7%94-%D7%99%D7%A8%D7%A7%D7%95%D7%A0%D7%99/</t>
-        </is>
       </c>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
@@ -13140,15 +13140,15 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE90" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%A1%D7%AA%D7%A8-%D7%A4%D7%9C%D7%99%D7%99%D7%A9%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF90" t="n">
         <v>2</v>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%A1%D7%AA%D7%A8-%D7%A4%D7%9C%D7%99%D7%99%D7%A9%D7%A8/</t>
-        </is>
       </c>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
@@ -13279,15 +13279,15 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE91" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%AA%D7%99-%D7%A1%D7%93%D7%9F-%D7%A7%D7%A0%D7%99%D7%A1/</t>
+        </is>
+      </c>
+      <c r="AF91" t="n">
         <v>2</v>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%AA%D7%99-%D7%A1%D7%93%D7%9F-%D7%A7%D7%A0%D7%99%D7%A1/</t>
-        </is>
       </c>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
@@ -13418,15 +13418,15 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE92" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A4%D7%A8%D7%A0%D7%A1%D7%99%D7%A1-%D7%A4%D7%A8%D7%9F-%D7%91%D7%A8%D7%95%D7%A0%D7%A9%D7%98%D7%99%D7%99%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF92" t="n">
         <v>2</v>
-      </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A4%D7%A8%D7%A0%D7%A1%D7%99%D7%A1-%D7%A4%D7%A8%D7%9F-%D7%91%D7%A8%D7%95%D7%A0%D7%A9%D7%98%D7%99%D7%99%D7%9F/</t>
-        </is>
       </c>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
@@ -13557,15 +13557,15 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE93" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%92%D7%91%D7%99-%D7%A4%D7%99%D7%A9%D7%9E%D7%9F-%D7%A4%D7%95%D7%A1%D7%91%D7%A8%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF93" t="n">
         <v>2</v>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%92%D7%91%D7%99-%D7%A4%D7%99%D7%A9%D7%9E%D7%9F-%D7%A4%D7%95%D7%A1%D7%91%D7%A8%D7%99/</t>
-        </is>
       </c>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
@@ -13696,15 +13696,15 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE94" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE94" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99-%D7%A7%D7%9E%D7%97%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF94" t="n">
         <v>2</v>
-      </c>
-      <c r="AF94" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99-%D7%A7%D7%9E%D7%97%D7%99/</t>
-        </is>
       </c>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
@@ -13835,15 +13835,15 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE95" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%90%D7%A4%D7%9C%D7%91%D7%95%D7%99%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AF95" t="n">
         <v>2</v>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%90%D7%A4%D7%9C%D7%91%D7%95%D7%99%D7%9D/</t>
-        </is>
       </c>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
@@ -13974,15 +13974,15 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE96" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%AA-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF96" t="n">
         <v>2</v>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%AA-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
@@ -14113,15 +14113,15 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE97" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF97" t="n">
         <v>2</v>
-      </c>
-      <c r="AF97" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
-        </is>
       </c>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
@@ -14252,15 +14252,15 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE98" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%92%D7%90%D7%99%D7%94-%D7%92%D7%95%D7%93%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF98" t="n">
         <v>2</v>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%92%D7%90%D7%99%D7%94-%D7%92%D7%95%D7%93%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
@@ -14391,15 +14391,15 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE99" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%94-%D7%90%D7%95%D7%A0%D7%92%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF99" t="n">
         <v>2</v>
-      </c>
-      <c r="AF99" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%94-%D7%90%D7%95%D7%A0%D7%92%D7%A8/</t>
-        </is>
       </c>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
@@ -14530,15 +14530,15 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE100" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%99%D7%94-%D7%93%D7%95%D7%9C%D7%91/</t>
+        </is>
+      </c>
+      <c r="AF100" t="n">
         <v>2</v>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%99%D7%94-%D7%93%D7%95%D7%9C%D7%91/</t>
-        </is>
       </c>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
@@ -14669,15 +14669,15 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE101" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%AA%D7%99%D7%AA-%D7%A9%D7%A4%D7%A8%D7%9C%D7%99%D7%A0%D7%92/</t>
+        </is>
+      </c>
+      <c r="AF101" t="n">
         <v>2</v>
-      </c>
-      <c r="AF101" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%AA%D7%99%D7%AA-%D7%A9%D7%A4%D7%A8%D7%9C%D7%99%D7%A0%D7%92/</t>
-        </is>
       </c>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
@@ -14808,15 +14808,15 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE102" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%9E%D7%95%D7%99%D7%90%D7%9C/</t>
+        </is>
+      </c>
+      <c r="AF102" t="n">
         <v>2</v>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%9E%D7%95%D7%99%D7%90%D7%9C/</t>
-        </is>
       </c>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
@@ -14947,15 +14947,15 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE103" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%98%D7%A1%D7%94/</t>
+        </is>
+      </c>
+      <c r="AF103" t="n">
         <v>2</v>
-      </c>
-      <c r="AF103" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%98%D7%A1%D7%94/</t>
-        </is>
       </c>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
@@ -15086,15 +15086,15 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE104" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1%D7%94-%D7%A4%D7%97%D7%9C%D7%99%D7%99%D7%91/</t>
+        </is>
+      </c>
+      <c r="AF104" t="n">
         <v>2</v>
-      </c>
-      <c r="AF104" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1%D7%94-%D7%A4%D7%97%D7%9C%D7%99%D7%99%D7%91/</t>
-        </is>
       </c>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
@@ -15225,15 +15225,15 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE105" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%97%D7%A0%D7%94-%D7%94%D7%A8%D7%95%D7%A9/</t>
+        </is>
+      </c>
+      <c r="AF105" t="n">
         <v>2</v>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%97%D7%A0%D7%94-%D7%94%D7%A8%D7%95%D7%A9/</t>
-        </is>
       </c>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
@@ -15364,15 +15364,15 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE106" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%99-%D7%94%D7%A8%D7%A4%D7%96/</t>
+        </is>
+      </c>
+      <c r="AF106" t="n">
         <v>2</v>
-      </c>
-      <c r="AF106" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%99-%D7%94%D7%A8%D7%A4%D7%96/</t>
-        </is>
       </c>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
@@ -15503,15 +15503,15 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE107" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9E%D7%93%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF107" t="n">
         <v>2</v>
-      </c>
-      <c r="AF107" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9E%D7%93%D7%A8/</t>
-        </is>
       </c>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
@@ -15642,15 +15642,15 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE108" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%99%D7%9C%D7%94-%D7%9C%D7%91-%D7%A8%D7%9F-%D7%97%D7%95%D7%AA%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AF108" t="n">
         <v>2</v>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%99%D7%9C%D7%94-%D7%9C%D7%91-%D7%A8%D7%9F-%D7%97%D7%95%D7%AA%D7%9D/</t>
-        </is>
       </c>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
@@ -15781,15 +15781,15 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE109" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%94%D7%95%D7%93%D7%99%D7%94-%D7%90%D7%99%D7%AA%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AF109" t="n">
         <v>2</v>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%94%D7%95%D7%93%D7%99%D7%94-%D7%90%D7%99%D7%AA%D7%9D/</t>
-        </is>
       </c>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
@@ -15920,15 +15920,15 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE110" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%9C-%D7%91%D7%95%D7%A0%D7%94/</t>
+        </is>
+      </c>
+      <c r="AF110" t="n">
         <v>2</v>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%9C-%D7%91%D7%95%D7%A0%D7%94/</t>
-        </is>
       </c>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
@@ -16059,15 +16059,15 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE111" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%A8-%D7%A7%D7%A8%D7%9F-%D7%A8%D7%98%D7%A0%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF111" t="n">
         <v>2</v>
-      </c>
-      <c r="AF111" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%A8-%D7%A7%D7%A8%D7%9F-%D7%A8%D7%98%D7%A0%D7%A8/</t>
-        </is>
       </c>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
@@ -16198,15 +16198,15 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE112" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%92%D7%B3%D7%95%D7%9C%D7%99-%D7%90%D7%A1%D7%AA%D7%99-%D7%A9%D7%9E%D7%A2%D7%95%D7%A0%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF112" t="n">
         <v>2</v>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%92%D7%B3%D7%95%D7%9C%D7%99-%D7%90%D7%A1%D7%AA%D7%99-%D7%A9%D7%9E%D7%A2%D7%95%D7%A0%D7%99/</t>
-        </is>
       </c>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
@@ -16337,15 +16337,15 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE113" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%92%D7%95%D7%9C%D7%99-%D7%A7%D7%A8%D7%A7%D7%95/</t>
+        </is>
+      </c>
+      <c r="AF113" t="n">
         <v>2</v>
-      </c>
-      <c r="AF113" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%92%D7%95%D7%9C%D7%99-%D7%A7%D7%A8%D7%A7%D7%95/</t>
-        </is>
       </c>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
@@ -16476,15 +16476,15 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE114" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A7%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%92%D7%9C%D7%99%D7%9F-%D7%A1%D7%9C%D7%A2/</t>
+        </is>
+      </c>
+      <c r="AF114" t="n">
         <v>2</v>
-      </c>
-      <c r="AF114" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A7%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%92%D7%9C%D7%99%D7%9F-%D7%A1%D7%9C%D7%A2/</t>
-        </is>
       </c>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
@@ -16615,15 +16615,15 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE115" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%92%D7%99%D7%91%D7%A8-%D7%A9%D7%92%D7%91/</t>
+        </is>
+      </c>
+      <c r="AF115" t="n">
         <v>2</v>
-      </c>
-      <c r="AF115" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%92%D7%99%D7%91%D7%A8-%D7%A9%D7%92%D7%91/</t>
-        </is>
       </c>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
@@ -16754,15 +16754,15 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE116" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%A1%D7%9C%D7%91%D7%95%D7%93%D7%A0%D7%99%D7%A7/</t>
+        </is>
+      </c>
+      <c r="AF116" t="n">
         <v>2</v>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%A1%D7%9C%D7%91%D7%95%D7%93%D7%A0%D7%99%D7%A7/</t>
-        </is>
       </c>
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
@@ -16893,15 +16893,15 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE117" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%95%D7%99%D7%99%D7%A1/</t>
+        </is>
+      </c>
+      <c r="AF117" t="n">
         <v>2</v>
-      </c>
-      <c r="AF117" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%95%D7%99%D7%99%D7%A1/</t>
-        </is>
       </c>
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
@@ -17032,15 +17032,15 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE118" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%90%D7%A0%D7%94-%D7%91%D7%A8%D7%99%D7%A7/</t>
+        </is>
+      </c>
+      <c r="AF118" t="n">
         <v>2</v>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%90%D7%A0%D7%94-%D7%91%D7%A8%D7%99%D7%A7/</t>
-        </is>
       </c>
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
@@ -17171,15 +17171,15 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE119" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99-%D7%90%D7%95%D7%A8-%D7%9C%D7%91%D7%A0%D7%96%D7%95%D7%9F-%D7%9B%D7%94%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF119" t="n">
         <v>2</v>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99-%D7%90%D7%95%D7%A8-%D7%9C%D7%91%D7%A0%D7%96%D7%95%D7%9F-%D7%9B%D7%94%D7%9F/</t>
-        </is>
       </c>
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
@@ -17310,15 +17310,15 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE120" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%A8%D7%95%D7%9F-%D7%A4%D7%99%D7%90%D7%97%D7%95%D7%98%D7%94-%D7%A1%D7%90%D7%9C%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AF120" t="n">
         <v>2</v>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%A8%D7%95%D7%9F-%D7%A4%D7%99%D7%90%D7%97%D7%95%D7%98%D7%94-%D7%A1%D7%90%D7%9C%D7%9D/</t>
-        </is>
       </c>
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
@@ -17449,15 +17449,15 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE121" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF121" t="n">
         <v>2</v>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
-        </is>
       </c>
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
@@ -17588,15 +17588,15 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE122" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%94-%D7%A7%D7%95%D7%92%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF122" t="n">
         <v>2</v>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%94-%D7%A7%D7%95%D7%92%D7%9F/</t>
-        </is>
       </c>
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
@@ -17727,15 +17727,15 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE123" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%90%D7%9F-%D7%A9%D7%95%D7%97%D7%98/</t>
+        </is>
+      </c>
+      <c r="AF123" t="n">
         <v>2</v>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%90%D7%9F-%D7%A9%D7%95%D7%97%D7%98/</t>
-        </is>
       </c>
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
@@ -17866,15 +17866,15 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE124" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99-%D7%A2%D7%95%D7%96%D7%99%D7%90%D7%9C/</t>
+        </is>
+      </c>
+      <c r="AF124" t="n">
         <v>2</v>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99-%D7%A2%D7%95%D7%96%D7%99%D7%90%D7%9C/</t>
-        </is>
       </c>
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
@@ -18005,15 +18005,15 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE125" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%9C%D7%93/</t>
+        </is>
+      </c>
+      <c r="AF125" t="n">
         <v>2</v>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%9C%D7%93/</t>
-        </is>
       </c>
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
@@ -18144,15 +18144,15 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE126" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8-%D7%9C%D7%95%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF126" t="n">
         <v>2</v>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8-%D7%9C%D7%95%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
-        </is>
       </c>
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
@@ -18283,15 +18283,15 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE127" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF127" t="n">
         <v>2</v>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
-        </is>
       </c>
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
@@ -18422,15 +18422,15 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE128" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%98%D7%95%D7%91-%D7%97%D7%99%D7%94-%D7%90%D7%99%D7%98%D7%94/</t>
+        </is>
+      </c>
+      <c r="AF128" t="n">
         <v>2</v>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%98%D7%95%D7%91-%D7%97%D7%99%D7%94-%D7%90%D7%99%D7%98%D7%94/</t>
-        </is>
       </c>
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
@@ -18561,15 +18561,15 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE129" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%A2%D7%99%D7%99%D7%9F-%D7%90%D7%9C%D7%9E%D7%92%D7%95%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF129" t="n">
         <v>2</v>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%A2%D7%99%D7%99%D7%9F-%D7%90%D7%9C%D7%9E%D7%92%D7%95%D7%A8/</t>
-        </is>
       </c>
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
@@ -18700,15 +18700,15 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE130" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99-%D7%93%D7%A8%D7%95%D7%A7%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF130" t="n">
         <v>2</v>
-      </c>
-      <c r="AF130" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99-%D7%93%D7%A8%D7%95%D7%A7%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
@@ -18839,15 +18839,15 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE131" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%94-%D7%92%D7%95%D7%A8%D7%92%D7%95%D7%91/</t>
+        </is>
+      </c>
+      <c r="AF131" t="n">
         <v>2</v>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%94-%D7%92%D7%95%D7%A8%D7%92%D7%95%D7%91/</t>
-        </is>
       </c>
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
@@ -18978,15 +18978,15 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE132" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%99-%D7%90%D7%95%D7%A4%D7%A0%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF132" t="n">
         <v>2</v>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%99-%D7%90%D7%95%D7%A4%D7%A0%D7%A8/</t>
-        </is>
       </c>
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
@@ -19117,15 +19117,15 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE133" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%A9%D7%97%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AF133" t="n">
         <v>2</v>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%A9%D7%97%D7%9D/</t>
-        </is>
       </c>
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
@@ -19256,15 +19256,15 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE134" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%95%D7%A4%D7%A8%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF134" t="n">
         <v>2</v>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%95%D7%A4%D7%A8%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
-        </is>
       </c>
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
@@ -19395,15 +19395,15 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE135" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99-%D7%9C%D7%91-%D7%A7%D7%9C%D7%99%D7%A9%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF135" t="n">
         <v>2</v>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99-%D7%9C%D7%91-%D7%A7%D7%9C%D7%99%D7%A9%D7%A8/</t>
-        </is>
       </c>
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
@@ -19534,15 +19534,15 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE136" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99%D7%94-%D7%90%D7%A0%D7%95%D7%9A/</t>
+        </is>
+      </c>
+      <c r="AF136" t="n">
         <v>2</v>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99%D7%94-%D7%90%D7%A0%D7%95%D7%9A/</t>
-        </is>
       </c>
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
@@ -19673,15 +19673,15 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE137" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%94-%D7%90%D7%99%D7%96%D7%A7%D7%A1/</t>
+        </is>
+      </c>
+      <c r="AF137" t="n">
         <v>2</v>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%94-%D7%90%D7%99%D7%96%D7%A7%D7%A1/</t>
-        </is>
       </c>
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
@@ -19812,15 +19812,15 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE138" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%91-%D7%A0%D7%97%D7%95%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AF138" t="n">
         <v>2</v>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%91-%D7%A0%D7%97%D7%95%D7%9D/</t>
-        </is>
       </c>
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
@@ -19951,15 +19951,15 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE139" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99%D7%A1%D7%94-%D7%91%D7%A8-%D7%90%D7%99%D7%9C%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF139" t="n">
         <v>2</v>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99%D7%A1%D7%94-%D7%91%D7%A8-%D7%90%D7%99%D7%9C%D7%9F/</t>
-        </is>
       </c>
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
@@ -20090,15 +20090,15 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE140" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%9B%D7%9C-%D7%96%D7%99%D7%9C%D7%91%D7%A8%D7%9E%D7%9F-%D7%A8%D7%99%D7%92%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF140" t="n">
         <v>2</v>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%9B%D7%9C-%D7%96%D7%99%D7%9C%D7%91%D7%A8%D7%9E%D7%9F-%D7%A8%D7%99%D7%92%D7%A8/</t>
-        </is>
       </c>
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
@@ -20229,15 +20229,15 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE141" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A7%D7%94-%D7%9B%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF141" t="n">
         <v>2</v>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A7%D7%94-%D7%9B%D7%A5/</t>
-        </is>
       </c>
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
@@ -20368,15 +20368,15 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE142" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99-%D7%A4%D7%91%D7%96%D7%A0%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF142" t="n">
         <v>2</v>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99-%D7%A4%D7%91%D7%96%D7%A0%D7%A8/</t>
-        </is>
       </c>
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
@@ -20507,15 +20507,15 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE143" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99%D7%AA-%D7%A8%D7%95%D7%96%D7%A0%D7%91%D7%90%D7%95%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AF143" t="n">
         <v>2</v>
-      </c>
-      <c r="AF143" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99%D7%AA-%D7%A8%D7%95%D7%96%D7%A0%D7%91%D7%90%D7%95%D7%9D/</t>
-        </is>
       </c>
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
@@ -20646,15 +20646,15 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE144" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8-%D7%92%D7%95%D7%9C%D7%93%D7%A0%D7%92%D7%95%D7%A8%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF144" t="n">
         <v>2</v>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8-%D7%92%D7%95%D7%9C%D7%93%D7%A0%D7%92%D7%95%D7%A8%D7%9F/</t>
-        </is>
       </c>
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
@@ -20785,15 +20785,15 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE145" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%9E%D7%9C%D7%A6%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF145" t="n">
         <v>2</v>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%9E%D7%9C%D7%A6%D7%A8/</t>
-        </is>
       </c>
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
@@ -20924,15 +20924,15 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE146" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%9C%D7%92%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF146" t="n">
         <v>2</v>
-      </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%9C%D7%92%D7%99/</t>
-        </is>
       </c>
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
@@ -21063,15 +21063,15 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE147" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%95%D7%95%D7%9C%D7%A4%D7%95%D7%91%D7%99%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF147" t="n">
         <v>2</v>
-      </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%95%D7%95%D7%9C%D7%A4%D7%95%D7%91%D7%99%D7%A5/</t>
-        </is>
       </c>
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr"/>
@@ -21202,15 +21202,15 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE148" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A2%D7%A8%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF148" t="n">
         <v>2</v>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A2%D7%A8%D7%9F/</t>
-        </is>
       </c>
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr"/>
@@ -21341,15 +21341,15 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE149" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A8%D7%99%D7%91%D7%9C%D7%99%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF149" t="n">
         <v>2</v>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A8%D7%99%D7%91%D7%9C%D7%99%D7%9F/</t>
-        </is>
       </c>
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
@@ -21480,15 +21480,15 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE150" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%A8%D7%A7%D7%99%D7%A1-%D7%A0%D7%A4%D7%AA%D7%9C%D7%95%D7%91%D7%99%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF150" t="n">
         <v>2</v>
-      </c>
-      <c r="AF150" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%A8%D7%A7%D7%99%D7%A1-%D7%A0%D7%A4%D7%AA%D7%9C%D7%95%D7%91%D7%99%D7%A5/</t>
-        </is>
       </c>
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
@@ -21619,15 +21619,15 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE151" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%A7%D7%A9%D7%99%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF151" t="n">
         <v>2</v>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%A7%D7%A9%D7%99%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
-        </is>
       </c>
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
@@ -21758,15 +21758,15 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE152" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%91%D7%9F-%D7%A9%D7%A9%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF152" t="n">
         <v>2</v>
-      </c>
-      <c r="AF152" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%91%D7%9F-%D7%A9%D7%A9%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
@@ -21897,15 +21897,15 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE153" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%A2-%D7%9B%D7%94%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF153" t="n">
         <v>2</v>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%A2-%D7%9B%D7%94%D7%9F/</t>
-        </is>
       </c>
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
@@ -22036,15 +22036,15 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE154" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A0%D7%94-%D7%91%D7%AA%D7%90%D7%A9%D7%95%D7%99%D7%9C%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF154" t="n">
         <v>2</v>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A0%D7%94-%D7%91%D7%AA%D7%90%D7%A9%D7%95%D7%99%D7%9C%D7%99/</t>
-        </is>
       </c>
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
@@ -22175,15 +22175,15 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE155" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A8%D7%99%D7%AA-%D7%90%D7%95%D7%9C%D7%99%D7%91%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF155" t="n">
         <v>2</v>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A8%D7%99%D7%AA-%D7%90%D7%95%D7%9C%D7%99%D7%91%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
-        </is>
       </c>
       <c r="AG155" t="inlineStr"/>
       <c r="AH155" t="inlineStr"/>
@@ -22314,15 +22314,15 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE156" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A6%D7%9F-%D7%99%D7%9E%D7%99%D7%A0%D7%99-%D7%97%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF156" t="n">
         <v>2</v>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A6%D7%9F-%D7%99%D7%9E%D7%99%D7%A0%D7%99-%D7%97%D7%99/</t>
-        </is>
       </c>
       <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr"/>
@@ -22453,15 +22453,15 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE157" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%91%D7%99-%D7%99%D7%A2%D7%A7%D7%91/</t>
+        </is>
+      </c>
+      <c r="AF157" t="n">
         <v>2</v>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%91%D7%99-%D7%99%D7%A2%D7%A7%D7%91/</t>
-        </is>
       </c>
       <c r="AG157" t="inlineStr"/>
       <c r="AH157" t="inlineStr"/>
@@ -22592,15 +22592,15 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE158" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A2%D7%94-%D7%95%D7%99%D7%A6%D7%9E%D7%9F-%D7%A8%D7%91%D7%99%D7%91%D7%95/</t>
+        </is>
+      </c>
+      <c r="AF158" t="n">
         <v>2</v>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A2%D7%94-%D7%95%D7%99%D7%A6%D7%9E%D7%9F-%D7%A8%D7%91%D7%99%D7%91%D7%95/</t>
-        </is>
       </c>
       <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr"/>
@@ -22731,15 +22731,15 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE159" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%91%D7%95%D7%A8%D7%92-%D7%A1%D7%92%D7%9F-%D7%9B%D7%94%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF159" t="n">
         <v>2</v>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%91%D7%95%D7%A8%D7%92-%D7%A1%D7%92%D7%9F-%D7%9B%D7%94%D7%9F/</t>
-        </is>
       </c>
       <c r="AG159" t="inlineStr"/>
       <c r="AH159" t="inlineStr"/>
@@ -22870,15 +22870,15 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE160" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%92%D7%95%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF160" t="n">
         <v>2</v>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%92%D7%95%D7%A8/</t>
-        </is>
       </c>
       <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr"/>
@@ -23009,15 +23009,15 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE161" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%A4%D7%99%D7%9C%D7%95%D7%A1%D7%95%D7%A3/</t>
+        </is>
+      </c>
+      <c r="AF161" t="n">
         <v>2</v>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%A4%D7%99%D7%9C%D7%95%D7%A1%D7%95%D7%A3/</t>
-        </is>
       </c>
       <c r="AG161" t="inlineStr"/>
       <c r="AH161" t="inlineStr"/>
@@ -23148,15 +23148,15 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE162" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%98%D7%95%D7%A9%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF162" t="n">
         <v>2</v>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%98%D7%95%D7%A9%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
-        </is>
       </c>
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr"/>
@@ -23287,15 +23287,15 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE163" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE163" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A8%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF163" t="n">
         <v>2</v>
-      </c>
-      <c r="AF163" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A8%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8/</t>
-        </is>
       </c>
       <c r="AG163" t="inlineStr"/>
       <c r="AH163" t="inlineStr"/>
@@ -23426,15 +23426,15 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE164" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%9C%D7%9B%D7%94-%D7%9B%D7%94%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF164" t="n">
         <v>2</v>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%9C%D7%9B%D7%94-%D7%9B%D7%94%D7%9F/</t>
-        </is>
       </c>
       <c r="AG164" t="inlineStr"/>
       <c r="AH164" t="inlineStr"/>
@@ -23565,15 +23565,15 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE165" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%9C%D7%92%D7%94-%D7%95%D7%A7%D7%A1%D7%9C%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF165" t="n">
         <v>2</v>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%9C%D7%92%D7%94-%D7%95%D7%A7%D7%A1%D7%9C%D7%A8/</t>
-        </is>
       </c>
       <c r="AG165" t="inlineStr"/>
       <c r="AH165" t="inlineStr"/>
@@ -23704,15 +23704,15 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE166" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%97%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF166" t="n">
         <v>2</v>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%97%D7%9F/</t>
-        </is>
       </c>
       <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr"/>
@@ -23843,15 +23843,15 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE167" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%9E%D7%9C%D7%99-%D7%94%D7%A0%D7%92%D7%91%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF167" t="n">
         <v>2</v>
-      </c>
-      <c r="AF167" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%9E%D7%9C%D7%99-%D7%94%D7%A0%D7%92%D7%91%D7%99/</t>
-        </is>
       </c>
       <c r="AG167" t="inlineStr"/>
       <c r="AH167" t="inlineStr"/>
@@ -23982,15 +23982,15 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE168" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%93%D7%99%D7%99%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF168" t="n">
         <v>2</v>
-      </c>
-      <c r="AF168" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%93%D7%99%D7%99%D7%9F/</t>
-        </is>
       </c>
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr"/>
@@ -24121,15 +24121,15 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE169" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%99%D7%A2%D7%A7%D7%91%D7%A1%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF169" t="n">
         <v>2</v>
-      </c>
-      <c r="AF169" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%99%D7%A2%D7%A7%D7%91%D7%A1%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr"/>
@@ -24260,15 +24260,15 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE170" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7-%D7%A0%D7%A7%D7%A9/</t>
+        </is>
+      </c>
+      <c r="AF170" t="n">
         <v>2</v>
-      </c>
-      <c r="AF170" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7-%D7%A0%D7%A7%D7%A9/</t>
-        </is>
       </c>
       <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr"/>
@@ -24399,15 +24399,15 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE171" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8-%D7%9B%D7%94%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF171" t="n">
         <v>2</v>
-      </c>
-      <c r="AF171" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8-%D7%9B%D7%94%D7%9F/</t>
-        </is>
       </c>
       <c r="AG171" t="inlineStr"/>
       <c r="AH171" t="inlineStr"/>
@@ -24538,15 +24538,15 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE172" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A4%D7%96-%D7%A8%D7%99%D7%99%D7%9B%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF172" t="n">
         <v>2</v>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A4%D7%96-%D7%A8%D7%99%D7%99%D7%9B%D7%A8/</t>
-        </is>
       </c>
       <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr"/>
@@ -24677,15 +24677,15 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE173" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%97%D7%9C-%D7%A4%D7%99%D7%A8%D7%A1%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF173" t="n">
         <v>2</v>
-      </c>
-      <c r="AF173" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%97%D7%9C-%D7%A4%D7%99%D7%A8%D7%A1%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG173" t="inlineStr"/>
       <c r="AH173" t="inlineStr"/>
@@ -24816,15 +24816,15 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE174" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE174" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%AA-%D7%9C%D7%91%D7%99%D7%90/</t>
+        </is>
+      </c>
+      <c r="AF174" t="n">
         <v>2</v>
-      </c>
-      <c r="AF174" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%AA-%D7%9C%D7%91%D7%99%D7%90/</t>
-        </is>
       </c>
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr"/>
@@ -24955,15 +24955,15 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE175" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%96-%D7%A2%D7%96%D7%A8%D7%90/</t>
+        </is>
+      </c>
+      <c r="AF175" t="n">
         <v>2</v>
-      </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%96-%D7%A2%D7%96%D7%A8%D7%90/</t>
-        </is>
       </c>
       <c r="AG175" t="inlineStr"/>
       <c r="AH175" t="inlineStr"/>
@@ -25094,15 +25094,15 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE176" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%A0%D7%A0%D7%94-%D7%95%D7%99%D7%A8%D7%A6%D7%91%D7%95%D7%A8%D7%92%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF176" t="n">
         <v>2</v>
-      </c>
-      <c r="AF176" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%A0%D7%A0%D7%94-%D7%95%D7%99%D7%A8%D7%A6%D7%91%D7%95%D7%A8%D7%92%D7%A8/</t>
-        </is>
       </c>
       <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
@@ -25233,15 +25233,15 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE177" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE177" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%A2%D7%95%D7%AA-%D7%94%D7%A8%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF177" t="n">
         <v>2</v>
-      </c>
-      <c r="AF177" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%A2%D7%95%D7%AA-%D7%94%D7%A8%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
-        </is>
       </c>
       <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
@@ -25372,15 +25372,15 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE178" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE178" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%98%D7%9C-%D7%90%D7%99%D7%A9-%D7%A9%D7%9C%D7%95%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AF178" t="n">
         <v>2</v>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%98%D7%9C-%D7%90%D7%99%D7%A9-%D7%A9%D7%9C%D7%95%D7%9D/</t>
-        </is>
       </c>
       <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
@@ -25511,15 +25511,15 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE179" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A7%D7%99-%D7%96%D7%9C%D7%9B%D7%94/</t>
+        </is>
+      </c>
+      <c r="AF179" t="n">
         <v>2</v>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A7%D7%99-%D7%96%D7%9C%D7%9B%D7%94/</t>
-        </is>
       </c>
       <c r="AG179" t="inlineStr"/>
       <c r="AH179" t="inlineStr"/>
@@ -25650,15 +25650,15 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE180" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A0%D7%AA-%D7%90%D7%9C%D7%93%D7%A8-%D7%92%D7%A8%D7%A9%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF180" t="n">
         <v>2</v>
-      </c>
-      <c r="AF180" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A0%D7%AA-%D7%90%D7%9C%D7%93%D7%A8-%D7%92%D7%A8%D7%A9%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr"/>
@@ -25789,15 +25789,15 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE181" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%97%D7%99-%D7%A8%D7%95%D7%96%D7%A0%D7%98%D7%9C/</t>
+        </is>
+      </c>
+      <c r="AF181" t="n">
         <v>2</v>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%97%D7%99-%D7%A8%D7%95%D7%96%D7%A0%D7%98%D7%9C/</t>
-        </is>
       </c>
       <c r="AG181" t="inlineStr"/>
       <c r="AH181" t="inlineStr"/>
@@ -25928,15 +25928,15 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE182" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE182" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99-%D7%A4%D7%A8%D7%9C/</t>
+        </is>
+      </c>
+      <c r="AF182" t="n">
         <v>2</v>
-      </c>
-      <c r="AF182" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99-%D7%A4%D7%A8%D7%9C/</t>
-        </is>
       </c>
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr"/>
@@ -26067,15 +26067,15 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE183" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF183" t="n">
         <v>2</v>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8%D7%99/</t>
-        </is>
       </c>
       <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr"/>
@@ -26206,15 +26206,15 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE184" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%9D-%D7%90%D7%9C%D7%9E%D7%95%D7%92/</t>
+        </is>
+      </c>
+      <c r="AF184" t="n">
         <v>2</v>
-      </c>
-      <c r="AF184" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%9D-%D7%90%D7%9C%D7%9E%D7%95%D7%92/</t>
-        </is>
       </c>
       <c r="AG184" t="inlineStr"/>
       <c r="AH184" t="inlineStr"/>
@@ -26345,15 +26345,15 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE185" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%99-%D7%98%D7%9C-%D7%9E%D7%99%D7%A8%D7%96/</t>
+        </is>
+      </c>
+      <c r="AF185" t="n">
         <v>2</v>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%99-%D7%98%D7%9C-%D7%9E%D7%99%D7%A8%D7%96/</t>
-        </is>
       </c>
       <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr"/>
@@ -26484,15 +26484,15 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE186" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%92%D7%99%D7%AA-%D7%9C%D7%91/</t>
+        </is>
+      </c>
+      <c r="AF186" t="n">
         <v>2</v>
-      </c>
-      <c r="AF186" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%92%D7%99%D7%AA-%D7%9C%D7%91/</t>
-        </is>
       </c>
       <c r="AG186" t="inlineStr"/>
       <c r="AH186" t="inlineStr"/>
@@ -26623,15 +26623,15 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE187" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE187" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF187" t="n">
         <v>2</v>
-      </c>
-      <c r="AF187" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
-        </is>
       </c>
       <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr"/>
@@ -26762,15 +26762,15 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE188" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE188" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%A9%D7%97%D7%A8-%D7%91%D7%9F-%D7%93%D7%95%D7%93/</t>
+        </is>
+      </c>
+      <c r="AF188" t="n">
         <v>2</v>
-      </c>
-      <c r="AF188" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%A9%D7%97%D7%A8-%D7%91%D7%9F-%D7%93%D7%95%D7%93/</t>
-        </is>
       </c>
       <c r="AG188" t="inlineStr"/>
       <c r="AH188" t="inlineStr"/>
@@ -26901,15 +26901,15 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE189" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE189" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%A7%D7%93-%D7%9C%D7%99%D7%91%D7%A0%D7%94/</t>
+        </is>
+      </c>
+      <c r="AF189" t="n">
         <v>2</v>
-      </c>
-      <c r="AF189" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%A7%D7%93-%D7%9C%D7%99%D7%91%D7%A0%D7%94/</t>
-        </is>
       </c>
       <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr"/>
@@ -27040,15 +27040,15 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE190" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE190" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%A0%D7%94-%D7%A0%D7%92%D7%91%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF190" t="n">
         <v>2</v>
-      </c>
-      <c r="AF190" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%A0%D7%94-%D7%A0%D7%92%D7%91%D7%99/</t>
-        </is>
       </c>
       <c r="AG190" t="inlineStr"/>
       <c r="AH190" t="inlineStr"/>
@@ -27179,15 +27179,15 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE191" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%9F-%D7%96%D7%9C%D7%9E%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF191" t="n">
         <v>2</v>
-      </c>
-      <c r="AF191" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%9F-%D7%96%D7%9C%D7%9E%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
-        </is>
       </c>
       <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr"/>
@@ -27318,15 +27318,15 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE192" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE192" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%99-%D7%97%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF192" t="n">
         <v>2</v>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%99-%D7%97%D7%9F/</t>
-        </is>
       </c>
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
@@ -27457,15 +27457,15 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE193" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%94-%D7%A1%D7%95%D7%A1%D7%99%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF193" t="n">
         <v>2</v>
-      </c>
-      <c r="AF193" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%94-%D7%A1%D7%95%D7%A1%D7%99%D7%9F/</t>
-        </is>
       </c>
       <c r="AG193" t="inlineStr"/>
       <c r="AH193" t="inlineStr"/>
@@ -27596,15 +27596,15 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE194" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%90%D7%9C-%D7%A8%D7%91%D7%A7%D7%94-%D7%99%D7%A4%D7%94/</t>
+        </is>
+      </c>
+      <c r="AF194" t="n">
         <v>2</v>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%90%D7%9C-%D7%A8%D7%91%D7%A7%D7%94-%D7%99%D7%A4%D7%94/</t>
-        </is>
       </c>
       <c r="AG194" t="inlineStr"/>
       <c r="AH194" t="inlineStr"/>
@@ -27735,15 +27735,15 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE195" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A4%D7%99%D7%99%D7%98%D7%9C%D7%A1%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF195" t="n">
         <v>2</v>
-      </c>
-      <c r="AF195" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A4%D7%99%D7%99%D7%98%D7%9C%D7%A1%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr"/>
@@ -27874,15 +27874,15 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE196" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%95%D7%98%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF196" t="n">
         <v>2</v>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%95%D7%98%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG196" t="inlineStr"/>
       <c r="AH196" t="inlineStr"/>
@@ -28013,15 +28013,15 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE197" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%A8%D7%95%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF197" t="n">
         <v>2</v>
-      </c>
-      <c r="AF197" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%A8%D7%95%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG197" t="inlineStr"/>
       <c r="AH197" t="inlineStr"/>
@@ -28152,15 +28152,15 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE198" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE198" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%98-%D7%93%D7%A8%D7%A1%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF198" t="n">
         <v>2</v>
-      </c>
-      <c r="AF198" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%98-%D7%93%D7%A8%D7%A1%D7%9F/</t>
-        </is>
       </c>
       <c r="AG198" t="inlineStr"/>
       <c r="AH198" t="inlineStr"/>
@@ -28291,15 +28291,15 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE199" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%92%D7%95%D7%96%D7%9C%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF199" t="n">
         <v>2</v>
-      </c>
-      <c r="AF199" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%92%D7%95%D7%96%D7%9C%D7%9F/</t>
-        </is>
       </c>
       <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr"/>
@@ -28430,15 +28430,15 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE200" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE200" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%94%D7%95%D7%9C%D7%A6%D7%91%D7%A8%D7%92-%D7%97%D7%99%D7%99%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AF200" t="n">
         <v>2</v>
-      </c>
-      <c r="AF200" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%94%D7%95%D7%9C%D7%A6%D7%91%D7%A8%D7%92-%D7%97%D7%99%D7%99%D7%9D/</t>
-        </is>
       </c>
       <c r="AG200" t="inlineStr"/>
       <c r="AH200" t="inlineStr"/>
@@ -28569,15 +28569,15 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE201" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE201" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A0%D7%93%D7%9C%D7%91%D7%90%D7%95%D7%9D/</t>
+        </is>
+      </c>
+      <c r="AF201" t="n">
         <v>2</v>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A0%D7%93%D7%9C%D7%91%D7%90%D7%95%D7%9D/</t>
-        </is>
       </c>
       <c r="AG201" t="inlineStr"/>
       <c r="AH201" t="inlineStr"/>
@@ -28708,15 +28708,15 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE202" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A8%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF202" t="n">
         <v>2</v>
-      </c>
-      <c r="AF202" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A8%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
-        </is>
       </c>
       <c r="AG202" t="inlineStr"/>
       <c r="AH202" t="inlineStr"/>
@@ -28847,15 +28847,15 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE203" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%9E%D7%9C%D7%9B%D7%94-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/</t>
+        </is>
+      </c>
+      <c r="AF203" t="n">
         <v>2</v>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%9E%D7%9C%D7%9B%D7%94-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/</t>
-        </is>
       </c>
       <c r="AG203" t="inlineStr"/>
       <c r="AH203" t="inlineStr"/>
@@ -28986,15 +28986,15 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE204" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%94%D7%9C%D7%A4%D7%A8%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF204" t="n">
         <v>2</v>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%94%D7%9C%D7%A4%D7%A8%D7%9F/</t>
-        </is>
       </c>
       <c r="AG204" t="inlineStr"/>
       <c r="AH204" t="inlineStr"/>
@@ -29125,15 +29125,15 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE205" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE205" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A1%D7%95%D7%A4%D7%99%D7%94-%D7%9E%D7%9C%D7%97%D7%96%D7%99%D7%90%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF205" t="n">
         <v>2</v>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A1%D7%95%D7%A4%D7%99%D7%94-%D7%9E%D7%9C%D7%97%D7%96%D7%99%D7%90%D7%9F/</t>
-        </is>
       </c>
       <c r="AG205" t="inlineStr"/>
       <c r="AH205" t="inlineStr"/>
@@ -29264,15 +29264,15 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE206" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%9E%D7%99%D7%98%D7%9C%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF206" t="n">
         <v>2</v>
-      </c>
-      <c r="AF206" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%9E%D7%99%D7%98%D7%9C%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr"/>
@@ -29403,15 +29403,15 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE207" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE207" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%A6%D7%A0%D7%A6%D7%99%D7%A4%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF207" t="n">
         <v>2</v>
-      </c>
-      <c r="AF207" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%A6%D7%A0%D7%A6%D7%99%D7%A4%D7%A8/</t>
-        </is>
       </c>
       <c r="AG207" t="inlineStr"/>
       <c r="AH207" t="inlineStr"/>
@@ -29542,15 +29542,15 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE208" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%91%D7%99%D7%A8%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF208" t="n">
         <v>2</v>
-      </c>
-      <c r="AF208" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%91%D7%99%D7%A8%D7%9F/</t>
-        </is>
       </c>
       <c r="AG208" t="inlineStr"/>
       <c r="AH208" t="inlineStr"/>
@@ -29681,15 +29681,15 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE209" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%A4%D7%9C%D7%93/</t>
+        </is>
+      </c>
+      <c r="AF209" t="n">
         <v>2</v>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%A4%D7%9C%D7%93/</t>
-        </is>
       </c>
       <c r="AG209" t="inlineStr"/>
       <c r="AH209" t="inlineStr"/>
@@ -29820,15 +29820,15 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE210" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99%D7%94-%D7%91%D7%9F-%D7%9E%D7%96%D7%99%D7%90/</t>
+        </is>
+      </c>
+      <c r="AF210" t="n">
         <v>2</v>
-      </c>
-      <c r="AF210" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99%D7%94-%D7%91%D7%9F-%D7%9E%D7%96%D7%99%D7%90/</t>
-        </is>
       </c>
       <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr"/>
@@ -29959,15 +29959,15 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE211" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE211" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%A8-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF211" t="n">
         <v>3</v>
-      </c>
-      <c r="AF211" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%A8-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr"/>
@@ -30098,15 +30098,15 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE212" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A9%D7%92%D7%91-%D7%90%D7%A8%D7%96/</t>
+        </is>
+      </c>
+      <c r="AF212" t="n">
         <v>2</v>
-      </c>
-      <c r="AF212" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A9%D7%92%D7%91-%D7%90%D7%A8%D7%96/</t>
-        </is>
       </c>
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr"/>
@@ -30237,15 +30237,15 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE213" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE213" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A2%D7%95%D7%A4%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF213" t="n">
         <v>2</v>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A2%D7%95%D7%A4%D7%A8/</t>
-        </is>
       </c>
       <c r="AG213" t="inlineStr"/>
       <c r="AH213" t="inlineStr"/>
@@ -30376,15 +30376,15 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE214" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE214" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99%D7%9E%D7%94-%D7%A9%D7%A2%D7%A9%D7%95%D7%A2/</t>
+        </is>
+      </c>
+      <c r="AF214" t="n">
         <v>2</v>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99%D7%9E%D7%94-%D7%A9%D7%A2%D7%A9%D7%95%D7%A2/</t>
-        </is>
       </c>
       <c r="AG214" t="inlineStr"/>
       <c r="AH214" t="inlineStr"/>
@@ -30515,15 +30515,15 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE215" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%AA%D7%A7%D7%95%D7%94-%D7%A6%D7%93%D7%95%D7%A7/</t>
+        </is>
+      </c>
+      <c r="AF215" t="n">
         <v>3</v>
-      </c>
-      <c r="AF215" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%AA%D7%A7%D7%95%D7%94-%D7%A6%D7%93%D7%95%D7%A7/</t>
-        </is>
       </c>
       <c r="AG215" t="inlineStr"/>
       <c r="AH215" t="inlineStr"/>
@@ -30654,15 +30654,15 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE216" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%98%D7%95%D7%91%D7%94-%D7%99%D7%95%D7%A1%D7%A4%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF216" t="n">
         <v>2</v>
-      </c>
-      <c r="AF216" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%98%D7%95%D7%91%D7%94-%D7%99%D7%95%D7%A1%D7%A4%D7%9F/</t>
-        </is>
       </c>
       <c r="AG216" t="inlineStr"/>
       <c r="AH216" t="inlineStr"/>
@@ -30793,15 +30793,15 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE217" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE217" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A6%D7%91%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF217" t="n">
         <v>2</v>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A6%D7%91%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
-        </is>
       </c>
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" t="inlineStr"/>
@@ -30932,15 +30932,15 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE218" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A6%D7%95%D7%A4%D7%99%D7%AA-%D7%93%D7%99%D7%A1%D7%98%D7%9C%D7%9E%D7%9F-%D7%9E%D7%99%D7%A8%D7%A7%D7%99%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF218" t="n">
         <v>2</v>
-      </c>
-      <c r="AF218" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A6%D7%95%D7%A4%D7%99%D7%AA-%D7%93%D7%99%D7%A1%D7%98%D7%9C%D7%9E%D7%9F-%D7%9E%D7%99%D7%A8%D7%A7%D7%99%D7%9F/</t>
-        </is>
       </c>
       <c r="AG218" t="inlineStr"/>
       <c r="AH218" t="inlineStr"/>
@@ -31071,15 +31071,15 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE219" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE219" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%95%D7%9C%D7%A8%D7%99-%D7%9E%D7%99%D7%9C%D7%94%D7%93%D7%95/</t>
+        </is>
+      </c>
+      <c r="AF219" t="n">
         <v>2</v>
-      </c>
-      <c r="AF219" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%95%D7%9C%D7%A8%D7%99-%D7%9E%D7%99%D7%9C%D7%94%D7%93%D7%95/</t>
-        </is>
       </c>
       <c r="AG219" t="inlineStr"/>
       <c r="AH219" t="inlineStr"/>
@@ -31210,15 +31210,15 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE220" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE220" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%91%D7%90%D7%A9%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF220" t="n">
         <v>2</v>
-      </c>
-      <c r="AF220" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%91%D7%90%D7%A9%D7%A8/</t>
-        </is>
       </c>
       <c r="AG220" t="inlineStr"/>
       <c r="AH220" t="inlineStr"/>
@@ -31349,15 +31349,15 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE221" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%95%D7%99%D7%A7%D7%98%D7%95%D7%A8%D7%99%D7%94-%D7%A7%D7%9E%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF221" t="n">
         <v>2</v>
-      </c>
-      <c r="AF221" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%95%D7%99%D7%A7%D7%98%D7%95%D7%A8%D7%99%D7%94-%D7%A7%D7%9E%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
-        </is>
       </c>
       <c r="AG221" t="inlineStr"/>
       <c r="AH221" t="inlineStr"/>
@@ -31488,15 +31488,15 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE222" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE222" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%95%D7%A4%D7%90%D7%90-%D7%90%D7%91%D7%95-%D7%90%D7%A1%D7%9E%D7%90%D7%A2%D7%99%D7%9C/</t>
+        </is>
+      </c>
+      <c r="AF222" t="n">
         <v>2</v>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%95%D7%A4%D7%90%D7%90-%D7%90%D7%91%D7%95-%D7%90%D7%A1%D7%9E%D7%90%D7%A2%D7%99%D7%9C/</t>
-        </is>
       </c>
       <c r="AG222" t="inlineStr"/>
       <c r="AH222" t="inlineStr"/>
@@ -31627,15 +31627,15 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE223" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%91%D7%90%D7%93%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF223" t="n">
         <v>2</v>
-      </c>
-      <c r="AF223" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%91%D7%90%D7%93%D7%A8/</t>
-        </is>
       </c>
       <c r="AG223" t="inlineStr"/>
       <c r="AH223" t="inlineStr"/>
@@ -31766,15 +31766,15 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE224" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE224" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%93%D7%95%D7%91%D7%93%D7%91%D7%9F-%D7%92%D7%9C%D7%95%D7%96%D7%9E%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF224" t="n">
         <v>2</v>
-      </c>
-      <c r="AF224" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%93%D7%95%D7%91%D7%93%D7%91%D7%9F-%D7%92%D7%9C%D7%95%D7%96%D7%9E%D7%9F/</t>
-        </is>
       </c>
       <c r="AG224" t="inlineStr"/>
       <c r="AH224" t="inlineStr"/>
@@ -31905,15 +31905,15 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE225" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%90%D7%98%D7%99%D7%90%D7%A1/</t>
+        </is>
+      </c>
+      <c r="AF225" t="n">
         <v>2</v>
-      </c>
-      <c r="AF225" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%90%D7%98%D7%99%D7%90%D7%A1/</t>
-        </is>
       </c>
       <c r="AG225" t="inlineStr"/>
       <c r="AH225" t="inlineStr"/>
@@ -32044,15 +32044,15 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE226" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%93%D7%95%D7%91%D7%A1%D7%98%D7%A8-%D7%93%D7%95%D7%93/</t>
+        </is>
+      </c>
+      <c r="AF226" t="n">
         <v>2</v>
-      </c>
-      <c r="AF226" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%93%D7%95%D7%91%D7%A1%D7%98%D7%A8-%D7%93%D7%95%D7%93/</t>
-        </is>
       </c>
       <c r="AG226" t="inlineStr"/>
       <c r="AH226" t="inlineStr"/>
@@ -32183,15 +32183,15 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE227" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/291/</t>
+        </is>
+      </c>
+      <c r="AF227" t="n">
         <v>2</v>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/291/</t>
-        </is>
       </c>
       <c r="AG227" t="inlineStr"/>
       <c r="AH227" t="inlineStr"/>
@@ -32322,15 +32322,15 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE228" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%96%D7%99%D7%AA-%D7%97%D7%92%D7%91%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF228" t="n">
         <v>2</v>
-      </c>
-      <c r="AF228" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%96%D7%99%D7%AA-%D7%97%D7%92%D7%91%D7%99/</t>
-        </is>
       </c>
       <c r="AG228" t="inlineStr"/>
       <c r="AH228" t="inlineStr"/>
@@ -32461,15 +32461,15 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE229" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE229" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%A6%D7%A0%D7%9C%D7%A1%D7%95%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF229" t="n">
         <v>2</v>
-      </c>
-      <c r="AF229" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%A6%D7%A0%D7%9C%D7%A1%D7%95%D7%9F/</t>
-        </is>
       </c>
       <c r="AG229" t="inlineStr"/>
       <c r="AH229" t="inlineStr"/>
@@ -32600,15 +32600,15 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE230" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE230" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A4%D7%9C%D7%92/</t>
+        </is>
+      </c>
+      <c r="AF230" t="n">
         <v>2</v>
-      </c>
-      <c r="AF230" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A4%D7%9C%D7%92/</t>
-        </is>
       </c>
       <c r="AG230" t="inlineStr"/>
       <c r="AH230" t="inlineStr"/>
@@ -32739,15 +32739,15 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE231" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF231" t="n">
         <v>2</v>
-      </c>
-      <c r="AF231" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8/</t>
-        </is>
       </c>
       <c r="AG231" t="inlineStr"/>
       <c r="AH231" t="inlineStr"/>
@@ -32878,15 +32878,15 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE232" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE232" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%90%D7%A0%D7%94-%D7%A4%D7%99%D7%A9%D7%91%D7%99%D7%99%D7%9F/</t>
+        </is>
+      </c>
+      <c r="AF232" t="n">
         <v>2</v>
-      </c>
-      <c r="AF232" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%90%D7%A0%D7%94-%D7%A4%D7%99%D7%A9%D7%91%D7%99%D7%99%D7%9F/</t>
-        </is>
       </c>
       <c r="AG232" t="inlineStr"/>
       <c r="AH232" t="inlineStr"/>
@@ -33017,15 +33017,15 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE233" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE233" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%9E%D7%95%D7%A8%D7%9C%D7%99/</t>
+        </is>
+      </c>
+      <c r="AF233" t="n">
         <v>2</v>
-      </c>
-      <c r="AF233" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%9E%D7%95%D7%A8%D7%9C%D7%99/</t>
-        </is>
       </c>
       <c r="AG233" t="inlineStr"/>
       <c r="AH233" t="inlineStr"/>
@@ -33156,15 +33156,15 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE234" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE234" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%A8%D7%95%D7%91/</t>
+        </is>
+      </c>
+      <c r="AF234" t="n">
         <v>2</v>
-      </c>
-      <c r="AF234" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%A8%D7%95%D7%91/</t>
-        </is>
       </c>
       <c r="AG234" t="inlineStr"/>
       <c r="AH234" t="inlineStr"/>
@@ -33295,15 +33295,15 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE235" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%99%D7%AA-%D7%9B%D7%A5-%D7%91%D7%A1%D7%98%D7%A7%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF235" t="n">
         <v>2</v>
-      </c>
-      <c r="AF235" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%99%D7%AA-%D7%9B%D7%A5-%D7%91%D7%A1%D7%98%D7%A7%D7%A8/</t>
-        </is>
       </c>
       <c r="AG235" t="inlineStr"/>
       <c r="AH235" t="inlineStr"/>
@@ -33434,15 +33434,15 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE236" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE236" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A2%D7%9E%D7%99%D7%AA/</t>
+        </is>
+      </c>
+      <c r="AF236" t="n">
         <v>2</v>
-      </c>
-      <c r="AF236" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A2%D7%9E%D7%99%D7%AA/</t>
-        </is>
       </c>
       <c r="AG236" t="inlineStr"/>
       <c r="AH236" t="inlineStr"/>
@@ -33573,15 +33573,15 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE237" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A8%D7%91%D7%99%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
+        </is>
+      </c>
+      <c r="AF237" t="n">
         <v>2</v>
-      </c>
-      <c r="AF237" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A8%D7%91%D7%99%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
-        </is>
       </c>
       <c r="AG237" t="inlineStr"/>
       <c r="AH237" t="inlineStr"/>
@@ -33712,15 +33712,15 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE238" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE238" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%91%D7%9C-%D7%A7%D7%A1%D7%98%D7%99%D7%9F-%D7%9B%D7%94%D7%A0%D7%90/</t>
+        </is>
+      </c>
+      <c r="AF238" t="n">
         <v>2</v>
-      </c>
-      <c r="AF238" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%91%D7%9C-%D7%A7%D7%A1%D7%98%D7%99%D7%9F-%D7%9B%D7%94%D7%A0%D7%90/</t>
-        </is>
       </c>
       <c r="AG238" t="inlineStr"/>
       <c r="AH238" t="inlineStr"/>
@@ -33851,15 +33851,15 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE239" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE239" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%9C%D7%91/</t>
+        </is>
+      </c>
+      <c r="AF239" t="n">
         <v>2</v>
-      </c>
-      <c r="AF239" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%9C%D7%91/</t>
-        </is>
       </c>
       <c r="AG239" t="inlineStr"/>
       <c r="AH239" t="inlineStr"/>
@@ -33996,15 +33996,15 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>7971696</v>
-      </c>
-      <c r="AE240" t="n">
+        <v>23915088</v>
+      </c>
+      <c r="AE240" t="inlineStr">
+        <is>
+          <t>https://nefeshachat.co.il/</t>
+        </is>
+      </c>
+      <c r="AF240" t="n">
         <v>2</v>
-      </c>
-      <c r="AF240" t="inlineStr">
-        <is>
-          <t>https://nefeshachat.co.il/</t>
-        </is>
       </c>
       <c r="AG240" t="inlineStr"/>
       <c r="AH240" t="inlineStr"/>
@@ -34135,15 +34135,15 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE241" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE241" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9B%D7%A4%D7%99%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF241" t="n">
         <v>2</v>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9B%D7%A4%D7%99%D7%A8/</t>
-        </is>
       </c>
       <c r="AG241" t="inlineStr"/>
       <c r="AH241" t="inlineStr"/>
@@ -34274,15 +34274,15 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE242" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/counselors/%D7%A8%D7%A9%D7%9C-%D7%98%D7%95%D7%94%D7%A8/</t>
+        </is>
+      </c>
+      <c r="AF242" t="n">
         <v>2</v>
-      </c>
-      <c r="AF242" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/counselors/%D7%A8%D7%A9%D7%9C-%D7%98%D7%95%D7%94%D7%A8/</t>
-        </is>
       </c>
       <c r="AG242" t="inlineStr"/>
       <c r="AH242" t="inlineStr"/>
@@ -34413,15 +34413,15 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE243" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>https://tzuna-tova.co.il/</t>
+        </is>
+      </c>
+      <c r="AF243" t="n">
         <v>2</v>
-      </c>
-      <c r="AF243" t="inlineStr">
-        <is>
-          <t>https://tzuna-tova.co.il/</t>
-        </is>
       </c>
       <c r="AG243" t="inlineStr"/>
       <c r="AH243" t="inlineStr"/>
@@ -34552,15 +34552,15 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE244" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>https://www.shiri-sleep.co.il/</t>
+        </is>
+      </c>
+      <c r="AF244" t="n">
         <v>2</v>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>https://www.shiri-sleep.co.il/</t>
-        </is>
       </c>
       <c r="AG244" t="inlineStr"/>
       <c r="AH244" t="inlineStr"/>
@@ -34589,12 +34589,12 @@
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="inlineStr">
         <is>
-          <t>תל אביב מדיקל סנטר</t>
+          <t>ייעוץ שינה</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>community_clinic</t>
+          <t>sleep_consultant</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -34604,23 +34604,23 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>https://tlvmed.co.il/</t>
+          <t>https://www.meitalk.co.il/ייעוץ-שינה/</t>
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>evgene@tlvmed.co.il</t>
+          <t>adi@goodnights.co.il</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -34629,11 +34629,11 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>https://tlvmed.co.il/</t>
+          <t>https://www.goodnights.co.il/contact</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -34643,17 +34643,17 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>אשמח לפנייתך לדוא”ל האישי שלי evgene@tlvmed.co.il מנכ”ל תל אביב מדיקל סנטר יבגני קצוביץ’</t>
+          <t>צור קשר עם עדי ולטר top of page להתחברות אשמח לשמוע מכם עדי ולטר יועצת שינה ומדירכת הורים ​ 054-7772904 Adi@goodnights.co.il ההודעה שלך נשלחה בהצלחה שלח שם מלא * דוא״ל * נושא הודעה צור קשר בלוג מאמרים וכתבות המלצות סרטונים הדרכת הורים מריבות בין אחים גידול תאומים ייעוץ שינה שינה של תינוקות וילדים לידה עד חמישה חודשים תהליך</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"ייעוץ שינה" יועצת שינה</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
@@ -34668,38 +34668,46 @@
         <v>0</v>
       </c>
       <c r="U245" t="inlineStr"/>
-      <c r="V245" t="inlineStr"/>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>2026-09-03T16:23:14.932899+00:00</t>
+        </is>
+      </c>
       <c r="W245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X245" t="n">
         <v>0</v>
       </c>
       <c r="Y245" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z245" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA245" t="n">
         <v>0</v>
       </c>
-      <c r="AB245" t="inlineStr"/>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>["https://tlvmed.co.il/", "https://tlvmed.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://tlvmed.co.il/%D7%99%D7%A6%D7%99%D7%A8%D7%AA-%D7%A7%D7%A9%D7%A8/"]</t>
+          <t>["https://www.meitalk.co.il/%D7%99%D7%99%D7%A2%D7%95%D7%A5-%D7%A9%D7%99%D7%A0%D7%94/", "https://www.meitalk.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/", "https://www.midrag.co.il/Content/SectorPortal/168", "https://www.lishon.co.il/%D7%99%D7%95%D7%A2%D7%A6%D7%AA-%D7%A9%D7%99%D7%A0%D7%94", "https://www.orelwaserman.co.il/", "https://www.florelsmedia.com/", "https://www.goodnights.co.il/", "https://www.goodnights.co.il/contact", "https://www.goodnights.co.il/about2"]</t>
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE245" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>https://www.goodnights.co.il/</t>
+        </is>
+      </c>
+      <c r="AF245" t="n">
         <v>2</v>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>https://tlvmed.co.il/</t>
-        </is>
       </c>
       <c r="AG245" t="inlineStr"/>
       <c r="AH245" t="inlineStr"/>
@@ -34725,17 +34733,15 @@
       <c r="A246" t="n">
         <v>12</v>
       </c>
-      <c r="B246" t="n">
-        <v>2</v>
-      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr">
         <is>
-          <t>אופיר קדרון</t>
+          <t>תל אביב מדיקל סנטר</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>family_doctor</t>
+          <t>community_clinic</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -34745,23 +34751,23 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>org</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
+          <t>https://tlvmed.co.il/</t>
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
-          <t>moh</t>
+          <t>web</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>editor@karmel.co.il</t>
+          <t>evgene@tlvmed.co.il</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -34770,11 +34776,11 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F</t>
+          <t>https://tlvmed.co.il/</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -34784,12 +34790,12 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>ניתן ליצור איתנו קשר ע"י מילוי ושליחת הטופס מטה או בקשר ישיר באמצעות: יצרת קשר טלפוני: 04-8396187, 054-5823934, 053-5823934 דוא"ל: editor@karmel.co.il</t>
+          <t>אשמח לפנייתך לדוא”ל האישי שלי evgene@tlvmed.co.il מנכ”ל תל אביב מדיקל סנטר יבגני קצוביץ’</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>"אופיר קדרון"</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
@@ -34809,46 +34815,38 @@
         <v>0</v>
       </c>
       <c r="U246" t="inlineStr"/>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>2026-09-03T21:37:11.264655+00:00</t>
-        </is>
-      </c>
+      <c r="V246" t="inlineStr"/>
       <c r="W246" t="n">
+        <v>0</v>
+      </c>
+      <c r="X246" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB246" t="inlineStr"/>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>["https://tlvmed.co.il/", "https://tlvmed.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95/", "https://tlvmed.co.il/%D7%99%D7%A6%D7%99%D7%A8%D7%AA-%D7%A7%D7%A9%D7%A8/"]</t>
+        </is>
+      </c>
+      <c r="AD246" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>https://tlvmed.co.il/</t>
+        </is>
+      </c>
+      <c r="AF246" t="n">
         <v>2</v>
-      </c>
-      <c r="X246" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y246" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z246" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA246" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>["https://www.instagram.com/ophirher/", "https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F", "https://www.karmel.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95", "https://www.karmel.co.il/%d7%90%d7%95%d7%93%d7%95%d7%aa%d7%99%d7%a0%d7%95"]</t>
-        </is>
-      </c>
-      <c r="AD246" t="n">
-        <v>6908733</v>
-      </c>
-      <c r="AE246" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF246" t="inlineStr">
-        <is>
-          <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F</t>
-        </is>
       </c>
       <c r="AG246" t="inlineStr"/>
       <c r="AH246" t="inlineStr"/>
@@ -34874,15 +34872,17 @@
       <c r="A247" t="n">
         <v>12</v>
       </c>
-      <c r="B247" t="inlineStr"/>
+      <c r="B247" t="n">
+        <v>2</v>
+      </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>מרכז רפואי רמת אביב</t>
+          <t>אופיר קדרון</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>community_clinic</t>
+          <t>family_doctor</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -34892,36 +34892,36 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>person</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>https://www.mcra.co.il/</t>
+          <t>https://data.gov.il/he/datasets/ministry-health/database-of-doctors-licenses-moh/9c64c522-bbc2-48fe-96fb-3b2a8626f59e</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>moh</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>info@mcra.co.il</t>
+          <t>editor@karmel.co.il</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L247" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>https://www.mcra.co.il/</t>
+          <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -34931,17 +34931,17 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>מערך דימות: רח' ברודצקי 43, כניסה א', פסאז', קומה 1 רמת אביב, ת"א 6905234 טלפון: 03-6401234 פקס: 03-6401291 דוא"ל: [email protected]</t>
+          <t>ניתן ליצור איתנו קשר ע"י מילוי ושליחת הטופס מטה או בקשר ישיר באמצעות: יצרת קשר טלפוני: 04-8396187, 054-5823934, 053-5823934 דוא"ל: editor@karmel.co.il</t>
         </is>
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"אופיר קדרון"</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>direct_cloudflare</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
@@ -34956,38 +34956,46 @@
         <v>0</v>
       </c>
       <c r="U247" t="inlineStr"/>
-      <c r="V247" t="inlineStr"/>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>2026-09-03T21:37:11.264655+00:00</t>
+        </is>
+      </c>
       <c r="W247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X247" t="n">
         <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z247" t="n">
         <v>1</v>
       </c>
       <c r="AA247" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB247" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>["https://www.mcra.co.il/", "https://www.mcra.co.il/about-mcra", "https://www.mcra.co.il/contactus", "https://www.mcra.co.il/cdn-cgi/l/email-protection#cda4a3aba28da0aebface3aea2e3a4a1", "https://www.mcra.co.il/cdn-cgi/l/email-protection#51383f373e113c3223307f323e7f383d"]</t>
+          <t>["https://www.instagram.com/ophirher/", "https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F", "https://www.karmel.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA%D7%99%D7%A0%D7%95", "https://www.karmel.co.il/%d7%90%d7%95%d7%93%d7%95%d7%aa%d7%99%d7%a0%d7%95"]</t>
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE247" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>https://www.mcra.co.il/</t>
-        </is>
+        <v>20726199</v>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F</t>
+        </is>
+      </c>
+      <c r="AF247" t="n">
+        <v>5</v>
       </c>
       <c r="AG247" t="inlineStr"/>
       <c r="AH247" t="inlineStr"/>
@@ -35016,17 +35024,17 @@
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="inlineStr">
         <is>
-          <t>בית הספר אמנות הלידה קורס דולות</t>
+          <t>מרכז רפואי רמת אביב</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>doula_school</t>
+          <t>community_clinic</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -35036,31 +35044,31 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>https://www.leidaschool.co.il/</t>
+          <t>https://www.mcra.co.il/</t>
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>web</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>ruti@leida.co.il</t>
+          <t>info@mcra.co.il</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L248" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>https://www.leidaschool.co.il/contact</t>
+          <t>https://www.mcra.co.il/</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -35070,7 +35078,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>אי לטעימה איך לבחור קורס דולות שנכון לך קורס דולות בלמידה מרחוק תואר אקדמי השלמת תעודה קורס מדריכות הסוכריות שלנו כמה עולה קורס דולות קורס דולות אודות תקנון שכר לימוד בית More Use tab to navigate through the menu items. ruti@leida.co.il בית הספר אמנות הלידה מרכז ברודט, צייטלין 22 ת"א טלפון  052-8374237 טלפון 052-8374237 שלחי לנו מייל ruti@leida.co.il ביה"ס אמנות הלידה מרכז ברודט, צייטלין 22 ת"א © 2014 כל הזכויות שמורות לביה"ס אמנות הליד</t>
+          <t>מערך דימות: רח' ברודצקי 43, כניסה א', פסאז', קומה 1 רמת אביב, ת"א 6905234 טלפון: 03-6401234 פקס: 03-6401291 דוא"ל: [email protected]</t>
         </is>
       </c>
       <c r="P248" t="inlineStr">
@@ -35080,7 +35088,7 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>linked_text</t>
+          <t>direct_cloudflare</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -35114,19 +35122,19 @@
       <c r="AB248" t="inlineStr"/>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>["https://www.leidaschool.co.il/", "https://www.leidaschool.co.il/contact", "https://www.leidaschool.co.il/untitled-c1pn", "https://www.leidaschool.co.il/about-4"]</t>
+          <t>["https://www.mcra.co.il/", "https://www.mcra.co.il/about-mcra", "https://www.mcra.co.il/contactus", "https://www.mcra.co.il/cdn-cgi/l/email-protection#cda4a3aba28da0aebface3aea2e3a4a1", "https://www.mcra.co.il/cdn-cgi/l/email-protection#51383f373e113c3223307f323e7f383d"]</t>
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE248" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>https://www.mcra.co.il/</t>
+        </is>
+      </c>
+      <c r="AF248" t="n">
         <v>2</v>
-      </c>
-      <c r="AF248" t="inlineStr">
-        <is>
-          <t>https://www.leidaschool.co.il/</t>
-        </is>
       </c>
       <c r="AG248" t="inlineStr"/>
       <c r="AH248" t="inlineStr"/>
@@ -35155,12 +35163,12 @@
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr">
         <is>
-          <t>הפריה חוץ גופית(IVF)</t>
+          <t>בית הספר אמנות הלידה קורס דולות</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>facebook_group_admin</t>
+          <t>doula_school</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -35170,12 +35178,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>community</t>
+          <t>org</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>https://www.barzilaimc.org.il/</t>
+          <t>https://www.leidaschool.co.il/</t>
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
@@ -35186,12 +35194,12 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>judithko@tlvmc.gov.il</t>
+          <t>ruti@leida.co.il</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L249" t="n">
@@ -35199,7 +35207,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/</t>
+          <t>https://www.leidaschool.co.il/contact</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -35209,76 +35217,68 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t xml:space="preserve"> הפגישות הינן פרטניות, זוגיות וקיימת גם קבוצת תמיכה ליחידניות לעתיד. השירות ניתן ע"י גב' ג'ודית קדוש קובלסקי, פסיכולוגית קלינית ופסיכולוגית המכון באמצעות טפסי 17 מקופות החולים. ליצירת קשר יש לפנות ל 03-6925753, או למייל judithko@tlvmc.gov.il . למידע נוסף אודות השירות הפסיכולוגי &gt; טפסים למטופלות היחידה אגרת למטופלת במסגרת הפריה חוץ גופית טופס הסכמה לטיפול IVF: עברית / אנגלית / ערבית / רוסית טופס הסכמה לאבחון גנטי טרום השרשה טופס הסכמה לש</t>
+          <t>אי לטעימה איך לבחור קורס דולות שנכון לך קורס דולות בלמידה מרחוק תואר אקדמי השלמת תעודה קורס מדריכות הסוכריות שלנו כמה עולה קורס דולות קורס דולות אודות תקנון שכר לימוד בית More Use tab to navigate through the menu items. ruti@leida.co.il בית הספר אמנות הלידה מרכז ברודט, צייטלין 22 ת"א טלפון  052-8374237 טלפון 052-8374237 שלחי לנו מייל ruti@leida.co.il ביה"ס אמנות הלידה מרכז ברודט, צייטלין 22 ת"א © 2014 כל הזכויות שמורות לביה"ס אמנות הליד</t>
         </is>
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>"הפריה חוץ גופית ivf" קבוצת פייסבוק</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>[{"email": "judithko@tlvmc.gov.il", "confidence": 95, "source_url": "https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/", "identity_url": "https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/", "evidence": " הפגישות הינן פרטניות, זוגיות וקיימת גם קבוצת תמיכה ליחידניות לעתיד. השירות ניתן ע\"י גב' ג'ודית קדוש קובלסקי, פסיכולוגית קלינית ופסיכולוגית המכון באמצעות טפסי 17 מקופות החולים. ליצירת קשר יש לפנות ל 03-6925753, או למייל judithko@tlvmc.gov.il . למידע נוסף אודות השירות הפסיכולוגי &gt; טפסים למטופלות היחידה אגרת למטופלת במסגרת הפריה חוץ גופית טופס הסכמה לטיפול IVF: עברית / אנגלית / ערבית / רוסית טופס הסכמה לאבחון גנטי טרום השרשה טופס הסכמה לש", "matched_query": "\"הפריה חוץ גופית ivf\" קבוצת פייסבוק", "extraction_method": "direct_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S249" t="n">
+        <v>1</v>
+      </c>
+      <c r="T249" t="n">
+        <v>0</v>
+      </c>
+      <c r="U249" t="inlineStr"/>
+      <c r="V249" t="inlineStr"/>
+      <c r="W249" t="n">
+        <v>0</v>
+      </c>
+      <c r="X249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB249" t="inlineStr"/>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>["https://www.leidaschool.co.il/", "https://www.leidaschool.co.il/contact", "https://www.leidaschool.co.il/untitled-c1pn", "https://www.leidaschool.co.il/about-4"]</t>
+        </is>
+      </c>
+      <c r="AD249" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>https://www.leidaschool.co.il/</t>
+        </is>
+      </c>
+      <c r="AF249" t="n">
         <v>2</v>
-      </c>
-      <c r="T249" t="n">
-        <v>0</v>
-      </c>
-      <c r="U249" t="inlineStr"/>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>2026-09-03T16:44:32.770725+00:00</t>
-        </is>
-      </c>
-      <c r="W249" t="n">
-        <v>2</v>
-      </c>
-      <c r="X249" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y249" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z249" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA249" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>["https://www.barzilaimc.org.il/", "https://www.gov.il/he/pages/in-vitro-fertilisation", "https://www.elishahospital.com/הפרייה-חוץ-גופית/", "https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/"]</t>
-        </is>
-      </c>
-      <c r="AD249" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE249" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/</t>
-        </is>
       </c>
       <c r="AG249" t="inlineStr"/>
       <c r="AH249" t="inlineStr"/>
       <c r="AI249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ249" t="b">
         <v>1</v>
@@ -35302,7 +35302,7 @@
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr">
         <is>
-          <t>ליגת לה לצ'ה</t>
+          <t>הפריה חוץ גופית(IVF)</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>https://www.lllisrael.org.il/</t>
+          <t>https://www.barzilaimc.org.il/</t>
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
@@ -35333,7 +35333,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>igudyhanaka@gmail.com</t>
+          <t>judithko@tlvmc.gov.il</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -35346,7 +35346,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>https://ialp.org.il/lllisrael/</t>
+          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -35356,12 +35356,12 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>ריכות מוסמכות של ליגת לה לצ’ה ישראל עונות בקו התמיכה בהתנדבות בטלפון: 1599-525-821 אתר אינטרנט - ניתן למצוא בו מאמרים רבים, סרטונים והקלטות בנושאים השונים הקשורים בהנקה: https://www.lllisrael.org.il/ צרי קשר 058-6400164 igudyhanaka@gmail.com עמוד האיגוד בפייסבוק © 2017 האיגוד הישראלי למקצועות ההנקה. All Rights Reserved.</t>
+          <t xml:space="preserve"> הפגישות הינן פרטניות, זוגיות וקיימת גם קבוצת תמיכה ליחידניות לעתיד. השירות ניתן ע"י גב' ג'ודית קדוש קובלסקי, פסיכולוגית קלינית ופסיכולוגית המכון באמצעות טפסי 17 מקופות החולים. ליצירת קשר יש לפנות ל 03-6925753, או למייל judithko@tlvmc.gov.il . למידע נוסף אודות השירות הפסיכולוגי &gt; טפסים למטופלות היחידה אגרת למטופלת במסגרת הפריה חוץ גופית טופס הסכמה לטיפול IVF: עברית / אנגלית / ערבית / רוסית טופס הסכמה לאבחון גנטי טרום השרשה טופס הסכמה לש</t>
         </is>
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>"ליגת לה לצ" קבוצת פייסבוק</t>
+          <t>"הפריה חוץ גופית ivf" קבוצת פייסבוק</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
@@ -35371,11 +35371,11 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "judithko@tlvmc.gov.il", "confidence": 95, "source_url": "https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/", "identity_url": "https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/", "evidence": " הפגישות הינן פרטניות, זוגיות וקיימת גם קבוצת תמיכה ליחידניות לעתיד. השירות ניתן ע\"י גב' ג'ודית קדוש קובלסקי, פסיכולוגית קלינית ופסיכולוגית המכון באמצעות טפסי 17 מקופות החולים. ליצירת קשר יש לפנות ל 03-6925753, או למייל judithko@tlvmc.gov.il . למידע נוסף אודות השירות הפסיכולוגי &gt; טפסים למטופלות היחידה אגרת למטופלת במסגרת הפריה חוץ גופית טופס הסכמה לטיפול IVF: עברית / אנגלית / ערבית / רוסית טופס הסכמה לאבחון גנטי טרום השרשה טופס הסכמה לש", "matched_query": "\"הפריה חוץ גופית ivf\" קבוצת פייסבוק", "extraction_method": "direct_text"}]</t>
         </is>
       </c>
       <c r="S250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T250" t="n">
         <v>0</v>
@@ -35383,7 +35383,7 @@
       <c r="U250" t="inlineStr"/>
       <c r="V250" t="inlineStr">
         <is>
-          <t>2026-09-03T17:23:47.503023+00:00</t>
+          <t>2026-09-03T16:44:32.770725+00:00</t>
         </is>
       </c>
       <c r="W250" t="n">
@@ -35393,13 +35393,13 @@
         <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z250" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA250" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB250" t="inlineStr">
         <is>
@@ -35408,24 +35408,24 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>["https://www.lllisrael.org.il/", "https://www.lllisrael.org.il/about-us", "https://www.lllisrael.org.il/team-2", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgroups%2Flllisrael2015%2F", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FLaLecheIsrael%2F", "https://ialp.org.il/lllisrael/", "https://ialp.org.il/lllisrael/#contact"]</t>
+          <t>["https://www.barzilaimc.org.il/", "https://www.gov.il/he/pages/in-vitro-fertilisation", "https://www.elishahospital.com/הפרייה-חוץ-גופית/", "https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/"]</t>
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE250" t="n">
-        <v>229</v>
-      </c>
-      <c r="AF250" t="inlineStr">
-        <is>
-          <t>https://ialp.org.il/lllisrael/</t>
-        </is>
+        <v>23914845</v>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/</t>
+        </is>
+      </c>
+      <c r="AF250" t="n">
+        <v>5</v>
       </c>
       <c r="AG250" t="inlineStr"/>
       <c r="AH250" t="inlineStr"/>
       <c r="AI250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ250" t="b">
         <v>1</v>
@@ -35446,17 +35446,15 @@
       <c r="A251" t="n">
         <v>12</v>
       </c>
-      <c r="B251" t="n">
-        <v>0</v>
-      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="inlineStr">
         <is>
-          <t>הריון</t>
+          <t>ליגת לה לצ'ה</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>parenting_site</t>
+          <t>facebook_group_admin</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -35466,36 +35464,36 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>org</t>
+          <t>community</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>https://www.yoledet.co.il/pregnancy/</t>
+          <t>https://www.lllisrael.org.il/</t>
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>eran1201@eran.org.il</t>
+          <t>igudyhanaka@gmail.com</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>PERSONAL_PROFESSIONAL</t>
+          <t>BUSINESS_OR_COMMUNITY</t>
         </is>
       </c>
       <c r="L251" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/</t>
+          <t>https://ialp.org.il/lllisrael/</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -35505,50 +35503,50 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>טלפון: 076-8844400 דואר: ת"ד 7137 נתניה 4217002 דוא"ל: eran1201@eran.org.il מוקד תרומות: 1-700-70-1201</t>
+          <t>ריכות מוסמכות של ליגת לה לצ’ה ישראל עונות בקו התמיכה בהתנדבות בטלפון: 1599-525-821 אתר אינטרנט - ניתן למצוא בו מאמרים רבים, סרטונים והקלטות בנושאים השונים הקשורים בהנקה: https://www.lllisrael.org.il/ צרי קשר 058-6400164 igudyhanaka@gmail.com עמוד האיגוד בפייסבוק © 2017 האיגוד הישראלי למקצועות ההנקה. All Rights Reserved.</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>"הריון" הורות</t>
+          <t>"ליגת לה לצ" קבוצת פייסבוק</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>direct_text</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>[{"email": "eran1201@eran.org.il", "confidence": 88, "source_url": "https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/", "identity_url": "https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/", "evidence": "טלפון: 076-8844400 דואר: ת\"ד 7137 נתניה 4217002 דוא\"ל: eran1201@eran.org.il מוקד תרומות: 1-700-70-1201", "matched_query": "\"הריון\" הורות", "extraction_method": "direct_mailto"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U251" t="inlineStr"/>
       <c r="V251" t="inlineStr">
         <is>
-          <t>2026-09-04T09:06:54.363066+00:00</t>
+          <t>2026-09-03T17:23:47.503023+00:00</t>
         </is>
       </c>
       <c r="W251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z251" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB251" t="inlineStr">
         <is>
@@ -35557,24 +35555,24 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>["https://www.yoledet.co.il/pregnancy/", "https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/", "https://www.eran.org.il/eran-for-the-community/arabic-helpline/", "https://www.eran.org.il/about-us/", "https://www.eran.org.il/about-us/staff/", "https://www.eran.org.il/about-us/donors/", "https://www.eran.org.il/about-us/october-7th/", "https://www.gov.il/he/departments/topics/pregnancy_and_birth/govil-landing-page", "https://www.israelibaby.co.il/", "https://www.israelibaby.co.il/about", "https://www.israelibaby.co.il/contact"]</t>
+          <t>["https://www.lllisrael.org.il/", "https://www.lllisrael.org.il/about-us", "https://www.lllisrael.org.il/team-2", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fgroups%2Flllisrael2015%2F", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FLaLecheIsrael%2F", "https://ialp.org.il/lllisrael/", "https://ialp.org.il/lllisrael/#contact"]</t>
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>7978176</v>
-      </c>
-      <c r="AE251" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/</t>
-        </is>
+        <v>23914845</v>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>https://ialp.org.il/lllisrael/</t>
+        </is>
+      </c>
+      <c r="AF251" t="n">
+        <v>229</v>
       </c>
       <c r="AG251" t="inlineStr"/>
       <c r="AH251" t="inlineStr"/>
       <c r="AI251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ251" t="b">
         <v>1</v>
@@ -35595,10 +35593,12 @@
       <c r="A252" t="n">
         <v>12</v>
       </c>
-      <c r="B252" t="inlineStr"/>
+      <c r="B252" t="n">
+        <v>0</v>
+      </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>באלעולם</t>
+          <t>הריון</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -35618,23 +35618,23 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>https://balaolam.co.il/</t>
+          <t>https://www.yoledet.co.il/pregnancy/</t>
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
-          <t>previous</t>
+          <t>web</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>info@balaolam.co.il</t>
+          <t>eran1201@eran.org.il</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>CLINIC_OR_ORGANIZATION</t>
+          <t>PERSONAL_PROFESSIONAL</t>
         </is>
       </c>
       <c r="L252" t="n">
@@ -35642,7 +35642,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>https://balaolam.co.il/</t>
+          <t>https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -35652,68 +35652,76 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>[email protected]</t>
+          <t>טלפון: 076-8844400 דואר: ת"ד 7137 נתניה 4217002 דוא"ל: eran1201@eran.org.il מוקד תרומות: 1-700-70-1201</t>
         </is>
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>seed_source</t>
+          <t>"הריון" הורות</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>direct_cloudflare</t>
+          <t>direct_mailto</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{"email": "eran1201@eran.org.il", "confidence": 88, "source_url": "https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/", "identity_url": "https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/", "evidence": "טלפון: 076-8844400 דואר: ת\"ד 7137 נתניה 4217002 דוא\"ל: eran1201@eran.org.il מוקד תרומות: 1-700-70-1201", "matched_query": "\"הריון\" הורות", "extraction_method": "direct_mailto"}]</t>
         </is>
       </c>
       <c r="S252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U252" t="inlineStr"/>
-      <c r="V252" t="inlineStr"/>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>2026-09-04T09:06:54.363066+00:00</t>
+        </is>
+      </c>
       <c r="W252" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y252" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA252" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB252" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>["https://balaolam.co.il/", "https://divinesites.co.il/", "https://balaolam.co.il/about/", "https://balaolam.co.il/contact/", "https://balaolam.co.il/cdn-cgi/l/email-protection#99d0f7fff6d9dbf8f5f8f6f5f8f4b7faf6b7f0f5"]</t>
+          <t>["https://www.yoledet.co.il/pregnancy/", "https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/", "https://www.eran.org.il/eran-for-the-community/arabic-helpline/", "https://www.eran.org.il/about-us/", "https://www.eran.org.il/about-us/staff/", "https://www.eran.org.il/about-us/donors/", "https://www.eran.org.il/about-us/october-7th/", "https://www.gov.il/he/departments/topics/pregnancy_and_birth/govil-landing-page", "https://www.israelibaby.co.il/", "https://www.israelibaby.co.il/about", "https://www.israelibaby.co.il/contact"]</t>
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>6377292</v>
-      </c>
-      <c r="AE252" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF252" t="inlineStr">
-        <is>
-          <t>https://balaolam.co.il/</t>
-        </is>
+        <v>23934528</v>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/</t>
+        </is>
+      </c>
+      <c r="AF252" t="n">
+        <v>4</v>
       </c>
       <c r="AG252" t="inlineStr"/>
       <c r="AH252" t="inlineStr"/>
       <c r="AI252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ252" t="b">
         <v>1</v>
@@ -35737,12 +35745,12 @@
       <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr">
         <is>
-          <t>מעקב הריון שבועי</t>
+          <t>באלעולם</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>women_health_creator</t>
+          <t>parenting_site</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -35752,28 +35760,28 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>creator</t>
+          <t>org</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>https://www.babylis.co.il/weekly-pregnancy-tracking-guide/</t>
+          <t>https://balaolam.co.il/</t>
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>previous</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>info@babyhub.co.il</t>
+          <t>info@balaolam.co.il</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>BUSINESS_OR_COMMUNITY</t>
+          <t>CLINIC_OR_ORGANIZATION</t>
         </is>
       </c>
       <c r="L253" t="n">
@@ -35781,7 +35789,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>https://babyhub.co.il/tools/pregnancy-tracker</t>
+          <t>https://balaolam.co.il/</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -35789,85 +35797,224 @@
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="O253" t="inlineStr"/>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>[email protected]</t>
+        </is>
+      </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>"מעקב הריון שבועי" מייל</t>
+          <t>seed_source</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>direct_mailto</t>
+          <t>direct_cloudflare</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>[{"email": "info@babyhub.co.il", "confidence": 88, "source_url": "https://babyhub.co.il/tools/pregnancy-tracker", "identity_url": "https://babyhub.co.il/tools/pregnancy-tracker", "evidence": "", "matched_query": "\"מעקב הריון שבועי\" מייל", "extraction_method": "direct_mailto"}, {"email": "info@medcalc.co.il", "confidence": 88, "source_url": "https://medcalc.co.il/about/", "identity_url": "https://medcalc.co.il/pregnancy-birth/pregnancy-weeks/pregnancy-tracking/", "evidence": "ומד מאחורי MedCalc? האתר מופעל על ידי צוות MedCalc ,\n        המתמחה בפיתוח כלים ומחשבונים איכותיים לציבור הישראלי. יצירת קשר מצאתם טעות במחשבון? יש לכם הצעה לשיפור? רוצים להציע מחשבון חדש?\n        נשמח לשמוע מכם בדוא\"ל: info@medcalc.co.il Med Calc מחשבונים רפואיים מדויקים ומבוססי מקורות מוכרים.\n          כלי עזר נגישים לבריאות יומיומית. מחשבונים פופולריים מחשבון הריון מחשבון ביוץ מחשבון תאריך לידה מחשבון בטא מחשבון בן או בת מחשבון דמי ל", "matched_query": "\"מעקב הריון שבועי\" מייל", "extraction_method": "linked_text"}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="S253" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T253" t="n">
         <v>0</v>
       </c>
       <c r="U253" t="inlineStr"/>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>2026-09-03T18:02:25.953887+00:00</t>
-        </is>
-      </c>
+      <c r="V253" t="inlineStr"/>
       <c r="W253" t="n">
+        <v>0</v>
+      </c>
+      <c r="X253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB253" t="inlineStr"/>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>["https://balaolam.co.il/", "https://divinesites.co.il/", "https://balaolam.co.il/about/", "https://balaolam.co.il/contact/", "https://balaolam.co.il/cdn-cgi/l/email-protection#99d0f7fff6d9dbf8f5f8f6f5f8f4b7faf6b7f0f5"]</t>
+        </is>
+      </c>
+      <c r="AD253" t="n">
+        <v>19131876</v>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>https://balaolam.co.il/</t>
+        </is>
+      </c>
+      <c r="AF253" t="n">
         <v>2</v>
-      </c>
-      <c r="X253" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y253" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z253" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA253" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>ddgs:bing</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>["https://www.babylis.co.il/weekly-pregnancy-tracking-guide/", "https://babyhub.co.il/tools/pregnancy-tracker", "https://babyhub.co.il/about", "https://babyhub.co.il/contact", "https://medcalc.co.il/pregnancy-birth/pregnancy-weeks/pregnancy-tracking/", "https://medcalc.co.il/about/", "https://medcalc.co.il/contact/", "https://www.yoledet.co.il/calculators-and-tools/", "https://www.babylis.co.il/staff/", "https://www.babylis.co.il/contact-us/", "https://www.babylis.co.il/contact-us/#tour", "https://www.babylis.co.il/about-us/"]</t>
-        </is>
-      </c>
-      <c r="AD253" t="n">
-        <v>7971615</v>
-      </c>
-      <c r="AE253" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>https://babyhub.co.il/tools/pregnancy-tracker</t>
-        </is>
       </c>
       <c r="AG253" t="inlineStr"/>
       <c r="AH253" t="inlineStr"/>
       <c r="AI253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ253" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK253" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>ORGANIZATION_OR_SHARED_ROUTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>12</v>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>מעקב הריון שבועי</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>women_health_creator</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>creator</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://www.babylis.co.il/weekly-pregnancy-tracking-guide/</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>info@babyhub.co.il</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>BUSINESS_OR_COMMUNITY</t>
+        </is>
+      </c>
+      <c r="L254" t="n">
+        <v>88</v>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>https://babyhub.co.il/tools/pregnancy-tracker</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>"מעקב הריון שבועי" מייל</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>direct_mailto</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>[{"email": "info@babyhub.co.il", "confidence": 88, "source_url": "https://babyhub.co.il/tools/pregnancy-tracker", "identity_url": "https://babyhub.co.il/tools/pregnancy-tracker", "evidence": "", "matched_query": "\"מעקב הריון שבועי\" מייל", "extraction_method": "direct_mailto"}, {"email": "info@medcalc.co.il", "confidence": 88, "source_url": "https://medcalc.co.il/about/", "identity_url": "https://medcalc.co.il/pregnancy-birth/pregnancy-weeks/pregnancy-tracking/", "evidence": "ומד מאחורי MedCalc? האתר מופעל על ידי צוות MedCalc ,\n        המתמחה בפיתוח כלים ומחשבונים איכותיים לציבור הישראלי. יצירת קשר מצאתם טעות במחשבון? יש לכם הצעה לשיפור? רוצים להציע מחשבון חדש?\n        נשמח לשמוע מכם בדוא\"ל: info@medcalc.co.il Med Calc מחשבונים רפואיים מדויקים ומבוססי מקורות מוכרים.\n          כלי עזר נגישים לבריאות יומיומית. מחשבונים פופולריים מחשבון הריון מחשבון ביוץ מחשבון תאריך לידה מחשבון בטא מחשבון בן או בת מחשבון דמי ל", "matched_query": "\"מעקב הריון שבועי\" מייל", "extraction_method": "linked_text"}]</t>
+        </is>
+      </c>
+      <c r="S254" t="n">
+        <v>3</v>
+      </c>
+      <c r="T254" t="n">
+        <v>0</v>
+      </c>
+      <c r="U254" t="inlineStr"/>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>2026-09-03T18:02:25.953887+00:00</t>
+        </is>
+      </c>
+      <c r="W254" t="n">
         <v>2</v>
       </c>
-      <c r="AJ253" t="b">
-        <v>1</v>
-      </c>
-      <c r="AK253" t="b">
-        <v>1</v>
-      </c>
-      <c r="AL253" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM253" t="inlineStr">
+      <c r="X254" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>ddgs:bing</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>["https://www.babylis.co.il/weekly-pregnancy-tracking-guide/", "https://babyhub.co.il/tools/pregnancy-tracker", "https://babyhub.co.il/about", "https://babyhub.co.il/contact", "https://medcalc.co.il/pregnancy-birth/pregnancy-weeks/pregnancy-tracking/", "https://medcalc.co.il/about/", "https://medcalc.co.il/contact/", "https://www.yoledet.co.il/calculators-and-tools/", "https://www.babylis.co.il/staff/", "https://www.babylis.co.il/contact-us/", "https://www.babylis.co.il/contact-us/#tour", "https://www.babylis.co.il/about-us/"]</t>
+        </is>
+      </c>
+      <c r="AD254" t="n">
+        <v>23914845</v>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>https://babyhub.co.il/tools/pregnancy-tracker</t>
+        </is>
+      </c>
+      <c r="AF254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG254" t="inlineStr"/>
+      <c r="AH254" t="inlineStr"/>
+      <c r="AI254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ254" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK254" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM254" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>shared_target_count</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>shared_target_count</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -742,15 +742,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>https://www.rofenashim.co.il/faq/faq-fertility/</t>
         </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>6</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
@@ -891,15 +891,15 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>28756863</v>
-      </c>
-      <c r="AE3" t="inlineStr">
+        <v>86270589</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>https://www.e-piryon.com/</t>
         </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -1040,15 +1040,15 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>19669878</v>
-      </c>
-      <c r="AE4" t="inlineStr">
+        <v>59009634</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>https://www.profyinoncohen.com/</t>
         </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>2</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
@@ -1187,15 +1187,15 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE5" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>https://www.leidaraka.co.il/</t>
         </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>3</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1334,15 +1334,15 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE6" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>https://kerenzohar.com/%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>2</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1483,15 +1483,15 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE7" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>https://hmc.co.il/doctor/%D7%A4%D7%A8%D7%95%D7%A4-%D7%93%D7%95%D7%93-%D7%9C%D7%91-%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>19</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -1630,15 +1630,15 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE8" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>https://www.israelidoula.co.il/courses-1/embryo-%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>7</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1779,15 +1779,15 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>19190925</v>
-      </c>
-      <c r="AE9" t="inlineStr">
+        <v>57572775</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>https://www.dr-paz.co.il/</t>
         </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>2</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
@@ -1926,15 +1926,15 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE10" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>https://www.israelivf.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>17</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
@@ -2065,15 +2065,15 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE11" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>https://www.shvil-haleida.co.il/%D7%A8%D7%99%D7%A9%D7%95%D7%9D-%D7%9C%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%9C%D7%99%D7%93%D7%94/</t>
         </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
@@ -2214,15 +2214,15 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE12" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94-9/</t>
         </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
@@ -2353,15 +2353,15 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE13" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>https://harechem.com/</t>
         </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>3</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
@@ -2496,15 +2496,15 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE14" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF14" t="inlineStr">
         <is>
           <t>http://www.amotatchen.org/</t>
         </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>3</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
@@ -2645,15 +2645,15 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE15" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
@@ -2794,15 +2794,15 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE16" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>https://dinadoula.com/%D7%93%D7%95%D7%9C%D7%94/</t>
         </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>2</v>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2943,15 +2943,15 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE17" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>https://www.surmom.co.il/%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/%D7%A4%D7%A8%D7%95%D7%A4-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F-%D7%90%D7%93%D7%A8%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
@@ -3092,15 +3092,15 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE18" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>https://hfhosp.org/he/%D7%A6%D7%95%D7%95%D7%AA-%D7%94%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/%D7%93%D7%A8-%D7%A0%D7%99%D7%A7%D7%95%D7%9C%D7%90-%D7%A4%D7%A8%D7%97</t>
         </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>5</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
@@ -3231,15 +3231,15 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE19" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>https://midwives.org.il/%D7%9C%D7%99%D7%95%D7%95%D7%99-%D7%9E%D7%A7%D7%A6%D7%95%D7%A2%D7%99-%D7%96%D7%94-%D7%9E%D7%99%D7%99%D7%9C%D7%93%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>9</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
@@ -3378,15 +3378,15 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE20" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>8</v>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
@@ -3525,15 +3525,15 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE21" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF21" t="n">
-        <v>11</v>
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
@@ -3664,15 +3664,15 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE22" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>https://www.israelibaby.co.il/where-to-get-birth</t>
         </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>11</v>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
@@ -3803,15 +3803,15 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE23" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF23" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/</t>
         </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>2</v>
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
@@ -3946,15 +3946,15 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE24" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF24" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/fertility-research/</t>
         </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>3</v>
       </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
@@ -4085,15 +4085,15 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE25" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>https://barakivf.com/</t>
         </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>3</v>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
@@ -4228,15 +4228,15 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE26" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>https://demayo.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94/</t>
         </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>3</v>
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
@@ -4375,15 +4375,15 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE27" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>https://bri.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/</t>
         </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>17</v>
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
@@ -4514,15 +4514,15 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE28" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>4</v>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
@@ -4653,15 +4653,15 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE29" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF29" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>4</v>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
@@ -4792,15 +4792,15 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE30" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF30" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>4</v>
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
@@ -4939,15 +4939,15 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE31" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF31" t="inlineStr">
         <is>
           <t>https://www.laniado.org.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%9C%D7%99%D7%93%D7%94-%D7%98%D7%91%D7%A2%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>2</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
@@ -5078,15 +5078,15 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE32" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=A6B809CAFEA13537A84D783709CF5EBB&amp;RequestId=00000000-0000-0000-0001-000000000325</t>
         </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>2</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
@@ -5217,15 +5217,15 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE33" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF33" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>8</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
@@ -5356,15 +5356,15 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE34" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF34" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%91%D7%9C%D7%94-%D7%A2%D7%91%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF34" t="n">
-        <v>2</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
@@ -5495,15 +5495,15 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE35" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF35" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%92%D7%9E%D7%95/</t>
         </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>2</v>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
@@ -5634,15 +5634,15 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE36" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%99%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>2</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -5773,15 +5773,15 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE37" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF37" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%9F-%D7%90%D7%A8%D7%99-%D7%A6%D7%90%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>2</v>
       </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
@@ -5912,15 +5912,15 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE38" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF38" t="n">
-        <v>2</v>
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
@@ -6051,15 +6051,15 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE39" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF39" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%95%D7%A8%D7%A0%D7%92%D7%95%D7%9C%D7%93-%D7%97%D7%99%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>2</v>
       </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
@@ -6190,15 +6190,15 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE40" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF40" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%9C%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF40" t="n">
-        <v>2</v>
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
@@ -6329,15 +6329,15 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE41" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%9C%D7%A0%D7%93%D7%94-%D7%A1%D7%95%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
@@ -6468,15 +6468,15 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE42" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF42" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%95%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%9C%D7%90/</t>
         </is>
-      </c>
-      <c r="AF42" t="n">
-        <v>2</v>
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
@@ -6607,15 +6607,15 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE43" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF43" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%9C%D7%99%D7%94-%D7%94%D7%95%D7%9C%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>2</v>
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
@@ -6746,15 +6746,15 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE44" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF44" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%9E%D7%99%D7%AA-%D7%93%D7%A0%D7%A1%D7%99%D7%95%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF44" t="n">
-        <v>2</v>
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
@@ -6885,15 +6885,15 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE45" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF45" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%9E%D7%95%D7%96%D7%A1-%D7%90%D7%9C%D7%91%D7%96/</t>
         </is>
-      </c>
-      <c r="AF45" t="n">
-        <v>2</v>
       </c>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
@@ -7024,15 +7024,15 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE46" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%A8%D7%95%D7%9F-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF46" t="n">
-        <v>2</v>
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
@@ -7163,15 +7163,15 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE47" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%99%D7%A2%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF47" t="n">
-        <v>2</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
@@ -7302,15 +7302,15 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE48" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF48" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%98%D7%94-%D7%A0%D7%95%D7%91%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF48" t="n">
-        <v>2</v>
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
@@ -7441,15 +7441,15 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE49" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%94-%D7%A4%D7%95%D7%9C%D7%99%D7%90%D7%A7%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF49" t="n">
-        <v>2</v>
       </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
@@ -7580,15 +7580,15 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE50" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF50" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%94-%D7%93%D7%9E%D7%A0%D7%98%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF50" t="n">
-        <v>2</v>
       </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
@@ -7719,15 +7719,15 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE51" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF51" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
         </is>
-      </c>
-      <c r="AF51" t="n">
-        <v>2</v>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
@@ -7858,15 +7858,15 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE52" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%96%D7%92%D7%95%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF52" t="n">
-        <v>2</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
@@ -7997,15 +7997,15 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE53" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF53" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8-%D7%95%D7%99%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF53" t="n">
-        <v>2</v>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
@@ -8136,15 +8136,15 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE54" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF54" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF54" t="n">
-        <v>2</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
@@ -8275,15 +8275,15 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE55" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF55" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%9C%D7%91%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF55" t="n">
-        <v>2</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
@@ -8414,15 +8414,15 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE56" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF56" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%90%D7%9D-%D7%9E%D7%95%D7%A8%D7%94-%D7%97%D7%9E%D7%90%D7%A8%D7%A9%D7%99/</t>
         </is>
-      </c>
-      <c r="AF56" t="n">
-        <v>2</v>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
@@ -8553,15 +8553,15 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE57" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF57" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%91%D7%A8%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF57" t="n">
-        <v>2</v>
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
@@ -8692,15 +8692,15 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE58" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF58" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%A6%D7%99%D7%91%D7%99%D7%90%D7%A7-%D7%93%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF58" t="n">
-        <v>2</v>
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
@@ -8831,15 +8831,15 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE59" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF59" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%9E%D7%95%D7%91%D7%A9%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF59" t="n">
-        <v>2</v>
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
@@ -8970,15 +8970,15 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE60" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF60" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%94-%D7%90%D7%96%D7%91%D7%A0%D7%93/</t>
         </is>
-      </c>
-      <c r="AF60" t="n">
-        <v>2</v>
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
@@ -9109,15 +9109,15 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE61" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%AA%D7%A9%D7%91%D7%A2-%D7%92%D7%A8%D7%A0%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF61" t="n">
-        <v>2</v>
       </c>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
@@ -9248,15 +9248,15 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE62" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%99%D7%9C%D7%99-%D7%90%D7%95%D7%91%D7%A8%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF62" t="n">
-        <v>2</v>
       </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
@@ -9387,15 +9387,15 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE63" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%9C%D7%99%D7%99%D7%A8-%D7%90%D7%9C%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF63" t="n">
-        <v>2</v>
       </c>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
@@ -9526,15 +9526,15 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE64" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF64" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%94%D7%A9%D7%9B%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF64" t="n">
-        <v>2</v>
       </c>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
@@ -9665,15 +9665,15 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE65" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF65" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%98%D7%9C-%D7%91%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF65" t="n">
-        <v>2</v>
       </c>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
@@ -9804,15 +9804,15 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE66" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF66" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%97%D7%95%D7%98%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF66" t="n">
-        <v>2</v>
       </c>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
@@ -9943,15 +9943,15 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE67" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF67" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%9C%D7%90%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF67" t="n">
-        <v>2</v>
       </c>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
@@ -10082,15 +10082,15 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE68" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF68" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%92%D7%93%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF68" t="n">
-        <v>2</v>
       </c>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
@@ -10221,15 +10221,15 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE69" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF69" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%9E%D7%A8%D7%90%D7%93/</t>
         </is>
-      </c>
-      <c r="AF69" t="n">
-        <v>2</v>
       </c>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
@@ -10360,15 +10360,15 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE70" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF70" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%A9%D7%95%D7%95%D7%A8%D7%A6%D7%91%D7%A8%D7%92/</t>
         </is>
-      </c>
-      <c r="AF70" t="n">
-        <v>2</v>
       </c>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
@@ -10499,15 +10499,15 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE71" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF71" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%99%D7%90%D7%9F-%D7%A9%D7%A4%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF71" t="n">
-        <v>2</v>
       </c>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
@@ -10638,15 +10638,15 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE72" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF72" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8-%D7%91%D7%99%D7%98%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF72" t="n">
-        <v>2</v>
       </c>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
@@ -10777,15 +10777,15 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE73" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF73" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8%D7%99%D7%9F-%D7%90%D7%9C%D7%A2%D7%93/</t>
         </is>
-      </c>
-      <c r="AF73" t="n">
-        <v>2</v>
       </c>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
@@ -10916,15 +10916,15 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE74" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF74" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/332/</t>
         </is>
-      </c>
-      <c r="AF74" t="n">
-        <v>2</v>
       </c>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
@@ -11055,15 +11055,15 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE75" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF75" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%91%D7%9F-%D7%A9%D7%A5-%D7%A4%D7%95%D7%A8%D7%A9%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF75" t="n">
-        <v>2</v>
       </c>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
@@ -11194,15 +11194,15 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE76" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF76" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%95%D7%95%D7%A8%D7%99%D7%99%D7%98/</t>
         </is>
-      </c>
-      <c r="AF76" t="n">
-        <v>2</v>
       </c>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
@@ -11333,15 +11333,15 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE77" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF77" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%99%D7%90%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF77" t="n">
-        <v>2</v>
       </c>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
@@ -11472,15 +11472,15 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE78" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF78" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%91%D7%92%D7%9C%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF78" t="n">
-        <v>2</v>
       </c>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
@@ -11611,15 +11611,15 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE79" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF79" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF79" t="n">
-        <v>2</v>
       </c>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
@@ -11750,15 +11750,15 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE80" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF80" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%9C%D7%A0%D7%94-%D7%A9%D7%99%D7%9C%D7%A7%D7%95/</t>
         </is>
-      </c>
-      <c r="AF80" t="n">
-        <v>2</v>
       </c>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
@@ -11889,15 +11889,15 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE81" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF81" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A2%D7%A0%D7%94-%D7%92%D7%95%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF81" t="n">
-        <v>2</v>
       </c>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
@@ -12028,15 +12028,15 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE82" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF82" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%91%D7%A8%D7%A7%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF82" t="n">
-        <v>2</v>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -12167,15 +12167,15 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE83" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF83" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A8%D7%96-%D7%92%D7%99%D7%9C%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF83" t="n">
-        <v>2</v>
       </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
@@ -12306,15 +12306,15 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE84" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF84" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A9%D7%91%D7%A2-%D7%92%D7%95%D7%A8%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF84" t="n">
-        <v>2</v>
       </c>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
@@ -12445,15 +12445,15 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE85" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF85" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%9C%D7%95%D7%A0%D7%92%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF85" t="n">
-        <v>2</v>
       </c>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
@@ -12584,15 +12584,15 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE86" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF86" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%9F-%D7%A9%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF86" t="n">
-        <v>2</v>
       </c>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
@@ -12723,15 +12723,15 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE87" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF87" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%94-%D7%90%D7%99%D7%AA%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF87" t="n">
-        <v>2</v>
       </c>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
@@ -12862,15 +12862,15 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE88" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF88" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%95%D7%A0%D7%94-%D7%95%D7%92%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF88" t="n">
-        <v>2</v>
       </c>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
@@ -13001,15 +13001,15 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE89" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF89" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%90%D7%9C%D7%94-%D7%99%D7%A8%D7%A7%D7%95%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF89" t="n">
-        <v>2</v>
       </c>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
@@ -13140,15 +13140,15 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE90" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF90" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A1%D7%AA%D7%A8-%D7%A4%D7%9C%D7%99%D7%99%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF90" t="n">
-        <v>2</v>
       </c>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
@@ -13279,15 +13279,15 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE91" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF91" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%AA%D7%99-%D7%A1%D7%93%D7%9F-%D7%A7%D7%A0%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF91" t="n">
-        <v>2</v>
       </c>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
@@ -13418,15 +13418,15 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE92" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF92" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A4%D7%A8%D7%A0%D7%A1%D7%99%D7%A1-%D7%A4%D7%A8%D7%9F-%D7%91%D7%A8%D7%95%D7%A0%D7%A9%D7%98%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF92" t="n">
-        <v>2</v>
       </c>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
@@ -13557,15 +13557,15 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE93" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF93" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%91%D7%99-%D7%A4%D7%99%D7%A9%D7%9E%D7%9F-%D7%A4%D7%95%D7%A1%D7%91%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF93" t="n">
-        <v>2</v>
       </c>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
@@ -13696,15 +13696,15 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE94" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF94" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99-%D7%A7%D7%9E%D7%97%D7%99/</t>
         </is>
-      </c>
-      <c r="AF94" t="n">
-        <v>2</v>
       </c>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
@@ -13835,15 +13835,15 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE95" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF95" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%90%D7%A4%D7%9C%D7%91%D7%95%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF95" t="n">
-        <v>2</v>
       </c>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
@@ -13974,15 +13974,15 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE96" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF96" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%AA-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF96" t="n">
-        <v>2</v>
       </c>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
@@ -14113,15 +14113,15 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE97" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF97" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF97" t="n">
-        <v>2</v>
       </c>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
@@ -14252,15 +14252,15 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE98" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF98" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%90%D7%99%D7%94-%D7%92%D7%95%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF98" t="n">
-        <v>2</v>
       </c>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
@@ -14391,15 +14391,15 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE99" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF99" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%94-%D7%90%D7%95%D7%A0%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF99" t="n">
-        <v>2</v>
       </c>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
@@ -14530,15 +14530,15 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE100" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF100" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%99%D7%94-%D7%93%D7%95%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF100" t="n">
-        <v>2</v>
       </c>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
@@ -14669,15 +14669,15 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE101" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF101" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%AA%D7%99%D7%AA-%D7%A9%D7%A4%D7%A8%D7%9C%D7%99%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF101" t="n">
-        <v>2</v>
       </c>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
@@ -14808,15 +14808,15 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE102" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF102" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%9E%D7%95%D7%99%D7%90%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF102" t="n">
-        <v>2</v>
       </c>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
@@ -14947,15 +14947,15 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE103" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF103" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%98%D7%A1%D7%94/</t>
         </is>
-      </c>
-      <c r="AF103" t="n">
-        <v>2</v>
       </c>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
@@ -15086,15 +15086,15 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE104" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF104" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1%D7%94-%D7%A4%D7%97%D7%9C%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF104" t="n">
-        <v>2</v>
       </c>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
@@ -15225,15 +15225,15 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE105" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF105" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%A0%D7%94-%D7%94%D7%A8%D7%95%D7%A9/</t>
         </is>
-      </c>
-      <c r="AF105" t="n">
-        <v>2</v>
       </c>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
@@ -15364,15 +15364,15 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE106" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF106" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%99-%D7%94%D7%A8%D7%A4%D7%96/</t>
         </is>
-      </c>
-      <c r="AF106" t="n">
-        <v>2</v>
       </c>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
@@ -15503,15 +15503,15 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE107" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF107" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9E%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF107" t="n">
-        <v>2</v>
       </c>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
@@ -15642,15 +15642,15 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE108" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF108" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%99%D7%9C%D7%94-%D7%9C%D7%91-%D7%A8%D7%9F-%D7%97%D7%95%D7%AA%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF108" t="n">
-        <v>2</v>
       </c>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
@@ -15781,15 +15781,15 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE109" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF109" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%95%D7%93%D7%99%D7%94-%D7%90%D7%99%D7%AA%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF109" t="n">
-        <v>2</v>
       </c>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
@@ -15920,15 +15920,15 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE110" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF110" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%9C-%D7%91%D7%95%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF110" t="n">
-        <v>2</v>
       </c>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
@@ -16059,15 +16059,15 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE111" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF111" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%A8-%D7%A7%D7%A8%D7%9F-%D7%A8%D7%98%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF111" t="n">
-        <v>2</v>
       </c>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
@@ -16198,15 +16198,15 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE112" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF112" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%B3%D7%95%D7%9C%D7%99-%D7%90%D7%A1%D7%AA%D7%99-%D7%A9%D7%9E%D7%A2%D7%95%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF112" t="n">
-        <v>2</v>
       </c>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
@@ -16337,15 +16337,15 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE113" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF113" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%95%D7%9C%D7%99-%D7%A7%D7%A8%D7%A7%D7%95/</t>
         </is>
-      </c>
-      <c r="AF113" t="n">
-        <v>2</v>
       </c>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
@@ -16476,15 +16476,15 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE114" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF114" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%92%D7%9C%D7%99%D7%9F-%D7%A1%D7%9C%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF114" t="n">
-        <v>2</v>
       </c>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
@@ -16615,15 +16615,15 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE115" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF115" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%92%D7%99%D7%91%D7%A8-%D7%A9%D7%92%D7%91/</t>
         </is>
-      </c>
-      <c r="AF115" t="n">
-        <v>2</v>
       </c>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
@@ -16754,15 +16754,15 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE116" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF116" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%A1%D7%9C%D7%91%D7%95%D7%93%D7%A0%D7%99%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF116" t="n">
-        <v>2</v>
       </c>
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
@@ -16893,15 +16893,15 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE117" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF117" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%95%D7%99%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF117" t="n">
-        <v>2</v>
       </c>
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
@@ -17032,15 +17032,15 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE118" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF118" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%90%D7%A0%D7%94-%D7%91%D7%A8%D7%99%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF118" t="n">
-        <v>2</v>
       </c>
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
@@ -17171,15 +17171,15 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE119" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF119" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99-%D7%90%D7%95%D7%A8-%D7%9C%D7%91%D7%A0%D7%96%D7%95%D7%9F-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF119" t="n">
-        <v>2</v>
       </c>
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
@@ -17310,15 +17310,15 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE120" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF120" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%A8%D7%95%D7%9F-%D7%A4%D7%99%D7%90%D7%97%D7%95%D7%98%D7%94-%D7%A1%D7%90%D7%9C%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF120" t="n">
-        <v>2</v>
       </c>
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
@@ -17449,15 +17449,15 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE121" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF121" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
         </is>
-      </c>
-      <c r="AF121" t="n">
-        <v>2</v>
       </c>
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
@@ -17588,15 +17588,15 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE122" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF122" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%94-%D7%A7%D7%95%D7%92%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF122" t="n">
-        <v>2</v>
       </c>
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
@@ -17727,15 +17727,15 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE123" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF123" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%90%D7%9F-%D7%A9%D7%95%D7%97%D7%98/</t>
         </is>
-      </c>
-      <c r="AF123" t="n">
-        <v>2</v>
       </c>
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
@@ -17866,15 +17866,15 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE124" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF124" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99-%D7%A2%D7%95%D7%96%D7%99%D7%90%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF124" t="n">
-        <v>2</v>
       </c>
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
@@ -18005,15 +18005,15 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE125" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF125" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF125" t="n">
-        <v>2</v>
       </c>
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
@@ -18144,15 +18144,15 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE126" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF126" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8-%D7%9C%D7%95%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF126" t="n">
-        <v>2</v>
       </c>
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
@@ -18283,15 +18283,15 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE127" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF127" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF127" t="n">
-        <v>2</v>
       </c>
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
@@ -18422,15 +18422,15 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE128" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF128" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%98%D7%95%D7%91-%D7%97%D7%99%D7%94-%D7%90%D7%99%D7%98%D7%94/</t>
         </is>
-      </c>
-      <c r="AF128" t="n">
-        <v>2</v>
       </c>
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
@@ -18561,15 +18561,15 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE129" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF129" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A2%D7%99%D7%99%D7%9F-%D7%90%D7%9C%D7%9E%D7%92%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF129" t="n">
-        <v>2</v>
       </c>
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
@@ -18700,15 +18700,15 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE130" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF130" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99-%D7%93%D7%A8%D7%95%D7%A7%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF130" t="n">
-        <v>2</v>
       </c>
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
@@ -18839,15 +18839,15 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE131" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF131" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%94-%D7%92%D7%95%D7%A8%D7%92%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF131" t="n">
-        <v>2</v>
       </c>
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
@@ -18978,15 +18978,15 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE132" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF132" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%99-%D7%90%D7%95%D7%A4%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF132" t="n">
-        <v>2</v>
       </c>
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
@@ -19117,15 +19117,15 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE133" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF133" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%A9%D7%97%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF133" t="n">
-        <v>2</v>
       </c>
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
@@ -19256,15 +19256,15 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE134" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF134" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%95%D7%A4%D7%A8%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF134" t="n">
-        <v>2</v>
       </c>
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
@@ -19395,15 +19395,15 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE135" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF135" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99-%D7%9C%D7%91-%D7%A7%D7%9C%D7%99%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF135" t="n">
-        <v>2</v>
       </c>
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
@@ -19534,15 +19534,15 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE136" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF136" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99%D7%94-%D7%90%D7%A0%D7%95%D7%9A/</t>
         </is>
-      </c>
-      <c r="AF136" t="n">
-        <v>2</v>
       </c>
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
@@ -19673,15 +19673,15 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE137" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF137" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%94-%D7%90%D7%99%D7%96%D7%A7%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF137" t="n">
-        <v>2</v>
       </c>
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
@@ -19812,15 +19812,15 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE138" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF138" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%91-%D7%A0%D7%97%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF138" t="n">
-        <v>2</v>
       </c>
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
@@ -19951,15 +19951,15 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE139" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF139" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99%D7%A1%D7%94-%D7%91%D7%A8-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF139" t="n">
-        <v>2</v>
       </c>
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
@@ -20090,15 +20090,15 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE140" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF140" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%9B%D7%9C-%D7%96%D7%99%D7%9C%D7%91%D7%A8%D7%9E%D7%9F-%D7%A8%D7%99%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF140" t="n">
-        <v>2</v>
       </c>
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
@@ -20229,15 +20229,15 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE141" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF141" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A7%D7%94-%D7%9B%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF141" t="n">
-        <v>2</v>
       </c>
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
@@ -20368,15 +20368,15 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE142" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF142" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99-%D7%A4%D7%91%D7%96%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF142" t="n">
-        <v>2</v>
       </c>
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
@@ -20507,15 +20507,15 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE143" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF143" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99%D7%AA-%D7%A8%D7%95%D7%96%D7%A0%D7%91%D7%90%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF143" t="n">
-        <v>2</v>
       </c>
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
@@ -20646,15 +20646,15 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE144" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF144" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8-%D7%92%D7%95%D7%9C%D7%93%D7%A0%D7%92%D7%95%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF144" t="n">
-        <v>2</v>
       </c>
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
@@ -20785,15 +20785,15 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE145" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF145" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%9E%D7%9C%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF145" t="n">
-        <v>2</v>
       </c>
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
@@ -20924,15 +20924,15 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE146" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF146" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%9C%D7%92%D7%99/</t>
         </is>
-      </c>
-      <c r="AF146" t="n">
-        <v>2</v>
       </c>
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
@@ -21063,15 +21063,15 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE147" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF147" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%95%D7%95%D7%9C%D7%A4%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF147" t="n">
-        <v>2</v>
       </c>
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr"/>
@@ -21202,15 +21202,15 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE148" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF148" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A2%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF148" t="n">
-        <v>2</v>
       </c>
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr"/>
@@ -21341,15 +21341,15 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE149" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF149" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A8%D7%99%D7%91%D7%9C%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF149" t="n">
-        <v>2</v>
       </c>
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
@@ -21480,15 +21480,15 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE150" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF150" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A8%D7%A7%D7%99%D7%A1-%D7%A0%D7%A4%D7%AA%D7%9C%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF150" t="n">
-        <v>2</v>
       </c>
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
@@ -21619,15 +21619,15 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE151" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF151" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%A7%D7%A9%D7%99%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF151" t="n">
-        <v>2</v>
       </c>
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
@@ -21758,15 +21758,15 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE152" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF152" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%91%D7%9F-%D7%A9%D7%A9%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF152" t="n">
-        <v>2</v>
       </c>
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
@@ -21897,15 +21897,15 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE153" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF153" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%A2-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF153" t="n">
-        <v>2</v>
       </c>
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
@@ -22036,15 +22036,15 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE154" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF154" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A0%D7%94-%D7%91%D7%AA%D7%90%D7%A9%D7%95%D7%99%D7%9C%D7%99/</t>
         </is>
-      </c>
-      <c r="AF154" t="n">
-        <v>2</v>
       </c>
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
@@ -22175,15 +22175,15 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE155" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF155" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A8%D7%99%D7%AA-%D7%90%D7%95%D7%9C%D7%99%D7%91%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF155" t="n">
-        <v>2</v>
       </c>
       <c r="AG155" t="inlineStr"/>
       <c r="AH155" t="inlineStr"/>
@@ -22314,15 +22314,15 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE156" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF156" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A6%D7%9F-%D7%99%D7%9E%D7%99%D7%A0%D7%99-%D7%97%D7%99/</t>
         </is>
-      </c>
-      <c r="AF156" t="n">
-        <v>2</v>
       </c>
       <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr"/>
@@ -22453,15 +22453,15 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE157" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF157" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%91%D7%99-%D7%99%D7%A2%D7%A7%D7%91/</t>
         </is>
-      </c>
-      <c r="AF157" t="n">
-        <v>2</v>
       </c>
       <c r="AG157" t="inlineStr"/>
       <c r="AH157" t="inlineStr"/>
@@ -22592,15 +22592,15 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE158" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF158" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A2%D7%94-%D7%95%D7%99%D7%A6%D7%9E%D7%9F-%D7%A8%D7%91%D7%99%D7%91%D7%95/</t>
         </is>
-      </c>
-      <c r="AF158" t="n">
-        <v>2</v>
       </c>
       <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr"/>
@@ -22731,15 +22731,15 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE159" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF159" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%91%D7%95%D7%A8%D7%92-%D7%A1%D7%92%D7%9F-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF159" t="n">
-        <v>2</v>
       </c>
       <c r="AG159" t="inlineStr"/>
       <c r="AH159" t="inlineStr"/>
@@ -22870,15 +22870,15 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE160" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF160" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%92%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF160" t="n">
-        <v>2</v>
       </c>
       <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr"/>
@@ -23009,15 +23009,15 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE161" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF161" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%A4%D7%99%D7%9C%D7%95%D7%A1%D7%95%D7%A3/</t>
         </is>
-      </c>
-      <c r="AF161" t="n">
-        <v>2</v>
       </c>
       <c r="AG161" t="inlineStr"/>
       <c r="AH161" t="inlineStr"/>
@@ -23148,15 +23148,15 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE162" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF162" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%98%D7%95%D7%A9%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF162" t="n">
-        <v>2</v>
       </c>
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr"/>
@@ -23287,15 +23287,15 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE163" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF163" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A8%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF163" t="n">
-        <v>2</v>
       </c>
       <c r="AG163" t="inlineStr"/>
       <c r="AH163" t="inlineStr"/>
@@ -23426,15 +23426,15 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE164" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF164" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%9C%D7%9B%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF164" t="n">
-        <v>2</v>
       </c>
       <c r="AG164" t="inlineStr"/>
       <c r="AH164" t="inlineStr"/>
@@ -23565,15 +23565,15 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE165" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF165" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%9C%D7%92%D7%94-%D7%95%D7%A7%D7%A1%D7%9C%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF165" t="n">
-        <v>2</v>
       </c>
       <c r="AG165" t="inlineStr"/>
       <c r="AH165" t="inlineStr"/>
@@ -23704,15 +23704,15 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE166" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF166" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%97%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF166" t="n">
-        <v>2</v>
       </c>
       <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr"/>
@@ -23843,15 +23843,15 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE167" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF167" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%9E%D7%9C%D7%99-%D7%94%D7%A0%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF167" t="n">
-        <v>2</v>
       </c>
       <c r="AG167" t="inlineStr"/>
       <c r="AH167" t="inlineStr"/>
@@ -23982,15 +23982,15 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE168" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF168" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%93%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF168" t="n">
-        <v>2</v>
       </c>
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr"/>
@@ -24121,15 +24121,15 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE169" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF169" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%99%D7%A2%D7%A7%D7%91%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF169" t="n">
-        <v>2</v>
       </c>
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr"/>
@@ -24260,15 +24260,15 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE170" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF170" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7-%D7%A0%D7%A7%D7%A9/</t>
         </is>
-      </c>
-      <c r="AF170" t="n">
-        <v>2</v>
       </c>
       <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr"/>
@@ -24399,15 +24399,15 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE171" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF171" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF171" t="n">
-        <v>2</v>
       </c>
       <c r="AG171" t="inlineStr"/>
       <c r="AH171" t="inlineStr"/>
@@ -24538,15 +24538,15 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE172" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF172" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A4%D7%96-%D7%A8%D7%99%D7%99%D7%9B%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF172" t="n">
-        <v>2</v>
       </c>
       <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr"/>
@@ -24677,15 +24677,15 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE173" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF173" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%97%D7%9C-%D7%A4%D7%99%D7%A8%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF173" t="n">
-        <v>2</v>
       </c>
       <c r="AG173" t="inlineStr"/>
       <c r="AH173" t="inlineStr"/>
@@ -24816,15 +24816,15 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE174" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF174" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%AA-%D7%9C%D7%91%D7%99%D7%90/</t>
         </is>
-      </c>
-      <c r="AF174" t="n">
-        <v>2</v>
       </c>
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr"/>
@@ -24955,15 +24955,15 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE175" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF175" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%96-%D7%A2%D7%96%D7%A8%D7%90/</t>
         </is>
-      </c>
-      <c r="AF175" t="n">
-        <v>2</v>
       </c>
       <c r="AG175" t="inlineStr"/>
       <c r="AH175" t="inlineStr"/>
@@ -25094,15 +25094,15 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE176" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF176" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A0%D7%A0%D7%94-%D7%95%D7%99%D7%A8%D7%A6%D7%91%D7%95%D7%A8%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF176" t="n">
-        <v>2</v>
       </c>
       <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
@@ -25233,15 +25233,15 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE177" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF177" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A2%D7%95%D7%AA-%D7%94%D7%A8%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF177" t="n">
-        <v>2</v>
       </c>
       <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
@@ -25372,15 +25372,15 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE178" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF178" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%98%D7%9C-%D7%90%D7%99%D7%A9-%D7%A9%D7%9C%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF178" t="n">
-        <v>2</v>
       </c>
       <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
@@ -25511,15 +25511,15 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE179" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF179" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A7%D7%99-%D7%96%D7%9C%D7%9B%D7%94/</t>
         </is>
-      </c>
-      <c r="AF179" t="n">
-        <v>2</v>
       </c>
       <c r="AG179" t="inlineStr"/>
       <c r="AH179" t="inlineStr"/>
@@ -25650,15 +25650,15 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE180" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF180" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A0%D7%AA-%D7%90%D7%9C%D7%93%D7%A8-%D7%92%D7%A8%D7%A9%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF180" t="n">
-        <v>2</v>
       </c>
       <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr"/>
@@ -25789,15 +25789,15 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE181" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF181" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%97%D7%99-%D7%A8%D7%95%D7%96%D7%A0%D7%98%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF181" t="n">
-        <v>2</v>
       </c>
       <c r="AG181" t="inlineStr"/>
       <c r="AH181" t="inlineStr"/>
@@ -25928,15 +25928,15 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE182" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF182" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99-%D7%A4%D7%A8%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF182" t="n">
-        <v>2</v>
       </c>
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr"/>
@@ -26067,15 +26067,15 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE183" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF183" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF183" t="n">
-        <v>2</v>
       </c>
       <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr"/>
@@ -26206,15 +26206,15 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE184" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF184" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%9D-%D7%90%D7%9C%D7%9E%D7%95%D7%92/</t>
         </is>
-      </c>
-      <c r="AF184" t="n">
-        <v>2</v>
       </c>
       <c r="AG184" t="inlineStr"/>
       <c r="AH184" t="inlineStr"/>
@@ -26345,15 +26345,15 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE185" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF185" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%99-%D7%98%D7%9C-%D7%9E%D7%99%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF185" t="n">
-        <v>2</v>
       </c>
       <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr"/>
@@ -26484,15 +26484,15 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE186" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF186" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%92%D7%99%D7%AA-%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF186" t="n">
-        <v>2</v>
       </c>
       <c r="AG186" t="inlineStr"/>
       <c r="AH186" t="inlineStr"/>
@@ -26623,15 +26623,15 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE187" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF187" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF187" t="n">
-        <v>2</v>
       </c>
       <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr"/>
@@ -26762,15 +26762,15 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE188" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF188" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%A9%D7%97%D7%A8-%D7%91%D7%9F-%D7%93%D7%95%D7%93/</t>
         </is>
-      </c>
-      <c r="AF188" t="n">
-        <v>2</v>
       </c>
       <c r="AG188" t="inlineStr"/>
       <c r="AH188" t="inlineStr"/>
@@ -26901,15 +26901,15 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE189" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF189" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A7%D7%93-%D7%9C%D7%99%D7%91%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF189" t="n">
-        <v>2</v>
       </c>
       <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr"/>
@@ -27040,15 +27040,15 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE190" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF190" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%A0%D7%94-%D7%A0%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF190" t="n">
-        <v>2</v>
       </c>
       <c r="AG190" t="inlineStr"/>
       <c r="AH190" t="inlineStr"/>
@@ -27179,15 +27179,15 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE191" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF191" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%9F-%D7%96%D7%9C%D7%9E%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF191" t="n">
-        <v>2</v>
       </c>
       <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr"/>
@@ -27318,15 +27318,15 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE192" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF192" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%99-%D7%97%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF192" t="n">
-        <v>2</v>
       </c>
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
@@ -27457,15 +27457,15 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE193" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF193" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%94-%D7%A1%D7%95%D7%A1%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF193" t="n">
-        <v>2</v>
       </c>
       <c r="AG193" t="inlineStr"/>
       <c r="AH193" t="inlineStr"/>
@@ -27596,15 +27596,15 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE194" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF194" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%90%D7%9C-%D7%A8%D7%91%D7%A7%D7%94-%D7%99%D7%A4%D7%94/</t>
         </is>
-      </c>
-      <c r="AF194" t="n">
-        <v>2</v>
       </c>
       <c r="AG194" t="inlineStr"/>
       <c r="AH194" t="inlineStr"/>
@@ -27735,15 +27735,15 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE195" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF195" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A4%D7%99%D7%99%D7%98%D7%9C%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF195" t="n">
-        <v>2</v>
       </c>
       <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr"/>
@@ -27874,15 +27874,15 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE196" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF196" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%95%D7%98%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF196" t="n">
-        <v>2</v>
       </c>
       <c r="AG196" t="inlineStr"/>
       <c r="AH196" t="inlineStr"/>
@@ -28013,15 +28013,15 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE197" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF197" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%A8%D7%95%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF197" t="n">
-        <v>2</v>
       </c>
       <c r="AG197" t="inlineStr"/>
       <c r="AH197" t="inlineStr"/>
@@ -28152,15 +28152,15 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE198" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF198" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%98-%D7%93%D7%A8%D7%A1%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF198" t="n">
-        <v>2</v>
       </c>
       <c r="AG198" t="inlineStr"/>
       <c r="AH198" t="inlineStr"/>
@@ -28291,15 +28291,15 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE199" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF199" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%92%D7%95%D7%96%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF199" t="n">
-        <v>2</v>
       </c>
       <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr"/>
@@ -28430,15 +28430,15 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE200" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF200" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%94%D7%95%D7%9C%D7%A6%D7%91%D7%A8%D7%92-%D7%97%D7%99%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF200" t="n">
-        <v>2</v>
       </c>
       <c r="AG200" t="inlineStr"/>
       <c r="AH200" t="inlineStr"/>
@@ -28569,15 +28569,15 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE201" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF201" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A0%D7%93%D7%9C%D7%91%D7%90%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF201" t="n">
-        <v>2</v>
       </c>
       <c r="AG201" t="inlineStr"/>
       <c r="AH201" t="inlineStr"/>
@@ -28708,15 +28708,15 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE202" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF202" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A8%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF202" t="n">
-        <v>2</v>
       </c>
       <c r="AG202" t="inlineStr"/>
       <c r="AH202" t="inlineStr"/>
@@ -28847,15 +28847,15 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE203" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF203" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%9E%D7%9C%D7%9B%D7%94-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF203" t="n">
-        <v>2</v>
       </c>
       <c r="AG203" t="inlineStr"/>
       <c r="AH203" t="inlineStr"/>
@@ -28986,15 +28986,15 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE204" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF204" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%94%D7%9C%D7%A4%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF204" t="n">
-        <v>2</v>
       </c>
       <c r="AG204" t="inlineStr"/>
       <c r="AH204" t="inlineStr"/>
@@ -29125,15 +29125,15 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE205" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF205" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%95%D7%A4%D7%99%D7%94-%D7%9E%D7%9C%D7%97%D7%96%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF205" t="n">
-        <v>2</v>
       </c>
       <c r="AG205" t="inlineStr"/>
       <c r="AH205" t="inlineStr"/>
@@ -29264,15 +29264,15 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE206" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF206" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%9E%D7%99%D7%98%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF206" t="n">
-        <v>2</v>
       </c>
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr"/>
@@ -29403,15 +29403,15 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE207" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF207" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%A6%D7%A0%D7%A6%D7%99%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF207" t="n">
-        <v>2</v>
       </c>
       <c r="AG207" t="inlineStr"/>
       <c r="AH207" t="inlineStr"/>
@@ -29542,15 +29542,15 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE208" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF208" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%91%D7%99%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF208" t="n">
-        <v>2</v>
       </c>
       <c r="AG208" t="inlineStr"/>
       <c r="AH208" t="inlineStr"/>
@@ -29681,15 +29681,15 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE209" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF209" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF209" t="n">
-        <v>2</v>
       </c>
       <c r="AG209" t="inlineStr"/>
       <c r="AH209" t="inlineStr"/>
@@ -29820,15 +29820,15 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE210" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF210" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99%D7%94-%D7%91%D7%9F-%D7%9E%D7%96%D7%99%D7%90/</t>
         </is>
-      </c>
-      <c r="AF210" t="n">
-        <v>2</v>
       </c>
       <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr"/>
@@ -29959,15 +29959,15 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE211" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF211" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%A8-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF211" t="n">
-        <v>3</v>
       </c>
       <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr"/>
@@ -30098,15 +30098,15 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE212" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF212" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A9%D7%92%D7%91-%D7%90%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF212" t="n">
-        <v>2</v>
       </c>
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr"/>
@@ -30237,15 +30237,15 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE213" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF213" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A2%D7%95%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF213" t="n">
-        <v>2</v>
       </c>
       <c r="AG213" t="inlineStr"/>
       <c r="AH213" t="inlineStr"/>
@@ -30376,15 +30376,15 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE214" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF214" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99%D7%9E%D7%94-%D7%A9%D7%A2%D7%A9%D7%95%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF214" t="n">
-        <v>2</v>
       </c>
       <c r="AG214" t="inlineStr"/>
       <c r="AH214" t="inlineStr"/>
@@ -30515,15 +30515,15 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE215" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF215" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%A7%D7%95%D7%94-%D7%A6%D7%93%D7%95%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF215" t="n">
-        <v>3</v>
       </c>
       <c r="AG215" t="inlineStr"/>
       <c r="AH215" t="inlineStr"/>
@@ -30654,15 +30654,15 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE216" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF216" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%95%D7%91%D7%94-%D7%99%D7%95%D7%A1%D7%A4%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF216" t="n">
-        <v>2</v>
       </c>
       <c r="AG216" t="inlineStr"/>
       <c r="AH216" t="inlineStr"/>
@@ -30793,15 +30793,15 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE217" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF217" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A6%D7%91%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF217" t="n">
-        <v>2</v>
       </c>
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" t="inlineStr"/>
@@ -30932,15 +30932,15 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE218" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF218" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A6%D7%95%D7%A4%D7%99%D7%AA-%D7%93%D7%99%D7%A1%D7%98%D7%9C%D7%9E%D7%9F-%D7%9E%D7%99%D7%A8%D7%A7%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF218" t="n">
-        <v>2</v>
       </c>
       <c r="AG218" t="inlineStr"/>
       <c r="AH218" t="inlineStr"/>
@@ -31071,15 +31071,15 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE219" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF219" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%9C%D7%A8%D7%99-%D7%9E%D7%99%D7%9C%D7%94%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF219" t="n">
-        <v>2</v>
       </c>
       <c r="AG219" t="inlineStr"/>
       <c r="AH219" t="inlineStr"/>
@@ -31210,15 +31210,15 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE220" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF220" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%91%D7%90%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF220" t="n">
-        <v>2</v>
       </c>
       <c r="AG220" t="inlineStr"/>
       <c r="AH220" t="inlineStr"/>
@@ -31349,15 +31349,15 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE221" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF221" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%99%D7%A7%D7%98%D7%95%D7%A8%D7%99%D7%94-%D7%A7%D7%9E%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF221" t="n">
-        <v>2</v>
       </c>
       <c r="AG221" t="inlineStr"/>
       <c r="AH221" t="inlineStr"/>
@@ -31488,15 +31488,15 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE222" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF222" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A4%D7%90%D7%90-%D7%90%D7%91%D7%95-%D7%90%D7%A1%D7%9E%D7%90%D7%A2%D7%99%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF222" t="n">
-        <v>2</v>
       </c>
       <c r="AG222" t="inlineStr"/>
       <c r="AH222" t="inlineStr"/>
@@ -31627,15 +31627,15 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE223" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF223" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%91%D7%90%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF223" t="n">
-        <v>2</v>
       </c>
       <c r="AG223" t="inlineStr"/>
       <c r="AH223" t="inlineStr"/>
@@ -31766,15 +31766,15 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE224" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF224" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%93%D7%95%D7%91%D7%93%D7%91%D7%9F-%D7%92%D7%9C%D7%95%D7%96%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF224" t="n">
-        <v>2</v>
       </c>
       <c r="AG224" t="inlineStr"/>
       <c r="AH224" t="inlineStr"/>
@@ -31905,15 +31905,15 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE225" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF225" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%90%D7%98%D7%99%D7%90%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF225" t="n">
-        <v>2</v>
       </c>
       <c r="AG225" t="inlineStr"/>
       <c r="AH225" t="inlineStr"/>
@@ -32044,15 +32044,15 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE226" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF226" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%93%D7%95%D7%91%D7%A1%D7%98%D7%A8-%D7%93%D7%95%D7%93/</t>
         </is>
-      </c>
-      <c r="AF226" t="n">
-        <v>2</v>
       </c>
       <c r="AG226" t="inlineStr"/>
       <c r="AH226" t="inlineStr"/>
@@ -32183,15 +32183,15 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE227" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF227" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/291/</t>
         </is>
-      </c>
-      <c r="AF227" t="n">
-        <v>2</v>
       </c>
       <c r="AG227" t="inlineStr"/>
       <c r="AH227" t="inlineStr"/>
@@ -32322,15 +32322,15 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE228" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF228" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%96%D7%99%D7%AA-%D7%97%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF228" t="n">
-        <v>2</v>
       </c>
       <c r="AG228" t="inlineStr"/>
       <c r="AH228" t="inlineStr"/>
@@ -32461,15 +32461,15 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE229" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF229" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%A6%D7%A0%D7%9C%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF229" t="n">
-        <v>2</v>
       </c>
       <c r="AG229" t="inlineStr"/>
       <c r="AH229" t="inlineStr"/>
@@ -32600,15 +32600,15 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE230" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF230" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A4%D7%9C%D7%92/</t>
         </is>
-      </c>
-      <c r="AF230" t="n">
-        <v>2</v>
       </c>
       <c r="AG230" t="inlineStr"/>
       <c r="AH230" t="inlineStr"/>
@@ -32739,15 +32739,15 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE231" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF231" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF231" t="n">
-        <v>2</v>
       </c>
       <c r="AG231" t="inlineStr"/>
       <c r="AH231" t="inlineStr"/>
@@ -32878,15 +32878,15 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE232" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF232" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%90%D7%A0%D7%94-%D7%A4%D7%99%D7%A9%D7%91%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF232" t="n">
-        <v>2</v>
       </c>
       <c r="AG232" t="inlineStr"/>
       <c r="AH232" t="inlineStr"/>
@@ -33017,15 +33017,15 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE233" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF233" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%9E%D7%95%D7%A8%D7%9C%D7%99/</t>
         </is>
-      </c>
-      <c r="AF233" t="n">
-        <v>2</v>
       </c>
       <c r="AG233" t="inlineStr"/>
       <c r="AH233" t="inlineStr"/>
@@ -33156,15 +33156,15 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE234" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF234" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%A8%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF234" t="n">
-        <v>2</v>
       </c>
       <c r="AG234" t="inlineStr"/>
       <c r="AH234" t="inlineStr"/>
@@ -33295,15 +33295,15 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE235" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF235" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%99%D7%AA-%D7%9B%D7%A5-%D7%91%D7%A1%D7%98%D7%A7%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF235" t="n">
-        <v>2</v>
       </c>
       <c r="AG235" t="inlineStr"/>
       <c r="AH235" t="inlineStr"/>
@@ -33434,15 +33434,15 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE236" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF236" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A2%D7%9E%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF236" t="n">
-        <v>2</v>
       </c>
       <c r="AG236" t="inlineStr"/>
       <c r="AH236" t="inlineStr"/>
@@ -33573,15 +33573,15 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE237" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF237" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A8%D7%91%D7%99%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF237" t="n">
-        <v>2</v>
       </c>
       <c r="AG237" t="inlineStr"/>
       <c r="AH237" t="inlineStr"/>
@@ -33712,15 +33712,15 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE238" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF238" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%91%D7%9C-%D7%A7%D7%A1%D7%98%D7%99%D7%9F-%D7%9B%D7%94%D7%A0%D7%90/</t>
         </is>
-      </c>
-      <c r="AF238" t="n">
-        <v>2</v>
       </c>
       <c r="AG238" t="inlineStr"/>
       <c r="AH238" t="inlineStr"/>
@@ -33851,15 +33851,15 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE239" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF239" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF239" t="n">
-        <v>2</v>
       </c>
       <c r="AG239" t="inlineStr"/>
       <c r="AH239" t="inlineStr"/>
@@ -33996,15 +33996,15 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>23915088</v>
-      </c>
-      <c r="AE240" t="inlineStr">
+        <v>71745264</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF240" t="inlineStr">
         <is>
           <t>https://nefeshachat.co.il/</t>
         </is>
-      </c>
-      <c r="AF240" t="n">
-        <v>2</v>
       </c>
       <c r="AG240" t="inlineStr"/>
       <c r="AH240" t="inlineStr"/>
@@ -34135,15 +34135,15 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE241" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF241" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9B%D7%A4%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF241" t="n">
-        <v>2</v>
       </c>
       <c r="AG241" t="inlineStr"/>
       <c r="AH241" t="inlineStr"/>
@@ -34274,15 +34274,15 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE242" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF242" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A9%D7%9C-%D7%98%D7%95%D7%94%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF242" t="n">
-        <v>2</v>
       </c>
       <c r="AG242" t="inlineStr"/>
       <c r="AH242" t="inlineStr"/>
@@ -34413,15 +34413,15 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE243" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF243" t="inlineStr">
         <is>
           <t>https://tzuna-tova.co.il/</t>
         </is>
-      </c>
-      <c r="AF243" t="n">
-        <v>2</v>
       </c>
       <c r="AG243" t="inlineStr"/>
       <c r="AH243" t="inlineStr"/>
@@ -34552,15 +34552,15 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE244" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF244" t="inlineStr">
         <is>
           <t>https://www.shiri-sleep.co.il/</t>
         </is>
-      </c>
-      <c r="AF244" t="n">
-        <v>2</v>
       </c>
       <c r="AG244" t="inlineStr"/>
       <c r="AH244" t="inlineStr"/>
@@ -34699,15 +34699,15 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE245" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF245" t="inlineStr">
         <is>
           <t>https://www.goodnights.co.il/</t>
         </is>
-      </c>
-      <c r="AF245" t="n">
-        <v>2</v>
       </c>
       <c r="AG245" t="inlineStr"/>
       <c r="AH245" t="inlineStr"/>
@@ -34838,15 +34838,15 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE246" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF246" t="inlineStr">
         <is>
           <t>https://tlvmed.co.il/</t>
         </is>
-      </c>
-      <c r="AF246" t="n">
-        <v>2</v>
       </c>
       <c r="AG246" t="inlineStr"/>
       <c r="AH246" t="inlineStr"/>
@@ -34987,15 +34987,15 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>20726199</v>
-      </c>
-      <c r="AE247" t="inlineStr">
+        <v>62178597</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF247" t="inlineStr">
         <is>
           <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F</t>
         </is>
-      </c>
-      <c r="AF247" t="n">
-        <v>5</v>
       </c>
       <c r="AG247" t="inlineStr"/>
       <c r="AH247" t="inlineStr"/>
@@ -35126,15 +35126,15 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE248" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF248" t="inlineStr">
         <is>
           <t>https://www.mcra.co.il/</t>
         </is>
-      </c>
-      <c r="AF248" t="n">
-        <v>2</v>
       </c>
       <c r="AG248" t="inlineStr"/>
       <c r="AH248" t="inlineStr"/>
@@ -35265,15 +35265,15 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE249" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF249" t="inlineStr">
         <is>
           <t>https://www.leidaschool.co.il/</t>
         </is>
-      </c>
-      <c r="AF249" t="n">
-        <v>2</v>
       </c>
       <c r="AG249" t="inlineStr"/>
       <c r="AH249" t="inlineStr"/>
@@ -35412,15 +35412,15 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE250" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF250" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/</t>
         </is>
-      </c>
-      <c r="AF250" t="n">
-        <v>5</v>
       </c>
       <c r="AG250" t="inlineStr"/>
       <c r="AH250" t="inlineStr"/>
@@ -35559,15 +35559,15 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE251" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>229</v>
+      </c>
+      <c r="AF251" t="inlineStr">
         <is>
           <t>https://ialp.org.il/lllisrael/</t>
         </is>
-      </c>
-      <c r="AF251" t="n">
-        <v>229</v>
       </c>
       <c r="AG251" t="inlineStr"/>
       <c r="AH251" t="inlineStr"/>
@@ -35708,15 +35708,15 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>23934528</v>
-      </c>
-      <c r="AE252" t="inlineStr">
+        <v>71803584</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF252" t="inlineStr">
         <is>
           <t>https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/</t>
         </is>
-      </c>
-      <c r="AF252" t="n">
-        <v>4</v>
       </c>
       <c r="AG252" t="inlineStr"/>
       <c r="AH252" t="inlineStr"/>
@@ -35847,15 +35847,15 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>19131876</v>
-      </c>
-      <c r="AE253" t="inlineStr">
+        <v>57395628</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF253" t="inlineStr">
         <is>
           <t>https://balaolam.co.il/</t>
         </is>
-      </c>
-      <c r="AF253" t="n">
-        <v>2</v>
       </c>
       <c r="AG253" t="inlineStr"/>
       <c r="AH253" t="inlineStr"/>
@@ -35990,15 +35990,15 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>23914845</v>
-      </c>
-      <c r="AE254" t="inlineStr">
+        <v>71744535</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF254" t="inlineStr">
         <is>
           <t>https://babyhub.co.il/tools/pregnancy-tracker</t>
         </is>
-      </c>
-      <c r="AF254" t="n">
-        <v>3</v>
       </c>
       <c r="AG254" t="inlineStr"/>
       <c r="AH254" t="inlineStr"/>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>86270589</v>
+        <v>258811767</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>59009634</v>
+        <v>177028902</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE5" t="n">
         <v>3</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE7" t="n">
         <v>19</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>57572775</v>
+        <v>172718325</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE10" t="n">
         <v>17</v>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE27" t="n">
         <v>17</v>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -7997,7 +7997,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9387,7 +9387,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11055,7 +11055,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -11611,7 +11611,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12306,7 +12306,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -12584,7 +12584,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13001,7 +13001,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13140,7 +13140,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13418,7 +13418,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -13835,7 +13835,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -13974,7 +13974,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14252,7 +14252,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14391,7 +14391,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -14530,7 +14530,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -14669,7 +14669,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -14808,7 +14808,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15086,7 +15086,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15364,7 +15364,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16059,7 +16059,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16198,7 +16198,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -16615,7 +16615,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -16754,7 +16754,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17032,7 +17032,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17310,7 +17310,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -17449,7 +17449,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -17866,7 +17866,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18144,7 +18144,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18283,7 +18283,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -18422,7 +18422,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -18561,7 +18561,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -18839,7 +18839,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -19395,7 +19395,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -19673,7 +19673,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -19951,7 +19951,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20090,7 +20090,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20229,7 +20229,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -20368,7 +20368,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -20785,7 +20785,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -20924,7 +20924,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21063,7 +21063,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21202,7 +21202,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -21341,7 +21341,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -21619,7 +21619,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -21758,7 +21758,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -21897,7 +21897,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22175,7 +22175,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -22314,7 +22314,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -22453,7 +22453,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -22592,7 +22592,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -22731,7 +22731,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -22870,7 +22870,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23148,7 +23148,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -23287,7 +23287,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -23426,7 +23426,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -23565,7 +23565,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -23982,7 +23982,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24121,7 +24121,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -24260,7 +24260,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -24399,7 +24399,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -24538,7 +24538,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -24677,7 +24677,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -24816,7 +24816,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -24955,7 +24955,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25094,7 +25094,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -25233,7 +25233,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -25372,7 +25372,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -25511,7 +25511,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -25650,7 +25650,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -25789,7 +25789,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -25928,7 +25928,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -26206,7 +26206,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -26345,7 +26345,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -26623,7 +26623,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -26762,7 +26762,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -26901,7 +26901,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -27040,7 +27040,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -27179,7 +27179,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -27318,7 +27318,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -27457,7 +27457,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -27874,7 +27874,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -28013,7 +28013,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -28152,7 +28152,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -28291,7 +28291,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -28430,7 +28430,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -28569,7 +28569,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -28708,7 +28708,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -28847,7 +28847,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -28986,7 +28986,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -29125,7 +29125,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -29264,7 +29264,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -29403,7 +29403,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -29542,7 +29542,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -29681,7 +29681,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -29820,7 +29820,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -29959,7 +29959,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -30098,7 +30098,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -30237,7 +30237,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -30376,7 +30376,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -30515,7 +30515,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -30654,7 +30654,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -30793,7 +30793,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -30932,7 +30932,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -31071,7 +31071,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -31210,7 +31210,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -31349,7 +31349,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -31627,7 +31627,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -31766,7 +31766,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -31905,7 +31905,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -32044,7 +32044,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -32183,7 +32183,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -32322,7 +32322,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -32461,7 +32461,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -32600,7 +32600,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -32739,7 +32739,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -32878,7 +32878,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -33017,7 +33017,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -33156,7 +33156,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -33434,7 +33434,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -33573,7 +33573,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -33712,7 +33712,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -33851,7 +33851,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -33996,7 +33996,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>71745264</v>
+        <v>215235792</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -34135,7 +34135,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -34274,7 +34274,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -34413,7 +34413,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -34552,7 +34552,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -34699,7 +34699,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -34838,7 +34838,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -34987,7 +34987,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>62178597</v>
+        <v>186535791</v>
       </c>
       <c r="AE247" t="n">
         <v>5</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -35265,7 +35265,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE250" t="n">
         <v>5</v>
@@ -35559,7 +35559,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE251" t="n">
         <v>229</v>
@@ -35708,7 +35708,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>71803584</v>
+        <v>215410752</v>
       </c>
       <c r="AE252" t="n">
         <v>4</v>
@@ -35847,7 +35847,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>57395628</v>
+        <v>172186884</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -35990,7 +35990,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>71744535</v>
+        <v>215233605</v>
       </c>
       <c r="AE254" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>258811767</v>
+        <v>776435301</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>177028902</v>
+        <v>531086706</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE5" t="n">
         <v>3</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE7" t="n">
         <v>19</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>172718325</v>
+        <v>518154975</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE10" t="n">
         <v>17</v>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE27" t="n">
         <v>17</v>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -7997,7 +7997,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9387,7 +9387,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11055,7 +11055,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -11611,7 +11611,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12306,7 +12306,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -12584,7 +12584,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13001,7 +13001,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13140,7 +13140,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13418,7 +13418,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -13835,7 +13835,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -13974,7 +13974,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14252,7 +14252,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14391,7 +14391,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -14530,7 +14530,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -14669,7 +14669,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -14808,7 +14808,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15086,7 +15086,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15364,7 +15364,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16059,7 +16059,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16198,7 +16198,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -16615,7 +16615,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -16754,7 +16754,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17032,7 +17032,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17310,7 +17310,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -17449,7 +17449,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -17866,7 +17866,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18144,7 +18144,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18283,7 +18283,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -18422,7 +18422,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -18561,7 +18561,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -18839,7 +18839,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -19395,7 +19395,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -19673,7 +19673,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -19951,7 +19951,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20090,7 +20090,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20229,7 +20229,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -20368,7 +20368,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -20785,7 +20785,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -20924,7 +20924,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21063,7 +21063,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21202,7 +21202,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -21341,7 +21341,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -21619,7 +21619,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -21758,7 +21758,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -21897,7 +21897,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22175,7 +22175,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -22314,7 +22314,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -22453,7 +22453,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -22592,7 +22592,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -22731,7 +22731,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -22870,7 +22870,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23148,7 +23148,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -23287,7 +23287,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -23426,7 +23426,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -23565,7 +23565,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -23982,7 +23982,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24121,7 +24121,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -24260,7 +24260,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -24399,7 +24399,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -24538,7 +24538,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -24677,7 +24677,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -24816,7 +24816,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -24955,7 +24955,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25094,7 +25094,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -25233,7 +25233,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -25372,7 +25372,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -25511,7 +25511,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -25650,7 +25650,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -25789,7 +25789,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -25928,7 +25928,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -26206,7 +26206,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -26345,7 +26345,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -26623,7 +26623,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -26762,7 +26762,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -26901,7 +26901,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -27040,7 +27040,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -27179,7 +27179,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -27318,7 +27318,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -27457,7 +27457,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -27874,7 +27874,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -28013,7 +28013,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -28152,7 +28152,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -28291,7 +28291,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -28430,7 +28430,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -28569,7 +28569,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -28708,7 +28708,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -28847,7 +28847,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -28986,7 +28986,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -29125,7 +29125,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -29264,7 +29264,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -29403,7 +29403,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -29542,7 +29542,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -29681,7 +29681,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -29820,7 +29820,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -29959,7 +29959,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -30098,7 +30098,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -30237,7 +30237,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -30376,7 +30376,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -30515,7 +30515,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -30654,7 +30654,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -30793,7 +30793,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -30932,7 +30932,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -31071,7 +31071,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -31210,7 +31210,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -31349,7 +31349,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -31627,7 +31627,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -31766,7 +31766,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -31905,7 +31905,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -32044,7 +32044,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -32183,7 +32183,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -32322,7 +32322,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -32461,7 +32461,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -32600,7 +32600,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -32739,7 +32739,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -32878,7 +32878,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -33017,7 +33017,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -33156,7 +33156,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -33434,7 +33434,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -33573,7 +33573,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -33712,7 +33712,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -33851,7 +33851,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -33996,7 +33996,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>215235792</v>
+        <v>645707376</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -34135,7 +34135,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -34274,7 +34274,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -34413,7 +34413,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -34552,7 +34552,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -34699,7 +34699,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -34838,7 +34838,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -34987,7 +34987,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>186535791</v>
+        <v>559607373</v>
       </c>
       <c r="AE247" t="n">
         <v>5</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -35265,7 +35265,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE250" t="n">
         <v>5</v>
@@ -35559,7 +35559,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE251" t="n">
         <v>229</v>
@@ -35708,7 +35708,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>215410752</v>
+        <v>646232256</v>
       </c>
       <c r="AE252" t="n">
         <v>4</v>
@@ -35847,7 +35847,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>172186884</v>
+        <v>516560652</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -35990,7 +35990,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>215233605</v>
+        <v>645700815</v>
       </c>
       <c r="AE254" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>776435301</v>
+        <v>2329305903</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>531086706</v>
+        <v>1593260118</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE5" t="n">
         <v>3</v>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE7" t="n">
         <v>19</v>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>518154975</v>
+        <v>1554464925</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE10" t="n">
         <v>17</v>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE27" t="n">
         <v>17</v>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7302,7 +7302,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -7719,7 +7719,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -7997,7 +7997,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9387,7 +9387,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10082,7 +10082,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -10777,7 +10777,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11055,7 +11055,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -11611,7 +11611,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12306,7 +12306,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -12584,7 +12584,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13001,7 +13001,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13140,7 +13140,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13279,7 +13279,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13418,7 +13418,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -13835,7 +13835,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -13974,7 +13974,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14113,7 +14113,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14252,7 +14252,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14391,7 +14391,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -14530,7 +14530,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -14669,7 +14669,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -14808,7 +14808,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15086,7 +15086,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15225,7 +15225,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15364,7 +15364,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -15503,7 +15503,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -15642,7 +15642,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -15920,7 +15920,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16059,7 +16059,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16198,7 +16198,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -16615,7 +16615,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -16754,7 +16754,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17032,7 +17032,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17310,7 +17310,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -17449,7 +17449,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -17727,7 +17727,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -17866,7 +17866,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18144,7 +18144,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18283,7 +18283,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -18422,7 +18422,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -18561,7 +18561,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -18839,7 +18839,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -19395,7 +19395,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -19673,7 +19673,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -19951,7 +19951,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20090,7 +20090,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20229,7 +20229,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -20368,7 +20368,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -20785,7 +20785,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -20924,7 +20924,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21063,7 +21063,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21202,7 +21202,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -21341,7 +21341,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -21480,7 +21480,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -21619,7 +21619,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -21758,7 +21758,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -21897,7 +21897,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22175,7 +22175,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -22314,7 +22314,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -22453,7 +22453,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -22592,7 +22592,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -22731,7 +22731,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -22870,7 +22870,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23009,7 +23009,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23148,7 +23148,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -23287,7 +23287,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -23426,7 +23426,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -23565,7 +23565,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -23704,7 +23704,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -23982,7 +23982,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24121,7 +24121,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -24260,7 +24260,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -24399,7 +24399,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -24538,7 +24538,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -24677,7 +24677,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -24816,7 +24816,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -24955,7 +24955,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25094,7 +25094,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -25233,7 +25233,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -25372,7 +25372,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -25511,7 +25511,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -25650,7 +25650,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -25789,7 +25789,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -25928,7 +25928,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -26206,7 +26206,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -26345,7 +26345,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -26484,7 +26484,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -26623,7 +26623,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -26762,7 +26762,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -26901,7 +26901,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -27040,7 +27040,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -27179,7 +27179,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -27318,7 +27318,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -27457,7 +27457,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -27874,7 +27874,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -28013,7 +28013,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -28152,7 +28152,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -28291,7 +28291,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -28430,7 +28430,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -28569,7 +28569,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -28708,7 +28708,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -28847,7 +28847,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -28986,7 +28986,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -29125,7 +29125,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -29264,7 +29264,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -29403,7 +29403,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -29542,7 +29542,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -29681,7 +29681,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -29820,7 +29820,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -29959,7 +29959,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -30098,7 +30098,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -30237,7 +30237,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -30376,7 +30376,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -30515,7 +30515,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -30654,7 +30654,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -30793,7 +30793,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -30932,7 +30932,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -31071,7 +31071,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -31210,7 +31210,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -31349,7 +31349,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -31488,7 +31488,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -31627,7 +31627,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -31766,7 +31766,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -31905,7 +31905,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -32044,7 +32044,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -32183,7 +32183,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -32322,7 +32322,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -32461,7 +32461,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -32600,7 +32600,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -32739,7 +32739,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -32878,7 +32878,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -33017,7 +33017,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -33156,7 +33156,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -33434,7 +33434,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -33573,7 +33573,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -33712,7 +33712,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -33851,7 +33851,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -33996,7 +33996,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>645707376</v>
+        <v>1937122128</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -34135,7 +34135,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -34274,7 +34274,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -34413,7 +34413,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -34552,7 +34552,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -34699,7 +34699,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -34838,7 +34838,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -34987,7 +34987,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>559607373</v>
+        <v>1678822119</v>
       </c>
       <c r="AE247" t="n">
         <v>5</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -35265,7 +35265,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE250" t="n">
         <v>5</v>
@@ -35559,7 +35559,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE251" t="n">
         <v>229</v>
@@ -35708,7 +35708,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>646232256</v>
+        <v>1938696768</v>
       </c>
       <c r="AE252" t="n">
         <v>4</v>
@@ -35847,7 +35847,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>516560652</v>
+        <v>1549681956</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -35990,7 +35990,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>645700815</v>
+        <v>1937102445</v>
       </c>
       <c r="AE254" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -581,12 +581,12 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>shared_target_count</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>identity_url</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>shared_target_count</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -742,15 +742,15 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE2" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>https://www.rofenashim.co.il/faq/faq-fertility/</t>
         </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>6</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
@@ -891,15 +891,15 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>6987917709</v>
-      </c>
-      <c r="AE3" t="inlineStr">
+        <v>20963753127</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>https://www.e-piryon.com/</t>
         </is>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -1040,15 +1040,15 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>4779780354</v>
-      </c>
-      <c r="AE4" t="inlineStr">
+        <v>14339341062</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>https://www.profyinoncohen.com/</t>
         </is>
-      </c>
-      <c r="AF4" t="n">
-        <v>2</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
@@ -1187,15 +1187,15 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE5" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>https://www.leidaraka.co.il/</t>
         </is>
-      </c>
-      <c r="AF5" t="n">
-        <v>3</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1334,15 +1334,15 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE6" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>https://kerenzohar.com/%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF6" t="n">
-        <v>2</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1483,15 +1483,15 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE7" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>https://hmc.co.il/doctor/%D7%A4%D7%A8%D7%95%D7%A4-%D7%93%D7%95%D7%93-%D7%9C%D7%91-%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF7" t="n">
-        <v>19</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -1630,15 +1630,15 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE8" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>https://www.israelidoula.co.il/courses-1/embryo-%D7%A7%D7%95%D7%A8%D7%A1-%D7%9E%D7%93%D7%A8%D7%99%D7%9B%D7%95%D7%AA-%D7%94%D7%9B%D7%A0%D7%94-%D7%9C%D7%9C%D7%99%D7%93%D7%94</t>
         </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>7</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1779,15 +1779,15 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>4663394775</v>
-      </c>
-      <c r="AE9" t="inlineStr">
+        <v>13990184325</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>https://www.dr-paz.co.il/</t>
         </is>
-      </c>
-      <c r="AF9" t="n">
-        <v>2</v>
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
@@ -1926,15 +1926,15 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE10" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>https://www.israelivf.co.il/%D7%90%D7%95%D7%93%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF10" t="n">
-        <v>17</v>
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
@@ -2074,15 +2074,15 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE11" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>https://boneiolam.co.il/%D7%A4%D7%A2%D7%99%D7%9C%D7%95%D7%AA-%D7%94%D7%90%D7%A8%D7%92%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
@@ -2213,15 +2213,15 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE12" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>https://www.shvil-haleida.co.il/%D7%A8%D7%99%D7%A9%D7%95%D7%9D-%D7%9C%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%9C%D7%99%D7%93%D7%94/</t>
         </is>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
@@ -2362,15 +2362,15 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>5816090304</v>
-      </c>
-      <c r="AE13" t="inlineStr">
+        <v>17448270912</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>https://serviced.co.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-%D7%A9%D7%99%D7%A8%D7%95%D7%AA-%D7%9C%D7%A7%D7%95%D7%97%D7%95%D7%AA-%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94-9/</t>
         </is>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
@@ -2501,15 +2501,15 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE14" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF14" t="inlineStr">
         <is>
           <t>https://harechem.com/</t>
         </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>3</v>
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
@@ -2644,15 +2644,15 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE15" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>http://www.amotatchen.org/</t>
         </is>
-      </c>
-      <c r="AF15" t="n">
-        <v>3</v>
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
@@ -2793,15 +2793,15 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE16" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>2</v>
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2942,15 +2942,15 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>5816090304</v>
-      </c>
-      <c r="AE17" t="inlineStr">
+        <v>17448270912</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>https://dinadoula.com/%D7%93%D7%95%D7%9C%D7%94/</t>
         </is>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
@@ -3091,15 +3091,15 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE18" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>https://www.surmom.co.il/%D7%A6%D7%95%D7%95%D7%AA-%D7%A9%D7%9C%D7%A0%D7%95/%D7%A4%D7%A8%D7%95%D7%A4-%D7%A9%D7%95%D7%9C%D7%9E%D7%9F-%D7%90%D7%93%D7%A8%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
@@ -3240,15 +3240,15 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE19" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>https://hfhosp.org/he/%D7%A6%D7%95%D7%95%D7%AA-%D7%94%D7%A8%D7%95%D7%A4%D7%90%D7%99%D7%9D/%D7%93%D7%A8-%D7%A0%D7%99%D7%A7%D7%95%D7%9C%D7%90-%D7%A4%D7%A8%D7%97</t>
         </is>
-      </c>
-      <c r="AF19" t="n">
-        <v>5</v>
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
@@ -3379,15 +3379,15 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE20" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>https://midwives.org.il/%D7%9C%D7%99%D7%95%D7%95%D7%99-%D7%9E%D7%A7%D7%A6%D7%95%D7%A2%D7%99-%D7%96%D7%94-%D7%9E%D7%99%D7%99%D7%9C%D7%93%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>9</v>
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
@@ -3526,15 +3526,15 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE21" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF21" t="n">
-        <v>8</v>
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
@@ -3673,15 +3673,15 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE22" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>11</v>
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
@@ -3812,15 +3812,15 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE23" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF23" t="inlineStr">
         <is>
           <t>https://www.israelibaby.co.il/where-to-get-birth</t>
         </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>11</v>
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
@@ -3951,15 +3951,15 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE24" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF24" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/</t>
         </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>2</v>
       </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
@@ -4094,15 +4094,15 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE25" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF25" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/fertility-research/</t>
         </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>3</v>
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
@@ -4233,15 +4233,15 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE26" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF26" t="inlineStr">
         <is>
           <t>https://barakivf.com/</t>
         </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>3</v>
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
@@ -4376,15 +4376,15 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE27" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF27" t="inlineStr">
         <is>
           <t>https://demayo.co.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%94%D7%90%D7%99%D7%A9%D7%94/</t>
         </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>3</v>
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
@@ -4523,15 +4523,15 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE28" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>https://bri.co.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/</t>
         </is>
-      </c>
-      <c r="AF28" t="n">
-        <v>17</v>
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
@@ -4662,15 +4662,15 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE29" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF29" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>4</v>
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
@@ -4801,15 +4801,15 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE30" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF30" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF30" t="n">
-        <v>4</v>
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
@@ -4940,15 +4940,15 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE31" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF31" t="inlineStr">
         <is>
           <t>https://hmc.co.il/operation/%D7%A9%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%95%D7%A8%D7%99%D7%95%D7%AA-%D7%94%D7%A7%D7%A4%D7%90%D7%AA-%D7%91%D7%99%D7%A6%D7%99%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>4</v>
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
@@ -5087,15 +5087,15 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE32" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF32" t="inlineStr">
         <is>
           <t>https://www.laniado.org.il/%D7%9E%D7%A8%D7%9B%D7%96-%D7%9C%D7%99%D7%93%D7%94-%D7%98%D7%91%D7%A2%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>2</v>
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
@@ -5226,15 +5226,15 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE33" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF33" t="inlineStr">
         <is>
           <t>https://go.serguide.maccabi4u.co.il/heb/labsandtherapists/labsandtherapistssearchresults/labsandtherapistsinfopage/?ItemKeyIndex=A6B809CAFEA13537A84D783709CF5EBB&amp;RequestId=00000000-0000-0000-0001-000000000325</t>
         </is>
-      </c>
-      <c r="AF33" t="n">
-        <v>2</v>
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
@@ -5365,15 +5365,15 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE34" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF34" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/</t>
         </is>
-      </c>
-      <c r="AF34" t="n">
-        <v>8</v>
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
@@ -5504,15 +5504,15 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE35" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF35" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%91%D7%9C%D7%94-%D7%A2%D7%91%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF35" t="n">
-        <v>2</v>
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
@@ -5643,15 +5643,15 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE36" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF36" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%92%D7%9E%D7%95/</t>
         </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>2</v>
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
@@ -5782,15 +5782,15 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE37" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF37" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%99%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>2</v>
       </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
@@ -5921,15 +5921,15 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE38" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF38" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%91%D7%9F-%D7%90%D7%A8%D7%99-%D7%A6%D7%90%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF38" t="n">
-        <v>2</v>
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
@@ -6060,15 +6060,15 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE39" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF39" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%90%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>2</v>
       </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
@@ -6199,15 +6199,15 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE40" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF40" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%A7%D7%95%D7%A8%D7%A0%D7%92%D7%95%D7%9C%D7%93-%D7%97%D7%99%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF40" t="n">
-        <v>2</v>
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
@@ -6338,15 +6338,15 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE41" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF41" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%93%D7%99-%D7%9C%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF41" t="n">
-        <v>2</v>
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
@@ -6477,15 +6477,15 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE42" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF42" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%9C%D7%A0%D7%93%D7%94-%D7%A1%D7%95%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF42" t="n">
-        <v>2</v>
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
@@ -6616,15 +6616,15 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE43" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF43" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%95%D7%A0%D7%94-%D7%91%D7%95%D7%A8%D7%9C%D7%90/</t>
         </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>2</v>
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
@@ -6755,15 +6755,15 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE44" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF44" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%9C%D7%99%D7%94-%D7%94%D7%95%D7%9C%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF44" t="n">
-        <v>2</v>
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
@@ -6894,15 +6894,15 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE45" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF45" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%9E%D7%99%D7%AA-%D7%93%D7%A0%D7%A1%D7%99%D7%95%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF45" t="n">
-        <v>2</v>
       </c>
       <c r="AG45" t="inlineStr"/>
       <c r="AH45" t="inlineStr"/>
@@ -7033,15 +7033,15 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE46" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF46" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%9E%D7%95%D7%96%D7%A1-%D7%90%D7%9C%D7%91%D7%96/</t>
         </is>
-      </c>
-      <c r="AF46" t="n">
-        <v>2</v>
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
@@ -7172,15 +7172,15 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE47" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF47" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%A8%D7%95%D7%9F-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF47" t="n">
-        <v>2</v>
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
@@ -7311,15 +7311,15 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE48" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF48" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%AA-%D7%99%D7%A2%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF48" t="n">
-        <v>2</v>
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
@@ -7450,15 +7450,15 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE49" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF49" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%98%D7%94-%D7%A0%D7%95%D7%91%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF49" t="n">
-        <v>2</v>
       </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
@@ -7589,15 +7589,15 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE50" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF50" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%94-%D7%A4%D7%95%D7%9C%D7%99%D7%90%D7%A7%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF50" t="n">
-        <v>2</v>
       </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
@@ -7728,15 +7728,15 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE51" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF51" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A0%D7%99%D7%94-%D7%93%D7%9E%D7%A0%D7%98%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF51" t="n">
-        <v>2</v>
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
@@ -7867,15 +7867,15 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE52" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF52" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
         </is>
-      </c>
-      <c r="AF52" t="n">
-        <v>2</v>
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
@@ -8006,15 +8006,15 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE53" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF53" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%99%D7%90%D7%9C%D7%94-%D7%96%D7%92%D7%95%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF53" t="n">
-        <v>2</v>
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
@@ -8145,15 +8145,15 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE54" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF54" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8-%D7%95%D7%99%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF54" t="n">
-        <v>2</v>
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
@@ -8284,15 +8284,15 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE55" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF55" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF55" t="n">
-        <v>2</v>
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
@@ -8423,15 +8423,15 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE56" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF56" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%98%D7%A8%D7%94-%D7%9C%D7%91%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF56" t="n">
-        <v>2</v>
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
@@ -8562,15 +8562,15 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE57" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF57" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%90%D7%9D-%D7%9E%D7%95%D7%A8%D7%94-%D7%97%D7%9E%D7%90%D7%A8%D7%A9%D7%99/</t>
         </is>
-      </c>
-      <c r="AF57" t="n">
-        <v>2</v>
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
@@ -8701,15 +8701,15 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE58" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF58" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%91%D7%A8%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF58" t="n">
-        <v>2</v>
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
@@ -8840,15 +8840,15 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE59" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF59" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%A6%D7%99%D7%91%D7%99%D7%90%D7%A7-%D7%93%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF59" t="n">
-        <v>2</v>
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
@@ -8979,15 +8979,15 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE60" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF60" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%99%D7%99%D7%9C%D7%AA-%D7%9E%D7%95%D7%91%D7%A9%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF60" t="n">
-        <v>2</v>
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
@@ -9118,15 +9118,15 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE61" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF61" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%94-%D7%90%D7%96%D7%91%D7%A0%D7%93/</t>
         </is>
-      </c>
-      <c r="AF61" t="n">
-        <v>2</v>
       </c>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
@@ -9257,15 +9257,15 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE62" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF62" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%AA%D7%A9%D7%91%D7%A2-%D7%92%D7%A8%D7%A0%D7%95%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF62" t="n">
-        <v>2</v>
       </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
@@ -9396,15 +9396,15 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE63" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF63" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%99%D7%9C%D7%99-%D7%90%D7%95%D7%91%D7%A8%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF63" t="n">
-        <v>2</v>
       </c>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
@@ -9535,15 +9535,15 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE64" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF64" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%9C%D7%99%D7%99%D7%A8-%D7%90%D7%9C%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF64" t="n">
-        <v>2</v>
       </c>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
@@ -9674,15 +9674,15 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE65" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF65" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%94%D7%A9%D7%9B%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF65" t="n">
-        <v>2</v>
       </c>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
@@ -9813,15 +9813,15 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE66" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF66" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%91%D7%A8%D7%9B%D7%94-%D7%98%D7%9C-%D7%91%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF66" t="n">
-        <v>2</v>
       </c>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
@@ -9952,15 +9952,15 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE67" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF67" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%97%D7%95%D7%98%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF67" t="n">
-        <v>2</v>
       </c>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
@@ -10091,15 +10091,15 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE68" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF68" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9B%D7%A8%D7%9E%D7%99%D7%AA-%D7%9C%D7%90%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF68" t="n">
-        <v>2</v>
       </c>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
@@ -10230,15 +10230,15 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE69" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF69" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%92%D7%93%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF69" t="n">
-        <v>2</v>
       </c>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
@@ -10369,15 +10369,15 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE70" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF70" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%9E%D7%A8%D7%90%D7%93/</t>
         </is>
-      </c>
-      <c r="AF70" t="n">
-        <v>2</v>
       </c>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
@@ -10508,15 +10508,15 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE71" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF71" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%A0%D7%94-%D7%A9%D7%95%D7%95%D7%A8%D7%A6%D7%91%D7%A8%D7%92/</t>
         </is>
-      </c>
-      <c r="AF71" t="n">
-        <v>2</v>
       </c>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
@@ -10647,15 +10647,15 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE72" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF72" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%99%D7%90%D7%9F-%D7%A9%D7%A4%D7%99%D7%92%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF72" t="n">
-        <v>2</v>
       </c>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
@@ -10786,15 +10786,15 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE73" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF73" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8-%D7%91%D7%99%D7%98%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF73" t="n">
-        <v>2</v>
       </c>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
@@ -10925,15 +10925,15 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE74" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF74" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%93%D7%95%D7%A8%D7%99%D7%9F-%D7%90%D7%9C%D7%A2%D7%93/</t>
         </is>
-      </c>
-      <c r="AF74" t="n">
-        <v>2</v>
       </c>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
@@ -11064,15 +11064,15 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE75" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF75" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/332/</t>
         </is>
-      </c>
-      <c r="AF75" t="n">
-        <v>2</v>
       </c>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
@@ -11203,15 +11203,15 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE76" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF76" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%91%D7%9F-%D7%A9%D7%A5-%D7%A4%D7%95%D7%A8%D7%A9%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF76" t="n">
-        <v>2</v>
       </c>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
@@ -11342,15 +11342,15 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE77" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF77" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%95%D7%95%D7%A8%D7%99%D7%99%D7%98/</t>
         </is>
-      </c>
-      <c r="AF77" t="n">
-        <v>2</v>
       </c>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
@@ -11481,15 +11481,15 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE78" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF78" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A4%D7%A8%D7%AA-%D7%99%D7%90%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF78" t="n">
-        <v>2</v>
       </c>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
@@ -11620,15 +11620,15 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE79" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF79" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%91%D7%92%D7%9C%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF79" t="n">
-        <v>2</v>
       </c>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
@@ -11759,15 +11759,15 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE80" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF80" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%99%D7%A0%D7%AA-%D7%98%D7%9C%D7%9E%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF80" t="n">
-        <v>2</v>
       </c>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
@@ -11898,15 +11898,15 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE81" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF81" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%9C%D7%A0%D7%94-%D7%A9%D7%99%D7%9C%D7%A7%D7%95/</t>
         </is>
-      </c>
-      <c r="AF81" t="n">
-        <v>2</v>
       </c>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
@@ -12037,15 +12037,15 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE82" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF82" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A2%D7%A0%D7%94-%D7%92%D7%95%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF82" t="n">
-        <v>2</v>
       </c>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
@@ -12176,15 +12176,15 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE83" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF83" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A0%D7%94-%D7%91%D7%A8%D7%A7%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF83" t="n">
-        <v>2</v>
       </c>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
@@ -12315,15 +12315,15 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE84" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF84" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A8%D7%96-%D7%92%D7%99%D7%9C%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF84" t="n">
-        <v>2</v>
       </c>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
@@ -12454,15 +12454,15 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE85" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF85" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%99%D7%A9%D7%91%D7%A2-%D7%92%D7%95%D7%A8%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF85" t="n">
-        <v>2</v>
       </c>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
@@ -12593,15 +12593,15 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE86" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF86" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%9C%D7%95%D7%A0%D7%92%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF86" t="n">
-        <v>2</v>
       </c>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
@@ -12732,15 +12732,15 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE87" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF87" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9C%D7%9F-%D7%A9%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF87" t="n">
-        <v>2</v>
       </c>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
@@ -12871,15 +12871,15 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE88" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF88" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%94-%D7%90%D7%99%D7%AA%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF88" t="n">
-        <v>2</v>
       </c>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
@@ -13010,15 +13010,15 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE89" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF89" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%9E%D7%95%D7%A0%D7%94-%D7%95%D7%92%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF89" t="n">
-        <v>2</v>
       </c>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
@@ -13149,15 +13149,15 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE90" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF90" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A8%D7%90%D7%9C%D7%94-%D7%99%D7%A8%D7%A7%D7%95%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF90" t="n">
-        <v>2</v>
       </c>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
@@ -13288,15 +13288,15 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE91" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF91" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%A1%D7%AA%D7%A8-%D7%A4%D7%9C%D7%99%D7%99%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF91" t="n">
-        <v>2</v>
       </c>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
@@ -13427,15 +13427,15 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE92" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF92" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%AA%D7%99-%D7%A1%D7%93%D7%9F-%D7%A7%D7%A0%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF92" t="n">
-        <v>2</v>
       </c>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
@@ -13566,15 +13566,15 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE93" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF93" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A4%D7%A8%D7%A0%D7%A1%D7%99%D7%A1-%D7%A4%D7%A8%D7%9F-%D7%91%D7%A8%D7%95%D7%A0%D7%A9%D7%98%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF93" t="n">
-        <v>2</v>
       </c>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
@@ -13705,15 +13705,15 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE94" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF94" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%91%D7%99-%D7%A4%D7%99%D7%A9%D7%9E%D7%9F-%D7%A4%D7%95%D7%A1%D7%91%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF94" t="n">
-        <v>2</v>
       </c>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
@@ -13844,15 +13844,15 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE95" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF95" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99-%D7%A7%D7%9E%D7%97%D7%99/</t>
         </is>
-      </c>
-      <c r="AF95" t="n">
-        <v>2</v>
       </c>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
@@ -13983,15 +13983,15 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE96" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF96" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%90%D7%A4%D7%9C%D7%91%D7%95%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF96" t="n">
-        <v>2</v>
       </c>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
@@ -14122,15 +14122,15 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE97" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF97" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%AA-%D7%9C%D7%99%D7%A8%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF97" t="n">
-        <v>2</v>
       </c>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
@@ -14261,15 +14261,15 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE98" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF98" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%9C%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF98" t="n">
-        <v>2</v>
       </c>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
@@ -14400,15 +14400,15 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE99" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF99" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%90%D7%99%D7%94-%D7%92%D7%95%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF99" t="n">
-        <v>2</v>
       </c>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
@@ -14539,15 +14539,15 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE100" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF100" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%94-%D7%90%D7%95%D7%A0%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF100" t="n">
-        <v>2</v>
       </c>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
@@ -14678,15 +14678,15 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE101" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF101" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%9C%D7%99%D7%94-%D7%93%D7%95%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF101" t="n">
-        <v>2</v>
       </c>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
@@ -14817,15 +14817,15 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE102" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF102" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%99%D7%AA%D7%99%D7%AA-%D7%A9%D7%A4%D7%A8%D7%9C%D7%99%D7%A0%D7%92/</t>
         </is>
-      </c>
-      <c r="AF102" t="n">
-        <v>2</v>
       </c>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
@@ -14956,15 +14956,15 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE103" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF103" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%9E%D7%95%D7%99%D7%90%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF103" t="n">
-        <v>2</v>
       </c>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
@@ -15095,15 +15095,15 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE104" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF104" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A8-%D7%98%D7%A1%D7%94/</t>
         </is>
-      </c>
-      <c r="AF104" t="n">
-        <v>2</v>
       </c>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
@@ -15234,15 +15234,15 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE105" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF105" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%A1%D7%94-%D7%A4%D7%97%D7%9C%D7%99%D7%99%D7%91/</t>
         </is>
-      </c>
-      <c r="AF105" t="n">
-        <v>2</v>
       </c>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
@@ -15373,15 +15373,15 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE106" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF106" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%A0%D7%94-%D7%94%D7%A8%D7%95%D7%A9/</t>
         </is>
-      </c>
-      <c r="AF106" t="n">
-        <v>2</v>
       </c>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
@@ -15512,15 +15512,15 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE107" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF107" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%93%D7%99-%D7%94%D7%A8%D7%A4%D7%96/</t>
         </is>
-      </c>
-      <c r="AF107" t="n">
-        <v>2</v>
       </c>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
@@ -15651,15 +15651,15 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE108" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF108" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9E%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF108" t="n">
-        <v>2</v>
       </c>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
@@ -15790,15 +15790,15 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE109" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF109" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%99%D7%9C%D7%94-%D7%9C%D7%91-%D7%A8%D7%9F-%D7%97%D7%95%D7%AA%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF109" t="n">
-        <v>2</v>
       </c>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
@@ -15929,15 +15929,15 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE110" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF110" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%94%D7%95%D7%93%D7%99%D7%94-%D7%90%D7%99%D7%AA%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF110" t="n">
-        <v>2</v>
       </c>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
@@ -16068,15 +16068,15 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE111" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF111" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%9C-%D7%91%D7%95%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF111" t="n">
-        <v>2</v>
       </c>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
@@ -16207,15 +16207,15 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE112" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF112" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%A0%D7%91%D7%A8-%D7%A7%D7%A8%D7%9F-%D7%A8%D7%98%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF112" t="n">
-        <v>2</v>
       </c>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
@@ -16346,15 +16346,15 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE113" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF113" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%B3%D7%95%D7%9C%D7%99-%D7%90%D7%A1%D7%AA%D7%99-%D7%A9%D7%9E%D7%A2%D7%95%D7%A0%D7%99/</t>
         </is>
-      </c>
-      <c r="AF113" t="n">
-        <v>2</v>
       </c>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
@@ -16485,15 +16485,15 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE114" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF114" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%92%D7%95%D7%9C%D7%99-%D7%A7%D7%A8%D7%A7%D7%95/</t>
         </is>
-      </c>
-      <c r="AF114" t="n">
-        <v>2</v>
       </c>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
@@ -16624,15 +16624,15 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE115" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF115" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%92%D7%9C%D7%99%D7%9F-%D7%A1%D7%9C%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF115" t="n">
-        <v>2</v>
       </c>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
@@ -16763,15 +16763,15 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE116" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF116" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%92%D7%99%D7%91%D7%A8-%D7%A9%D7%92%D7%91/</t>
         </is>
-      </c>
-      <c r="AF116" t="n">
-        <v>2</v>
       </c>
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
@@ -16902,15 +16902,15 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE117" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF117" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%A1%D7%9C%D7%91%D7%95%D7%93%D7%A0%D7%99%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF117" t="n">
-        <v>2</v>
       </c>
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
@@ -17041,15 +17041,15 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE118" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF118" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A7%D7%A8%D7%9F-%D7%95%D7%99%D7%99%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF118" t="n">
-        <v>2</v>
       </c>
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
@@ -17180,15 +17180,15 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE119" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF119" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%90%D7%A0%D7%94-%D7%91%D7%A8%D7%99%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF119" t="n">
-        <v>2</v>
       </c>
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
@@ -17319,15 +17319,15 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE120" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF120" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99-%D7%90%D7%95%D7%A8-%D7%9C%D7%91%D7%A0%D7%96%D7%95%D7%9F-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF120" t="n">
-        <v>2</v>
       </c>
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
@@ -17458,15 +17458,15 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE121" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF121" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%A8%D7%95%D7%9F-%D7%A4%D7%99%D7%90%D7%97%D7%95%D7%98%D7%94-%D7%A1%D7%90%D7%9C%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF121" t="n">
-        <v>2</v>
       </c>
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
@@ -17597,15 +17597,15 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE122" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF122" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%94-%D7%9C%D7%95%D7%99/</t>
         </is>
-      </c>
-      <c r="AF122" t="n">
-        <v>2</v>
       </c>
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
@@ -17736,15 +17736,15 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE123" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF123" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%94-%D7%A7%D7%95%D7%92%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF123" t="n">
-        <v>2</v>
       </c>
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
@@ -17875,15 +17875,15 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE124" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF124" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99%D7%90%D7%9F-%D7%A9%D7%95%D7%97%D7%98/</t>
         </is>
-      </c>
-      <c r="AF124" t="n">
-        <v>2</v>
       </c>
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
@@ -18014,15 +18014,15 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE125" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF125" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9C%D7%99-%D7%A2%D7%95%D7%96%D7%99%D7%90%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF125" t="n">
-        <v>2</v>
       </c>
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
@@ -18153,15 +18153,15 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE126" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF126" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%9E%D7%95%D7%A8-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF126" t="n">
-        <v>2</v>
       </c>
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
@@ -18292,15 +18292,15 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE127" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF127" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8-%D7%9C%D7%95%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF127" t="n">
-        <v>2</v>
       </c>
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
@@ -18431,15 +18431,15 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE128" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF128" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%90%D7%95%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF128" t="n">
-        <v>2</v>
       </c>
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
@@ -18570,15 +18570,15 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE129" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF129" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9C%D7%99%D7%98%D7%95%D7%91-%D7%97%D7%99%D7%94-%D7%90%D7%99%D7%98%D7%94/</t>
         </is>
-      </c>
-      <c r="AF129" t="n">
-        <v>2</v>
       </c>
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
@@ -18709,15 +18709,15 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE130" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF130" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A2%D7%99%D7%99%D7%9F-%D7%90%D7%9C%D7%9E%D7%92%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF130" t="n">
-        <v>2</v>
       </c>
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
@@ -18848,15 +18848,15 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE131" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF131" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99-%D7%93%D7%A8%D7%95%D7%A7%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF131" t="n">
-        <v>2</v>
       </c>
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
@@ -18987,15 +18987,15 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE132" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF132" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%94-%D7%92%D7%95%D7%A8%D7%92%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF132" t="n">
-        <v>2</v>
       </c>
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
@@ -19126,15 +19126,15 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE133" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF133" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%9B%D7%99-%D7%90%D7%95%D7%A4%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF133" t="n">
-        <v>2</v>
       </c>
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
@@ -19265,15 +19265,15 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE134" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF134" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%A9%D7%97%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF134" t="n">
-        <v>2</v>
       </c>
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
@@ -19404,15 +19404,15 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE135" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF135" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%A8%D7%99%D7%90%D7%A0%D7%94-%D7%95%D7%A4%D7%A8%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF135" t="n">
-        <v>2</v>
       </c>
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
@@ -19543,15 +19543,15 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE136" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF136" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99-%D7%9C%D7%91-%D7%A7%D7%9C%D7%99%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF136" t="n">
-        <v>2</v>
       </c>
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
@@ -19682,15 +19682,15 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE137" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF137" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%90%D7%99%D7%94-%D7%90%D7%A0%D7%95%D7%9A/</t>
         </is>
-      </c>
-      <c r="AF137" t="n">
-        <v>2</v>
       </c>
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
@@ -19821,15 +19821,15 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE138" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF138" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%94-%D7%90%D7%99%D7%96%D7%A7%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF138" t="n">
-        <v>2</v>
       </c>
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
@@ -19960,15 +19960,15 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE139" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF139" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%91-%D7%A0%D7%97%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF139" t="n">
-        <v>2</v>
       </c>
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
@@ -20099,15 +20099,15 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE140" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF140" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%9C%D7%99%D7%A1%D7%94-%D7%91%D7%A8-%D7%90%D7%99%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF140" t="n">
-        <v>2</v>
       </c>
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
@@ -20238,15 +20238,15 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE141" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF141" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%9B%D7%9C-%D7%96%D7%99%D7%9C%D7%91%D7%A8%D7%9E%D7%9F-%D7%A8%D7%99%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF141" t="n">
-        <v>2</v>
       </c>
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
@@ -20377,15 +20377,15 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE142" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF142" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A7%D7%94-%D7%9B%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF142" t="n">
-        <v>2</v>
       </c>
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
@@ -20516,15 +20516,15 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE143" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF143" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99-%D7%A4%D7%91%D7%96%D7%A0%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF143" t="n">
-        <v>2</v>
       </c>
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
@@ -20655,15 +20655,15 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE144" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF144" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%99%D7%A8%D7%99%D7%AA-%D7%A8%D7%95%D7%96%D7%A0%D7%91%D7%90%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF144" t="n">
-        <v>2</v>
       </c>
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
@@ -20794,15 +20794,15 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE145" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF145" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8-%D7%92%D7%95%D7%9C%D7%93%D7%A0%D7%92%D7%95%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF145" t="n">
-        <v>2</v>
       </c>
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
@@ -20933,15 +20933,15 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE146" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF146" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%9E%D7%9C%D7%A6%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF146" t="n">
-        <v>2</v>
       </c>
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
@@ -21072,15 +21072,15 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE147" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF147" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%A4%D7%9C%D7%92%D7%99/</t>
         </is>
-      </c>
-      <c r="AF147" t="n">
-        <v>2</v>
       </c>
       <c r="AG147" t="inlineStr"/>
       <c r="AH147" t="inlineStr"/>
@@ -21211,15 +21211,15 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE148" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF148" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%9E%D7%95%D7%A8%D7%9F-%D7%95%D7%95%D7%9C%D7%A4%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF148" t="n">
-        <v>2</v>
       </c>
       <c r="AG148" t="inlineStr"/>
       <c r="AH148" t="inlineStr"/>
@@ -21350,15 +21350,15 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE149" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF149" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A2%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF149" t="n">
-        <v>2</v>
       </c>
       <c r="AG149" t="inlineStr"/>
       <c r="AH149" t="inlineStr"/>
@@ -21489,15 +21489,15 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE150" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF150" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A2%D7%9E%D7%94-%D7%A8%D7%99%D7%91%D7%9C%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF150" t="n">
-        <v>2</v>
       </c>
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
@@ -21628,15 +21628,15 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE151" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF151" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%A8%D7%A7%D7%99%D7%A1-%D7%A0%D7%A4%D7%AA%D7%9C%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF151" t="n">
-        <v>2</v>
       </c>
       <c r="AG151" t="inlineStr"/>
       <c r="AH151" t="inlineStr"/>
@@ -21767,15 +21767,15 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE152" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF152" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%A7%D7%A9%D7%99%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF152" t="n">
-        <v>2</v>
       </c>
       <c r="AG152" t="inlineStr"/>
       <c r="AH152" t="inlineStr"/>
@@ -21906,15 +21906,15 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE153" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF153" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%9C%D7%99-%D7%91%D7%9F-%D7%A9%D7%A9%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF153" t="n">
-        <v>2</v>
       </c>
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
@@ -22045,15 +22045,15 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE154" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF154" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%98%D7%A2-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF154" t="n">
-        <v>2</v>
       </c>
       <c r="AG154" t="inlineStr"/>
       <c r="AH154" t="inlineStr"/>
@@ -22184,15 +22184,15 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE155" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF155" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A0%D7%94-%D7%91%D7%AA%D7%90%D7%A9%D7%95%D7%99%D7%9C%D7%99/</t>
         </is>
-      </c>
-      <c r="AF155" t="n">
-        <v>2</v>
       </c>
       <c r="AG155" t="inlineStr"/>
       <c r="AH155" t="inlineStr"/>
@@ -22323,15 +22323,15 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE156" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF156" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A8%D7%99%D7%AA-%D7%90%D7%95%D7%9C%D7%99%D7%91%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF156" t="n">
-        <v>2</v>
       </c>
       <c r="AG156" t="inlineStr"/>
       <c r="AH156" t="inlineStr"/>
@@ -22462,15 +22462,15 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE157" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF157" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%A6%D7%9F-%D7%99%D7%9E%D7%99%D7%A0%D7%99-%D7%97%D7%99/</t>
         </is>
-      </c>
-      <c r="AF157" t="n">
-        <v>2</v>
       </c>
       <c r="AG157" t="inlineStr"/>
       <c r="AH157" t="inlineStr"/>
@@ -22601,15 +22601,15 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE158" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF158" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%99%D7%91%D7%99-%D7%99%D7%A2%D7%A7%D7%91/</t>
         </is>
-      </c>
-      <c r="AF158" t="n">
-        <v>2</v>
       </c>
       <c r="AG158" t="inlineStr"/>
       <c r="AH158" t="inlineStr"/>
@@ -22740,15 +22740,15 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE159" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF159" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A2%D7%94-%D7%95%D7%99%D7%A6%D7%9E%D7%9F-%D7%A8%D7%91%D7%99%D7%91%D7%95/</t>
         </is>
-      </c>
-      <c r="AF159" t="n">
-        <v>2</v>
       </c>
       <c r="AG159" t="inlineStr"/>
       <c r="AH159" t="inlineStr"/>
@@ -22879,15 +22879,15 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE160" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF160" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%91%D7%95%D7%A8%D7%92-%D7%A1%D7%92%D7%9F-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF160" t="n">
-        <v>2</v>
       </c>
       <c r="AG160" t="inlineStr"/>
       <c r="AH160" t="inlineStr"/>
@@ -23018,15 +23018,15 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE161" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF161" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%92%D7%95%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF161" t="n">
-        <v>2</v>
       </c>
       <c r="AG161" t="inlineStr"/>
       <c r="AH161" t="inlineStr"/>
@@ -23157,15 +23157,15 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE162" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF162" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%A4%D7%99%D7%9C%D7%95%D7%A1%D7%95%D7%A3/</t>
         </is>
-      </c>
-      <c r="AF162" t="n">
-        <v>2</v>
       </c>
       <c r="AG162" t="inlineStr"/>
       <c r="AH162" t="inlineStr"/>
@@ -23296,15 +23296,15 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE163" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF163" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%92%D7%94-%D7%98%D7%95%D7%A9%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF163" t="n">
-        <v>2</v>
       </c>
       <c r="AG163" t="inlineStr"/>
       <c r="AH163" t="inlineStr"/>
@@ -23435,15 +23435,15 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE164" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF164" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A0%D7%95%D7%A8%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF164" t="n">
-        <v>2</v>
       </c>
       <c r="AG164" t="inlineStr"/>
       <c r="AH164" t="inlineStr"/>
@@ -23574,15 +23574,15 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE165" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF165" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%93%D7%9C%D7%99%D7%94-%D7%96%D7%99%D7%9C%D7%9B%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF165" t="n">
-        <v>2</v>
       </c>
       <c r="AG165" t="inlineStr"/>
       <c r="AH165" t="inlineStr"/>
@@ -23713,15 +23713,15 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE166" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF166" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%9C%D7%92%D7%94-%D7%95%D7%A7%D7%A1%D7%9C%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF166" t="n">
-        <v>2</v>
       </c>
       <c r="AG166" t="inlineStr"/>
       <c r="AH166" t="inlineStr"/>
@@ -23852,15 +23852,15 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE167" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF167" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%97%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF167" t="n">
-        <v>2</v>
       </c>
       <c r="AG167" t="inlineStr"/>
       <c r="AH167" t="inlineStr"/>
@@ -23991,15 +23991,15 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE168" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF168" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A2%D7%95%D7%9E%D7%A8-%D7%9E%D7%9C%D7%99-%D7%94%D7%A0%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF168" t="n">
-        <v>2</v>
       </c>
       <c r="AG168" t="inlineStr"/>
       <c r="AH168" t="inlineStr"/>
@@ -24130,15 +24130,15 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE169" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF169" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%93%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF169" t="n">
-        <v>2</v>
       </c>
       <c r="AG169" t="inlineStr"/>
       <c r="AH169" t="inlineStr"/>
@@ -24269,15 +24269,15 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE170" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF170" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%99%D7%AA-%D7%99%D7%A2%D7%A7%D7%91%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF170" t="n">
-        <v>2</v>
       </c>
       <c r="AG170" t="inlineStr"/>
       <c r="AH170" t="inlineStr"/>
@@ -24408,15 +24408,15 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE171" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF171" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8%D7%9C%D7%99-%D7%92%D7%9C%D7%99%D7%A7-%D7%A0%D7%A7%D7%A9/</t>
         </is>
-      </c>
-      <c r="AF171" t="n">
-        <v>2</v>
       </c>
       <c r="AG171" t="inlineStr"/>
       <c r="AH171" t="inlineStr"/>
@@ -24547,15 +24547,15 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE172" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF172" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%90%D7%95%D7%A8-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF172" t="n">
-        <v>2</v>
       </c>
       <c r="AG172" t="inlineStr"/>
       <c r="AH172" t="inlineStr"/>
@@ -24686,15 +24686,15 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE173" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF173" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A4%D7%96-%D7%A8%D7%99%D7%99%D7%9B%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF173" t="n">
-        <v>2</v>
       </c>
       <c r="AG173" t="inlineStr"/>
       <c r="AH173" t="inlineStr"/>
@@ -24825,15 +24825,15 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE174" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF174" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%97%D7%9C-%D7%A4%D7%99%D7%A8%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF174" t="n">
-        <v>2</v>
       </c>
       <c r="AG174" t="inlineStr"/>
       <c r="AH174" t="inlineStr"/>
@@ -24964,15 +24964,15 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE175" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF175" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%AA-%D7%9C%D7%91%D7%99%D7%90/</t>
         </is>
-      </c>
-      <c r="AF175" t="n">
-        <v>2</v>
       </c>
       <c r="AG175" t="inlineStr"/>
       <c r="AH175" t="inlineStr"/>
@@ -25103,15 +25103,15 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE176" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF176" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%96-%D7%A2%D7%96%D7%A8%D7%90/</t>
         </is>
-      </c>
-      <c r="AF176" t="n">
-        <v>2</v>
       </c>
       <c r="AG176" t="inlineStr"/>
       <c r="AH176" t="inlineStr"/>
@@ -25242,15 +25242,15 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE177" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF177" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A0%D7%A0%D7%94-%D7%95%D7%99%D7%A8%D7%A6%D7%91%D7%95%D7%A8%D7%92%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF177" t="n">
-        <v>2</v>
       </c>
       <c r="AG177" t="inlineStr"/>
       <c r="AH177" t="inlineStr"/>
@@ -25381,15 +25381,15 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE178" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF178" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A2%D7%95%D7%AA-%D7%94%D7%A8%D7%A9%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF178" t="n">
-        <v>2</v>
       </c>
       <c r="AG178" t="inlineStr"/>
       <c r="AH178" t="inlineStr"/>
@@ -25520,15 +25520,15 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE179" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF179" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%99%D7%98%D7%9C-%D7%90%D7%99%D7%A9-%D7%A9%D7%9C%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF179" t="n">
-        <v>2</v>
       </c>
       <c r="AG179" t="inlineStr"/>
       <c r="AH179" t="inlineStr"/>
@@ -25659,15 +25659,15 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE180" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF180" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A7%D7%99-%D7%96%D7%9C%D7%9B%D7%94/</t>
         </is>
-      </c>
-      <c r="AF180" t="n">
-        <v>2</v>
       </c>
       <c r="AG180" t="inlineStr"/>
       <c r="AH180" t="inlineStr"/>
@@ -25798,15 +25798,15 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE181" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF181" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%99%D7%A0%D7%AA-%D7%90%D7%9C%D7%93%D7%A8-%D7%92%D7%A8%D7%A9%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF181" t="n">
-        <v>2</v>
       </c>
       <c r="AG181" t="inlineStr"/>
       <c r="AH181" t="inlineStr"/>
@@ -25937,15 +25937,15 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE182" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF182" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%97%D7%99-%D7%A8%D7%95%D7%96%D7%A0%D7%98%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF182" t="n">
-        <v>2</v>
       </c>
       <c r="AG182" t="inlineStr"/>
       <c r="AH182" t="inlineStr"/>
@@ -26076,15 +26076,15 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE183" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF183" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99-%D7%A4%D7%A8%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF183" t="n">
-        <v>2</v>
       </c>
       <c r="AG183" t="inlineStr"/>
       <c r="AH183" t="inlineStr"/>
@@ -26215,15 +26215,15 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE184" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF184" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%A0%D7%99%D7%AA-%D7%9E%D7%90%D7%99%D7%A8%D7%99/</t>
         </is>
-      </c>
-      <c r="AF184" t="n">
-        <v>2</v>
       </c>
       <c r="AG184" t="inlineStr"/>
       <c r="AH184" t="inlineStr"/>
@@ -26354,15 +26354,15 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE185" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF185" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%9D-%D7%90%D7%9C%D7%9E%D7%95%D7%92/</t>
         </is>
-      </c>
-      <c r="AF185" t="n">
-        <v>2</v>
       </c>
       <c r="AG185" t="inlineStr"/>
       <c r="AH185" t="inlineStr"/>
@@ -26493,15 +26493,15 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE186" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF186" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%95%D7%AA%D7%99-%D7%98%D7%9C-%D7%9E%D7%99%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF186" t="n">
-        <v>2</v>
       </c>
       <c r="AG186" t="inlineStr"/>
       <c r="AH186" t="inlineStr"/>
@@ -26632,15 +26632,15 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE187" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF187" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%92%D7%99%D7%AA-%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF187" t="n">
-        <v>2</v>
       </c>
       <c r="AG187" t="inlineStr"/>
       <c r="AH187" t="inlineStr"/>
@@ -26771,15 +26771,15 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE188" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF188" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%9C%D7%95%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF188" t="n">
-        <v>2</v>
       </c>
       <c r="AG188" t="inlineStr"/>
       <c r="AH188" t="inlineStr"/>
@@ -26910,15 +26910,15 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE189" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF189" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%94-%D7%A9%D7%97%D7%A8-%D7%91%D7%9F-%D7%93%D7%95%D7%93/</t>
         </is>
-      </c>
-      <c r="AF189" t="n">
-        <v>2</v>
       </c>
       <c r="AG189" t="inlineStr"/>
       <c r="AH189" t="inlineStr"/>
@@ -27049,15 +27049,15 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE190" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF190" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A7%D7%93-%D7%9C%D7%99%D7%91%D7%A0%D7%94/</t>
         </is>
-      </c>
-      <c r="AF190" t="n">
-        <v>2</v>
       </c>
       <c r="AG190" t="inlineStr"/>
       <c r="AH190" t="inlineStr"/>
@@ -27188,15 +27188,15 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE191" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF191" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%A0%D7%94-%D7%A0%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF191" t="n">
-        <v>2</v>
       </c>
       <c r="AG191" t="inlineStr"/>
       <c r="AH191" t="inlineStr"/>
@@ -27327,15 +27327,15 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE192" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE192" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF192" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%A8%D7%95%D7%9F-%D7%96%D7%9C%D7%9E%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF192" t="n">
-        <v>2</v>
       </c>
       <c r="AG192" t="inlineStr"/>
       <c r="AH192" t="inlineStr"/>
@@ -27466,15 +27466,15 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE193" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE193" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF193" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%99-%D7%97%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF193" t="n">
-        <v>2</v>
       </c>
       <c r="AG193" t="inlineStr"/>
       <c r="AH193" t="inlineStr"/>
@@ -27605,15 +27605,15 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE194" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE194" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF194" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%94-%D7%A1%D7%95%D7%A1%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF194" t="n">
-        <v>2</v>
       </c>
       <c r="AG194" t="inlineStr"/>
       <c r="AH194" t="inlineStr"/>
@@ -27744,15 +27744,15 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE195" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF195" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%90%D7%9C-%D7%A8%D7%91%D7%A7%D7%94-%D7%99%D7%A4%D7%94/</t>
         </is>
-      </c>
-      <c r="AF195" t="n">
-        <v>2</v>
       </c>
       <c r="AG195" t="inlineStr"/>
       <c r="AH195" t="inlineStr"/>
@@ -27883,15 +27883,15 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE196" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF196" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%A4%D7%99%D7%99%D7%98%D7%9C%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF196" t="n">
-        <v>2</v>
       </c>
       <c r="AG196" t="inlineStr"/>
       <c r="AH196" t="inlineStr"/>
@@ -28022,15 +28022,15 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE197" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF197" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%95%D7%98%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF197" t="n">
-        <v>2</v>
       </c>
       <c r="AG197" t="inlineStr"/>
       <c r="AH197" t="inlineStr"/>
@@ -28161,15 +28161,15 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE198" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF198" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%92%D7%A8%D7%95%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF198" t="n">
-        <v>2</v>
       </c>
       <c r="AG198" t="inlineStr"/>
       <c r="AH198" t="inlineStr"/>
@@ -28300,15 +28300,15 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE199" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF199" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%99%D7%A8%D7%9C%D7%99-%D7%9C%D7%95%D7%99%D7%98-%D7%93%D7%A8%D7%A1%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF199" t="n">
-        <v>2</v>
       </c>
       <c r="AG199" t="inlineStr"/>
       <c r="AH199" t="inlineStr"/>
@@ -28439,15 +28439,15 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE200" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF200" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%92%D7%95%D7%96%D7%9C%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF200" t="n">
-        <v>2</v>
       </c>
       <c r="AG200" t="inlineStr"/>
       <c r="AH200" t="inlineStr"/>
@@ -28578,15 +28578,15 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE201" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF201" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%94%D7%95%D7%9C%D7%A6%D7%91%D7%A8%D7%92-%D7%97%D7%99%D7%99%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF201" t="n">
-        <v>2</v>
       </c>
       <c r="AG201" t="inlineStr"/>
       <c r="AH201" t="inlineStr"/>
@@ -28717,15 +28717,15 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE202" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF202" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A0%D7%93%D7%9C%D7%91%D7%90%D7%95%D7%9D/</t>
         </is>
-      </c>
-      <c r="AF202" t="n">
-        <v>2</v>
       </c>
       <c r="AG202" t="inlineStr"/>
       <c r="AH202" t="inlineStr"/>
@@ -28856,15 +28856,15 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE203" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF203" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A9%D7%9C%D7%95%D7%9E%D7%99%D7%AA-%D7%9E%D7%A8%D7%A7%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF203" t="n">
-        <v>2</v>
       </c>
       <c r="AG203" t="inlineStr"/>
       <c r="AH203" t="inlineStr"/>
@@ -28995,15 +28995,15 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE204" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF204" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%9E%D7%9C%D7%9B%D7%94-%D7%9C%D7%A0%D7%99%D7%90%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF204" t="n">
-        <v>2</v>
       </c>
       <c r="AG204" t="inlineStr"/>
       <c r="AH204" t="inlineStr"/>
@@ -29134,15 +29134,15 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE205" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF205" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%99%D7%95%D7%9F-%D7%94%D7%9C%D7%A4%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF205" t="n">
-        <v>2</v>
       </c>
       <c r="AG205" t="inlineStr"/>
       <c r="AH205" t="inlineStr"/>
@@ -29273,15 +29273,15 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE206" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF206" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A1%D7%95%D7%A4%D7%99%D7%94-%D7%9E%D7%9C%D7%97%D7%96%D7%99%D7%90%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF206" t="n">
-        <v>2</v>
       </c>
       <c r="AG206" t="inlineStr"/>
       <c r="AH206" t="inlineStr"/>
@@ -29412,15 +29412,15 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE207" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF207" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%9E%D7%99%D7%98%D7%9C%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF207" t="n">
-        <v>2</v>
       </c>
       <c r="AG207" t="inlineStr"/>
       <c r="AH207" t="inlineStr"/>
@@ -29551,15 +29551,15 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE208" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF208" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C-%D7%A6%D7%A0%D7%A6%D7%99%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF208" t="n">
-        <v>2</v>
       </c>
       <c r="AG208" t="inlineStr"/>
       <c r="AH208" t="inlineStr"/>
@@ -29690,15 +29690,15 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE209" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF209" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%91%D7%99%D7%A8%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF209" t="n">
-        <v>2</v>
       </c>
       <c r="AG209" t="inlineStr"/>
       <c r="AH209" t="inlineStr"/>
@@ -29829,15 +29829,15 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE210" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF210" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99-%D7%A4%D7%9C%D7%93/</t>
         </is>
-      </c>
-      <c r="AF210" t="n">
-        <v>2</v>
       </c>
       <c r="AG210" t="inlineStr"/>
       <c r="AH210" t="inlineStr"/>
@@ -29968,15 +29968,15 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE211" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF211" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%9C%D7%99%D7%94-%D7%91%D7%9F-%D7%9E%D7%96%D7%99%D7%90/</t>
         </is>
-      </c>
-      <c r="AF211" t="n">
-        <v>2</v>
       </c>
       <c r="AG211" t="inlineStr"/>
       <c r="AH211" t="inlineStr"/>
@@ -30107,15 +30107,15 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE212" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF212" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%A8-%D7%A4%D7%9C%D7%93%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF212" t="n">
-        <v>3</v>
       </c>
       <c r="AG212" t="inlineStr"/>
       <c r="AH212" t="inlineStr"/>
@@ -30246,15 +30246,15 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE213" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF213" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A9%D7%92%D7%91-%D7%90%D7%A8%D7%96/</t>
         </is>
-      </c>
-      <c r="AF213" t="n">
-        <v>2</v>
       </c>
       <c r="AG213" t="inlineStr"/>
       <c r="AH213" t="inlineStr"/>
@@ -30385,15 +30385,15 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE214" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF214" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99-%D7%A2%D7%95%D7%A4%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF214" t="n">
-        <v>2</v>
       </c>
       <c r="AG214" t="inlineStr"/>
       <c r="AH214" t="inlineStr"/>
@@ -30524,15 +30524,15 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE215" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF215" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%9E%D7%99%D7%9E%D7%94-%D7%A9%D7%A2%D7%A9%D7%95%D7%A2/</t>
         </is>
-      </c>
-      <c r="AF215" t="n">
-        <v>2</v>
       </c>
       <c r="AG215" t="inlineStr"/>
       <c r="AH215" t="inlineStr"/>
@@ -30663,15 +30663,15 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE216" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF216" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%AA%D7%A7%D7%95%D7%94-%D7%A6%D7%93%D7%95%D7%A7/</t>
         </is>
-      </c>
-      <c r="AF216" t="n">
-        <v>3</v>
       </c>
       <c r="AG216" t="inlineStr"/>
       <c r="AH216" t="inlineStr"/>
@@ -30802,15 +30802,15 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE217" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF217" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%98%D7%95%D7%91%D7%94-%D7%99%D7%95%D7%A1%D7%A4%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF217" t="n">
-        <v>2</v>
       </c>
       <c r="AG217" t="inlineStr"/>
       <c r="AH217" t="inlineStr"/>
@@ -30941,15 +30941,15 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE218" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF218" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A6%D7%91%D7%99%D7%94-%D7%9B%D7%94%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF218" t="n">
-        <v>2</v>
       </c>
       <c r="AG218" t="inlineStr"/>
       <c r="AH218" t="inlineStr"/>
@@ -31080,15 +31080,15 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE219" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF219" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A6%D7%95%D7%A4%D7%99%D7%AA-%D7%93%D7%99%D7%A1%D7%98%D7%9C%D7%9E%D7%9F-%D7%9E%D7%99%D7%A8%D7%A7%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF219" t="n">
-        <v>2</v>
       </c>
       <c r="AG219" t="inlineStr"/>
       <c r="AH219" t="inlineStr"/>
@@ -31219,15 +31219,15 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE220" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF220" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%9C%D7%A8%D7%99-%D7%9E%D7%99%D7%9C%D7%94%D7%93%D7%95/</t>
         </is>
-      </c>
-      <c r="AF220" t="n">
-        <v>2</v>
       </c>
       <c r="AG220" t="inlineStr"/>
       <c r="AH220" t="inlineStr"/>
@@ -31358,15 +31358,15 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE221" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF221" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%91%D7%90%D7%A9%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF221" t="n">
-        <v>2</v>
       </c>
       <c r="AG221" t="inlineStr"/>
       <c r="AH221" t="inlineStr"/>
@@ -31497,15 +31497,15 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE222" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF222" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%99%D7%A7%D7%98%D7%95%D7%A8%D7%99%D7%94-%D7%A7%D7%9E%D7%99%D7%A0%D7%A1%D7%A7%D7%99/</t>
         </is>
-      </c>
-      <c r="AF222" t="n">
-        <v>2</v>
       </c>
       <c r="AG222" t="inlineStr"/>
       <c r="AH222" t="inlineStr"/>
@@ -31636,15 +31636,15 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE223" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF223" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A4%D7%90%D7%90-%D7%90%D7%91%D7%95-%D7%90%D7%A1%D7%9E%D7%90%D7%A2%D7%99%D7%9C/</t>
         </is>
-      </c>
-      <c r="AF223" t="n">
-        <v>2</v>
       </c>
       <c r="AG223" t="inlineStr"/>
       <c r="AH223" t="inlineStr"/>
@@ -31775,15 +31775,15 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE224" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF224" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%91%D7%90%D7%93%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF224" t="n">
-        <v>2</v>
       </c>
       <c r="AG224" t="inlineStr"/>
       <c r="AH224" t="inlineStr"/>
@@ -31914,15 +31914,15 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE225" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF225" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%A8%D7%94-%D7%93%D7%95%D7%91%D7%93%D7%91%D7%9F-%D7%92%D7%9C%D7%95%D7%96%D7%9E%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF225" t="n">
-        <v>2</v>
       </c>
       <c r="AG225" t="inlineStr"/>
       <c r="AH225" t="inlineStr"/>
@@ -32053,15 +32053,15 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE226" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF226" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%90%D7%98%D7%99%D7%90%D7%A1/</t>
         </is>
-      </c>
-      <c r="AF226" t="n">
-        <v>2</v>
       </c>
       <c r="AG226" t="inlineStr"/>
       <c r="AH226" t="inlineStr"/>
@@ -32192,15 +32192,15 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE227" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF227" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%93%D7%95%D7%91%D7%A1%D7%98%D7%A8-%D7%93%D7%95%D7%93/</t>
         </is>
-      </c>
-      <c r="AF227" t="n">
-        <v>2</v>
       </c>
       <c r="AG227" t="inlineStr"/>
       <c r="AH227" t="inlineStr"/>
@@ -32331,15 +32331,15 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE228" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF228" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/291/</t>
         </is>
-      </c>
-      <c r="AF228" t="n">
-        <v>2</v>
       </c>
       <c r="AG228" t="inlineStr"/>
       <c r="AH228" t="inlineStr"/>
@@ -32470,15 +32470,15 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE229" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF229" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%92%D7%96%D7%99%D7%AA-%D7%97%D7%92%D7%91%D7%99/</t>
         </is>
-      </c>
-      <c r="AF229" t="n">
-        <v>2</v>
       </c>
       <c r="AG229" t="inlineStr"/>
       <c r="AH229" t="inlineStr"/>
@@ -32609,15 +32609,15 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE230" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF230" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%9B%D7%A6%D7%A0%D7%9C%D7%A1%D7%95%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF230" t="n">
-        <v>2</v>
       </c>
       <c r="AG230" t="inlineStr"/>
       <c r="AH230" t="inlineStr"/>
@@ -32748,15 +32748,15 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE231" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF231" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A4%D7%9C%D7%92/</t>
         </is>
-      </c>
-      <c r="AF231" t="n">
-        <v>2</v>
       </c>
       <c r="AG231" t="inlineStr"/>
       <c r="AH231" t="inlineStr"/>
@@ -32887,15 +32887,15 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE232" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF232" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%A2%D7%9C-%D7%A9%D7%A4%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF232" t="n">
-        <v>2</v>
       </c>
       <c r="AG232" t="inlineStr"/>
       <c r="AH232" t="inlineStr"/>
@@ -33026,15 +33026,15 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE233" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF233" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%90%D7%A0%D7%94-%D7%A4%D7%99%D7%A9%D7%91%D7%99%D7%99%D7%9F/</t>
         </is>
-      </c>
-      <c r="AF233" t="n">
-        <v>2</v>
       </c>
       <c r="AG233" t="inlineStr"/>
       <c r="AH233" t="inlineStr"/>
@@ -33165,15 +33165,15 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE234" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF234" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%9E%D7%95%D7%A8%D7%9C%D7%99/</t>
         </is>
-      </c>
-      <c r="AF234" t="n">
-        <v>2</v>
       </c>
       <c r="AG234" t="inlineStr"/>
       <c r="AH234" t="inlineStr"/>
@@ -33304,15 +33304,15 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE235" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF235" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%94-%D7%A8%D7%95%D7%91/</t>
         </is>
-      </c>
-      <c r="AF235" t="n">
-        <v>2</v>
       </c>
       <c r="AG235" t="inlineStr"/>
       <c r="AH235" t="inlineStr"/>
@@ -33443,15 +33443,15 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE236" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF236" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%A0%D7%99%D7%AA-%D7%9B%D7%A5-%D7%91%D7%A1%D7%98%D7%A7%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF236" t="n">
-        <v>2</v>
       </c>
       <c r="AG236" t="inlineStr"/>
       <c r="AH236" t="inlineStr"/>
@@ -33582,15 +33582,15 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE237" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF237" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A2%D7%9E%D7%99%D7%AA/</t>
         </is>
-      </c>
-      <c r="AF237" t="n">
-        <v>2</v>
       </c>
       <c r="AG237" t="inlineStr"/>
       <c r="AH237" t="inlineStr"/>
@@ -33721,15 +33721,15 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE238" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF238" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%9C%D7%99%D7%94-%D7%A8%D7%91%D7%99%D7%A0%D7%95%D7%91%D7%99%D7%A5/</t>
         </is>
-      </c>
-      <c r="AF238" t="n">
-        <v>2</v>
       </c>
       <c r="AG238" t="inlineStr"/>
       <c r="AH238" t="inlineStr"/>
@@ -33860,15 +33860,15 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE239" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF239" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%99%D7%95%D7%91%D7%9C-%D7%A7%D7%A1%D7%98%D7%99%D7%9F-%D7%9B%D7%94%D7%A0%D7%90/</t>
         </is>
-      </c>
-      <c r="AF239" t="n">
-        <v>2</v>
       </c>
       <c r="AG239" t="inlineStr"/>
       <c r="AH239" t="inlineStr"/>
@@ -33999,15 +33999,15 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE240" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF240" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%95%D7%A8%D7%93-%D7%9C%D7%91/</t>
         </is>
-      </c>
-      <c r="AF240" t="n">
-        <v>2</v>
       </c>
       <c r="AG240" t="inlineStr"/>
       <c r="AH240" t="inlineStr"/>
@@ -34144,15 +34144,15 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>5811366384</v>
-      </c>
-      <c r="AE241" t="inlineStr">
+        <v>17434099152</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF241" t="inlineStr">
         <is>
           <t>https://nefeshachat.co.il/</t>
         </is>
-      </c>
-      <c r="AF241" t="n">
-        <v>2</v>
       </c>
       <c r="AG241" t="inlineStr"/>
       <c r="AH241" t="inlineStr"/>
@@ -34283,15 +34283,15 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE242" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF242" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%97%D7%9F-%D7%9B%D7%A4%D7%99%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF242" t="n">
-        <v>2</v>
       </c>
       <c r="AG242" t="inlineStr"/>
       <c r="AH242" t="inlineStr"/>
@@ -34422,15 +34422,15 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE243" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF243" t="inlineStr">
         <is>
           <t>https://ialp.org.il/counselors/%D7%A8%D7%A9%D7%9C-%D7%98%D7%95%D7%94%D7%A8/</t>
         </is>
-      </c>
-      <c r="AF243" t="n">
-        <v>2</v>
       </c>
       <c r="AG243" t="inlineStr"/>
       <c r="AH243" t="inlineStr"/>
@@ -34561,15 +34561,15 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE244" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF244" t="inlineStr">
         <is>
           <t>https://tzuna-tova.co.il/</t>
         </is>
-      </c>
-      <c r="AF244" t="n">
-        <v>2</v>
       </c>
       <c r="AG244" t="inlineStr"/>
       <c r="AH244" t="inlineStr"/>
@@ -34700,15 +34700,15 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE245" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF245" t="inlineStr">
         <is>
           <t>https://www.shiri-sleep.co.il/</t>
         </is>
-      </c>
-      <c r="AF245" t="n">
-        <v>2</v>
       </c>
       <c r="AG245" t="inlineStr"/>
       <c r="AH245" t="inlineStr"/>
@@ -34847,15 +34847,15 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE246" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF246" t="inlineStr">
         <is>
           <t>https://www.goodnights.co.il/</t>
         </is>
-      </c>
-      <c r="AF246" t="n">
-        <v>2</v>
       </c>
       <c r="AG246" t="inlineStr"/>
       <c r="AH246" t="inlineStr"/>
@@ -34986,15 +34986,15 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE247" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF247" t="inlineStr">
         <is>
           <t>https://tlvmed.co.il/</t>
         </is>
-      </c>
-      <c r="AF247" t="n">
-        <v>2</v>
       </c>
       <c r="AG247" t="inlineStr"/>
       <c r="AH247" t="inlineStr"/>
@@ -35135,15 +35135,15 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>5036466357</v>
-      </c>
-      <c r="AE248" t="inlineStr">
+        <v>15109399071</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF248" t="inlineStr">
         <is>
           <t>https://www.karmel.co.il/%D7%A9%D7%95%D7%A0%D7%95%D7%AA/%D7%94%D7%A9%D7%9C%D7%99%D7%97%D7%95%D7%AA-%D7%94%D7%9E%D7%A9%D7%95%D7%AA%D7%A4%D7%AA-%D7%A9%D7%9C-%D7%93-%D7%A8-%D7%90%D7%95%D7%A4%D7%99%D7%A8-%D7%95%D7%90%D7%9E%D7%A8%D7%99-%D7%A7%D7%93%D7%A8%D7%95%D7%9F</t>
         </is>
-      </c>
-      <c r="AF248" t="n">
-        <v>5</v>
       </c>
       <c r="AG248" t="inlineStr"/>
       <c r="AH248" t="inlineStr"/>
@@ -35274,15 +35274,15 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE249" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF249" t="inlineStr">
         <is>
           <t>https://www.mcra.co.il/</t>
         </is>
-      </c>
-      <c r="AF249" t="n">
-        <v>2</v>
       </c>
       <c r="AG249" t="inlineStr"/>
       <c r="AH249" t="inlineStr"/>
@@ -35413,15 +35413,15 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE250" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF250" t="inlineStr">
         <is>
           <t>https://www.leidaschool.co.il/</t>
         </is>
-      </c>
-      <c r="AF250" t="n">
-        <v>2</v>
       </c>
       <c r="AG250" t="inlineStr"/>
       <c r="AH250" t="inlineStr"/>
@@ -35560,15 +35560,15 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE251" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF251" t="inlineStr">
         <is>
           <t>https://www.tasmc.org.il/lis/lis-units/fertility-intro/ivf/</t>
         </is>
-      </c>
-      <c r="AF251" t="n">
-        <v>5</v>
       </c>
       <c r="AG251" t="inlineStr"/>
       <c r="AH251" t="inlineStr"/>
@@ -35707,15 +35707,15 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE252" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>229</v>
+      </c>
+      <c r="AF252" t="inlineStr">
         <is>
           <t>https://ialp.org.il/lllisrael/</t>
         </is>
-      </c>
-      <c r="AF252" t="n">
-        <v>229</v>
       </c>
       <c r="AG252" t="inlineStr"/>
       <c r="AH252" t="inlineStr"/>
@@ -35856,15 +35856,15 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>5816090304</v>
-      </c>
-      <c r="AE253" t="inlineStr">
+        <v>17448270912</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF253" t="inlineStr">
         <is>
           <t>https://www.eran.org.il/knowledge-center/pregnancy-and-parenthood/</t>
         </is>
-      </c>
-      <c r="AF253" t="n">
-        <v>4</v>
       </c>
       <c r="AG253" t="inlineStr"/>
       <c r="AH253" t="inlineStr"/>
@@ -35995,15 +35995,15 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>4649045868</v>
-      </c>
-      <c r="AE254" t="inlineStr">
+        <v>13947137604</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF254" t="inlineStr">
         <is>
           <t>https://balaolam.co.il/</t>
         </is>
-      </c>
-      <c r="AF254" t="n">
-        <v>2</v>
       </c>
       <c r="AG254" t="inlineStr"/>
       <c r="AH254" t="inlineStr"/>
@@ -36138,15 +36138,15 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>5811307335</v>
-      </c>
-      <c r="AE255" t="inlineStr">
+        <v>17433922005</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF255" t="inlineStr">
         <is>
           <t>https://babyhub.co.il/tools/pregnancy-tracker</t>
         </is>
-      </c>
-      <c r="AF255" t="n">
-        <v>3</v>
       </c>
       <c r="AG255" t="inlineStr"/>
       <c r="AH255" t="inlineStr"/>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,217 +429,217 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>algo_version</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>physician_search_version</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>target_kind</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seed_source</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>license_number</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>seed_type</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>email_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>matched_query</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>extraction_method</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>alternate_emails</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>candidate_count</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>retry_count</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>next_retry_at</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>last_attempt_at</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>search_queries</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>search_errors</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>search_results</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pages_fetched</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>fetch_failures</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>search_provider</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>attempted_urls</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>merged_checkpoint_rows</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>shared_target_count</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>unchanged_search_count</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>identity_url</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>resolution_reason</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>search_fingerprint</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>previous_status</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>verification_review_required</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>resolution_reason</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>search_fingerprint</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>candidate_rank</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>shared_contact</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>send_eligible</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>personalization_safe</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>outreach_scope</t>
         </is>
@@ -750,7 +762,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -905,7 +917,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>41927506254</v>
+        <v>125782518762</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -919,11 +931,11 @@
         </is>
       </c>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AK3" t="b">
+        <v>0</v>
+      </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
         <v>1</v>
@@ -1062,7 +1074,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>28678682124</v>
+        <v>86036046372</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1076,11 +1088,11 @@
         </is>
       </c>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AK4" t="b">
+        <v>0</v>
+      </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
         <v>1</v>
@@ -1217,7 +1229,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1372,7 +1384,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE6" t="n">
         <v>19</v>
@@ -1386,11 +1398,11 @@
         </is>
       </c>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AK6" t="b">
+        <v>0</v>
+      </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
         <v>1</v>
@@ -1527,7 +1539,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1682,7 +1694,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>27980368650</v>
+        <v>83941105950</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1696,11 +1708,11 @@
         </is>
       </c>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AK8" t="b">
+        <v>0</v>
+      </c>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="n">
         <v>1</v>
@@ -1837,7 +1849,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -1991,7 +2003,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2136,7 +2148,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2291,7 +2303,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2436,7 +2448,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2585,7 +2597,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2740,7 +2752,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2754,11 +2766,11 @@
         </is>
       </c>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
+      <c r="AK15" t="b">
+        <v>0</v>
+      </c>
       <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="n">
         <v>2</v>
@@ -2897,7 +2909,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3052,7 +3064,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3066,11 +3078,11 @@
         </is>
       </c>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+      <c r="AK17" t="b">
+        <v>0</v>
+      </c>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="n">
         <v>1</v>
@@ -3209,7 +3221,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3223,11 +3235,11 @@
         </is>
       </c>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
+      <c r="AK18" t="b">
+        <v>0</v>
+      </c>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="n">
         <v>1</v>
@@ -3356,7 +3368,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3509,7 +3521,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3662,7 +3674,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3807,7 +3819,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3952,7 +3964,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4101,7 +4113,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4246,7 +4258,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4395,7 +4407,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4548,7 +4560,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE27" t="n">
         <v>17</v>
@@ -4693,7 +4705,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4838,7 +4850,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4983,7 +4995,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -5136,7 +5148,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5281,7 +5293,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5426,7 +5438,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5571,7 +5583,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5716,7 +5728,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5861,7 +5873,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6006,7 +6018,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6151,7 +6163,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6296,7 +6308,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6441,7 +6453,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6586,7 +6598,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6731,7 +6743,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6876,7 +6888,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7021,7 +7033,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7166,7 +7178,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7311,7 +7323,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7456,7 +7468,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7601,7 +7613,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7746,7 +7758,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7891,7 +7903,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8036,7 +8048,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8181,7 +8193,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8326,7 +8338,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8471,7 +8483,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8616,7 +8628,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8761,7 +8773,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8906,7 +8918,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9051,7 +9063,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9196,7 +9208,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9341,7 +9353,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9486,7 +9498,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9631,7 +9643,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9776,7 +9788,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9921,7 +9933,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10066,7 +10078,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10211,7 +10223,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10356,7 +10368,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10501,7 +10513,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10646,7 +10658,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10791,7 +10803,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10936,7 +10948,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11081,7 +11093,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11226,7 +11238,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11371,7 +11383,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11516,7 +11528,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11661,7 +11673,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11806,7 +11818,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11951,7 +11963,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12096,7 +12108,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12241,7 +12253,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12386,7 +12398,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12531,7 +12543,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12676,7 +12688,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12821,7 +12833,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12966,7 +12978,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13111,7 +13123,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13256,7 +13268,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13401,7 +13413,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13546,7 +13558,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13691,7 +13703,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13836,7 +13848,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13981,7 +13993,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14126,7 +14138,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14271,7 +14283,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14416,7 +14428,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14561,7 +14573,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14706,7 +14718,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14851,7 +14863,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14996,7 +15008,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15141,7 +15153,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15286,7 +15298,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15431,7 +15443,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -15576,7 +15588,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15721,7 +15733,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15866,7 +15878,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16011,7 +16023,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16156,7 +16168,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16301,7 +16313,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16446,7 +16458,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -16591,7 +16603,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16736,7 +16748,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16881,7 +16893,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17026,7 +17038,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17171,7 +17183,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17316,7 +17328,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17461,7 +17473,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -17606,7 +17618,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17751,7 +17763,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17896,7 +17908,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18041,7 +18053,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18186,7 +18198,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18331,7 +18343,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -18476,7 +18488,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -18621,7 +18633,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18766,7 +18778,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18911,7 +18923,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19056,7 +19068,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19201,7 +19213,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19346,7 +19358,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -19491,7 +19503,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -19636,7 +19648,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -19781,7 +19793,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19926,7 +19938,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20071,7 +20083,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20216,7 +20228,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20361,7 +20373,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20506,7 +20518,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20651,7 +20663,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20796,7 +20808,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20941,7 +20953,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21086,7 +21098,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21231,7 +21243,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21376,7 +21388,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21521,7 +21533,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21666,7 +21678,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21811,7 +21823,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21956,7 +21968,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22101,7 +22113,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22246,7 +22258,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22391,7 +22403,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22536,7 +22548,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22681,7 +22693,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22826,7 +22838,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22971,7 +22983,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23116,7 +23128,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23261,7 +23273,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23406,7 +23418,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23551,7 +23563,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23696,7 +23708,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23841,7 +23853,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23986,7 +23998,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24131,7 +24143,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24276,7 +24288,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24421,7 +24433,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24566,7 +24578,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24711,7 +24723,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24856,7 +24868,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25001,7 +25013,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25146,7 +25158,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25291,7 +25303,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25436,7 +25448,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25581,7 +25593,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25726,7 +25738,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25871,7 +25883,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26016,7 +26028,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26161,7 +26173,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -26306,7 +26318,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26451,7 +26463,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26596,7 +26608,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26741,7 +26753,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26886,7 +26898,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27031,7 +27043,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27176,7 +27188,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -27321,7 +27333,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27466,7 +27478,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27611,7 +27623,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27756,7 +27768,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27901,7 +27913,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28046,7 +28058,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28191,7 +28203,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -28336,7 +28348,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28481,7 +28493,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28626,7 +28638,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28771,7 +28783,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28916,7 +28928,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29061,7 +29073,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29206,7 +29218,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -29351,7 +29363,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29496,7 +29508,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29641,7 +29653,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29786,7 +29798,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29931,7 +29943,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -30076,7 +30088,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30221,7 +30233,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -30366,7 +30378,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30511,7 +30523,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30656,7 +30668,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30801,7 +30813,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30946,7 +30958,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -31091,7 +31103,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31236,7 +31248,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -31381,7 +31393,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31526,7 +31538,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31671,7 +31683,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31816,7 +31828,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -31961,7 +31973,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -32106,7 +32118,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32251,7 +32263,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -32396,7 +32408,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -32541,7 +32553,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32686,7 +32698,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32831,7 +32843,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32976,7 +32988,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -33121,7 +33133,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33266,7 +33278,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -33411,7 +33423,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -33556,7 +33568,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33701,7 +33713,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33846,7 +33858,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33991,7 +34003,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -34136,7 +34148,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34281,7 +34293,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -34426,7 +34438,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -34571,7 +34583,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34716,7 +34728,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34861,7 +34873,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -35006,7 +35018,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -35151,7 +35163,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35296,7 +35308,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -35447,7 +35459,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>34868198304</v>
+        <v>104604594912</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -35592,7 +35604,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35737,7 +35749,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35882,7 +35894,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -36027,7 +36039,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -36172,7 +36184,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -36327,7 +36339,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>30218798142</v>
+        <v>90656394426</v>
       </c>
       <c r="AE246" t="n">
         <v>5</v>
@@ -36341,11 +36353,11 @@
         </is>
       </c>
       <c r="AH246" t="inlineStr"/>
-      <c r="AI246" t="b">
-        <v>0</v>
-      </c>
+      <c r="AI246" t="inlineStr"/>
       <c r="AJ246" t="inlineStr"/>
-      <c r="AK246" t="inlineStr"/>
+      <c r="AK246" t="b">
+        <v>0</v>
+      </c>
       <c r="AL246" t="inlineStr"/>
       <c r="AM246" t="n">
         <v>1</v>
@@ -36474,7 +36486,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -36619,7 +36631,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36772,7 +36784,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE249" t="n">
         <v>5</v>
@@ -36925,7 +36937,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE250" t="n">
         <v>229</v>
@@ -37070,7 +37082,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -37225,7 +37237,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>34896541824</v>
+        <v>104689625472</v>
       </c>
       <c r="AE252" t="n">
         <v>4</v>
@@ -37370,7 +37382,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>27894275208</v>
+        <v>83682825624</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -37519,7 +37531,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>34867844010</v>
+        <v>104603532030</v>
       </c>
       <c r="AE254" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>125782518762</v>
+        <v>377347556286</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>86036046372</v>
+        <v>258108139116</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE6" t="n">
         <v>19</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>83941105950</v>
+        <v>251823317850</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE27" t="n">
         <v>17</v>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5438,7 +5438,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6598,7 +6598,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7323,7 +7323,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7613,7 +7613,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8483,7 +8483,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9208,7 +9208,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10223,7 +10223,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10368,7 +10368,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11093,7 +11093,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11238,7 +11238,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11383,7 +11383,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12398,7 +12398,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12833,7 +12833,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13268,7 +13268,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13413,7 +13413,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13848,7 +13848,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14138,7 +14138,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14283,7 +14283,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14718,7 +14718,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14863,7 +14863,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15008,7 +15008,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15298,7 +15298,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15443,7 +15443,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -15588,7 +15588,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15733,7 +15733,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16023,7 +16023,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16168,7 +16168,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16313,7 +16313,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16458,7 +16458,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16748,7 +16748,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17038,7 +17038,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17183,7 +17183,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17473,7 +17473,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -17618,7 +17618,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17763,7 +17763,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18343,7 +18343,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -18488,7 +18488,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -18633,7 +18633,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18923,7 +18923,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19068,7 +19068,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19213,7 +19213,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19358,7 +19358,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -19648,7 +19648,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -19793,7 +19793,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19938,7 +19938,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20083,7 +20083,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20518,7 +20518,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20663,7 +20663,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20808,7 +20808,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21098,7 +21098,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21533,7 +21533,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21678,7 +21678,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21823,7 +21823,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21968,7 +21968,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22113,7 +22113,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22258,7 +22258,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22403,7 +22403,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22548,7 +22548,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22693,7 +22693,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22983,7 +22983,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23128,7 +23128,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23273,7 +23273,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23418,7 +23418,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23563,7 +23563,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23853,7 +23853,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23998,7 +23998,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24143,7 +24143,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24433,7 +24433,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24578,7 +24578,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24723,7 +24723,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24868,7 +24868,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25013,7 +25013,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25158,7 +25158,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25303,7 +25303,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25448,7 +25448,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25738,7 +25738,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25883,7 +25883,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26028,7 +26028,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26173,7 +26173,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -26318,7 +26318,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26463,7 +26463,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26608,7 +26608,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26753,7 +26753,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26898,7 +26898,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27188,7 +27188,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -27333,7 +27333,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27478,7 +27478,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27623,7 +27623,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27768,7 +27768,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27913,7 +27913,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28058,7 +28058,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28203,7 +28203,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -28348,7 +28348,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28493,7 +28493,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28638,7 +28638,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28783,7 +28783,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28928,7 +28928,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29073,7 +29073,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29218,7 +29218,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -29363,7 +29363,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29653,7 +29653,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29798,7 +29798,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29943,7 +29943,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -30088,7 +30088,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30233,7 +30233,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30523,7 +30523,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30668,7 +30668,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30813,7 +30813,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30958,7 +30958,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -31103,7 +31103,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31248,7 +31248,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -31393,7 +31393,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31538,7 +31538,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31828,7 +31828,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -31973,7 +31973,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -32118,7 +32118,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32263,7 +32263,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -32408,7 +32408,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -32553,7 +32553,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32698,7 +32698,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32843,7 +32843,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32988,7 +32988,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -33133,7 +33133,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33278,7 +33278,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -33423,7 +33423,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -33568,7 +33568,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33713,7 +33713,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33858,7 +33858,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -34003,7 +34003,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -34148,7 +34148,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34293,7 +34293,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -34438,7 +34438,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -34583,7 +34583,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34873,7 +34873,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -35018,7 +35018,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -35163,7 +35163,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35308,7 +35308,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -35459,7 +35459,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>104604594912</v>
+        <v>313813784736</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -35604,7 +35604,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35749,7 +35749,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35894,7 +35894,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -36039,7 +36039,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -36184,7 +36184,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -36339,7 +36339,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>90656394426</v>
+        <v>271969183278</v>
       </c>
       <c r="AE246" t="n">
         <v>5</v>
@@ -36486,7 +36486,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -36631,7 +36631,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36784,7 +36784,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE249" t="n">
         <v>5</v>
@@ -36937,7 +36937,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE250" t="n">
         <v>229</v>
@@ -37082,7 +37082,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -37237,7 +37237,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>104689625472</v>
+        <v>314068876416</v>
       </c>
       <c r="AE252" t="n">
         <v>4</v>
@@ -37382,7 +37382,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>83682825624</v>
+        <v>251048476872</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -37531,7 +37531,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>104603532030</v>
+        <v>313810596090</v>
       </c>
       <c r="AE254" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>377347556286</v>
+        <v>1132042668858</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>258108139116</v>
+        <v>774324417348</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE6" t="n">
         <v>19</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>251823317850</v>
+        <v>755469953550</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3819,7 +3819,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE27" t="n">
         <v>17</v>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5438,7 +5438,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6598,7 +6598,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7323,7 +7323,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7613,7 +7613,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8483,7 +8483,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9208,7 +9208,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9498,7 +9498,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10223,7 +10223,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10368,7 +10368,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10513,7 +10513,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11093,7 +11093,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11238,7 +11238,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11383,7 +11383,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11818,7 +11818,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11963,7 +11963,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12108,7 +12108,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12398,7 +12398,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12833,7 +12833,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13268,7 +13268,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13413,7 +13413,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13848,7 +13848,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14138,7 +14138,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14283,7 +14283,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14428,7 +14428,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14718,7 +14718,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14863,7 +14863,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15008,7 +15008,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15298,7 +15298,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15443,7 +15443,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -15588,7 +15588,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15733,7 +15733,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15878,7 +15878,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16023,7 +16023,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16168,7 +16168,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16313,7 +16313,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16458,7 +16458,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16748,7 +16748,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16893,7 +16893,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17038,7 +17038,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17183,7 +17183,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17328,7 +17328,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17473,7 +17473,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -17618,7 +17618,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17763,7 +17763,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17908,7 +17908,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18343,7 +18343,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -18488,7 +18488,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -18633,7 +18633,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18778,7 +18778,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18923,7 +18923,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19068,7 +19068,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19213,7 +19213,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19358,7 +19358,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -19503,7 +19503,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -19648,7 +19648,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -19793,7 +19793,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19938,7 +19938,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20083,7 +20083,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20228,7 +20228,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20518,7 +20518,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20663,7 +20663,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20808,7 +20808,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20953,7 +20953,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21098,7 +21098,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21533,7 +21533,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21678,7 +21678,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21823,7 +21823,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21968,7 +21968,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22113,7 +22113,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22258,7 +22258,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22403,7 +22403,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22548,7 +22548,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22693,7 +22693,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22983,7 +22983,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23128,7 +23128,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23273,7 +23273,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23418,7 +23418,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23563,7 +23563,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23853,7 +23853,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23998,7 +23998,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24143,7 +24143,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24433,7 +24433,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24578,7 +24578,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24723,7 +24723,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24868,7 +24868,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25013,7 +25013,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25158,7 +25158,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25303,7 +25303,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25448,7 +25448,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25593,7 +25593,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25738,7 +25738,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25883,7 +25883,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26028,7 +26028,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26173,7 +26173,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -26318,7 +26318,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26463,7 +26463,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26608,7 +26608,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26753,7 +26753,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26898,7 +26898,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27188,7 +27188,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -27333,7 +27333,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27478,7 +27478,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27623,7 +27623,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27768,7 +27768,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27913,7 +27913,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28058,7 +28058,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28203,7 +28203,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -28348,7 +28348,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28493,7 +28493,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28638,7 +28638,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28783,7 +28783,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28928,7 +28928,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29073,7 +29073,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29218,7 +29218,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -29363,7 +29363,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29508,7 +29508,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29653,7 +29653,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29798,7 +29798,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29943,7 +29943,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -30088,7 +30088,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30233,7 +30233,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30523,7 +30523,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30668,7 +30668,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30813,7 +30813,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30958,7 +30958,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -31103,7 +31103,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31248,7 +31248,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -31393,7 +31393,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31538,7 +31538,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31828,7 +31828,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -31973,7 +31973,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -32118,7 +32118,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32263,7 +32263,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -32408,7 +32408,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -32553,7 +32553,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32698,7 +32698,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32843,7 +32843,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32988,7 +32988,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -33133,7 +33133,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33278,7 +33278,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -33423,7 +33423,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -33568,7 +33568,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33713,7 +33713,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33858,7 +33858,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -34003,7 +34003,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -34148,7 +34148,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34293,7 +34293,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -34438,7 +34438,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -34583,7 +34583,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34728,7 +34728,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34873,7 +34873,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -35018,7 +35018,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -35163,7 +35163,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35308,7 +35308,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -35459,7 +35459,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>313813784736</v>
+        <v>941441354208</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -35604,7 +35604,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35749,7 +35749,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35894,7 +35894,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -36039,7 +36039,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -36184,7 +36184,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -36339,7 +36339,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>271969183278</v>
+        <v>815907549834</v>
       </c>
       <c r="AE246" t="n">
         <v>5</v>
@@ -36486,7 +36486,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -36631,7 +36631,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36784,7 +36784,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE249" t="n">
         <v>5</v>
@@ -36937,7 +36937,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE250" t="n">
         <v>229</v>
@@ -37082,7 +37082,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -37237,7 +37237,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>314068876416</v>
+        <v>942206629248</v>
       </c>
       <c r="AE252" t="n">
         <v>4</v>
@@ -37382,7 +37382,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>251048476872</v>
+        <v>753145430616</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -37531,7 +37531,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>313810596090</v>
+        <v>941431788270</v>
       </c>
       <c r="AE254" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ254"/>
+  <dimension ref="A1:AP254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,30 +616,25 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>previous_candidate</t>
+          <t>candidate_rank</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>candidate_rank</t>
+          <t>shared_contact</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>shared_contact</t>
+          <t>send_eligible</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>send_eligible</t>
+          <t>personalization_safe</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>personalization_safe</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>outreach_scope</t>
         </is>
@@ -762,7 +757,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -779,20 +774,19 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="b">
         <v>1</v>
       </c>
       <c r="AN2" t="b">
         <v>1</v>
       </c>
       <c r="AO2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -917,7 +911,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1132042668858</v>
+        <v>3396128006574</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -936,20 +930,19 @@
       <c r="AK3" t="b">
         <v>0</v>
       </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="n">
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="b">
         <v>1</v>
       </c>
       <c r="AN3" t="b">
         <v>1</v>
       </c>
       <c r="AO3" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -1074,7 +1067,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>774324417348</v>
+        <v>2322973252044</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1093,20 +1086,19 @@
       <c r="AK4" t="b">
         <v>0</v>
       </c>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="n">
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="b">
         <v>1</v>
       </c>
       <c r="AN4" t="b">
         <v>1</v>
       </c>
       <c r="AO4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -1229,7 +1221,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1246,20 +1238,19 @@
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="n">
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="b">
         <v>1</v>
       </c>
       <c r="AN5" t="b">
         <v>1</v>
       </c>
       <c r="AO5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -1384,7 +1375,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE6" t="n">
         <v>19</v>
@@ -1403,20 +1394,19 @@
       <c r="AK6" t="b">
         <v>0</v>
       </c>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="n">
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="b">
         <v>1</v>
       </c>
       <c r="AN6" t="b">
         <v>1</v>
       </c>
       <c r="AO6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -1539,7 +1529,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1556,20 +1546,19 @@
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="n">
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="b">
         <v>1</v>
       </c>
       <c r="AN7" t="b">
         <v>1</v>
       </c>
       <c r="AO7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -1694,7 +1683,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>755469953550</v>
+        <v>2266409860650</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1713,20 +1702,19 @@
       <c r="AK8" t="b">
         <v>0</v>
       </c>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="n">
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="b">
         <v>1</v>
       </c>
       <c r="AN8" t="b">
         <v>1</v>
       </c>
       <c r="AO8" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -1849,7 +1837,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -1866,20 +1854,19 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="n">
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="b">
         <v>1</v>
       </c>
       <c r="AN9" t="b">
         <v>1</v>
       </c>
       <c r="AO9" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -2003,7 +1990,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2020,20 +2007,19 @@
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="n">
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="b">
         <v>1</v>
       </c>
       <c r="AN10" t="b">
         <v>1</v>
       </c>
       <c r="AO10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -2148,7 +2134,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2165,20 +2151,19 @@
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="n">
+      <c r="AL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="b">
         <v>1</v>
       </c>
       <c r="AN11" t="b">
         <v>1</v>
       </c>
       <c r="AO11" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -2303,7 +2288,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>942206629248</v>
+        <v>2826619887744</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2320,20 +2305,19 @@
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="n">
+      <c r="AL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" t="b">
         <v>1</v>
       </c>
       <c r="AN12" t="b">
         <v>1</v>
       </c>
       <c r="AO12" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -2448,7 +2432,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2465,20 +2449,19 @@
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="n">
+      <c r="AL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" t="b">
         <v>1</v>
       </c>
       <c r="AN13" t="b">
         <v>1</v>
       </c>
       <c r="AO13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -2597,7 +2580,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2614,20 +2597,19 @@
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="n">
+      <c r="AL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" t="b">
         <v>1</v>
       </c>
       <c r="AN14" t="b">
         <v>1</v>
       </c>
       <c r="AO14" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -2752,7 +2734,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2771,20 +2753,19 @@
       <c r="AK15" t="b">
         <v>0</v>
       </c>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="n">
+      <c r="AL15" t="n">
         <v>2</v>
       </c>
+      <c r="AM15" t="b">
+        <v>1</v>
+      </c>
       <c r="AN15" t="b">
         <v>1</v>
       </c>
       <c r="AO15" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -2909,7 +2890,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>942206629248</v>
+        <v>2826619887744</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -2926,20 +2907,19 @@
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="n">
+      <c r="AL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" t="b">
         <v>1</v>
       </c>
       <c r="AN16" t="b">
         <v>1</v>
       </c>
       <c r="AO16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -3064,7 +3044,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3083,20 +3063,19 @@
       <c r="AK17" t="b">
         <v>0</v>
       </c>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="n">
+      <c r="AL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" t="b">
         <v>1</v>
       </c>
       <c r="AN17" t="b">
         <v>1</v>
       </c>
       <c r="AO17" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -3221,7 +3200,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3240,20 +3219,19 @@
       <c r="AK18" t="b">
         <v>0</v>
       </c>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="n">
+      <c r="AL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" t="b">
         <v>1</v>
       </c>
       <c r="AN18" t="b">
         <v>1</v>
       </c>
       <c r="AO18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -3368,7 +3346,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3385,20 +3363,19 @@
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="n">
+      <c r="AL19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM19" t="b">
         <v>1</v>
       </c>
       <c r="AN19" t="b">
         <v>1</v>
       </c>
       <c r="AO19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -3521,7 +3498,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3538,20 +3515,19 @@
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="n">
+      <c r="AL20" t="n">
         <v>2</v>
       </c>
+      <c r="AM20" t="b">
+        <v>1</v>
+      </c>
       <c r="AN20" t="b">
         <v>1</v>
       </c>
       <c r="AO20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -3674,7 +3650,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3691,20 +3667,19 @@
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="n">
+      <c r="AL21" t="n">
         <v>3</v>
       </c>
+      <c r="AM21" t="b">
+        <v>1</v>
+      </c>
       <c r="AN21" t="b">
         <v>1</v>
       </c>
       <c r="AO21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -3819,7 +3794,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3836,20 +3811,19 @@
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="n">
+      <c r="AL22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM22" t="b">
         <v>1</v>
       </c>
       <c r="AN22" t="b">
         <v>1</v>
       </c>
       <c r="AO22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -3964,7 +3938,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -3981,20 +3955,19 @@
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="n">
+      <c r="AL23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM23" t="b">
         <v>1</v>
       </c>
       <c r="AN23" t="b">
         <v>1</v>
       </c>
       <c r="AO23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -4113,7 +4086,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4130,20 +4103,19 @@
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="n">
+      <c r="AL24" t="n">
         <v>2</v>
       </c>
+      <c r="AM24" t="b">
+        <v>1</v>
+      </c>
       <c r="AN24" t="b">
         <v>1</v>
       </c>
       <c r="AO24" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -4258,7 +4230,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4275,20 +4247,19 @@
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="n">
+      <c r="AL25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM25" t="b">
         <v>1</v>
       </c>
       <c r="AN25" t="b">
         <v>1</v>
       </c>
       <c r="AO25" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -4407,7 +4378,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4424,20 +4395,19 @@
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="n">
+      <c r="AL26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM26" t="b">
         <v>1</v>
       </c>
       <c r="AN26" t="b">
         <v>1</v>
       </c>
       <c r="AO26" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -4560,7 +4530,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE27" t="n">
         <v>17</v>
@@ -4577,20 +4547,19 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="n">
+      <c r="AL27" t="n">
         <v>2</v>
       </c>
+      <c r="AM27" t="b">
+        <v>1</v>
+      </c>
       <c r="AN27" t="b">
         <v>1</v>
       </c>
       <c r="AO27" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -4705,7 +4674,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4722,20 +4691,19 @@
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="n">
+      <c r="AL28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM28" t="b">
         <v>1</v>
       </c>
       <c r="AN28" t="b">
         <v>1</v>
       </c>
       <c r="AO28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -4850,7 +4818,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4867,20 +4835,19 @@
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="n">
+      <c r="AL29" t="n">
         <v>2</v>
       </c>
+      <c r="AM29" t="b">
+        <v>1</v>
+      </c>
       <c r="AN29" t="b">
         <v>1</v>
       </c>
       <c r="AO29" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -4995,7 +4962,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -5012,20 +4979,19 @@
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="n">
+      <c r="AL30" t="n">
         <v>3</v>
       </c>
+      <c r="AM30" t="b">
+        <v>1</v>
+      </c>
       <c r="AN30" t="b">
         <v>1</v>
       </c>
       <c r="AO30" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -5148,7 +5114,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5165,20 +5131,19 @@
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="n">
+      <c r="AL31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM31" t="b">
         <v>1</v>
       </c>
       <c r="AN31" t="b">
         <v>1</v>
       </c>
       <c r="AO31" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -5293,7 +5258,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5310,20 +5275,19 @@
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="n">
+      <c r="AL32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM32" t="b">
         <v>1</v>
       </c>
       <c r="AN32" t="b">
         <v>1</v>
       </c>
       <c r="AO32" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -5438,7 +5402,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5455,20 +5419,19 @@
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="n">
+      <c r="AL33" t="n">
         <v>3</v>
       </c>
+      <c r="AM33" t="b">
+        <v>1</v>
+      </c>
       <c r="AN33" t="b">
         <v>1</v>
       </c>
       <c r="AO33" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -5583,7 +5546,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5600,20 +5563,19 @@
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="n">
+      <c r="AL34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM34" t="b">
         <v>1</v>
       </c>
       <c r="AN34" t="b">
         <v>1</v>
       </c>
       <c r="AO34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -5728,7 +5690,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5745,20 +5707,19 @@
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="n">
+      <c r="AL35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM35" t="b">
         <v>1</v>
       </c>
       <c r="AN35" t="b">
         <v>1</v>
       </c>
       <c r="AO35" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -5873,7 +5834,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5890,20 +5851,19 @@
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="n">
+      <c r="AL36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM36" t="b">
         <v>1</v>
       </c>
       <c r="AN36" t="b">
         <v>1</v>
       </c>
       <c r="AO36" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -6018,7 +5978,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6035,20 +5995,19 @@
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="n">
+      <c r="AL37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM37" t="b">
         <v>1</v>
       </c>
       <c r="AN37" t="b">
         <v>1</v>
       </c>
       <c r="AO37" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ37" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -6163,7 +6122,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6180,20 +6139,19 @@
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="n">
+      <c r="AL38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM38" t="b">
         <v>1</v>
       </c>
       <c r="AN38" t="b">
         <v>1</v>
       </c>
       <c r="AO38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -6308,7 +6266,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6325,20 +6283,19 @@
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="n">
+      <c r="AL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM39" t="b">
         <v>1</v>
       </c>
       <c r="AN39" t="b">
         <v>1</v>
       </c>
       <c r="AO39" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -6453,7 +6410,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6470,20 +6427,19 @@
       <c r="AI40" t="inlineStr"/>
       <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="n">
+      <c r="AL40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM40" t="b">
         <v>1</v>
       </c>
       <c r="AN40" t="b">
         <v>1</v>
       </c>
       <c r="AO40" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -6598,7 +6554,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6615,20 +6571,19 @@
       <c r="AI41" t="inlineStr"/>
       <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="n">
+      <c r="AL41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM41" t="b">
         <v>1</v>
       </c>
       <c r="AN41" t="b">
         <v>1</v>
       </c>
       <c r="AO41" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -6743,7 +6698,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6760,20 +6715,19 @@
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="n">
+      <c r="AL42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM42" t="b">
         <v>1</v>
       </c>
       <c r="AN42" t="b">
         <v>1</v>
       </c>
       <c r="AO42" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -6888,7 +6842,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6905,20 +6859,19 @@
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="n">
+      <c r="AL43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM43" t="b">
         <v>1</v>
       </c>
       <c r="AN43" t="b">
         <v>1</v>
       </c>
       <c r="AO43" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ43" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -7033,7 +6986,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7050,20 +7003,19 @@
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="n">
+      <c r="AL44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM44" t="b">
         <v>1</v>
       </c>
       <c r="AN44" t="b">
         <v>1</v>
       </c>
       <c r="AO44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ44" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -7178,7 +7130,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7195,20 +7147,19 @@
       <c r="AI45" t="inlineStr"/>
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="n">
+      <c r="AL45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM45" t="b">
         <v>1</v>
       </c>
       <c r="AN45" t="b">
         <v>1</v>
       </c>
       <c r="AO45" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ45" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -7323,7 +7274,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7340,20 +7291,19 @@
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr"/>
       <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="n">
+      <c r="AL46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM46" t="b">
         <v>1</v>
       </c>
       <c r="AN46" t="b">
         <v>1</v>
       </c>
       <c r="AO46" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -7468,7 +7418,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7485,20 +7435,19 @@
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="n">
+      <c r="AL47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM47" t="b">
         <v>1</v>
       </c>
       <c r="AN47" t="b">
         <v>1</v>
       </c>
       <c r="AO47" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ47" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -7613,7 +7562,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7630,20 +7579,19 @@
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="n">
+      <c r="AL48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM48" t="b">
         <v>1</v>
       </c>
       <c r="AN48" t="b">
         <v>1</v>
       </c>
       <c r="AO48" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ48" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -7758,7 +7706,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7775,20 +7723,19 @@
       <c r="AI49" t="inlineStr"/>
       <c r="AJ49" t="inlineStr"/>
       <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="n">
+      <c r="AL49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM49" t="b">
         <v>1</v>
       </c>
       <c r="AN49" t="b">
         <v>1</v>
       </c>
       <c r="AO49" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ49" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -7903,7 +7850,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -7920,20 +7867,19 @@
       <c r="AI50" t="inlineStr"/>
       <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="inlineStr"/>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="n">
+      <c r="AL50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM50" t="b">
         <v>1</v>
       </c>
       <c r="AN50" t="b">
         <v>1</v>
       </c>
       <c r="AO50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ50" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -8048,7 +7994,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8065,20 +8011,19 @@
       <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="n">
+      <c r="AL51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM51" t="b">
         <v>1</v>
       </c>
       <c r="AN51" t="b">
         <v>1</v>
       </c>
       <c r="AO51" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ51" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -8193,7 +8138,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8210,20 +8155,19 @@
       <c r="AI52" t="inlineStr"/>
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="n">
+      <c r="AL52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM52" t="b">
         <v>1</v>
       </c>
       <c r="AN52" t="b">
         <v>1</v>
       </c>
       <c r="AO52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ52" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP52" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -8338,7 +8282,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8355,20 +8299,19 @@
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="n">
+      <c r="AL53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM53" t="b">
         <v>1</v>
       </c>
       <c r="AN53" t="b">
         <v>1</v>
       </c>
       <c r="AO53" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ53" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -8483,7 +8426,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8500,20 +8443,19 @@
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="n">
+      <c r="AL54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM54" t="b">
         <v>1</v>
       </c>
       <c r="AN54" t="b">
         <v>1</v>
       </c>
       <c r="AO54" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ54" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -8628,7 +8570,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8645,20 +8587,19 @@
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="n">
+      <c r="AL55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM55" t="b">
         <v>1</v>
       </c>
       <c r="AN55" t="b">
         <v>1</v>
       </c>
       <c r="AO55" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ55" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -8773,7 +8714,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8790,20 +8731,19 @@
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr"/>
       <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="n">
+      <c r="AL56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM56" t="b">
         <v>1</v>
       </c>
       <c r="AN56" t="b">
         <v>1</v>
       </c>
       <c r="AO56" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ56" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -8918,7 +8858,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -8935,20 +8875,19 @@
       <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr"/>
       <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="n">
+      <c r="AL57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM57" t="b">
         <v>1</v>
       </c>
       <c r="AN57" t="b">
         <v>1</v>
       </c>
       <c r="AO57" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ57" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP57" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -9063,7 +9002,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9080,20 +9019,19 @@
       <c r="AI58" t="inlineStr"/>
       <c r="AJ58" t="inlineStr"/>
       <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="n">
+      <c r="AL58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM58" t="b">
         <v>1</v>
       </c>
       <c r="AN58" t="b">
         <v>1</v>
       </c>
       <c r="AO58" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ58" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP58" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -9208,7 +9146,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9225,20 +9163,19 @@
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="n">
+      <c r="AL59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM59" t="b">
         <v>1</v>
       </c>
       <c r="AN59" t="b">
         <v>1</v>
       </c>
       <c r="AO59" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ59" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP59" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -9353,7 +9290,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9370,20 +9307,19 @@
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="inlineStr"/>
-      <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="n">
+      <c r="AL60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM60" t="b">
         <v>1</v>
       </c>
       <c r="AN60" t="b">
         <v>1</v>
       </c>
       <c r="AO60" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ60" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP60" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -9498,7 +9434,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9515,20 +9451,19 @@
       <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
       <c r="AK61" t="inlineStr"/>
-      <c r="AL61" t="inlineStr"/>
-      <c r="AM61" t="n">
+      <c r="AL61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM61" t="b">
         <v>1</v>
       </c>
       <c r="AN61" t="b">
         <v>1</v>
       </c>
       <c r="AO61" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ61" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP61" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -9643,7 +9578,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9660,20 +9595,19 @@
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
-      <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="n">
+      <c r="AL62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM62" t="b">
         <v>1</v>
       </c>
       <c r="AN62" t="b">
         <v>1</v>
       </c>
       <c r="AO62" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ62" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP62" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -9788,7 +9722,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9805,20 +9739,19 @@
       <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="inlineStr"/>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="n">
+      <c r="AL63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM63" t="b">
         <v>1</v>
       </c>
       <c r="AN63" t="b">
         <v>1</v>
       </c>
       <c r="AO63" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ63" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP63" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -9933,7 +9866,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -9950,20 +9883,19 @@
       <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="inlineStr"/>
-      <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="n">
+      <c r="AL64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM64" t="b">
         <v>1</v>
       </c>
       <c r="AN64" t="b">
         <v>1</v>
       </c>
       <c r="AO64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ64" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP64" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -10078,7 +10010,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10095,20 +10027,19 @@
       <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="inlineStr"/>
-      <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="n">
+      <c r="AL65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM65" t="b">
         <v>1</v>
       </c>
       <c r="AN65" t="b">
         <v>1</v>
       </c>
       <c r="AO65" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ65" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP65" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -10223,7 +10154,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10240,20 +10171,19 @@
       <c r="AI66" t="inlineStr"/>
       <c r="AJ66" t="inlineStr"/>
       <c r="AK66" t="inlineStr"/>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="n">
+      <c r="AL66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM66" t="b">
         <v>1</v>
       </c>
       <c r="AN66" t="b">
         <v>1</v>
       </c>
       <c r="AO66" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ66" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP66" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -10368,7 +10298,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10385,20 +10315,19 @@
       <c r="AI67" t="inlineStr"/>
       <c r="AJ67" t="inlineStr"/>
       <c r="AK67" t="inlineStr"/>
-      <c r="AL67" t="inlineStr"/>
-      <c r="AM67" t="n">
+      <c r="AL67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM67" t="b">
         <v>1</v>
       </c>
       <c r="AN67" t="b">
         <v>1</v>
       </c>
       <c r="AO67" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ67" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP67" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -10513,7 +10442,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10530,20 +10459,19 @@
       <c r="AI68" t="inlineStr"/>
       <c r="AJ68" t="inlineStr"/>
       <c r="AK68" t="inlineStr"/>
-      <c r="AL68" t="inlineStr"/>
-      <c r="AM68" t="n">
+      <c r="AL68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM68" t="b">
         <v>1</v>
       </c>
       <c r="AN68" t="b">
         <v>1</v>
       </c>
       <c r="AO68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ68" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP68" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -10658,7 +10586,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10675,20 +10603,19 @@
       <c r="AI69" t="inlineStr"/>
       <c r="AJ69" t="inlineStr"/>
       <c r="AK69" t="inlineStr"/>
-      <c r="AL69" t="inlineStr"/>
-      <c r="AM69" t="n">
+      <c r="AL69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM69" t="b">
         <v>1</v>
       </c>
       <c r="AN69" t="b">
         <v>1</v>
       </c>
       <c r="AO69" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ69" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP69" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -10803,7 +10730,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10820,20 +10747,19 @@
       <c r="AI70" t="inlineStr"/>
       <c r="AJ70" t="inlineStr"/>
       <c r="AK70" t="inlineStr"/>
-      <c r="AL70" t="inlineStr"/>
-      <c r="AM70" t="n">
+      <c r="AL70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM70" t="b">
         <v>1</v>
       </c>
       <c r="AN70" t="b">
         <v>1</v>
       </c>
       <c r="AO70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ70" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP70" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -10948,7 +10874,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -10965,20 +10891,19 @@
       <c r="AI71" t="inlineStr"/>
       <c r="AJ71" t="inlineStr"/>
       <c r="AK71" t="inlineStr"/>
-      <c r="AL71" t="inlineStr"/>
-      <c r="AM71" t="n">
+      <c r="AL71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM71" t="b">
         <v>1</v>
       </c>
       <c r="AN71" t="b">
         <v>1</v>
       </c>
       <c r="AO71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ71" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP71" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -11093,7 +11018,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11110,20 +11035,19 @@
       <c r="AI72" t="inlineStr"/>
       <c r="AJ72" t="inlineStr"/>
       <c r="AK72" t="inlineStr"/>
-      <c r="AL72" t="inlineStr"/>
-      <c r="AM72" t="n">
+      <c r="AL72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM72" t="b">
         <v>1</v>
       </c>
       <c r="AN72" t="b">
         <v>1</v>
       </c>
       <c r="AO72" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ72" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP72" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -11238,7 +11162,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11255,20 +11179,19 @@
       <c r="AI73" t="inlineStr"/>
       <c r="AJ73" t="inlineStr"/>
       <c r="AK73" t="inlineStr"/>
-      <c r="AL73" t="inlineStr"/>
-      <c r="AM73" t="n">
+      <c r="AL73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM73" t="b">
         <v>1</v>
       </c>
       <c r="AN73" t="b">
         <v>1</v>
       </c>
       <c r="AO73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ73" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP73" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -11383,7 +11306,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11400,20 +11323,19 @@
       <c r="AI74" t="inlineStr"/>
       <c r="AJ74" t="inlineStr"/>
       <c r="AK74" t="inlineStr"/>
-      <c r="AL74" t="inlineStr"/>
-      <c r="AM74" t="n">
+      <c r="AL74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM74" t="b">
         <v>1</v>
       </c>
       <c r="AN74" t="b">
         <v>1</v>
       </c>
       <c r="AO74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ74" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP74" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -11528,7 +11450,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11545,20 +11467,19 @@
       <c r="AI75" t="inlineStr"/>
       <c r="AJ75" t="inlineStr"/>
       <c r="AK75" t="inlineStr"/>
-      <c r="AL75" t="inlineStr"/>
-      <c r="AM75" t="n">
+      <c r="AL75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM75" t="b">
         <v>1</v>
       </c>
       <c r="AN75" t="b">
         <v>1</v>
       </c>
       <c r="AO75" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ75" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP75" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -11673,7 +11594,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11690,20 +11611,19 @@
       <c r="AI76" t="inlineStr"/>
       <c r="AJ76" t="inlineStr"/>
       <c r="AK76" t="inlineStr"/>
-      <c r="AL76" t="inlineStr"/>
-      <c r="AM76" t="n">
+      <c r="AL76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM76" t="b">
         <v>1</v>
       </c>
       <c r="AN76" t="b">
         <v>1</v>
       </c>
       <c r="AO76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ76" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP76" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -11818,7 +11738,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11835,20 +11755,19 @@
       <c r="AI77" t="inlineStr"/>
       <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="inlineStr"/>
-      <c r="AL77" t="inlineStr"/>
-      <c r="AM77" t="n">
+      <c r="AL77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM77" t="b">
         <v>1</v>
       </c>
       <c r="AN77" t="b">
         <v>1</v>
       </c>
       <c r="AO77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ77" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP77" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -11963,7 +11882,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -11980,20 +11899,19 @@
       <c r="AI78" t="inlineStr"/>
       <c r="AJ78" t="inlineStr"/>
       <c r="AK78" t="inlineStr"/>
-      <c r="AL78" t="inlineStr"/>
-      <c r="AM78" t="n">
+      <c r="AL78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM78" t="b">
         <v>1</v>
       </c>
       <c r="AN78" t="b">
         <v>1</v>
       </c>
       <c r="AO78" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ78" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP78" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -12108,7 +12026,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12125,20 +12043,19 @@
       <c r="AI79" t="inlineStr"/>
       <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="inlineStr"/>
-      <c r="AL79" t="inlineStr"/>
-      <c r="AM79" t="n">
+      <c r="AL79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM79" t="b">
         <v>1</v>
       </c>
       <c r="AN79" t="b">
         <v>1</v>
       </c>
       <c r="AO79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ79" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP79" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -12253,7 +12170,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12270,20 +12187,19 @@
       <c r="AI80" t="inlineStr"/>
       <c r="AJ80" t="inlineStr"/>
       <c r="AK80" t="inlineStr"/>
-      <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="n">
+      <c r="AL80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM80" t="b">
         <v>1</v>
       </c>
       <c r="AN80" t="b">
         <v>1</v>
       </c>
       <c r="AO80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ80" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP80" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -12398,7 +12314,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12415,20 +12331,19 @@
       <c r="AI81" t="inlineStr"/>
       <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="inlineStr"/>
-      <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="n">
+      <c r="AL81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM81" t="b">
         <v>1</v>
       </c>
       <c r="AN81" t="b">
         <v>1</v>
       </c>
       <c r="AO81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ81" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP81" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -12543,7 +12458,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12560,20 +12475,19 @@
       <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
-      <c r="AL82" t="inlineStr"/>
-      <c r="AM82" t="n">
+      <c r="AL82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM82" t="b">
         <v>1</v>
       </c>
       <c r="AN82" t="b">
         <v>1</v>
       </c>
       <c r="AO82" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ82" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP82" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -12688,7 +12602,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12705,20 +12619,19 @@
       <c r="AI83" t="inlineStr"/>
       <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="inlineStr"/>
-      <c r="AL83" t="inlineStr"/>
-      <c r="AM83" t="n">
+      <c r="AL83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM83" t="b">
         <v>1</v>
       </c>
       <c r="AN83" t="b">
         <v>1</v>
       </c>
       <c r="AO83" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ83" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP83" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -12833,7 +12746,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12850,20 +12763,19 @@
       <c r="AI84" t="inlineStr"/>
       <c r="AJ84" t="inlineStr"/>
       <c r="AK84" t="inlineStr"/>
-      <c r="AL84" t="inlineStr"/>
-      <c r="AM84" t="n">
+      <c r="AL84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM84" t="b">
         <v>1</v>
       </c>
       <c r="AN84" t="b">
         <v>1</v>
       </c>
       <c r="AO84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ84" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP84" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -12978,7 +12890,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -12995,20 +12907,19 @@
       <c r="AI85" t="inlineStr"/>
       <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="inlineStr"/>
-      <c r="AL85" t="inlineStr"/>
-      <c r="AM85" t="n">
+      <c r="AL85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM85" t="b">
         <v>1</v>
       </c>
       <c r="AN85" t="b">
         <v>1</v>
       </c>
       <c r="AO85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ85" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP85" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -13123,7 +13034,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13140,20 +13051,19 @@
       <c r="AI86" t="inlineStr"/>
       <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="inlineStr"/>
-      <c r="AL86" t="inlineStr"/>
-      <c r="AM86" t="n">
+      <c r="AL86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM86" t="b">
         <v>1</v>
       </c>
       <c r="AN86" t="b">
         <v>1</v>
       </c>
       <c r="AO86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ86" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP86" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -13268,7 +13178,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13285,20 +13195,19 @@
       <c r="AI87" t="inlineStr"/>
       <c r="AJ87" t="inlineStr"/>
       <c r="AK87" t="inlineStr"/>
-      <c r="AL87" t="inlineStr"/>
-      <c r="AM87" t="n">
+      <c r="AL87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM87" t="b">
         <v>1</v>
       </c>
       <c r="AN87" t="b">
         <v>1</v>
       </c>
       <c r="AO87" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ87" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP87" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -13413,7 +13322,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13430,20 +13339,19 @@
       <c r="AI88" t="inlineStr"/>
       <c r="AJ88" t="inlineStr"/>
       <c r="AK88" t="inlineStr"/>
-      <c r="AL88" t="inlineStr"/>
-      <c r="AM88" t="n">
+      <c r="AL88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM88" t="b">
         <v>1</v>
       </c>
       <c r="AN88" t="b">
         <v>1</v>
       </c>
       <c r="AO88" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ88" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP88" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -13558,7 +13466,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13575,20 +13483,19 @@
       <c r="AI89" t="inlineStr"/>
       <c r="AJ89" t="inlineStr"/>
       <c r="AK89" t="inlineStr"/>
-      <c r="AL89" t="inlineStr"/>
-      <c r="AM89" t="n">
+      <c r="AL89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM89" t="b">
         <v>1</v>
       </c>
       <c r="AN89" t="b">
         <v>1</v>
       </c>
       <c r="AO89" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ89" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP89" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -13703,7 +13610,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13720,20 +13627,19 @@
       <c r="AI90" t="inlineStr"/>
       <c r="AJ90" t="inlineStr"/>
       <c r="AK90" t="inlineStr"/>
-      <c r="AL90" t="inlineStr"/>
-      <c r="AM90" t="n">
+      <c r="AL90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM90" t="b">
         <v>1</v>
       </c>
       <c r="AN90" t="b">
         <v>1</v>
       </c>
       <c r="AO90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ90" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP90" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -13848,7 +13754,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13865,20 +13771,19 @@
       <c r="AI91" t="inlineStr"/>
       <c r="AJ91" t="inlineStr"/>
       <c r="AK91" t="inlineStr"/>
-      <c r="AL91" t="inlineStr"/>
-      <c r="AM91" t="n">
+      <c r="AL91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM91" t="b">
         <v>1</v>
       </c>
       <c r="AN91" t="b">
         <v>1</v>
       </c>
       <c r="AO91" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ91" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP91" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -13993,7 +13898,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14010,20 +13915,19 @@
       <c r="AI92" t="inlineStr"/>
       <c r="AJ92" t="inlineStr"/>
       <c r="AK92" t="inlineStr"/>
-      <c r="AL92" t="inlineStr"/>
-      <c r="AM92" t="n">
+      <c r="AL92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM92" t="b">
         <v>1</v>
       </c>
       <c r="AN92" t="b">
         <v>1</v>
       </c>
       <c r="AO92" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ92" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP92" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -14138,7 +14042,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14155,20 +14059,19 @@
       <c r="AI93" t="inlineStr"/>
       <c r="AJ93" t="inlineStr"/>
       <c r="AK93" t="inlineStr"/>
-      <c r="AL93" t="inlineStr"/>
-      <c r="AM93" t="n">
+      <c r="AL93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM93" t="b">
         <v>1</v>
       </c>
       <c r="AN93" t="b">
         <v>1</v>
       </c>
       <c r="AO93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ93" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP93" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -14283,7 +14186,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14300,20 +14203,19 @@
       <c r="AI94" t="inlineStr"/>
       <c r="AJ94" t="inlineStr"/>
       <c r="AK94" t="inlineStr"/>
-      <c r="AL94" t="inlineStr"/>
-      <c r="AM94" t="n">
+      <c r="AL94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM94" t="b">
         <v>1</v>
       </c>
       <c r="AN94" t="b">
         <v>1</v>
       </c>
       <c r="AO94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ94" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP94" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -14428,7 +14330,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14445,20 +14347,19 @@
       <c r="AI95" t="inlineStr"/>
       <c r="AJ95" t="inlineStr"/>
       <c r="AK95" t="inlineStr"/>
-      <c r="AL95" t="inlineStr"/>
-      <c r="AM95" t="n">
+      <c r="AL95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM95" t="b">
         <v>1</v>
       </c>
       <c r="AN95" t="b">
         <v>1</v>
       </c>
       <c r="AO95" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ95" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP95" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -14573,7 +14474,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14590,20 +14491,19 @@
       <c r="AI96" t="inlineStr"/>
       <c r="AJ96" t="inlineStr"/>
       <c r="AK96" t="inlineStr"/>
-      <c r="AL96" t="inlineStr"/>
-      <c r="AM96" t="n">
+      <c r="AL96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM96" t="b">
         <v>1</v>
       </c>
       <c r="AN96" t="b">
         <v>1</v>
       </c>
       <c r="AO96" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ96" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP96" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -14718,7 +14618,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14735,20 +14635,19 @@
       <c r="AI97" t="inlineStr"/>
       <c r="AJ97" t="inlineStr"/>
       <c r="AK97" t="inlineStr"/>
-      <c r="AL97" t="inlineStr"/>
-      <c r="AM97" t="n">
+      <c r="AL97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM97" t="b">
         <v>1</v>
       </c>
       <c r="AN97" t="b">
         <v>1</v>
       </c>
       <c r="AO97" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP97" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ97" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP97" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -14863,7 +14762,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14880,20 +14779,19 @@
       <c r="AI98" t="inlineStr"/>
       <c r="AJ98" t="inlineStr"/>
       <c r="AK98" t="inlineStr"/>
-      <c r="AL98" t="inlineStr"/>
-      <c r="AM98" t="n">
+      <c r="AL98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM98" t="b">
         <v>1</v>
       </c>
       <c r="AN98" t="b">
         <v>1</v>
       </c>
       <c r="AO98" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP98" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ98" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP98" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -15008,7 +14906,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15025,20 +14923,19 @@
       <c r="AI99" t="inlineStr"/>
       <c r="AJ99" t="inlineStr"/>
       <c r="AK99" t="inlineStr"/>
-      <c r="AL99" t="inlineStr"/>
-      <c r="AM99" t="n">
+      <c r="AL99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM99" t="b">
         <v>1</v>
       </c>
       <c r="AN99" t="b">
         <v>1</v>
       </c>
       <c r="AO99" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ99" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP99" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -15153,7 +15050,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15170,20 +15067,19 @@
       <c r="AI100" t="inlineStr"/>
       <c r="AJ100" t="inlineStr"/>
       <c r="AK100" t="inlineStr"/>
-      <c r="AL100" t="inlineStr"/>
-      <c r="AM100" t="n">
+      <c r="AL100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM100" t="b">
         <v>1</v>
       </c>
       <c r="AN100" t="b">
         <v>1</v>
       </c>
       <c r="AO100" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP100" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ100" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP100" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -15298,7 +15194,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15315,20 +15211,19 @@
       <c r="AI101" t="inlineStr"/>
       <c r="AJ101" t="inlineStr"/>
       <c r="AK101" t="inlineStr"/>
-      <c r="AL101" t="inlineStr"/>
-      <c r="AM101" t="n">
+      <c r="AL101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM101" t="b">
         <v>1</v>
       </c>
       <c r="AN101" t="b">
         <v>1</v>
       </c>
       <c r="AO101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP101" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ101" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP101" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -15443,7 +15338,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -15460,20 +15355,19 @@
       <c r="AI102" t="inlineStr"/>
       <c r="AJ102" t="inlineStr"/>
       <c r="AK102" t="inlineStr"/>
-      <c r="AL102" t="inlineStr"/>
-      <c r="AM102" t="n">
+      <c r="AL102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM102" t="b">
         <v>1</v>
       </c>
       <c r="AN102" t="b">
         <v>1</v>
       </c>
       <c r="AO102" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP102" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ102" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP102" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -15588,7 +15482,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15605,20 +15499,19 @@
       <c r="AI103" t="inlineStr"/>
       <c r="AJ103" t="inlineStr"/>
       <c r="AK103" t="inlineStr"/>
-      <c r="AL103" t="inlineStr"/>
-      <c r="AM103" t="n">
+      <c r="AL103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM103" t="b">
         <v>1</v>
       </c>
       <c r="AN103" t="b">
         <v>1</v>
       </c>
       <c r="AO103" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP103" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ103" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP103" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -15733,7 +15626,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15750,20 +15643,19 @@
       <c r="AI104" t="inlineStr"/>
       <c r="AJ104" t="inlineStr"/>
       <c r="AK104" t="inlineStr"/>
-      <c r="AL104" t="inlineStr"/>
-      <c r="AM104" t="n">
+      <c r="AL104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM104" t="b">
         <v>1</v>
       </c>
       <c r="AN104" t="b">
         <v>1</v>
       </c>
       <c r="AO104" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP104" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ104" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP104" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -15878,7 +15770,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15895,20 +15787,19 @@
       <c r="AI105" t="inlineStr"/>
       <c r="AJ105" t="inlineStr"/>
       <c r="AK105" t="inlineStr"/>
-      <c r="AL105" t="inlineStr"/>
-      <c r="AM105" t="n">
+      <c r="AL105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM105" t="b">
         <v>1</v>
       </c>
       <c r="AN105" t="b">
         <v>1</v>
       </c>
       <c r="AO105" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP105" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ105" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP105" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -16023,7 +15914,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16040,20 +15931,19 @@
       <c r="AI106" t="inlineStr"/>
       <c r="AJ106" t="inlineStr"/>
       <c r="AK106" t="inlineStr"/>
-      <c r="AL106" t="inlineStr"/>
-      <c r="AM106" t="n">
+      <c r="AL106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM106" t="b">
         <v>1</v>
       </c>
       <c r="AN106" t="b">
         <v>1</v>
       </c>
       <c r="AO106" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP106" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ106" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP106" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -16168,7 +16058,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16185,20 +16075,19 @@
       <c r="AI107" t="inlineStr"/>
       <c r="AJ107" t="inlineStr"/>
       <c r="AK107" t="inlineStr"/>
-      <c r="AL107" t="inlineStr"/>
-      <c r="AM107" t="n">
+      <c r="AL107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM107" t="b">
         <v>1</v>
       </c>
       <c r="AN107" t="b">
         <v>1</v>
       </c>
       <c r="AO107" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP107" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ107" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP107" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -16313,7 +16202,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16330,20 +16219,19 @@
       <c r="AI108" t="inlineStr"/>
       <c r="AJ108" t="inlineStr"/>
       <c r="AK108" t="inlineStr"/>
-      <c r="AL108" t="inlineStr"/>
-      <c r="AM108" t="n">
+      <c r="AL108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM108" t="b">
         <v>1</v>
       </c>
       <c r="AN108" t="b">
         <v>1</v>
       </c>
       <c r="AO108" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ108" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP108" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -16458,7 +16346,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -16475,20 +16363,19 @@
       <c r="AI109" t="inlineStr"/>
       <c r="AJ109" t="inlineStr"/>
       <c r="AK109" t="inlineStr"/>
-      <c r="AL109" t="inlineStr"/>
-      <c r="AM109" t="n">
+      <c r="AL109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM109" t="b">
         <v>1</v>
       </c>
       <c r="AN109" t="b">
         <v>1</v>
       </c>
       <c r="AO109" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ109" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP109" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -16603,7 +16490,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16620,20 +16507,19 @@
       <c r="AI110" t="inlineStr"/>
       <c r="AJ110" t="inlineStr"/>
       <c r="AK110" t="inlineStr"/>
-      <c r="AL110" t="inlineStr"/>
-      <c r="AM110" t="n">
+      <c r="AL110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM110" t="b">
         <v>1</v>
       </c>
       <c r="AN110" t="b">
         <v>1</v>
       </c>
       <c r="AO110" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ110" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP110" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -16748,7 +16634,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16765,20 +16651,19 @@
       <c r="AI111" t="inlineStr"/>
       <c r="AJ111" t="inlineStr"/>
       <c r="AK111" t="inlineStr"/>
-      <c r="AL111" t="inlineStr"/>
-      <c r="AM111" t="n">
+      <c r="AL111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM111" t="b">
         <v>1</v>
       </c>
       <c r="AN111" t="b">
         <v>1</v>
       </c>
       <c r="AO111" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP111" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ111" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP111" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -16893,7 +16778,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16910,20 +16795,19 @@
       <c r="AI112" t="inlineStr"/>
       <c r="AJ112" t="inlineStr"/>
       <c r="AK112" t="inlineStr"/>
-      <c r="AL112" t="inlineStr"/>
-      <c r="AM112" t="n">
+      <c r="AL112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM112" t="b">
         <v>1</v>
       </c>
       <c r="AN112" t="b">
         <v>1</v>
       </c>
       <c r="AO112" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP112" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ112" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP112" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -17038,7 +16922,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17055,20 +16939,19 @@
       <c r="AI113" t="inlineStr"/>
       <c r="AJ113" t="inlineStr"/>
       <c r="AK113" t="inlineStr"/>
-      <c r="AL113" t="inlineStr"/>
-      <c r="AM113" t="n">
+      <c r="AL113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM113" t="b">
         <v>1</v>
       </c>
       <c r="AN113" t="b">
         <v>1</v>
       </c>
       <c r="AO113" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP113" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ113" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP113" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -17183,7 +17066,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17200,20 +17083,19 @@
       <c r="AI114" t="inlineStr"/>
       <c r="AJ114" t="inlineStr"/>
       <c r="AK114" t="inlineStr"/>
-      <c r="AL114" t="inlineStr"/>
-      <c r="AM114" t="n">
+      <c r="AL114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM114" t="b">
         <v>1</v>
       </c>
       <c r="AN114" t="b">
         <v>1</v>
       </c>
       <c r="AO114" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP114" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ114" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP114" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -17328,7 +17210,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17345,20 +17227,19 @@
       <c r="AI115" t="inlineStr"/>
       <c r="AJ115" t="inlineStr"/>
       <c r="AK115" t="inlineStr"/>
-      <c r="AL115" t="inlineStr"/>
-      <c r="AM115" t="n">
+      <c r="AL115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM115" t="b">
         <v>1</v>
       </c>
       <c r="AN115" t="b">
         <v>1</v>
       </c>
       <c r="AO115" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP115" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ115" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP115" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -17473,7 +17354,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -17490,20 +17371,19 @@
       <c r="AI116" t="inlineStr"/>
       <c r="AJ116" t="inlineStr"/>
       <c r="AK116" t="inlineStr"/>
-      <c r="AL116" t="inlineStr"/>
-      <c r="AM116" t="n">
+      <c r="AL116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM116" t="b">
         <v>1</v>
       </c>
       <c r="AN116" t="b">
         <v>1</v>
       </c>
       <c r="AO116" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP116" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ116" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP116" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -17618,7 +17498,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17635,20 +17515,19 @@
       <c r="AI117" t="inlineStr"/>
       <c r="AJ117" t="inlineStr"/>
       <c r="AK117" t="inlineStr"/>
-      <c r="AL117" t="inlineStr"/>
-      <c r="AM117" t="n">
+      <c r="AL117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM117" t="b">
         <v>1</v>
       </c>
       <c r="AN117" t="b">
         <v>1</v>
       </c>
       <c r="AO117" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP117" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ117" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP117" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -17763,7 +17642,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17780,20 +17659,19 @@
       <c r="AI118" t="inlineStr"/>
       <c r="AJ118" t="inlineStr"/>
       <c r="AK118" t="inlineStr"/>
-      <c r="AL118" t="inlineStr"/>
-      <c r="AM118" t="n">
+      <c r="AL118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM118" t="b">
         <v>1</v>
       </c>
       <c r="AN118" t="b">
         <v>1</v>
       </c>
       <c r="AO118" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP118" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ118" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP118" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -17908,7 +17786,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17925,20 +17803,19 @@
       <c r="AI119" t="inlineStr"/>
       <c r="AJ119" t="inlineStr"/>
       <c r="AK119" t="inlineStr"/>
-      <c r="AL119" t="inlineStr"/>
-      <c r="AM119" t="n">
+      <c r="AL119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM119" t="b">
         <v>1</v>
       </c>
       <c r="AN119" t="b">
         <v>1</v>
       </c>
       <c r="AO119" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP119" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ119" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP119" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -18053,7 +17930,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18070,20 +17947,19 @@
       <c r="AI120" t="inlineStr"/>
       <c r="AJ120" t="inlineStr"/>
       <c r="AK120" t="inlineStr"/>
-      <c r="AL120" t="inlineStr"/>
-      <c r="AM120" t="n">
+      <c r="AL120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM120" t="b">
         <v>1</v>
       </c>
       <c r="AN120" t="b">
         <v>1</v>
       </c>
       <c r="AO120" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP120" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ120" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP120" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -18198,7 +18074,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18215,20 +18091,19 @@
       <c r="AI121" t="inlineStr"/>
       <c r="AJ121" t="inlineStr"/>
       <c r="AK121" t="inlineStr"/>
-      <c r="AL121" t="inlineStr"/>
-      <c r="AM121" t="n">
+      <c r="AL121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM121" t="b">
         <v>1</v>
       </c>
       <c r="AN121" t="b">
         <v>1</v>
       </c>
       <c r="AO121" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP121" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ121" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP121" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -18343,7 +18218,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -18360,20 +18235,19 @@
       <c r="AI122" t="inlineStr"/>
       <c r="AJ122" t="inlineStr"/>
       <c r="AK122" t="inlineStr"/>
-      <c r="AL122" t="inlineStr"/>
-      <c r="AM122" t="n">
+      <c r="AL122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM122" t="b">
         <v>1</v>
       </c>
       <c r="AN122" t="b">
         <v>1</v>
       </c>
       <c r="AO122" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP122" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ122" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP122" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -18488,7 +18362,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -18505,20 +18379,19 @@
       <c r="AI123" t="inlineStr"/>
       <c r="AJ123" t="inlineStr"/>
       <c r="AK123" t="inlineStr"/>
-      <c r="AL123" t="inlineStr"/>
-      <c r="AM123" t="n">
+      <c r="AL123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM123" t="b">
         <v>1</v>
       </c>
       <c r="AN123" t="b">
         <v>1</v>
       </c>
       <c r="AO123" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP123" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ123" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP123" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -18633,7 +18506,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18650,20 +18523,19 @@
       <c r="AI124" t="inlineStr"/>
       <c r="AJ124" t="inlineStr"/>
       <c r="AK124" t="inlineStr"/>
-      <c r="AL124" t="inlineStr"/>
-      <c r="AM124" t="n">
+      <c r="AL124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM124" t="b">
         <v>1</v>
       </c>
       <c r="AN124" t="b">
         <v>1</v>
       </c>
       <c r="AO124" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP124" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ124" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP124" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -18778,7 +18650,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18795,20 +18667,19 @@
       <c r="AI125" t="inlineStr"/>
       <c r="AJ125" t="inlineStr"/>
       <c r="AK125" t="inlineStr"/>
-      <c r="AL125" t="inlineStr"/>
-      <c r="AM125" t="n">
+      <c r="AL125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM125" t="b">
         <v>1</v>
       </c>
       <c r="AN125" t="b">
         <v>1</v>
       </c>
       <c r="AO125" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP125" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ125" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP125" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -18923,7 +18794,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18940,20 +18811,19 @@
       <c r="AI126" t="inlineStr"/>
       <c r="AJ126" t="inlineStr"/>
       <c r="AK126" t="inlineStr"/>
-      <c r="AL126" t="inlineStr"/>
-      <c r="AM126" t="n">
+      <c r="AL126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM126" t="b">
         <v>1</v>
       </c>
       <c r="AN126" t="b">
         <v>1</v>
       </c>
       <c r="AO126" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP126" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ126" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP126" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -19068,7 +18938,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19085,20 +18955,19 @@
       <c r="AI127" t="inlineStr"/>
       <c r="AJ127" t="inlineStr"/>
       <c r="AK127" t="inlineStr"/>
-      <c r="AL127" t="inlineStr"/>
-      <c r="AM127" t="n">
+      <c r="AL127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM127" t="b">
         <v>1</v>
       </c>
       <c r="AN127" t="b">
         <v>1</v>
       </c>
       <c r="AO127" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP127" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ127" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP127" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -19213,7 +19082,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19230,20 +19099,19 @@
       <c r="AI128" t="inlineStr"/>
       <c r="AJ128" t="inlineStr"/>
       <c r="AK128" t="inlineStr"/>
-      <c r="AL128" t="inlineStr"/>
-      <c r="AM128" t="n">
+      <c r="AL128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM128" t="b">
         <v>1</v>
       </c>
       <c r="AN128" t="b">
         <v>1</v>
       </c>
       <c r="AO128" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP128" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ128" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP128" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -19358,7 +19226,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -19375,20 +19243,19 @@
       <c r="AI129" t="inlineStr"/>
       <c r="AJ129" t="inlineStr"/>
       <c r="AK129" t="inlineStr"/>
-      <c r="AL129" t="inlineStr"/>
-      <c r="AM129" t="n">
+      <c r="AL129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM129" t="b">
         <v>1</v>
       </c>
       <c r="AN129" t="b">
         <v>1</v>
       </c>
       <c r="AO129" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP129" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ129" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP129" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -19503,7 +19370,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -19520,20 +19387,19 @@
       <c r="AI130" t="inlineStr"/>
       <c r="AJ130" t="inlineStr"/>
       <c r="AK130" t="inlineStr"/>
-      <c r="AL130" t="inlineStr"/>
-      <c r="AM130" t="n">
+      <c r="AL130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM130" t="b">
         <v>1</v>
       </c>
       <c r="AN130" t="b">
         <v>1</v>
       </c>
       <c r="AO130" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP130" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ130" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP130" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -19648,7 +19514,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -19665,20 +19531,19 @@
       <c r="AI131" t="inlineStr"/>
       <c r="AJ131" t="inlineStr"/>
       <c r="AK131" t="inlineStr"/>
-      <c r="AL131" t="inlineStr"/>
-      <c r="AM131" t="n">
+      <c r="AL131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM131" t="b">
         <v>1</v>
       </c>
       <c r="AN131" t="b">
         <v>1</v>
       </c>
       <c r="AO131" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP131" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ131" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP131" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -19793,7 +19658,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19810,20 +19675,19 @@
       <c r="AI132" t="inlineStr"/>
       <c r="AJ132" t="inlineStr"/>
       <c r="AK132" t="inlineStr"/>
-      <c r="AL132" t="inlineStr"/>
-      <c r="AM132" t="n">
+      <c r="AL132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM132" t="b">
         <v>1</v>
       </c>
       <c r="AN132" t="b">
         <v>1</v>
       </c>
       <c r="AO132" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP132" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ132" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP132" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -19938,7 +19802,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19955,20 +19819,19 @@
       <c r="AI133" t="inlineStr"/>
       <c r="AJ133" t="inlineStr"/>
       <c r="AK133" t="inlineStr"/>
-      <c r="AL133" t="inlineStr"/>
-      <c r="AM133" t="n">
+      <c r="AL133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM133" t="b">
         <v>1</v>
       </c>
       <c r="AN133" t="b">
         <v>1</v>
       </c>
       <c r="AO133" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP133" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ133" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP133" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -20083,7 +19946,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20100,20 +19963,19 @@
       <c r="AI134" t="inlineStr"/>
       <c r="AJ134" t="inlineStr"/>
       <c r="AK134" t="inlineStr"/>
-      <c r="AL134" t="inlineStr"/>
-      <c r="AM134" t="n">
+      <c r="AL134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM134" t="b">
         <v>1</v>
       </c>
       <c r="AN134" t="b">
         <v>1</v>
       </c>
       <c r="AO134" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP134" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ134" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP134" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -20228,7 +20090,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20245,20 +20107,19 @@
       <c r="AI135" t="inlineStr"/>
       <c r="AJ135" t="inlineStr"/>
       <c r="AK135" t="inlineStr"/>
-      <c r="AL135" t="inlineStr"/>
-      <c r="AM135" t="n">
+      <c r="AL135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM135" t="b">
         <v>1</v>
       </c>
       <c r="AN135" t="b">
         <v>1</v>
       </c>
       <c r="AO135" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP135" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ135" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP135" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -20373,7 +20234,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20390,20 +20251,19 @@
       <c r="AI136" t="inlineStr"/>
       <c r="AJ136" t="inlineStr"/>
       <c r="AK136" t="inlineStr"/>
-      <c r="AL136" t="inlineStr"/>
-      <c r="AM136" t="n">
+      <c r="AL136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM136" t="b">
         <v>1</v>
       </c>
       <c r="AN136" t="b">
         <v>1</v>
       </c>
       <c r="AO136" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP136" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ136" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP136" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -20518,7 +20378,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20535,20 +20395,19 @@
       <c r="AI137" t="inlineStr"/>
       <c r="AJ137" t="inlineStr"/>
       <c r="AK137" t="inlineStr"/>
-      <c r="AL137" t="inlineStr"/>
-      <c r="AM137" t="n">
+      <c r="AL137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM137" t="b">
         <v>1</v>
       </c>
       <c r="AN137" t="b">
         <v>1</v>
       </c>
       <c r="AO137" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP137" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ137" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP137" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -20663,7 +20522,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20680,20 +20539,19 @@
       <c r="AI138" t="inlineStr"/>
       <c r="AJ138" t="inlineStr"/>
       <c r="AK138" t="inlineStr"/>
-      <c r="AL138" t="inlineStr"/>
-      <c r="AM138" t="n">
+      <c r="AL138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM138" t="b">
         <v>1</v>
       </c>
       <c r="AN138" t="b">
         <v>1</v>
       </c>
       <c r="AO138" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP138" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ138" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP138" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -20808,7 +20666,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20825,20 +20683,19 @@
       <c r="AI139" t="inlineStr"/>
       <c r="AJ139" t="inlineStr"/>
       <c r="AK139" t="inlineStr"/>
-      <c r="AL139" t="inlineStr"/>
-      <c r="AM139" t="n">
+      <c r="AL139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM139" t="b">
         <v>1</v>
       </c>
       <c r="AN139" t="b">
         <v>1</v>
       </c>
       <c r="AO139" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP139" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ139" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP139" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -20953,7 +20810,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20970,20 +20827,19 @@
       <c r="AI140" t="inlineStr"/>
       <c r="AJ140" t="inlineStr"/>
       <c r="AK140" t="inlineStr"/>
-      <c r="AL140" t="inlineStr"/>
-      <c r="AM140" t="n">
+      <c r="AL140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM140" t="b">
         <v>1</v>
       </c>
       <c r="AN140" t="b">
         <v>1</v>
       </c>
       <c r="AO140" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP140" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ140" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP140" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -21098,7 +20954,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21115,20 +20971,19 @@
       <c r="AI141" t="inlineStr"/>
       <c r="AJ141" t="inlineStr"/>
       <c r="AK141" t="inlineStr"/>
-      <c r="AL141" t="inlineStr"/>
-      <c r="AM141" t="n">
+      <c r="AL141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM141" t="b">
         <v>1</v>
       </c>
       <c r="AN141" t="b">
         <v>1</v>
       </c>
       <c r="AO141" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP141" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ141" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP141" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -21243,7 +21098,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21260,20 +21115,19 @@
       <c r="AI142" t="inlineStr"/>
       <c r="AJ142" t="inlineStr"/>
       <c r="AK142" t="inlineStr"/>
-      <c r="AL142" t="inlineStr"/>
-      <c r="AM142" t="n">
+      <c r="AL142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM142" t="b">
         <v>1</v>
       </c>
       <c r="AN142" t="b">
         <v>1</v>
       </c>
       <c r="AO142" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP142" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ142" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP142" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -21388,7 +21242,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21405,20 +21259,19 @@
       <c r="AI143" t="inlineStr"/>
       <c r="AJ143" t="inlineStr"/>
       <c r="AK143" t="inlineStr"/>
-      <c r="AL143" t="inlineStr"/>
-      <c r="AM143" t="n">
+      <c r="AL143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM143" t="b">
         <v>1</v>
       </c>
       <c r="AN143" t="b">
         <v>1</v>
       </c>
       <c r="AO143" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP143" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ143" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP143" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -21533,7 +21386,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21550,20 +21403,19 @@
       <c r="AI144" t="inlineStr"/>
       <c r="AJ144" t="inlineStr"/>
       <c r="AK144" t="inlineStr"/>
-      <c r="AL144" t="inlineStr"/>
-      <c r="AM144" t="n">
+      <c r="AL144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM144" t="b">
         <v>1</v>
       </c>
       <c r="AN144" t="b">
         <v>1</v>
       </c>
       <c r="AO144" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP144" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ144" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP144" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -21678,7 +21530,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21695,20 +21547,19 @@
       <c r="AI145" t="inlineStr"/>
       <c r="AJ145" t="inlineStr"/>
       <c r="AK145" t="inlineStr"/>
-      <c r="AL145" t="inlineStr"/>
-      <c r="AM145" t="n">
+      <c r="AL145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM145" t="b">
         <v>1</v>
       </c>
       <c r="AN145" t="b">
         <v>1</v>
       </c>
       <c r="AO145" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP145" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ145" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP145" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -21823,7 +21674,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21840,20 +21691,19 @@
       <c r="AI146" t="inlineStr"/>
       <c r="AJ146" t="inlineStr"/>
       <c r="AK146" t="inlineStr"/>
-      <c r="AL146" t="inlineStr"/>
-      <c r="AM146" t="n">
+      <c r="AL146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM146" t="b">
         <v>1</v>
       </c>
       <c r="AN146" t="b">
         <v>1</v>
       </c>
       <c r="AO146" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP146" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ146" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP146" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -21968,7 +21818,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21985,20 +21835,19 @@
       <c r="AI147" t="inlineStr"/>
       <c r="AJ147" t="inlineStr"/>
       <c r="AK147" t="inlineStr"/>
-      <c r="AL147" t="inlineStr"/>
-      <c r="AM147" t="n">
+      <c r="AL147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM147" t="b">
         <v>1</v>
       </c>
       <c r="AN147" t="b">
         <v>1</v>
       </c>
       <c r="AO147" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP147" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ147" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP147" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -22113,7 +21962,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22130,20 +21979,19 @@
       <c r="AI148" t="inlineStr"/>
       <c r="AJ148" t="inlineStr"/>
       <c r="AK148" t="inlineStr"/>
-      <c r="AL148" t="inlineStr"/>
-      <c r="AM148" t="n">
+      <c r="AL148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM148" t="b">
         <v>1</v>
       </c>
       <c r="AN148" t="b">
         <v>1</v>
       </c>
       <c r="AO148" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP148" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ148" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP148" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -22258,7 +22106,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22275,20 +22123,19 @@
       <c r="AI149" t="inlineStr"/>
       <c r="AJ149" t="inlineStr"/>
       <c r="AK149" t="inlineStr"/>
-      <c r="AL149" t="inlineStr"/>
-      <c r="AM149" t="n">
+      <c r="AL149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM149" t="b">
         <v>1</v>
       </c>
       <c r="AN149" t="b">
         <v>1</v>
       </c>
       <c r="AO149" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP149" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ149" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP149" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -22403,7 +22250,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22420,20 +22267,19 @@
       <c r="AI150" t="inlineStr"/>
       <c r="AJ150" t="inlineStr"/>
       <c r="AK150" t="inlineStr"/>
-      <c r="AL150" t="inlineStr"/>
-      <c r="AM150" t="n">
+      <c r="AL150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM150" t="b">
         <v>1</v>
       </c>
       <c r="AN150" t="b">
         <v>1</v>
       </c>
       <c r="AO150" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP150" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ150" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP150" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -22548,7 +22394,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22565,20 +22411,19 @@
       <c r="AI151" t="inlineStr"/>
       <c r="AJ151" t="inlineStr"/>
       <c r="AK151" t="inlineStr"/>
-      <c r="AL151" t="inlineStr"/>
-      <c r="AM151" t="n">
+      <c r="AL151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM151" t="b">
         <v>1</v>
       </c>
       <c r="AN151" t="b">
         <v>1</v>
       </c>
       <c r="AO151" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP151" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ151" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP151" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -22693,7 +22538,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22710,20 +22555,19 @@
       <c r="AI152" t="inlineStr"/>
       <c r="AJ152" t="inlineStr"/>
       <c r="AK152" t="inlineStr"/>
-      <c r="AL152" t="inlineStr"/>
-      <c r="AM152" t="n">
+      <c r="AL152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM152" t="b">
         <v>1</v>
       </c>
       <c r="AN152" t="b">
         <v>1</v>
       </c>
       <c r="AO152" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP152" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ152" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP152" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -22838,7 +22682,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22855,20 +22699,19 @@
       <c r="AI153" t="inlineStr"/>
       <c r="AJ153" t="inlineStr"/>
       <c r="AK153" t="inlineStr"/>
-      <c r="AL153" t="inlineStr"/>
-      <c r="AM153" t="n">
+      <c r="AL153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM153" t="b">
         <v>1</v>
       </c>
       <c r="AN153" t="b">
         <v>1</v>
       </c>
       <c r="AO153" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP153" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ153" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP153" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -22983,7 +22826,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23000,20 +22843,19 @@
       <c r="AI154" t="inlineStr"/>
       <c r="AJ154" t="inlineStr"/>
       <c r="AK154" t="inlineStr"/>
-      <c r="AL154" t="inlineStr"/>
-      <c r="AM154" t="n">
+      <c r="AL154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM154" t="b">
         <v>1</v>
       </c>
       <c r="AN154" t="b">
         <v>1</v>
       </c>
       <c r="AO154" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP154" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ154" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP154" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -23128,7 +22970,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23145,20 +22987,19 @@
       <c r="AI155" t="inlineStr"/>
       <c r="AJ155" t="inlineStr"/>
       <c r="AK155" t="inlineStr"/>
-      <c r="AL155" t="inlineStr"/>
-      <c r="AM155" t="n">
+      <c r="AL155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM155" t="b">
         <v>1</v>
       </c>
       <c r="AN155" t="b">
         <v>1</v>
       </c>
       <c r="AO155" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP155" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ155" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP155" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -23273,7 +23114,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23290,20 +23131,19 @@
       <c r="AI156" t="inlineStr"/>
       <c r="AJ156" t="inlineStr"/>
       <c r="AK156" t="inlineStr"/>
-      <c r="AL156" t="inlineStr"/>
-      <c r="AM156" t="n">
+      <c r="AL156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM156" t="b">
         <v>1</v>
       </c>
       <c r="AN156" t="b">
         <v>1</v>
       </c>
       <c r="AO156" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP156" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ156" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP156" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -23418,7 +23258,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23435,20 +23275,19 @@
       <c r="AI157" t="inlineStr"/>
       <c r="AJ157" t="inlineStr"/>
       <c r="AK157" t="inlineStr"/>
-      <c r="AL157" t="inlineStr"/>
-      <c r="AM157" t="n">
+      <c r="AL157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM157" t="b">
         <v>1</v>
       </c>
       <c r="AN157" t="b">
         <v>1</v>
       </c>
       <c r="AO157" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP157" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ157" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP157" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -23563,7 +23402,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23580,20 +23419,19 @@
       <c r="AI158" t="inlineStr"/>
       <c r="AJ158" t="inlineStr"/>
       <c r="AK158" t="inlineStr"/>
-      <c r="AL158" t="inlineStr"/>
-      <c r="AM158" t="n">
+      <c r="AL158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM158" t="b">
         <v>1</v>
       </c>
       <c r="AN158" t="b">
         <v>1</v>
       </c>
       <c r="AO158" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP158" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ158" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP158" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -23708,7 +23546,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23725,20 +23563,19 @@
       <c r="AI159" t="inlineStr"/>
       <c r="AJ159" t="inlineStr"/>
       <c r="AK159" t="inlineStr"/>
-      <c r="AL159" t="inlineStr"/>
-      <c r="AM159" t="n">
+      <c r="AL159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM159" t="b">
         <v>1</v>
       </c>
       <c r="AN159" t="b">
         <v>1</v>
       </c>
       <c r="AO159" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP159" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ159" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP159" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -23853,7 +23690,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23870,20 +23707,19 @@
       <c r="AI160" t="inlineStr"/>
       <c r="AJ160" t="inlineStr"/>
       <c r="AK160" t="inlineStr"/>
-      <c r="AL160" t="inlineStr"/>
-      <c r="AM160" t="n">
+      <c r="AL160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM160" t="b">
         <v>1</v>
       </c>
       <c r="AN160" t="b">
         <v>1</v>
       </c>
       <c r="AO160" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP160" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ160" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP160" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -23998,7 +23834,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24015,20 +23851,19 @@
       <c r="AI161" t="inlineStr"/>
       <c r="AJ161" t="inlineStr"/>
       <c r="AK161" t="inlineStr"/>
-      <c r="AL161" t="inlineStr"/>
-      <c r="AM161" t="n">
+      <c r="AL161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM161" t="b">
         <v>1</v>
       </c>
       <c r="AN161" t="b">
         <v>1</v>
       </c>
       <c r="AO161" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP161" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ161" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP161" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -24143,7 +23978,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24160,20 +23995,19 @@
       <c r="AI162" t="inlineStr"/>
       <c r="AJ162" t="inlineStr"/>
       <c r="AK162" t="inlineStr"/>
-      <c r="AL162" t="inlineStr"/>
-      <c r="AM162" t="n">
+      <c r="AL162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM162" t="b">
         <v>1</v>
       </c>
       <c r="AN162" t="b">
         <v>1</v>
       </c>
       <c r="AO162" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP162" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ162" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP162" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -24288,7 +24122,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24305,20 +24139,19 @@
       <c r="AI163" t="inlineStr"/>
       <c r="AJ163" t="inlineStr"/>
       <c r="AK163" t="inlineStr"/>
-      <c r="AL163" t="inlineStr"/>
-      <c r="AM163" t="n">
+      <c r="AL163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM163" t="b">
         <v>1</v>
       </c>
       <c r="AN163" t="b">
         <v>1</v>
       </c>
       <c r="AO163" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP163" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ163" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP163" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -24433,7 +24266,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24450,20 +24283,19 @@
       <c r="AI164" t="inlineStr"/>
       <c r="AJ164" t="inlineStr"/>
       <c r="AK164" t="inlineStr"/>
-      <c r="AL164" t="inlineStr"/>
-      <c r="AM164" t="n">
+      <c r="AL164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM164" t="b">
         <v>1</v>
       </c>
       <c r="AN164" t="b">
         <v>1</v>
       </c>
       <c r="AO164" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP164" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ164" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP164" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -24578,7 +24410,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24595,20 +24427,19 @@
       <c r="AI165" t="inlineStr"/>
       <c r="AJ165" t="inlineStr"/>
       <c r="AK165" t="inlineStr"/>
-      <c r="AL165" t="inlineStr"/>
-      <c r="AM165" t="n">
+      <c r="AL165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM165" t="b">
         <v>1</v>
       </c>
       <c r="AN165" t="b">
         <v>1</v>
       </c>
       <c r="AO165" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP165" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ165" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP165" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -24723,7 +24554,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24740,20 +24571,19 @@
       <c r="AI166" t="inlineStr"/>
       <c r="AJ166" t="inlineStr"/>
       <c r="AK166" t="inlineStr"/>
-      <c r="AL166" t="inlineStr"/>
-      <c r="AM166" t="n">
+      <c r="AL166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM166" t="b">
         <v>1</v>
       </c>
       <c r="AN166" t="b">
         <v>1</v>
       </c>
       <c r="AO166" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP166" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ166" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP166" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -24868,7 +24698,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24885,20 +24715,19 @@
       <c r="AI167" t="inlineStr"/>
       <c r="AJ167" t="inlineStr"/>
       <c r="AK167" t="inlineStr"/>
-      <c r="AL167" t="inlineStr"/>
-      <c r="AM167" t="n">
+      <c r="AL167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM167" t="b">
         <v>1</v>
       </c>
       <c r="AN167" t="b">
         <v>1</v>
       </c>
       <c r="AO167" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP167" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ167" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP167" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -25013,7 +24842,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25030,20 +24859,19 @@
       <c r="AI168" t="inlineStr"/>
       <c r="AJ168" t="inlineStr"/>
       <c r="AK168" t="inlineStr"/>
-      <c r="AL168" t="inlineStr"/>
-      <c r="AM168" t="n">
+      <c r="AL168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM168" t="b">
         <v>1</v>
       </c>
       <c r="AN168" t="b">
         <v>1</v>
       </c>
       <c r="AO168" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP168" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ168" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP168" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -25158,7 +24986,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25175,20 +25003,19 @@
       <c r="AI169" t="inlineStr"/>
       <c r="AJ169" t="inlineStr"/>
       <c r="AK169" t="inlineStr"/>
-      <c r="AL169" t="inlineStr"/>
-      <c r="AM169" t="n">
+      <c r="AL169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM169" t="b">
         <v>1</v>
       </c>
       <c r="AN169" t="b">
         <v>1</v>
       </c>
       <c r="AO169" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP169" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ169" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP169" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -25303,7 +25130,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25320,20 +25147,19 @@
       <c r="AI170" t="inlineStr"/>
       <c r="AJ170" t="inlineStr"/>
       <c r="AK170" t="inlineStr"/>
-      <c r="AL170" t="inlineStr"/>
-      <c r="AM170" t="n">
+      <c r="AL170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM170" t="b">
         <v>1</v>
       </c>
       <c r="AN170" t="b">
         <v>1</v>
       </c>
       <c r="AO170" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP170" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ170" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP170" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -25448,7 +25274,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25465,20 +25291,19 @@
       <c r="AI171" t="inlineStr"/>
       <c r="AJ171" t="inlineStr"/>
       <c r="AK171" t="inlineStr"/>
-      <c r="AL171" t="inlineStr"/>
-      <c r="AM171" t="n">
+      <c r="AL171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM171" t="b">
         <v>1</v>
       </c>
       <c r="AN171" t="b">
         <v>1</v>
       </c>
       <c r="AO171" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP171" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ171" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP171" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -25593,7 +25418,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25610,20 +25435,19 @@
       <c r="AI172" t="inlineStr"/>
       <c r="AJ172" t="inlineStr"/>
       <c r="AK172" t="inlineStr"/>
-      <c r="AL172" t="inlineStr"/>
-      <c r="AM172" t="n">
+      <c r="AL172" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM172" t="b">
         <v>1</v>
       </c>
       <c r="AN172" t="b">
         <v>1</v>
       </c>
       <c r="AO172" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP172" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ172" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP172" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -25738,7 +25562,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25755,20 +25579,19 @@
       <c r="AI173" t="inlineStr"/>
       <c r="AJ173" t="inlineStr"/>
       <c r="AK173" t="inlineStr"/>
-      <c r="AL173" t="inlineStr"/>
-      <c r="AM173" t="n">
+      <c r="AL173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM173" t="b">
         <v>1</v>
       </c>
       <c r="AN173" t="b">
         <v>1</v>
       </c>
       <c r="AO173" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP173" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ173" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP173" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -25883,7 +25706,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25900,20 +25723,19 @@
       <c r="AI174" t="inlineStr"/>
       <c r="AJ174" t="inlineStr"/>
       <c r="AK174" t="inlineStr"/>
-      <c r="AL174" t="inlineStr"/>
-      <c r="AM174" t="n">
+      <c r="AL174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM174" t="b">
         <v>1</v>
       </c>
       <c r="AN174" t="b">
         <v>1</v>
       </c>
       <c r="AO174" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP174" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ174" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP174" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -26028,7 +25850,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26045,20 +25867,19 @@
       <c r="AI175" t="inlineStr"/>
       <c r="AJ175" t="inlineStr"/>
       <c r="AK175" t="inlineStr"/>
-      <c r="AL175" t="inlineStr"/>
-      <c r="AM175" t="n">
+      <c r="AL175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM175" t="b">
         <v>1</v>
       </c>
       <c r="AN175" t="b">
         <v>1</v>
       </c>
       <c r="AO175" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP175" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ175" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP175" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -26173,7 +25994,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -26190,20 +26011,19 @@
       <c r="AI176" t="inlineStr"/>
       <c r="AJ176" t="inlineStr"/>
       <c r="AK176" t="inlineStr"/>
-      <c r="AL176" t="inlineStr"/>
-      <c r="AM176" t="n">
+      <c r="AL176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM176" t="b">
         <v>1</v>
       </c>
       <c r="AN176" t="b">
         <v>1</v>
       </c>
       <c r="AO176" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP176" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ176" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP176" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -26318,7 +26138,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26335,20 +26155,19 @@
       <c r="AI177" t="inlineStr"/>
       <c r="AJ177" t="inlineStr"/>
       <c r="AK177" t="inlineStr"/>
-      <c r="AL177" t="inlineStr"/>
-      <c r="AM177" t="n">
+      <c r="AL177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM177" t="b">
         <v>1</v>
       </c>
       <c r="AN177" t="b">
         <v>1</v>
       </c>
       <c r="AO177" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP177" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ177" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP177" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -26463,7 +26282,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26480,20 +26299,19 @@
       <c r="AI178" t="inlineStr"/>
       <c r="AJ178" t="inlineStr"/>
       <c r="AK178" t="inlineStr"/>
-      <c r="AL178" t="inlineStr"/>
-      <c r="AM178" t="n">
+      <c r="AL178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM178" t="b">
         <v>1</v>
       </c>
       <c r="AN178" t="b">
         <v>1</v>
       </c>
       <c r="AO178" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP178" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ178" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP178" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -26608,7 +26426,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26625,20 +26443,19 @@
       <c r="AI179" t="inlineStr"/>
       <c r="AJ179" t="inlineStr"/>
       <c r="AK179" t="inlineStr"/>
-      <c r="AL179" t="inlineStr"/>
-      <c r="AM179" t="n">
+      <c r="AL179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM179" t="b">
         <v>1</v>
       </c>
       <c r="AN179" t="b">
         <v>1</v>
       </c>
       <c r="AO179" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP179" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ179" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP179" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -26753,7 +26570,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26770,20 +26587,19 @@
       <c r="AI180" t="inlineStr"/>
       <c r="AJ180" t="inlineStr"/>
       <c r="AK180" t="inlineStr"/>
-      <c r="AL180" t="inlineStr"/>
-      <c r="AM180" t="n">
+      <c r="AL180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM180" t="b">
         <v>1</v>
       </c>
       <c r="AN180" t="b">
         <v>1</v>
       </c>
       <c r="AO180" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP180" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ180" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP180" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -26898,7 +26714,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26915,20 +26731,19 @@
       <c r="AI181" t="inlineStr"/>
       <c r="AJ181" t="inlineStr"/>
       <c r="AK181" t="inlineStr"/>
-      <c r="AL181" t="inlineStr"/>
-      <c r="AM181" t="n">
+      <c r="AL181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM181" t="b">
         <v>1</v>
       </c>
       <c r="AN181" t="b">
         <v>1</v>
       </c>
       <c r="AO181" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP181" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ181" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP181" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -27043,7 +26858,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27060,20 +26875,19 @@
       <c r="AI182" t="inlineStr"/>
       <c r="AJ182" t="inlineStr"/>
       <c r="AK182" t="inlineStr"/>
-      <c r="AL182" t="inlineStr"/>
-      <c r="AM182" t="n">
+      <c r="AL182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM182" t="b">
         <v>1</v>
       </c>
       <c r="AN182" t="b">
         <v>1</v>
       </c>
       <c r="AO182" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP182" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ182" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP182" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -27188,7 +27002,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -27205,20 +27019,19 @@
       <c r="AI183" t="inlineStr"/>
       <c r="AJ183" t="inlineStr"/>
       <c r="AK183" t="inlineStr"/>
-      <c r="AL183" t="inlineStr"/>
-      <c r="AM183" t="n">
+      <c r="AL183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM183" t="b">
         <v>1</v>
       </c>
       <c r="AN183" t="b">
         <v>1</v>
       </c>
       <c r="AO183" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP183" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ183" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP183" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -27333,7 +27146,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27350,20 +27163,19 @@
       <c r="AI184" t="inlineStr"/>
       <c r="AJ184" t="inlineStr"/>
       <c r="AK184" t="inlineStr"/>
-      <c r="AL184" t="inlineStr"/>
-      <c r="AM184" t="n">
+      <c r="AL184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM184" t="b">
         <v>1</v>
       </c>
       <c r="AN184" t="b">
         <v>1</v>
       </c>
       <c r="AO184" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP184" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ184" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP184" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -27478,7 +27290,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27495,20 +27307,19 @@
       <c r="AI185" t="inlineStr"/>
       <c r="AJ185" t="inlineStr"/>
       <c r="AK185" t="inlineStr"/>
-      <c r="AL185" t="inlineStr"/>
-      <c r="AM185" t="n">
+      <c r="AL185" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM185" t="b">
         <v>1</v>
       </c>
       <c r="AN185" t="b">
         <v>1</v>
       </c>
       <c r="AO185" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP185" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ185" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP185" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -27623,7 +27434,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27640,20 +27451,19 @@
       <c r="AI186" t="inlineStr"/>
       <c r="AJ186" t="inlineStr"/>
       <c r="AK186" t="inlineStr"/>
-      <c r="AL186" t="inlineStr"/>
-      <c r="AM186" t="n">
+      <c r="AL186" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM186" t="b">
         <v>1</v>
       </c>
       <c r="AN186" t="b">
         <v>1</v>
       </c>
       <c r="AO186" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP186" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ186" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP186" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -27768,7 +27578,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27785,20 +27595,19 @@
       <c r="AI187" t="inlineStr"/>
       <c r="AJ187" t="inlineStr"/>
       <c r="AK187" t="inlineStr"/>
-      <c r="AL187" t="inlineStr"/>
-      <c r="AM187" t="n">
+      <c r="AL187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM187" t="b">
         <v>1</v>
       </c>
       <c r="AN187" t="b">
         <v>1</v>
       </c>
       <c r="AO187" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP187" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ187" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP187" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -27913,7 +27722,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27930,20 +27739,19 @@
       <c r="AI188" t="inlineStr"/>
       <c r="AJ188" t="inlineStr"/>
       <c r="AK188" t="inlineStr"/>
-      <c r="AL188" t="inlineStr"/>
-      <c r="AM188" t="n">
+      <c r="AL188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM188" t="b">
         <v>1</v>
       </c>
       <c r="AN188" t="b">
         <v>1</v>
       </c>
       <c r="AO188" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP188" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ188" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP188" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -28058,7 +27866,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28075,20 +27883,19 @@
       <c r="AI189" t="inlineStr"/>
       <c r="AJ189" t="inlineStr"/>
       <c r="AK189" t="inlineStr"/>
-      <c r="AL189" t="inlineStr"/>
-      <c r="AM189" t="n">
+      <c r="AL189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM189" t="b">
         <v>1</v>
       </c>
       <c r="AN189" t="b">
         <v>1</v>
       </c>
       <c r="AO189" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP189" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ189" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP189" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -28203,7 +28010,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -28220,20 +28027,19 @@
       <c r="AI190" t="inlineStr"/>
       <c r="AJ190" t="inlineStr"/>
       <c r="AK190" t="inlineStr"/>
-      <c r="AL190" t="inlineStr"/>
-      <c r="AM190" t="n">
+      <c r="AL190" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM190" t="b">
         <v>1</v>
       </c>
       <c r="AN190" t="b">
         <v>1</v>
       </c>
       <c r="AO190" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP190" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ190" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP190" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -28348,7 +28154,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28365,20 +28171,19 @@
       <c r="AI191" t="inlineStr"/>
       <c r="AJ191" t="inlineStr"/>
       <c r="AK191" t="inlineStr"/>
-      <c r="AL191" t="inlineStr"/>
-      <c r="AM191" t="n">
+      <c r="AL191" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM191" t="b">
         <v>1</v>
       </c>
       <c r="AN191" t="b">
         <v>1</v>
       </c>
       <c r="AO191" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP191" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ191" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP191" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -28493,7 +28298,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28510,20 +28315,19 @@
       <c r="AI192" t="inlineStr"/>
       <c r="AJ192" t="inlineStr"/>
       <c r="AK192" t="inlineStr"/>
-      <c r="AL192" t="inlineStr"/>
-      <c r="AM192" t="n">
+      <c r="AL192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM192" t="b">
         <v>1</v>
       </c>
       <c r="AN192" t="b">
         <v>1</v>
       </c>
       <c r="AO192" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP192" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ192" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP192" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -28638,7 +28442,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28655,20 +28459,19 @@
       <c r="AI193" t="inlineStr"/>
       <c r="AJ193" t="inlineStr"/>
       <c r="AK193" t="inlineStr"/>
-      <c r="AL193" t="inlineStr"/>
-      <c r="AM193" t="n">
+      <c r="AL193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM193" t="b">
         <v>1</v>
       </c>
       <c r="AN193" t="b">
         <v>1</v>
       </c>
       <c r="AO193" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP193" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ193" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP193" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -28783,7 +28586,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28800,20 +28603,19 @@
       <c r="AI194" t="inlineStr"/>
       <c r="AJ194" t="inlineStr"/>
       <c r="AK194" t="inlineStr"/>
-      <c r="AL194" t="inlineStr"/>
-      <c r="AM194" t="n">
+      <c r="AL194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM194" t="b">
         <v>1</v>
       </c>
       <c r="AN194" t="b">
         <v>1</v>
       </c>
       <c r="AO194" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP194" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ194" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP194" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -28928,7 +28730,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28945,20 +28747,19 @@
       <c r="AI195" t="inlineStr"/>
       <c r="AJ195" t="inlineStr"/>
       <c r="AK195" t="inlineStr"/>
-      <c r="AL195" t="inlineStr"/>
-      <c r="AM195" t="n">
+      <c r="AL195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM195" t="b">
         <v>1</v>
       </c>
       <c r="AN195" t="b">
         <v>1</v>
       </c>
       <c r="AO195" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP195" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ195" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP195" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -29073,7 +28874,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29090,20 +28891,19 @@
       <c r="AI196" t="inlineStr"/>
       <c r="AJ196" t="inlineStr"/>
       <c r="AK196" t="inlineStr"/>
-      <c r="AL196" t="inlineStr"/>
-      <c r="AM196" t="n">
+      <c r="AL196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM196" t="b">
         <v>1</v>
       </c>
       <c r="AN196" t="b">
         <v>1</v>
       </c>
       <c r="AO196" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP196" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ196" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP196" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -29218,7 +29018,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -29235,20 +29035,19 @@
       <c r="AI197" t="inlineStr"/>
       <c r="AJ197" t="inlineStr"/>
       <c r="AK197" t="inlineStr"/>
-      <c r="AL197" t="inlineStr"/>
-      <c r="AM197" t="n">
+      <c r="AL197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM197" t="b">
         <v>1</v>
       </c>
       <c r="AN197" t="b">
         <v>1</v>
       </c>
       <c r="AO197" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP197" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ197" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP197" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -29363,7 +29162,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29380,20 +29179,19 @@
       <c r="AI198" t="inlineStr"/>
       <c r="AJ198" t="inlineStr"/>
       <c r="AK198" t="inlineStr"/>
-      <c r="AL198" t="inlineStr"/>
-      <c r="AM198" t="n">
+      <c r="AL198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM198" t="b">
         <v>1</v>
       </c>
       <c r="AN198" t="b">
         <v>1</v>
       </c>
       <c r="AO198" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP198" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ198" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP198" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -29508,7 +29306,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29525,20 +29323,19 @@
       <c r="AI199" t="inlineStr"/>
       <c r="AJ199" t="inlineStr"/>
       <c r="AK199" t="inlineStr"/>
-      <c r="AL199" t="inlineStr"/>
-      <c r="AM199" t="n">
+      <c r="AL199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM199" t="b">
         <v>1</v>
       </c>
       <c r="AN199" t="b">
         <v>1</v>
       </c>
       <c r="AO199" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP199" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ199" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP199" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -29653,7 +29450,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29670,20 +29467,19 @@
       <c r="AI200" t="inlineStr"/>
       <c r="AJ200" t="inlineStr"/>
       <c r="AK200" t="inlineStr"/>
-      <c r="AL200" t="inlineStr"/>
-      <c r="AM200" t="n">
+      <c r="AL200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM200" t="b">
         <v>1</v>
       </c>
       <c r="AN200" t="b">
         <v>1</v>
       </c>
       <c r="AO200" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP200" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ200" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP200" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -29798,7 +29594,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29815,20 +29611,19 @@
       <c r="AI201" t="inlineStr"/>
       <c r="AJ201" t="inlineStr"/>
       <c r="AK201" t="inlineStr"/>
-      <c r="AL201" t="inlineStr"/>
-      <c r="AM201" t="n">
+      <c r="AL201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM201" t="b">
         <v>1</v>
       </c>
       <c r="AN201" t="b">
         <v>1</v>
       </c>
       <c r="AO201" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP201" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ201" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP201" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -29943,7 +29738,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29960,20 +29755,19 @@
       <c r="AI202" t="inlineStr"/>
       <c r="AJ202" t="inlineStr"/>
       <c r="AK202" t="inlineStr"/>
-      <c r="AL202" t="inlineStr"/>
-      <c r="AM202" t="n">
+      <c r="AL202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM202" t="b">
         <v>1</v>
       </c>
       <c r="AN202" t="b">
         <v>1</v>
       </c>
       <c r="AO202" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP202" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ202" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP202" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -30088,7 +29882,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30105,20 +29899,19 @@
       <c r="AI203" t="inlineStr"/>
       <c r="AJ203" t="inlineStr"/>
       <c r="AK203" t="inlineStr"/>
-      <c r="AL203" t="inlineStr"/>
-      <c r="AM203" t="n">
+      <c r="AL203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM203" t="b">
         <v>1</v>
       </c>
       <c r="AN203" t="b">
         <v>1</v>
       </c>
       <c r="AO203" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP203" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ203" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP203" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -30233,7 +30026,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -30250,20 +30043,19 @@
       <c r="AI204" t="inlineStr"/>
       <c r="AJ204" t="inlineStr"/>
       <c r="AK204" t="inlineStr"/>
-      <c r="AL204" t="inlineStr"/>
-      <c r="AM204" t="n">
+      <c r="AL204" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM204" t="b">
         <v>1</v>
       </c>
       <c r="AN204" t="b">
         <v>1</v>
       </c>
       <c r="AO204" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP204" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ204" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP204" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -30378,7 +30170,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30395,20 +30187,19 @@
       <c r="AI205" t="inlineStr"/>
       <c r="AJ205" t="inlineStr"/>
       <c r="AK205" t="inlineStr"/>
-      <c r="AL205" t="inlineStr"/>
-      <c r="AM205" t="n">
+      <c r="AL205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM205" t="b">
         <v>1</v>
       </c>
       <c r="AN205" t="b">
         <v>1</v>
       </c>
       <c r="AO205" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP205" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ205" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP205" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -30523,7 +30314,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30540,20 +30331,19 @@
       <c r="AI206" t="inlineStr"/>
       <c r="AJ206" t="inlineStr"/>
       <c r="AK206" t="inlineStr"/>
-      <c r="AL206" t="inlineStr"/>
-      <c r="AM206" t="n">
+      <c r="AL206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM206" t="b">
         <v>1</v>
       </c>
       <c r="AN206" t="b">
         <v>1</v>
       </c>
       <c r="AO206" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP206" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ206" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP206" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -30668,7 +30458,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30685,20 +30475,19 @@
       <c r="AI207" t="inlineStr"/>
       <c r="AJ207" t="inlineStr"/>
       <c r="AK207" t="inlineStr"/>
-      <c r="AL207" t="inlineStr"/>
-      <c r="AM207" t="n">
+      <c r="AL207" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM207" t="b">
         <v>1</v>
       </c>
       <c r="AN207" t="b">
         <v>1</v>
       </c>
       <c r="AO207" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP207" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ207" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP207" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -30813,7 +30602,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30830,20 +30619,19 @@
       <c r="AI208" t="inlineStr"/>
       <c r="AJ208" t="inlineStr"/>
       <c r="AK208" t="inlineStr"/>
-      <c r="AL208" t="inlineStr"/>
-      <c r="AM208" t="n">
+      <c r="AL208" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM208" t="b">
         <v>1</v>
       </c>
       <c r="AN208" t="b">
         <v>1</v>
       </c>
       <c r="AO208" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP208" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ208" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP208" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -30958,7 +30746,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30975,20 +30763,19 @@
       <c r="AI209" t="inlineStr"/>
       <c r="AJ209" t="inlineStr"/>
       <c r="AK209" t="inlineStr"/>
-      <c r="AL209" t="inlineStr"/>
-      <c r="AM209" t="n">
+      <c r="AL209" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM209" t="b">
         <v>1</v>
       </c>
       <c r="AN209" t="b">
         <v>1</v>
       </c>
       <c r="AO209" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP209" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ209" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP209" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -31103,7 +30890,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31120,20 +30907,19 @@
       <c r="AI210" t="inlineStr"/>
       <c r="AJ210" t="inlineStr"/>
       <c r="AK210" t="inlineStr"/>
-      <c r="AL210" t="inlineStr"/>
-      <c r="AM210" t="n">
+      <c r="AL210" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM210" t="b">
         <v>1</v>
       </c>
       <c r="AN210" t="b">
         <v>1</v>
       </c>
       <c r="AO210" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP210" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ210" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP210" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -31248,7 +31034,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -31265,20 +31051,19 @@
       <c r="AI211" t="inlineStr"/>
       <c r="AJ211" t="inlineStr"/>
       <c r="AK211" t="inlineStr"/>
-      <c r="AL211" t="inlineStr"/>
-      <c r="AM211" t="n">
+      <c r="AL211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM211" t="b">
         <v>1</v>
       </c>
       <c r="AN211" t="b">
         <v>1</v>
       </c>
       <c r="AO211" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP211" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ211" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP211" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -31393,7 +31178,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31410,20 +31195,19 @@
       <c r="AI212" t="inlineStr"/>
       <c r="AJ212" t="inlineStr"/>
       <c r="AK212" t="inlineStr"/>
-      <c r="AL212" t="inlineStr"/>
-      <c r="AM212" t="n">
+      <c r="AL212" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM212" t="b">
         <v>1</v>
       </c>
       <c r="AN212" t="b">
         <v>1</v>
       </c>
       <c r="AO212" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP212" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ212" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP212" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -31538,7 +31322,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31555,20 +31339,19 @@
       <c r="AI213" t="inlineStr"/>
       <c r="AJ213" t="inlineStr"/>
       <c r="AK213" t="inlineStr"/>
-      <c r="AL213" t="inlineStr"/>
-      <c r="AM213" t="n">
+      <c r="AL213" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM213" t="b">
         <v>1</v>
       </c>
       <c r="AN213" t="b">
         <v>1</v>
       </c>
       <c r="AO213" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP213" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ213" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP213" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -31683,7 +31466,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31700,20 +31483,19 @@
       <c r="AI214" t="inlineStr"/>
       <c r="AJ214" t="inlineStr"/>
       <c r="AK214" t="inlineStr"/>
-      <c r="AL214" t="inlineStr"/>
-      <c r="AM214" t="n">
+      <c r="AL214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM214" t="b">
         <v>1</v>
       </c>
       <c r="AN214" t="b">
         <v>1</v>
       </c>
       <c r="AO214" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP214" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ214" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP214" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -31828,7 +31610,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -31845,20 +31627,19 @@
       <c r="AI215" t="inlineStr"/>
       <c r="AJ215" t="inlineStr"/>
       <c r="AK215" t="inlineStr"/>
-      <c r="AL215" t="inlineStr"/>
-      <c r="AM215" t="n">
+      <c r="AL215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM215" t="b">
         <v>1</v>
       </c>
       <c r="AN215" t="b">
         <v>1</v>
       </c>
       <c r="AO215" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP215" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ215" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP215" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -31973,7 +31754,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -31990,20 +31771,19 @@
       <c r="AI216" t="inlineStr"/>
       <c r="AJ216" t="inlineStr"/>
       <c r="AK216" t="inlineStr"/>
-      <c r="AL216" t="inlineStr"/>
-      <c r="AM216" t="n">
+      <c r="AL216" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM216" t="b">
         <v>1</v>
       </c>
       <c r="AN216" t="b">
         <v>1</v>
       </c>
       <c r="AO216" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP216" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ216" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP216" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -32118,7 +31898,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32135,20 +31915,19 @@
       <c r="AI217" t="inlineStr"/>
       <c r="AJ217" t="inlineStr"/>
       <c r="AK217" t="inlineStr"/>
-      <c r="AL217" t="inlineStr"/>
-      <c r="AM217" t="n">
+      <c r="AL217" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM217" t="b">
         <v>1</v>
       </c>
       <c r="AN217" t="b">
         <v>1</v>
       </c>
       <c r="AO217" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP217" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ217" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP217" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -32263,7 +32042,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -32280,20 +32059,19 @@
       <c r="AI218" t="inlineStr"/>
       <c r="AJ218" t="inlineStr"/>
       <c r="AK218" t="inlineStr"/>
-      <c r="AL218" t="inlineStr"/>
-      <c r="AM218" t="n">
+      <c r="AL218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM218" t="b">
         <v>1</v>
       </c>
       <c r="AN218" t="b">
         <v>1</v>
       </c>
       <c r="AO218" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP218" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ218" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP218" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -32408,7 +32186,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -32425,20 +32203,19 @@
       <c r="AI219" t="inlineStr"/>
       <c r="AJ219" t="inlineStr"/>
       <c r="AK219" t="inlineStr"/>
-      <c r="AL219" t="inlineStr"/>
-      <c r="AM219" t="n">
+      <c r="AL219" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM219" t="b">
         <v>1</v>
       </c>
       <c r="AN219" t="b">
         <v>1</v>
       </c>
       <c r="AO219" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP219" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ219" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP219" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -32553,7 +32330,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32570,20 +32347,19 @@
       <c r="AI220" t="inlineStr"/>
       <c r="AJ220" t="inlineStr"/>
       <c r="AK220" t="inlineStr"/>
-      <c r="AL220" t="inlineStr"/>
-      <c r="AM220" t="n">
+      <c r="AL220" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM220" t="b">
         <v>1</v>
       </c>
       <c r="AN220" t="b">
         <v>1</v>
       </c>
       <c r="AO220" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP220" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ220" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP220" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -32698,7 +32474,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32715,20 +32491,19 @@
       <c r="AI221" t="inlineStr"/>
       <c r="AJ221" t="inlineStr"/>
       <c r="AK221" t="inlineStr"/>
-      <c r="AL221" t="inlineStr"/>
-      <c r="AM221" t="n">
+      <c r="AL221" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM221" t="b">
         <v>1</v>
       </c>
       <c r="AN221" t="b">
         <v>1</v>
       </c>
       <c r="AO221" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP221" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ221" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP221" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -32843,7 +32618,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32860,20 +32635,19 @@
       <c r="AI222" t="inlineStr"/>
       <c r="AJ222" t="inlineStr"/>
       <c r="AK222" t="inlineStr"/>
-      <c r="AL222" t="inlineStr"/>
-      <c r="AM222" t="n">
+      <c r="AL222" t="n">
         <v>2</v>
       </c>
+      <c r="AM222" t="b">
+        <v>1</v>
+      </c>
       <c r="AN222" t="b">
         <v>1</v>
       </c>
       <c r="AO222" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP222" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ222" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP222" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -32988,7 +32762,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -33005,20 +32779,19 @@
       <c r="AI223" t="inlineStr"/>
       <c r="AJ223" t="inlineStr"/>
       <c r="AK223" t="inlineStr"/>
-      <c r="AL223" t="inlineStr"/>
-      <c r="AM223" t="n">
+      <c r="AL223" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM223" t="b">
         <v>1</v>
       </c>
       <c r="AN223" t="b">
         <v>1</v>
       </c>
       <c r="AO223" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP223" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ223" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP223" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -33133,7 +32906,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33150,20 +32923,19 @@
       <c r="AI224" t="inlineStr"/>
       <c r="AJ224" t="inlineStr"/>
       <c r="AK224" t="inlineStr"/>
-      <c r="AL224" t="inlineStr"/>
-      <c r="AM224" t="n">
+      <c r="AL224" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM224" t="b">
         <v>1</v>
       </c>
       <c r="AN224" t="b">
         <v>1</v>
       </c>
       <c r="AO224" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP224" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ224" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP224" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -33278,7 +33050,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -33295,20 +33067,19 @@
       <c r="AI225" t="inlineStr"/>
       <c r="AJ225" t="inlineStr"/>
       <c r="AK225" t="inlineStr"/>
-      <c r="AL225" t="inlineStr"/>
-      <c r="AM225" t="n">
+      <c r="AL225" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM225" t="b">
         <v>1</v>
       </c>
       <c r="AN225" t="b">
         <v>1</v>
       </c>
       <c r="AO225" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP225" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ225" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP225" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -33423,7 +33194,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -33440,20 +33211,19 @@
       <c r="AI226" t="inlineStr"/>
       <c r="AJ226" t="inlineStr"/>
       <c r="AK226" t="inlineStr"/>
-      <c r="AL226" t="inlineStr"/>
-      <c r="AM226" t="n">
+      <c r="AL226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM226" t="b">
         <v>1</v>
       </c>
       <c r="AN226" t="b">
         <v>1</v>
       </c>
       <c r="AO226" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP226" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ226" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP226" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -33568,7 +33338,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33585,20 +33355,19 @@
       <c r="AI227" t="inlineStr"/>
       <c r="AJ227" t="inlineStr"/>
       <c r="AK227" t="inlineStr"/>
-      <c r="AL227" t="inlineStr"/>
-      <c r="AM227" t="n">
+      <c r="AL227" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM227" t="b">
         <v>1</v>
       </c>
       <c r="AN227" t="b">
         <v>1</v>
       </c>
       <c r="AO227" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP227" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ227" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP227" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -33713,7 +33482,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33730,20 +33499,19 @@
       <c r="AI228" t="inlineStr"/>
       <c r="AJ228" t="inlineStr"/>
       <c r="AK228" t="inlineStr"/>
-      <c r="AL228" t="inlineStr"/>
-      <c r="AM228" t="n">
+      <c r="AL228" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM228" t="b">
         <v>1</v>
       </c>
       <c r="AN228" t="b">
         <v>1</v>
       </c>
       <c r="AO228" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP228" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ228" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP228" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -33858,7 +33626,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33875,20 +33643,19 @@
       <c r="AI229" t="inlineStr"/>
       <c r="AJ229" t="inlineStr"/>
       <c r="AK229" t="inlineStr"/>
-      <c r="AL229" t="inlineStr"/>
-      <c r="AM229" t="n">
+      <c r="AL229" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM229" t="b">
         <v>1</v>
       </c>
       <c r="AN229" t="b">
         <v>1</v>
       </c>
       <c r="AO229" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP229" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ229" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP229" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -34003,7 +33770,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -34020,20 +33787,19 @@
       <c r="AI230" t="inlineStr"/>
       <c r="AJ230" t="inlineStr"/>
       <c r="AK230" t="inlineStr"/>
-      <c r="AL230" t="inlineStr"/>
-      <c r="AM230" t="n">
+      <c r="AL230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM230" t="b">
         <v>1</v>
       </c>
       <c r="AN230" t="b">
         <v>1</v>
       </c>
       <c r="AO230" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP230" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ230" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP230" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -34148,7 +33914,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34165,20 +33931,19 @@
       <c r="AI231" t="inlineStr"/>
       <c r="AJ231" t="inlineStr"/>
       <c r="AK231" t="inlineStr"/>
-      <c r="AL231" t="inlineStr"/>
-      <c r="AM231" t="n">
+      <c r="AL231" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM231" t="b">
         <v>1</v>
       </c>
       <c r="AN231" t="b">
         <v>1</v>
       </c>
       <c r="AO231" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP231" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ231" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP231" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -34293,7 +34058,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -34310,20 +34075,19 @@
       <c r="AI232" t="inlineStr"/>
       <c r="AJ232" t="inlineStr"/>
       <c r="AK232" t="inlineStr"/>
-      <c r="AL232" t="inlineStr"/>
-      <c r="AM232" t="n">
+      <c r="AL232" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM232" t="b">
         <v>1</v>
       </c>
       <c r="AN232" t="b">
         <v>1</v>
       </c>
       <c r="AO232" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP232" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ232" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP232" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -34438,7 +34202,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -34455,20 +34219,19 @@
       <c r="AI233" t="inlineStr"/>
       <c r="AJ233" t="inlineStr"/>
       <c r="AK233" t="inlineStr"/>
-      <c r="AL233" t="inlineStr"/>
-      <c r="AM233" t="n">
+      <c r="AL233" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM233" t="b">
         <v>1</v>
       </c>
       <c r="AN233" t="b">
         <v>1</v>
       </c>
       <c r="AO233" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP233" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ233" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP233" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -34583,7 +34346,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34600,20 +34363,19 @@
       <c r="AI234" t="inlineStr"/>
       <c r="AJ234" t="inlineStr"/>
       <c r="AK234" t="inlineStr"/>
-      <c r="AL234" t="inlineStr"/>
-      <c r="AM234" t="n">
+      <c r="AL234" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM234" t="b">
         <v>1</v>
       </c>
       <c r="AN234" t="b">
         <v>1</v>
       </c>
       <c r="AO234" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP234" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ234" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP234" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -34728,7 +34490,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34745,20 +34507,19 @@
       <c r="AI235" t="inlineStr"/>
       <c r="AJ235" t="inlineStr"/>
       <c r="AK235" t="inlineStr"/>
-      <c r="AL235" t="inlineStr"/>
-      <c r="AM235" t="n">
+      <c r="AL235" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM235" t="b">
         <v>1</v>
       </c>
       <c r="AN235" t="b">
         <v>1</v>
       </c>
       <c r="AO235" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP235" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ235" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP235" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -34873,7 +34634,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34890,20 +34651,19 @@
       <c r="AI236" t="inlineStr"/>
       <c r="AJ236" t="inlineStr"/>
       <c r="AK236" t="inlineStr"/>
-      <c r="AL236" t="inlineStr"/>
-      <c r="AM236" t="n">
+      <c r="AL236" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM236" t="b">
         <v>1</v>
       </c>
       <c r="AN236" t="b">
         <v>1</v>
       </c>
       <c r="AO236" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP236" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ236" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP236" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -35018,7 +34778,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -35035,20 +34795,19 @@
       <c r="AI237" t="inlineStr"/>
       <c r="AJ237" t="inlineStr"/>
       <c r="AK237" t="inlineStr"/>
-      <c r="AL237" t="inlineStr"/>
-      <c r="AM237" t="n">
+      <c r="AL237" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM237" t="b">
         <v>1</v>
       </c>
       <c r="AN237" t="b">
         <v>1</v>
       </c>
       <c r="AO237" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP237" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ237" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP237" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -35163,7 +34922,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35180,20 +34939,19 @@
       <c r="AI238" t="inlineStr"/>
       <c r="AJ238" t="inlineStr"/>
       <c r="AK238" t="inlineStr"/>
-      <c r="AL238" t="inlineStr"/>
-      <c r="AM238" t="n">
+      <c r="AL238" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM238" t="b">
         <v>1</v>
       </c>
       <c r="AN238" t="b">
         <v>1</v>
       </c>
       <c r="AO238" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP238" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ238" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP238" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -35308,7 +35066,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -35325,20 +35083,19 @@
       <c r="AI239" t="inlineStr"/>
       <c r="AJ239" t="inlineStr"/>
       <c r="AK239" t="inlineStr"/>
-      <c r="AL239" t="inlineStr"/>
-      <c r="AM239" t="n">
+      <c r="AL239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM239" t="b">
         <v>1</v>
       </c>
       <c r="AN239" t="b">
         <v>1</v>
       </c>
       <c r="AO239" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP239" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ239" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP239" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -35459,7 +35216,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>941441354208</v>
+        <v>2824324062624</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -35476,20 +35233,19 @@
       <c r="AI240" t="inlineStr"/>
       <c r="AJ240" t="inlineStr"/>
       <c r="AK240" t="inlineStr"/>
-      <c r="AL240" t="inlineStr"/>
-      <c r="AM240" t="n">
+      <c r="AL240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM240" t="b">
         <v>1</v>
       </c>
       <c r="AN240" t="b">
         <v>1</v>
       </c>
       <c r="AO240" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP240" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ240" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP240" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -35604,7 +35360,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35621,20 +35377,19 @@
       <c r="AI241" t="inlineStr"/>
       <c r="AJ241" t="inlineStr"/>
       <c r="AK241" t="inlineStr"/>
-      <c r="AL241" t="inlineStr"/>
-      <c r="AM241" t="n">
+      <c r="AL241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM241" t="b">
         <v>1</v>
       </c>
       <c r="AN241" t="b">
         <v>1</v>
       </c>
       <c r="AO241" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP241" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ241" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP241" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -35749,7 +35504,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35766,20 +35521,19 @@
       <c r="AI242" t="inlineStr"/>
       <c r="AJ242" t="inlineStr"/>
       <c r="AK242" t="inlineStr"/>
-      <c r="AL242" t="inlineStr"/>
-      <c r="AM242" t="n">
+      <c r="AL242" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM242" t="b">
         <v>1</v>
       </c>
       <c r="AN242" t="b">
         <v>1</v>
       </c>
       <c r="AO242" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP242" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ242" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP242" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -35894,7 +35648,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35911,20 +35665,19 @@
       <c r="AI243" t="inlineStr"/>
       <c r="AJ243" t="inlineStr"/>
       <c r="AK243" t="inlineStr"/>
-      <c r="AL243" t="inlineStr"/>
-      <c r="AM243" t="n">
+      <c r="AL243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM243" t="b">
         <v>1</v>
       </c>
       <c r="AN243" t="b">
         <v>1</v>
       </c>
       <c r="AO243" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP243" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ243" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP243" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -36039,7 +35792,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -36056,20 +35809,19 @@
       <c r="AI244" t="inlineStr"/>
       <c r="AJ244" t="inlineStr"/>
       <c r="AK244" t="inlineStr"/>
-      <c r="AL244" t="inlineStr"/>
-      <c r="AM244" t="n">
+      <c r="AL244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM244" t="b">
         <v>1</v>
       </c>
       <c r="AN244" t="b">
         <v>1</v>
       </c>
       <c r="AO244" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP244" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ244" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP244" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -36184,7 +35936,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -36201,20 +35953,19 @@
       <c r="AI245" t="inlineStr"/>
       <c r="AJ245" t="inlineStr"/>
       <c r="AK245" t="inlineStr"/>
-      <c r="AL245" t="inlineStr"/>
-      <c r="AM245" t="n">
+      <c r="AL245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM245" t="b">
         <v>1</v>
       </c>
       <c r="AN245" t="b">
         <v>1</v>
       </c>
       <c r="AO245" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP245" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ245" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP245" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -36339,7 +36090,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>815907549834</v>
+        <v>2447722649502</v>
       </c>
       <c r="AE246" t="n">
         <v>5</v>
@@ -36358,20 +36109,19 @@
       <c r="AK246" t="b">
         <v>0</v>
       </c>
-      <c r="AL246" t="inlineStr"/>
-      <c r="AM246" t="n">
+      <c r="AL246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM246" t="b">
         <v>1</v>
       </c>
       <c r="AN246" t="b">
         <v>1</v>
       </c>
       <c r="AO246" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP246" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ246" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP246" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -36486,7 +36236,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE247" t="n">
         <v>2</v>
@@ -36503,20 +36253,19 @@
       <c r="AI247" t="inlineStr"/>
       <c r="AJ247" t="inlineStr"/>
       <c r="AK247" t="inlineStr"/>
-      <c r="AL247" t="inlineStr"/>
-      <c r="AM247" t="n">
+      <c r="AL247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM247" t="b">
         <v>1</v>
       </c>
       <c r="AN247" t="b">
         <v>1</v>
       </c>
       <c r="AO247" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP247" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ247" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP247" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -36631,7 +36380,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36648,20 +36397,19 @@
       <c r="AI248" t="inlineStr"/>
       <c r="AJ248" t="inlineStr"/>
       <c r="AK248" t="inlineStr"/>
-      <c r="AL248" t="inlineStr"/>
-      <c r="AM248" t="n">
+      <c r="AL248" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM248" t="b">
         <v>1</v>
       </c>
       <c r="AN248" t="b">
         <v>1</v>
       </c>
       <c r="AO248" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP248" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ248" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP248" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -36784,7 +36532,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE249" t="n">
         <v>5</v>
@@ -36801,20 +36549,19 @@
       <c r="AI249" t="inlineStr"/>
       <c r="AJ249" t="inlineStr"/>
       <c r="AK249" t="inlineStr"/>
-      <c r="AL249" t="inlineStr"/>
-      <c r="AM249" t="n">
+      <c r="AL249" t="n">
         <v>2</v>
       </c>
+      <c r="AM249" t="b">
+        <v>1</v>
+      </c>
       <c r="AN249" t="b">
         <v>1</v>
       </c>
       <c r="AO249" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP249" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ249" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP249" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -36937,7 +36684,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE250" t="n">
         <v>229</v>
@@ -36954,20 +36701,19 @@
       <c r="AI250" t="inlineStr"/>
       <c r="AJ250" t="inlineStr"/>
       <c r="AK250" t="inlineStr"/>
-      <c r="AL250" t="inlineStr"/>
-      <c r="AM250" t="n">
+      <c r="AL250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM250" t="b">
         <v>1</v>
       </c>
       <c r="AN250" t="b">
         <v>1</v>
       </c>
       <c r="AO250" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP250" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ250" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP250" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -37082,7 +36828,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -37099,20 +36845,19 @@
       <c r="AI251" t="inlineStr"/>
       <c r="AJ251" t="inlineStr"/>
       <c r="AK251" t="inlineStr"/>
-      <c r="AL251" t="inlineStr"/>
-      <c r="AM251" t="n">
+      <c r="AL251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM251" t="b">
         <v>1</v>
       </c>
       <c r="AN251" t="b">
         <v>1</v>
       </c>
       <c r="AO251" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP251" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ251" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP251" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -37237,7 +36982,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>942206629248</v>
+        <v>2826619887744</v>
       </c>
       <c r="AE252" t="n">
         <v>4</v>
@@ -37254,20 +36999,19 @@
       <c r="AI252" t="inlineStr"/>
       <c r="AJ252" t="inlineStr"/>
       <c r="AK252" t="inlineStr"/>
-      <c r="AL252" t="inlineStr"/>
-      <c r="AM252" t="n">
+      <c r="AL252" t="n">
         <v>2</v>
       </c>
+      <c r="AM252" t="b">
+        <v>1</v>
+      </c>
       <c r="AN252" t="b">
         <v>1</v>
       </c>
       <c r="AO252" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP252" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ252" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP252" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -37382,7 +37126,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>753145430616</v>
+        <v>2259436291848</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -37399,20 +37143,19 @@
       <c r="AI253" t="inlineStr"/>
       <c r="AJ253" t="inlineStr"/>
       <c r="AK253" t="inlineStr"/>
-      <c r="AL253" t="inlineStr"/>
-      <c r="AM253" t="n">
+      <c r="AL253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM253" t="b">
         <v>1</v>
       </c>
       <c r="AN253" t="b">
         <v>1</v>
       </c>
       <c r="AO253" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP253" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ253" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP253" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>
@@ -37531,7 +37274,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>941431788270</v>
+        <v>2824295364810</v>
       </c>
       <c r="AE254" t="n">
         <v>3</v>
@@ -37548,20 +37291,19 @@
       <c r="AI254" t="inlineStr"/>
       <c r="AJ254" t="inlineStr"/>
       <c r="AK254" t="inlineStr"/>
-      <c r="AL254" t="inlineStr"/>
-      <c r="AM254" t="n">
+      <c r="AL254" t="n">
         <v>2</v>
       </c>
+      <c r="AM254" t="b">
+        <v>1</v>
+      </c>
       <c r="AN254" t="b">
         <v>1</v>
       </c>
       <c r="AO254" t="b">
-        <v>1</v>
-      </c>
-      <c r="AP254" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ254" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="AP254" t="inlineStr">
         <is>
           <t>ORGANIZATION_OR_SHARED_ROUTE</t>
         </is>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -797,7 +797,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>3396128006574</v>
+        <v>10188384019722</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -953,7 +953,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>2322973252044</v>
+        <v>6968919756132</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1261,7 +1261,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2447722649502</v>
+        <v>7343167948506</v>
       </c>
       <c r="AE6" t="n">
         <v>19</v>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1569,7 +1569,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>2266409860650</v>
+        <v>6799229581950</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>2826619887744</v>
+        <v>8479859663232</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2620,7 +2620,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>2447722649502</v>
+        <v>7343167948506</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2826619887744</v>
+        <v>8479859663232</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -2930,7 +2930,7 @@
         <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>2447722649502</v>
+        <v>7343167948506</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3086,7 +3086,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2447722649502</v>
+        <v>7343167948506</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -7994,7 +7994,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8714,7 +8714,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9290,7 +9290,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10442,7 +10442,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10586,7 +10586,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11162,7 +11162,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11738,7 +11738,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12026,7 +12026,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12170,7 +12170,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12458,7 +12458,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12746,7 +12746,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12890,7 +12890,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13466,7 +13466,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13754,7 +13754,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13898,7 +13898,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14042,7 +14042,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14186,7 +14186,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14330,7 +14330,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14474,7 +14474,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14618,7 +14618,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14762,7 +14762,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14906,7 +14906,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15050,7 +15050,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15194,7 +15194,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15338,7 +15338,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -15482,7 +15482,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15626,7 +15626,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15770,7 +15770,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15914,7 +15914,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16058,7 +16058,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16202,7 +16202,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16346,7 +16346,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16634,7 +16634,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16922,7 +16922,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17066,7 +17066,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17354,7 +17354,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -17498,7 +17498,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17642,7 +17642,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17786,7 +17786,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17930,7 +17930,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18074,7 +18074,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -18362,7 +18362,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -18506,7 +18506,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18650,7 +18650,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18794,7 +18794,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19082,7 +19082,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -19370,7 +19370,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -19514,7 +19514,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -19658,7 +19658,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19802,7 +19802,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20090,7 +20090,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20234,7 +20234,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20522,7 +20522,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20666,7 +20666,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20810,7 +20810,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20954,7 +20954,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21098,7 +21098,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21242,7 +21242,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21386,7 +21386,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21530,7 +21530,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21674,7 +21674,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21818,7 +21818,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21962,7 +21962,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22250,7 +22250,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22394,7 +22394,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22538,7 +22538,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22826,7 +22826,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22970,7 +22970,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23114,7 +23114,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23258,7 +23258,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23402,7 +23402,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23546,7 +23546,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23690,7 +23690,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23834,7 +23834,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23978,7 +23978,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24122,7 +24122,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24266,7 +24266,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24554,7 +24554,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24698,7 +24698,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24986,7 +24986,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25130,7 +25130,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25562,7 +25562,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25706,7 +25706,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25850,7 +25850,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25994,7 +25994,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -26138,7 +26138,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26282,7 +26282,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26426,7 +26426,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26570,7 +26570,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26714,7 +26714,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26858,7 +26858,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27002,7 +27002,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -27146,7 +27146,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27290,7 +27290,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27434,7 +27434,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27578,7 +27578,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27722,7 +27722,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27866,7 +27866,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28010,7 +28010,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -28154,7 +28154,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28298,7 +28298,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28442,7 +28442,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28586,7 +28586,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28730,7 +28730,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28874,7 +28874,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29018,7 +29018,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -29162,7 +29162,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29306,7 +29306,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29450,7 +29450,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29594,7 +29594,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29738,7 +29738,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30026,7 +30026,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -30170,7 +30170,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30314,7 +30314,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30458,7 +30458,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30602,7 +30602,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30746,7 +30746,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31034,7 +31034,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -31178,7 +31178,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31322,7 +31322,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31466,7 +31466,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31610,7 +31610,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -31754,7 +31754,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -31898,7 +31898,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32042,7 +32042,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -32186,7 +32186,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -32330,7 +32330,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32474,7 +32474,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32618,7 +32618,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32762,7 +32762,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -32906,7 +32906,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33050,7 +33050,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -33194,7 +33194,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -33338,7 +33338,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33626,7 +33626,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33770,7 +33770,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -33914,7 +33914,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -34202,7 +34202,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -34346,7 +34346,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34490,7 +34490,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34634,7 +34634,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34778,7 +34778,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -34922,7 +34922,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35066,7 +35066,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -35216,7 +35216,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>2824324062624</v>
+        <v>8472972187872</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -35360,7 +35360,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35504,7 +35504,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35792,7 +35792,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -35936,7 +35936,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -35976,7 +35976,7 @@
         <v>12</v>
       </c>
       <c r="B246" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>2447722649502</v>
+        <v>7343167948506</v>
       </c>
       <c r="AE246" t="n">
         <v>5</v>
@@ -36236,10 +36236,10 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE247" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF247" t="n">
         <v>0</v>
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36532,7 +36532,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE249" t="n">
         <v>5</v>
@@ -36684,7 +36684,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE250" t="n">
         <v>229</v>
@@ -36828,7 +36828,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -36982,7 +36982,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>2826619887744</v>
+        <v>8479859663232</v>
       </c>
       <c r="AE252" t="n">
         <v>4</v>
@@ -37126,7 +37126,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>2259436291848</v>
+        <v>6778308875544</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -37274,7 +37274,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>2824295364810</v>
+        <v>8472886094430</v>
       </c>
       <c r="AE254" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -797,7 +797,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>10188384019722</v>
+        <v>30565152059166</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -953,7 +953,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>6968919756132</v>
+        <v>20906759268396</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1261,7 +1261,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE6" t="n">
         <v>19</v>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1569,7 +1569,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>6799229581950</v>
+        <v>20397688745850</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>8479859663232</v>
+        <v>25439578989696</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2620,7 +2620,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>8479859663232</v>
+        <v>25439578989696</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -2930,7 +2930,7 @@
         <v>12</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3086,7 +3086,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE27" t="n">
         <v>18</v>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -7994,7 +7994,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8714,7 +8714,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9290,7 +9290,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10442,7 +10442,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10586,7 +10586,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11162,7 +11162,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11738,7 +11738,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12026,7 +12026,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12170,7 +12170,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12458,7 +12458,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12746,7 +12746,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12890,7 +12890,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13466,7 +13466,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13754,7 +13754,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13898,7 +13898,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14042,7 +14042,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14186,7 +14186,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14330,7 +14330,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14474,7 +14474,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14618,7 +14618,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14762,7 +14762,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14906,7 +14906,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15050,7 +15050,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15194,7 +15194,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15338,7 +15338,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -15482,7 +15482,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15626,7 +15626,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15770,7 +15770,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15914,7 +15914,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16058,7 +16058,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16202,7 +16202,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16346,7 +16346,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16634,7 +16634,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16922,7 +16922,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17066,7 +17066,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17354,7 +17354,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -17498,7 +17498,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17642,7 +17642,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17786,7 +17786,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17930,7 +17930,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18074,7 +18074,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -18362,7 +18362,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -18506,7 +18506,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18650,7 +18650,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18794,7 +18794,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19082,7 +19082,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -19370,7 +19370,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -19514,7 +19514,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -19658,7 +19658,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19802,7 +19802,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20090,7 +20090,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20234,7 +20234,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20522,7 +20522,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20666,7 +20666,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20810,7 +20810,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20954,7 +20954,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21098,7 +21098,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21242,7 +21242,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21386,7 +21386,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21530,7 +21530,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21674,7 +21674,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21818,7 +21818,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21962,7 +21962,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22250,7 +22250,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22394,7 +22394,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22538,7 +22538,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22826,7 +22826,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22970,7 +22970,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23114,7 +23114,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23258,7 +23258,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23402,7 +23402,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23546,7 +23546,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23690,7 +23690,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23834,7 +23834,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23978,7 +23978,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24122,7 +24122,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24266,7 +24266,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24554,7 +24554,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24698,7 +24698,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24986,7 +24986,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25130,7 +25130,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25562,7 +25562,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25706,7 +25706,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25850,7 +25850,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25994,7 +25994,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -26138,7 +26138,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26282,7 +26282,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26426,7 +26426,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26570,7 +26570,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26714,7 +26714,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26858,7 +26858,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27002,7 +27002,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -27146,7 +27146,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27290,7 +27290,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27434,7 +27434,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27578,7 +27578,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27722,7 +27722,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27866,7 +27866,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28010,7 +28010,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -28154,7 +28154,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28298,7 +28298,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28442,7 +28442,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28586,7 +28586,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28730,7 +28730,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28874,7 +28874,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29018,7 +29018,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -29162,7 +29162,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29306,7 +29306,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29450,7 +29450,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29594,7 +29594,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29738,7 +29738,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30026,7 +30026,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -30170,7 +30170,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30314,7 +30314,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30458,7 +30458,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30602,7 +30602,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30746,7 +30746,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31034,7 +31034,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -31178,7 +31178,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31322,7 +31322,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31466,7 +31466,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31610,7 +31610,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -31754,7 +31754,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -31898,7 +31898,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32042,7 +32042,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -32186,7 +32186,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -32330,7 +32330,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32474,7 +32474,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32618,7 +32618,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32762,7 +32762,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -32906,7 +32906,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33050,7 +33050,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -33194,7 +33194,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -33338,7 +33338,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33626,7 +33626,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33770,7 +33770,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -33914,7 +33914,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -34202,7 +34202,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -34346,7 +34346,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34490,7 +34490,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34634,7 +34634,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34778,7 +34778,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -34922,7 +34922,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35066,7 +35066,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -35216,7 +35216,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>8472972187872</v>
+        <v>25418916563616</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -35360,7 +35360,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35504,7 +35504,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35792,7 +35792,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -35936,7 +35936,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -35976,7 +35976,7 @@
         <v>12</v>
       </c>
       <c r="B246" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>7343167948506</v>
+        <v>22029503845518</v>
       </c>
       <c r="AE246" t="n">
         <v>5</v>
@@ -36236,7 +36236,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE247" t="n">
         <v>3</v>
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36532,7 +36532,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE249" t="n">
         <v>5</v>
@@ -36684,7 +36684,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE250" t="n">
         <v>229</v>
@@ -36828,7 +36828,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -36982,7 +36982,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>8479859663232</v>
+        <v>25439578989696</v>
       </c>
       <c r="AE252" t="n">
         <v>4</v>
@@ -37126,7 +37126,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>6778308875544</v>
+        <v>20334926626632</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -37274,7 +37274,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>8472886094430</v>
+        <v>25418658283290</v>
       </c>
       <c r="AE254" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>30565152059166</v>
+        <v>91695456177498</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>20906759268396</v>
+        <v>62720277805188</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE6" t="n">
         <v>19</v>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>20397688745850</v>
+        <v>61193066237550</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE18" t="n">
         <v>5</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE19" t="n">
         <v>9</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE20" t="n">
         <v>8</v>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE21" t="n">
         <v>11</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4086,7 +4086,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE27" t="n">
         <v>18</v>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5402,7 +5402,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE33" t="n">
         <v>8</v>
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6122,7 +6122,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7274,7 +7274,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -7994,7 +7994,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8282,7 +8282,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8714,7 +8714,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9290,7 +9290,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9722,7 +9722,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9866,7 +9866,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10442,7 +10442,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10586,7 +10586,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10730,7 +10730,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11162,7 +11162,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11594,7 +11594,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11738,7 +11738,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12026,7 +12026,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12170,7 +12170,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12458,7 +12458,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12602,7 +12602,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12746,7 +12746,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12890,7 +12890,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13034,7 +13034,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13466,7 +13466,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13754,7 +13754,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13898,7 +13898,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14042,7 +14042,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14186,7 +14186,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14330,7 +14330,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14474,7 +14474,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14618,7 +14618,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14762,7 +14762,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14906,7 +14906,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15050,7 +15050,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15194,7 +15194,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15338,7 +15338,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -15482,7 +15482,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15626,7 +15626,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15770,7 +15770,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15914,7 +15914,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16058,7 +16058,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16202,7 +16202,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16346,7 +16346,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16634,7 +16634,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16778,7 +16778,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16922,7 +16922,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17066,7 +17066,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17210,7 +17210,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17354,7 +17354,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -17498,7 +17498,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17642,7 +17642,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17786,7 +17786,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17930,7 +17930,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18074,7 +18074,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18218,7 +18218,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -18362,7 +18362,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -18506,7 +18506,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18650,7 +18650,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18794,7 +18794,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19082,7 +19082,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -19370,7 +19370,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -19514,7 +19514,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -19658,7 +19658,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19802,7 +19802,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20090,7 +20090,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20234,7 +20234,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20378,7 +20378,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20522,7 +20522,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20666,7 +20666,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20810,7 +20810,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20954,7 +20954,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21098,7 +21098,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21242,7 +21242,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21386,7 +21386,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21530,7 +21530,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21674,7 +21674,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21818,7 +21818,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21962,7 +21962,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22250,7 +22250,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22394,7 +22394,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22538,7 +22538,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22826,7 +22826,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22970,7 +22970,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23114,7 +23114,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23258,7 +23258,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23402,7 +23402,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23546,7 +23546,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23690,7 +23690,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23834,7 +23834,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23978,7 +23978,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24122,7 +24122,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24266,7 +24266,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24410,7 +24410,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24554,7 +24554,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24698,7 +24698,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24986,7 +24986,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25130,7 +25130,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25562,7 +25562,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25706,7 +25706,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25850,7 +25850,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -25994,7 +25994,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -26138,7 +26138,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26282,7 +26282,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26426,7 +26426,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26570,7 +26570,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26714,7 +26714,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26858,7 +26858,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27002,7 +27002,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -27146,7 +27146,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27290,7 +27290,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27434,7 +27434,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27578,7 +27578,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27722,7 +27722,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27866,7 +27866,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28010,7 +28010,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -28154,7 +28154,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28298,7 +28298,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28442,7 +28442,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28586,7 +28586,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28730,7 +28730,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28874,7 +28874,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29018,7 +29018,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -29162,7 +29162,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29306,7 +29306,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29450,7 +29450,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29594,7 +29594,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29738,7 +29738,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29882,7 +29882,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30026,7 +30026,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -30170,7 +30170,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30314,7 +30314,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30458,7 +30458,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30602,7 +30602,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30746,7 +30746,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31034,7 +31034,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -31178,7 +31178,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -31322,7 +31322,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31466,7 +31466,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31610,7 +31610,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE215" t="n">
         <v>3</v>
@@ -31754,7 +31754,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -31898,7 +31898,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32042,7 +32042,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -32186,7 +32186,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -32330,7 +32330,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32474,7 +32474,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32618,7 +32618,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32762,7 +32762,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -32906,7 +32906,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33050,7 +33050,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -33194,7 +33194,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -33338,7 +33338,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33482,7 +33482,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33626,7 +33626,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33770,7 +33770,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -33914,7 +33914,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -34202,7 +34202,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -34346,7 +34346,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34490,7 +34490,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34634,7 +34634,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34778,7 +34778,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -34922,7 +34922,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35066,7 +35066,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -35216,7 +35216,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>25418916563616</v>
+        <v>76256749690848</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -35360,7 +35360,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35504,7 +35504,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35792,7 +35792,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -35936,7 +35936,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -36090,7 +36090,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>22029503845518</v>
+        <v>66088511536554</v>
       </c>
       <c r="AE246" t="n">
         <v>5</v>
@@ -36236,7 +36236,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE247" t="n">
         <v>3</v>
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE248" t="n">
         <v>2</v>
@@ -36532,7 +36532,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE249" t="n">
         <v>5</v>
@@ -36684,7 +36684,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE250" t="n">
         <v>229</v>
@@ -36828,7 +36828,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE251" t="n">
         <v>2</v>
@@ -36982,7 +36982,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>25439578989696</v>
+        <v>76318736969088</v>
       </c>
       <c r="AE252" t="n">
         <v>4</v>
@@ -37126,7 +37126,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>20334926626632</v>
+        <v>61004779879896</v>
       </c>
       <c r="AE253" t="n">
         <v>2</v>
@@ -37274,7 +37274,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>25418658283290</v>
+        <v>76255974849870</v>
       </c>
       <c r="AE254" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>275086368532494</v>
+        <v>825259105597482</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>188160833415564</v>
+        <v>564482500246692</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE6" t="n">
         <v>19</v>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>183579198712650</v>
+        <v>550737596137950</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>198330650074290</v>
+        <v>594991950222870</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE19" t="n">
         <v>5</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -3804,7 +3804,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE23" t="n">
         <v>11</v>
@@ -4092,7 +4092,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE27" t="n">
         <v>3</v>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE28" t="n">
         <v>18</v>
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE31" t="n">
         <v>4</v>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5412,7 +5412,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE34" t="n">
         <v>8</v>
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6132,7 +6132,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7284,7 +7284,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9156,7 +9156,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9588,7 +9588,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9732,7 +9732,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10020,7 +10020,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10164,7 +10164,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10452,7 +10452,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11172,7 +11172,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11604,7 +11604,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11748,7 +11748,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11892,7 +11892,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12036,7 +12036,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12324,7 +12324,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12612,7 +12612,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12756,7 +12756,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12900,7 +12900,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13044,7 +13044,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13188,7 +13188,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13332,7 +13332,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13476,7 +13476,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13620,7 +13620,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13764,7 +13764,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14052,7 +14052,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14196,7 +14196,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14340,7 +14340,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14484,7 +14484,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14628,7 +14628,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14772,7 +14772,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14916,7 +14916,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15060,7 +15060,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15204,7 +15204,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15348,7 +15348,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -15492,7 +15492,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15780,7 +15780,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15924,7 +15924,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16212,7 +16212,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16356,7 +16356,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -16500,7 +16500,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16644,7 +16644,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16788,7 +16788,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16932,7 +16932,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17076,7 +17076,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17220,7 +17220,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17364,7 +17364,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -17508,7 +17508,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17652,7 +17652,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17796,7 +17796,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17940,7 +17940,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18084,7 +18084,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18228,7 +18228,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -18372,7 +18372,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -18516,7 +18516,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18660,7 +18660,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18804,7 +18804,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18948,7 +18948,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19092,7 +19092,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19236,7 +19236,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -19380,7 +19380,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -19524,7 +19524,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -19668,7 +19668,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19956,7 +19956,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20100,7 +20100,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20244,7 +20244,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20388,7 +20388,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20532,7 +20532,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20676,7 +20676,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20964,7 +20964,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21108,7 +21108,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21396,7 +21396,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21540,7 +21540,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21684,7 +21684,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21972,7 +21972,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22116,7 +22116,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22260,7 +22260,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22404,7 +22404,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22548,7 +22548,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22692,7 +22692,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22836,7 +22836,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22980,7 +22980,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23124,7 +23124,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23268,7 +23268,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23412,7 +23412,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23700,7 +23700,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23844,7 +23844,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23988,7 +23988,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24132,7 +24132,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24276,7 +24276,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24564,7 +24564,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24708,7 +24708,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24852,7 +24852,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24996,7 +24996,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25140,7 +25140,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25284,7 +25284,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25428,7 +25428,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25572,7 +25572,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25716,7 +25716,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25860,7 +25860,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26004,7 +26004,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -26148,7 +26148,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26436,7 +26436,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26580,7 +26580,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26724,7 +26724,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26868,7 +26868,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27012,7 +27012,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -27156,7 +27156,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27300,7 +27300,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27444,7 +27444,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27588,7 +27588,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27732,7 +27732,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27876,7 +27876,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28020,7 +28020,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -28164,7 +28164,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28308,7 +28308,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28452,7 +28452,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28596,7 +28596,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28740,7 +28740,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28884,7 +28884,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29028,7 +29028,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -29172,7 +29172,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29316,7 +29316,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29460,7 +29460,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29604,7 +29604,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29748,7 +29748,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29892,7 +29892,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -30180,7 +30180,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30324,7 +30324,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30468,7 +30468,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30612,7 +30612,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30756,7 +30756,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30900,7 +30900,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31044,7 +31044,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -31188,7 +31188,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE212" t="n">
         <v>3</v>
@@ -31332,7 +31332,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31476,7 +31476,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31620,7 +31620,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -31764,7 +31764,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE216" t="n">
         <v>3</v>
@@ -31908,7 +31908,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32052,7 +32052,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -32196,7 +32196,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -32340,7 +32340,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32484,7 +32484,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32628,7 +32628,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32772,7 +32772,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -32916,7 +32916,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33060,7 +33060,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -33204,7 +33204,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -33348,7 +33348,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33492,7 +33492,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33636,7 +33636,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33780,7 +33780,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -33924,7 +33924,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34068,7 +34068,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -34212,7 +34212,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -34356,7 +34356,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34500,7 +34500,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34644,7 +34644,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34788,7 +34788,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -34932,7 +34932,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35076,7 +35076,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -35220,7 +35220,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -35370,7 +35370,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>228770249072544</v>
+        <v>686310747217632</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35514,7 +35514,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35658,7 +35658,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35802,7 +35802,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -35946,7 +35946,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -36090,7 +36090,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -36244,7 +36244,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>198265534609662</v>
+        <v>594796603828986</v>
       </c>
       <c r="AE247" t="n">
         <v>5</v>
@@ -36390,7 +36390,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE248" t="n">
         <v>3</v>
@@ -36534,7 +36534,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -36686,7 +36686,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE250" t="n">
         <v>5</v>
@@ -36838,7 +36838,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE251" t="n">
         <v>229</v>
@@ -36982,7 +36982,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -37136,7 +37136,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>228956210907264</v>
+        <v>686868632721792</v>
       </c>
       <c r="AE253" t="n">
         <v>4</v>
@@ -37280,7 +37280,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>183014339639688</v>
+        <v>549043018919064</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -37428,7 +37428,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>228767924549610</v>
+        <v>686303773648830</v>
       </c>
       <c r="AE255" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>825259105597482</v>
+        <v>2475777316792446</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>564482500246692</v>
+        <v>1693447500740076</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>594796603828986</v>
+        <v>1784389811486958</v>
       </c>
       <c r="AE6" t="n">
         <v>19</v>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>550737596137950</v>
+        <v>1652212788413850</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>686868632721792</v>
+        <v>2060605898165376</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ד"ר צוקרמן צבי</t>
+          <t>ד"ר לוריא מיכל</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167</t>
+          <t>https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
+          <t>https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2678,26 +2678,27 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>קס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה 49600 איט"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט</t>
+          <t>ter.rotem.www שעות פעילות: שעות פעילות:
+א'-ה' 08.00-22.00 | ו' 8.00-15.00 איט"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי 052-2528020 מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>"צוקרמן צבי"</t>
+          <t>"לוריא מיכל" יילוד מרפאה</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>direct_text</t>
+          <t>linked_text</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "evidence": "קס': 03-9310870 Zukerman_z@hotmail.com ברנדה 4 פתח תקווה 49600 ברנדה 4 פתח תקווה 49600 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "direct_text"}, {"email": "info@israeli-expert.co.il", "confidence": 80, "source_url": "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "identity_url": "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "evidence": "info@israeli-expert.co.il Moriya Av. 105, Haifa 34616 Phone: 04-8244633, Fax: 04-8113444", "matched_query": "\"צוקרמן צבי\"", "extraction_method": "linked_mailto"}]</t>
+          <t>[{"email": "itam.hasmacha@gmail.com", "confidence": 92, "source_url": "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "identity_url": "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "evidence": "ter.rotem.www שעות פעילות: שעות פעילות:\r\nא'-ה' 08.00-22.00 | ו' 8.00-15.00 איט\"ם, האגודה הישראלית לטיפול מיני, נוסדה בשנת 1983, ומאגדת את המטפלים והמטפלות המיניים בישראל. יצירת קשר טלפון ראשי 052-2528020 מייל ועדת הסמכה itam.hasmacha@gmail.com שעות פעילות ימים א׳–ה׳, 09:00–16:00 כתובת Facebook-f Youtube עמודים נוספים הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום הגנת פרטיות תקנון האגודה הצהרת נגישות דבר פרסום ניווט באתר עמוד בית מהו ט", "matched_query": "\"לוריא מיכל\" יילוד מרפאה", "extraction_method": "linked_text"}]</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -2705,54 +2706,52 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-09-03T21:00:59.983523+00:00</t>
+          <t>2026-09-08T23:26:20.598402+00:00</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>ddgs:bing</t>
+          <t>ddgs:yahoo</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=ce204428-9658-48fd-9895-62695b31e167", "https://www.facebook.com/people/%D7%A6%D7%91%D7%99-%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F/pfbid02E1Nxj3wfhR6MF8D6JXXRW7A6Jhoq792SjPLH1nRCvRmFTDrKUVsZSCxcg5BXdSXDl/", "https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2Fzby.zwqrmn%2F", "https://benyehuda.org/read/38950", "https://www.israeli-expert.co.il/index2.php?id=13310&amp;lang=HEB", "https://www.interuse.co.il/", "https://www.israeli-expert.co.il/about-en", "https://www.israeli-expert.co.il/index2.php?id=5149&amp;lang=HEB", "https://www.israeli-expert.co.il/about", "https://www.israeli-expert.co.il/index2.php?id=3&amp;lang=HEB", "https://www.palmach.org.il/veterans/veteranpage/?itemId=73755", "https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
+          <t>["https://www.ima.org.il/doctorsindex/DoctorProfile.aspx?uDoc=8e800bc1-5c51-41bc-b5cd-3fd5e719dca4", "https://www.meuhedet.co.il/poi/Doctors/000250300130100613000000000000_0", "https://doctorindex.co.il/%D7%93%D7%95%D7%A7%D7%98%D7%95%D7%A8-%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C/", "https://www.doctorita.co.il/experts/72051", "https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/", "https://itam.org.il/%D7%9E%D7%99-%D7%90%D7%A0%D7%97%D7%A0%D7%95/", "https://itam.org.il/public-clinics/", "https://itam.org.il/%D7%A6%D7%95%D7%A8-%D7%A7%D7%A9%D7%A8-2/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A8%D7%95%D7%AA%D7%9D-%D7%94%D7%9E%D7%A8%D7%9B%D7%96-%D7%94%D7%99%D7%A9%D7%A8%D7%90%D7%9C%D7%99-%D7%9C%D7%98%D7%99%D7%A4%D7%95%D7%9C-%D7%9E%D7%99%D7%A0%D7%99/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%A4%D7%90%D7%AA-%D7%B4%D7%9E%D7%99%D7%9F-%D7%94%D7%A2%D7%9E%D7%A7%D7%B4/", "https://itam.org.il/clinics/%D7%9E%D7%A8%D7%9B%D7%96-%D7%A9%D7%A7%D7%9E%D7%94-%D7%9C%D7%91%D7%A8%D7%99%D7%90%D7%95%D7%AA-%D7%9E%D7%99%D7%A0%D7%99%D7%AA-%D7%91%D7%99%D7%AA-%D7%97%D7%95%D7%9C%D7%99%D7%9D-%D7%A8%D7%A2%D7%95%D7%AA/"]</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>594796603828986</v>
+        <v>1786105568815239</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>https://itam.org.il/therapists/%D7%A6%D7%95%D7%A7%D7%A8%D7%9E%D7%9F-%D7%A6%D7%91%D7%99/</t>
+          <t>https://itam.org.il/therapists/%D7%9C%D7%95%D7%A8%D7%99%D7%90-%D7%9E%D7%99%D7%9B%D7%9C-%D7%93%D7%A8/</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="b">
-        <v>0</v>
-      </c>
+      <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
         <v>2</v>
       </c>
@@ -2890,7 +2889,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>686868632721792</v>
+        <v>2060605898165376</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3044,7 +3043,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>594991950222870</v>
+        <v>1784975850668610</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3198,7 +3197,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>594796603828986</v>
+        <v>1784389811486958</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3354,7 +3353,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>594796603828986</v>
+        <v>1784389811486958</v>
       </c>
       <c r="AE19" t="n">
         <v>5</v>
@@ -3500,7 +3499,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
@@ -3652,7 +3651,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -3804,7 +3803,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3948,7 +3947,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE23" t="n">
         <v>11</v>
@@ -4092,7 +4091,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4240,7 +4239,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4384,7 +4383,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4532,7 +4531,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE27" t="n">
         <v>3</v>
@@ -4684,7 +4683,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE28" t="n">
         <v>18</v>
@@ -4828,7 +4827,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4972,7 +4971,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -5116,7 +5115,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE31" t="n">
         <v>4</v>
@@ -5268,7 +5267,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5412,7 +5411,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5556,7 +5555,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE34" t="n">
         <v>8</v>
@@ -5700,7 +5699,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5844,7 +5843,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5988,7 +5987,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6132,7 +6131,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6276,7 +6275,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6420,7 +6419,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6564,7 +6563,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6708,7 +6707,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6852,7 +6851,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6996,7 +6995,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7140,7 +7139,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7284,7 +7283,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7428,7 +7427,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7572,7 +7571,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7716,7 +7715,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7860,7 +7859,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8004,7 +8003,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8148,7 +8147,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8292,7 +8291,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8436,7 +8435,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8580,7 +8579,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8724,7 +8723,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8868,7 +8867,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9012,7 +9011,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9156,7 +9155,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9300,7 +9299,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9444,7 +9443,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9588,7 +9587,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9732,7 +9731,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9876,7 +9875,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10020,7 +10019,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10164,7 +10163,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10308,7 +10307,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10452,7 +10451,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10596,7 +10595,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10740,7 +10739,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10884,7 +10883,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11028,7 +11027,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11172,7 +11171,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11316,7 +11315,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11460,7 +11459,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11604,7 +11603,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11748,7 +11747,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11892,7 +11891,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12036,7 +12035,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12180,7 +12179,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12324,7 +12323,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12468,7 +12467,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12612,7 +12611,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12756,7 +12755,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12900,7 +12899,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13044,7 +13043,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13188,7 +13187,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13332,7 +13331,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13476,7 +13475,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13620,7 +13619,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13764,7 +13763,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13908,7 +13907,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14052,7 +14051,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14196,7 +14195,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14340,7 +14339,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14484,7 +14483,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14628,7 +14627,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14772,7 +14771,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14916,7 +14915,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15060,7 +15059,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15204,7 +15203,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15348,7 +15347,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -15492,7 +15491,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15636,7 +15635,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15780,7 +15779,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15924,7 +15923,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16068,7 +16067,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16212,7 +16211,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16356,7 +16355,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -16500,7 +16499,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16644,7 +16643,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16788,7 +16787,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16932,7 +16931,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17076,7 +17075,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17220,7 +17219,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17364,7 +17363,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -17508,7 +17507,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17652,7 +17651,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17796,7 +17795,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17940,7 +17939,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18084,7 +18083,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18228,7 +18227,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -18372,7 +18371,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -18516,7 +18515,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18660,7 +18659,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18804,7 +18803,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18948,7 +18947,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19092,7 +19091,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19236,7 +19235,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -19380,7 +19379,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -19524,7 +19523,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -19668,7 +19667,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19812,7 +19811,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19956,7 +19955,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20100,7 +20099,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20244,7 +20243,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20388,7 +20387,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20532,7 +20531,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20676,7 +20675,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20820,7 +20819,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20964,7 +20963,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21108,7 +21107,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21252,7 +21251,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21396,7 +21395,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21540,7 +21539,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21684,7 +21683,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21828,7 +21827,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21972,7 +21971,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22116,7 +22115,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22260,7 +22259,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22404,7 +22403,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22548,7 +22547,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22692,7 +22691,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22836,7 +22835,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22980,7 +22979,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23124,7 +23123,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23268,7 +23267,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23412,7 +23411,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23556,7 +23555,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23700,7 +23699,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23844,7 +23843,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23988,7 +23987,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24132,7 +24131,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24276,7 +24275,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24420,7 +24419,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24564,7 +24563,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24708,7 +24707,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24852,7 +24851,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24996,7 +24995,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25140,7 +25139,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25284,7 +25283,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25428,7 +25427,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25572,7 +25571,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25716,7 +25715,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25860,7 +25859,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26004,7 +26003,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -26148,7 +26147,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26292,7 +26291,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26436,7 +26435,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26580,7 +26579,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26724,7 +26723,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26868,7 +26867,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27012,7 +27011,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -27156,7 +27155,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27300,7 +27299,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27444,7 +27443,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27588,7 +27587,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27732,7 +27731,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27876,7 +27875,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28020,7 +28019,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -28164,7 +28163,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28308,7 +28307,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28452,7 +28451,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28596,7 +28595,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28740,7 +28739,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28884,7 +28883,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29028,7 +29027,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -29172,7 +29171,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29316,7 +29315,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29460,7 +29459,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29604,7 +29603,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29748,7 +29747,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29892,7 +29891,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30036,7 +30035,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -30180,7 +30179,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30324,7 +30323,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30468,7 +30467,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30612,7 +30611,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30756,7 +30755,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30900,7 +30899,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31044,7 +31043,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -31188,7 +31187,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE212" t="n">
         <v>3</v>
@@ -31332,7 +31331,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31476,7 +31475,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31620,7 +31619,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -31764,7 +31763,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE216" t="n">
         <v>3</v>
@@ -31908,7 +31907,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32052,7 +32051,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -32196,7 +32195,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -32340,7 +32339,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32484,7 +32483,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32628,7 +32627,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32772,7 +32771,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -32916,7 +32915,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33060,7 +33059,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -33204,7 +33203,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -33348,7 +33347,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33492,7 +33491,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33636,7 +33635,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33780,7 +33779,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -33924,7 +33923,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34068,7 +34067,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -34212,7 +34211,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -34356,7 +34355,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34500,7 +34499,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34644,7 +34643,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34788,7 +34787,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -34932,7 +34931,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35076,7 +35075,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -35220,7 +35219,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -35370,7 +35369,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>686310747217632</v>
+        <v>2058932241652896</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35514,7 +35513,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35658,7 +35657,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35802,7 +35801,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -35946,7 +35945,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -36090,7 +36089,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -36244,7 +36243,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>594796603828986</v>
+        <v>1784389811486958</v>
       </c>
       <c r="AE247" t="n">
         <v>5</v>
@@ -36390,7 +36389,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE248" t="n">
         <v>3</v>
@@ -36534,7 +36533,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -36686,7 +36685,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE250" t="n">
         <v>5</v>
@@ -36838,7 +36837,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE251" t="n">
         <v>229</v>
@@ -36982,7 +36981,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -37136,7 +37135,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>686868632721792</v>
+        <v>2060605898165376</v>
       </c>
       <c r="AE253" t="n">
         <v>4</v>
@@ -37280,7 +37279,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>549043018919064</v>
+        <v>1647129056757192</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -37428,7 +37427,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>686303773648830</v>
+        <v>2058911320946490</v>
       </c>
       <c r="AE255" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>2475777316792446</v>
+        <v>7427331950377338</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1693447500740076</v>
+        <v>5080342502220228</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE6" t="n">
         <v>19</v>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE7" t="n">
         <v>7</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1652212788413850</v>
+        <v>4956638365241550</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1786105568815239</v>
+        <v>5358316706445717</v>
       </c>
       <c r="AE15" t="n">
         <v>3</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1784975850668610</v>
+        <v>5354927552005830</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE19" t="n">
         <v>5</v>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE22" t="n">
         <v>11</v>
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE23" t="n">
         <v>11</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE25" t="n">
         <v>3</v>
@@ -4383,7 +4383,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE26" t="n">
         <v>3</v>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE27" t="n">
         <v>3</v>
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE28" t="n">
         <v>18</v>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE29" t="n">
         <v>4</v>
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE30" t="n">
         <v>4</v>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE31" t="n">
         <v>4</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE34" t="n">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -6851,7 +6851,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -6995,7 +6995,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7139,7 +7139,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7427,7 +7427,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8291,7 +8291,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8435,7 +8435,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9587,7 +9587,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10163,7 +10163,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -10739,7 +10739,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -10883,7 +10883,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11027,7 +11027,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11171,7 +11171,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11315,7 +11315,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -11747,7 +11747,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -11891,7 +11891,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12323,7 +12323,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12467,7 +12467,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -12611,7 +12611,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13043,7 +13043,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13187,7 +13187,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13331,7 +13331,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -13619,7 +13619,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -13763,7 +13763,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14051,7 +14051,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14195,7 +14195,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14339,7 +14339,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14483,7 +14483,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -14627,7 +14627,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -14771,7 +14771,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -14915,7 +14915,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15059,7 +15059,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15203,7 +15203,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15347,7 +15347,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -15491,7 +15491,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -15635,7 +15635,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -15779,7 +15779,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -15923,7 +15923,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16211,7 +16211,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16355,7 +16355,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -16499,7 +16499,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -16643,7 +16643,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -16787,7 +16787,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -16931,7 +16931,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17075,7 +17075,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17219,7 +17219,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17363,7 +17363,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -17507,7 +17507,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -17651,7 +17651,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -17795,7 +17795,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -17939,7 +17939,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18083,7 +18083,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -18371,7 +18371,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -18515,7 +18515,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -18659,7 +18659,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -18947,7 +18947,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19091,7 +19091,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -19379,7 +19379,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -19523,7 +19523,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -19667,7 +19667,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -19811,7 +19811,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -19955,7 +19955,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20099,7 +20099,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20243,7 +20243,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -20387,7 +20387,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -20531,7 +20531,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -20675,7 +20675,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -20819,7 +20819,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -20963,7 +20963,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21107,7 +21107,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -21251,7 +21251,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -21395,7 +21395,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -21539,7 +21539,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -21683,7 +21683,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -21827,7 +21827,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -21971,7 +21971,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22115,7 +22115,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -22259,7 +22259,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -22403,7 +22403,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -22547,7 +22547,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -22691,7 +22691,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -22835,7 +22835,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -22979,7 +22979,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23123,7 +23123,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -23267,7 +23267,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -23411,7 +23411,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -23555,7 +23555,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -23699,7 +23699,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -23987,7 +23987,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -24131,7 +24131,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -24275,7 +24275,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -24419,7 +24419,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -24563,7 +24563,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -24707,7 +24707,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -24995,7 +24995,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -25139,7 +25139,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -25283,7 +25283,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -25427,7 +25427,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -25571,7 +25571,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -25715,7 +25715,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -25859,7 +25859,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26003,7 +26003,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -26147,7 +26147,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -26291,7 +26291,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -26435,7 +26435,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -26579,7 +26579,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -26723,7 +26723,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -26867,7 +26867,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -27011,7 +27011,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -27155,7 +27155,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -27299,7 +27299,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -27443,7 +27443,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -27587,7 +27587,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -27731,7 +27731,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -27875,7 +27875,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -28163,7 +28163,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -28307,7 +28307,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -28451,7 +28451,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -28595,7 +28595,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -28739,7 +28739,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -28883,7 +28883,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -29027,7 +29027,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -29171,7 +29171,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -29315,7 +29315,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -29459,7 +29459,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -29603,7 +29603,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -29747,7 +29747,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -29891,7 +29891,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -30035,7 +30035,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -30179,7 +30179,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -30323,7 +30323,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -30467,7 +30467,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -30611,7 +30611,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -30755,7 +30755,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -30899,7 +30899,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -31043,7 +31043,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -31187,7 +31187,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE212" t="n">
         <v>3</v>
@@ -31331,7 +31331,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -31475,7 +31475,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -31619,7 +31619,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -31763,7 +31763,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE216" t="n">
         <v>3</v>
@@ -31907,7 +31907,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -32051,7 +32051,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -32195,7 +32195,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -32339,7 +32339,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -32483,7 +32483,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -32627,7 +32627,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -32771,7 +32771,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -32915,7 +32915,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -33059,7 +33059,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -33203,7 +33203,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -33347,7 +33347,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -33491,7 +33491,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -33779,7 +33779,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -33923,7 +33923,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -34067,7 +34067,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -34211,7 +34211,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -34355,7 +34355,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -34499,7 +34499,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -34643,7 +34643,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -34787,7 +34787,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -34931,7 +34931,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -35075,7 +35075,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -35219,7 +35219,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -35369,7 +35369,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>2058932241652896</v>
+        <v>6176796724958688</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -35513,7 +35513,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -35657,7 +35657,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -35801,7 +35801,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -35945,7 +35945,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>
@@ -36089,7 +36089,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>
@@ -36243,7 +36243,7 @@
         </is>
       </c>
       <c r="AD247" t="n">
-        <v>1784389811486958</v>
+        <v>5353169434460874</v>
       </c>
       <c r="AE247" t="n">
         <v>5</v>
@@ -36389,7 +36389,7 @@
         </is>
       </c>
       <c r="AD248" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE248" t="n">
         <v>3</v>
@@ -36533,7 +36533,7 @@
         </is>
       </c>
       <c r="AD249" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE249" t="n">
         <v>2</v>
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="AD250" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE250" t="n">
         <v>5</v>
@@ -36837,7 +36837,7 @@
         </is>
       </c>
       <c r="AD251" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE251" t="n">
         <v>229</v>
@@ -36981,7 +36981,7 @@
         </is>
       </c>
       <c r="AD252" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE252" t="n">
         <v>2</v>
@@ -37135,7 +37135,7 @@
         </is>
       </c>
       <c r="AD253" t="n">
-        <v>2060605898165376</v>
+        <v>6181817694496128</v>
       </c>
       <c r="AE253" t="n">
         <v>4</v>
@@ -37279,7 +37279,7 @@
         </is>
       </c>
       <c r="AD254" t="n">
-        <v>1647129056757192</v>
+        <v>4941387170271576</v>
       </c>
       <c r="AE254" t="n">
         <v>2</v>
@@ -37427,7 +37427,7 @@
         </is>
       </c>
       <c r="AD255" t="n">
-        <v>2058911320946490</v>
+        <v>6176733962839470</v>
       </c>
       <c r="AE255" t="n">
         <v>3</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE4" t="n">
         <v>7</v>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE8" t="n">
         <v>3</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE14" t="n">
         <v>11</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE19" t="n">
         <v>4</v>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>5.559060566555523e+16</v>
+        <v>1.667718169966657e+17</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE25" t="n">
         <v>4</v>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>4.460974528876827e+16</v>
+        <v>1.338292358663048e+17</v>
       </c>
       <c r="AE26" t="n">
         <v>2</v>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>5.929664604485323e+16</v>
+        <v>1.778899381345597e+17</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12295,7 +12295,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12745,7 +12745,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14395,7 +14395,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14695,7 +14695,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14845,7 +14845,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14995,7 +14995,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15595,7 +15595,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16045,7 +16045,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16645,7 +16645,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17095,7 +17095,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17395,7 +17395,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17695,7 +17695,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17845,7 +17845,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18445,7 +18445,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18595,7 +18595,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18745,7 +18745,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18895,7 +18895,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19045,7 +19045,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19345,7 +19345,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19495,7 +19495,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19645,7 +19645,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19795,7 +19795,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20095,7 +20095,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20545,7 +20545,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20695,7 +20695,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20845,7 +20845,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20995,7 +20995,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21145,7 +21145,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21295,7 +21295,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21445,7 +21445,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21745,7 +21745,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22195,7 +22195,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22495,7 +22495,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22645,7 +22645,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22795,7 +22795,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23095,7 +23095,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23245,7 +23245,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23395,7 +23395,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23545,7 +23545,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23695,7 +23695,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23845,7 +23845,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23995,7 +23995,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24295,7 +24295,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24595,7 +24595,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24745,7 +24745,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24895,7 +24895,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25045,7 +25045,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25195,7 +25195,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25345,7 +25345,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25495,7 +25495,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25795,7 +25795,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26395,7 +26395,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26695,7 +26695,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26845,7 +26845,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26995,7 +26995,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27145,7 +27145,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27445,7 +27445,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27595,7 +27595,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27745,7 +27745,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27895,7 +27895,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28045,7 +28045,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28195,7 +28195,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28495,7 +28495,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28795,7 +28795,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28945,7 +28945,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29095,7 +29095,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29245,7 +29245,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29395,7 +29395,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29545,7 +29545,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29695,7 +29695,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29845,7 +29845,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29995,7 +29995,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30145,7 +30145,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30295,7 +30295,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30445,7 +30445,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30595,7 +30595,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30745,7 +30745,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30895,7 +30895,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31045,7 +31045,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31345,7 +31345,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31495,7 +31495,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE206" t="n">
         <v>3</v>
@@ -31645,7 +31645,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31795,7 +31795,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31945,7 +31945,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE210" t="n">
         <v>3</v>
@@ -32245,7 +32245,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32395,7 +32395,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32545,7 +32545,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32695,7 +32695,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32845,7 +32845,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32995,7 +32995,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33145,7 +33145,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE217" t="n">
         <v>229</v>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33445,7 +33445,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33595,7 +33595,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33745,7 +33745,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33895,7 +33895,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34045,7 +34045,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34195,7 +34195,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34345,7 +34345,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34495,7 +34495,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34645,7 +34645,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34795,7 +34795,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34945,7 +34945,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35245,7 +35245,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35395,7 +35395,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35545,7 +35545,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35695,7 +35695,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35845,7 +35845,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36001,7 +36001,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>5.559117052462819e+16</v>
+        <v>1.667735115738846e+17</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36151,7 +36151,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36301,7 +36301,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36451,7 +36451,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36601,7 +36601,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36751,7 +36751,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36901,7 +36901,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37211,7 +37211,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>5.563635925046515e+16</v>
+        <v>1.669090777513955e+17</v>
       </c>
       <c r="AE244" t="n">
         <v>4</v>
@@ -37361,7 +37361,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>4.447248453244418e+16</v>
+        <v>1.334174535973325e+17</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE4" t="n">
         <v>7</v>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE8" t="n">
         <v>3</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE14" t="n">
         <v>11</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE19" t="n">
         <v>4</v>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.667718169966657e+17</v>
+        <v>5.003154509899971e+17</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE25" t="n">
         <v>4</v>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.338292358663048e+17</v>
+        <v>4.014877075989144e+17</v>
       </c>
       <c r="AE26" t="n">
         <v>2</v>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.778899381345597e+17</v>
+        <v>5.336698144036791e+17</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12295,7 +12295,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12745,7 +12745,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14395,7 +14395,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14695,7 +14695,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14845,7 +14845,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14995,7 +14995,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15595,7 +15595,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16045,7 +16045,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16645,7 +16645,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17095,7 +17095,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17395,7 +17395,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17695,7 +17695,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17845,7 +17845,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18445,7 +18445,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18595,7 +18595,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18745,7 +18745,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18895,7 +18895,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19045,7 +19045,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19345,7 +19345,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19495,7 +19495,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19645,7 +19645,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19795,7 +19795,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20095,7 +20095,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20545,7 +20545,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20695,7 +20695,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20845,7 +20845,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20995,7 +20995,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21145,7 +21145,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21295,7 +21295,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21445,7 +21445,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21745,7 +21745,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22195,7 +22195,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22495,7 +22495,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22645,7 +22645,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22795,7 +22795,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23095,7 +23095,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23245,7 +23245,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23395,7 +23395,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23545,7 +23545,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23695,7 +23695,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23845,7 +23845,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23995,7 +23995,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24295,7 +24295,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24595,7 +24595,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24745,7 +24745,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24895,7 +24895,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25045,7 +25045,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25195,7 +25195,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25345,7 +25345,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25495,7 +25495,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25795,7 +25795,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26395,7 +26395,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26695,7 +26695,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26845,7 +26845,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26995,7 +26995,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27145,7 +27145,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27445,7 +27445,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27595,7 +27595,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27745,7 +27745,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27895,7 +27895,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28045,7 +28045,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28195,7 +28195,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28495,7 +28495,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28795,7 +28795,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28945,7 +28945,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29095,7 +29095,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29245,7 +29245,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29395,7 +29395,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29545,7 +29545,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29695,7 +29695,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29845,7 +29845,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29995,7 +29995,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30145,7 +30145,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30295,7 +30295,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30445,7 +30445,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30595,7 +30595,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30745,7 +30745,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30895,7 +30895,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31045,7 +31045,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31345,7 +31345,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31495,7 +31495,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE206" t="n">
         <v>3</v>
@@ -31645,7 +31645,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31795,7 +31795,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31945,7 +31945,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE210" t="n">
         <v>3</v>
@@ -32245,7 +32245,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32395,7 +32395,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32545,7 +32545,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32695,7 +32695,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32845,7 +32845,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32995,7 +32995,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33145,7 +33145,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE217" t="n">
         <v>229</v>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33445,7 +33445,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33595,7 +33595,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33745,7 +33745,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33895,7 +33895,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34045,7 +34045,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34195,7 +34195,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34345,7 +34345,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34495,7 +34495,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34645,7 +34645,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34795,7 +34795,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34945,7 +34945,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35245,7 +35245,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35395,7 +35395,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35545,7 +35545,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35695,7 +35695,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35845,7 +35845,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36001,7 +36001,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>1.667735115738846e+17</v>
+        <v>5.003205347216538e+17</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36151,7 +36151,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36301,7 +36301,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36451,7 +36451,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36601,7 +36601,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36751,7 +36751,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36901,7 +36901,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37211,7 +37211,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>1.669090777513955e+17</v>
+        <v>5.007272332541864e+17</v>
       </c>
       <c r="AE244" t="n">
         <v>4</v>
@@ -37361,7 +37361,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>1.334174535973325e+17</v>
+        <v>4.002523607919976e+17</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -616,32 +616,32 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
+          <t>verification_schema_version</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>identity_name_verified</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>identity_specialty_verified</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>identity_evidence</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>verification_review_required</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>previous_candidate</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>verification_schema_version</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>identity_name_verified</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>identity_specialty_verified</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>identity_evidence</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE4" t="n">
         <v>7</v>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>5.007272332541864e+17</v>
+        <v>1.502181699762559e+18</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE8" t="n">
         <v>3</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>5.007272332541864e+17</v>
+        <v>1.502181699762559e+18</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE14" t="n">
         <v>11</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE19" t="n">
         <v>4</v>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>5.003154509899971e+17</v>
+        <v>1.500946352969991e+18</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE25" t="n">
         <v>4</v>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>4.014877075989144e+17</v>
+        <v>1.204463122796743e+18</v>
       </c>
       <c r="AE26" t="n">
         <v>2</v>
@@ -4502,13 +4502,13 @@
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
+      <c r="AP26" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ26" t="inlineStr"/>
       <c r="AR26" t="n">
         <v>1</v>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>5.336698144036791e+17</v>
+        <v>1.601009443211037e+18</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -4664,13 +4664,13 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="b">
-        <v>0</v>
-      </c>
+      <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
+      <c r="AP27" t="b">
+        <v>0</v>
+      </c>
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="n">
         <v>1</v>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12295,7 +12295,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12745,7 +12745,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14395,7 +14395,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14695,7 +14695,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14845,7 +14845,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14995,7 +14995,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15595,7 +15595,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16045,7 +16045,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16645,7 +16645,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17095,7 +17095,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17395,7 +17395,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17695,7 +17695,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17845,7 +17845,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18445,7 +18445,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18595,7 +18595,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18745,7 +18745,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18895,7 +18895,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19045,7 +19045,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19345,7 +19345,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19495,7 +19495,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19645,7 +19645,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19795,7 +19795,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20095,7 +20095,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20545,7 +20545,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20695,7 +20695,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20845,7 +20845,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20995,7 +20995,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21145,7 +21145,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21295,7 +21295,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21445,7 +21445,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21745,7 +21745,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22195,7 +22195,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22495,7 +22495,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22645,7 +22645,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22795,7 +22795,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23095,7 +23095,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23245,7 +23245,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23395,7 +23395,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23545,7 +23545,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23695,7 +23695,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23845,7 +23845,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23995,7 +23995,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24295,7 +24295,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24595,7 +24595,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24745,7 +24745,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24895,7 +24895,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25045,7 +25045,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25195,7 +25195,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25345,7 +25345,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25495,7 +25495,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25795,7 +25795,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26395,7 +26395,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26695,7 +26695,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26845,7 +26845,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26995,7 +26995,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27145,7 +27145,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27445,7 +27445,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27595,7 +27595,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27745,7 +27745,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27895,7 +27895,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28045,7 +28045,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28195,7 +28195,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28495,7 +28495,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28795,7 +28795,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28945,7 +28945,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29095,7 +29095,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29245,7 +29245,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29395,7 +29395,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29545,7 +29545,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29695,7 +29695,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29845,7 +29845,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29995,7 +29995,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30145,7 +30145,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30295,7 +30295,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30445,7 +30445,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30595,7 +30595,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30745,7 +30745,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30895,7 +30895,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31045,7 +31045,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31345,7 +31345,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31495,7 +31495,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE206" t="n">
         <v>3</v>
@@ -31645,7 +31645,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31795,7 +31795,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31945,7 +31945,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE210" t="n">
         <v>3</v>
@@ -32245,7 +32245,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32395,7 +32395,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32545,7 +32545,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32695,7 +32695,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32845,7 +32845,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32995,7 +32995,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33145,7 +33145,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE217" t="n">
         <v>229</v>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33445,7 +33445,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33595,7 +33595,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33745,7 +33745,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33895,7 +33895,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34045,7 +34045,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34195,7 +34195,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34345,7 +34345,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34495,7 +34495,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34645,7 +34645,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34795,7 +34795,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34945,7 +34945,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35245,7 +35245,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35395,7 +35395,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35545,7 +35545,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35695,7 +35695,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35845,7 +35845,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36001,7 +36001,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>5.003205347216538e+17</v>
+        <v>1.500961604164961e+18</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36151,7 +36151,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36301,7 +36301,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36451,7 +36451,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36601,7 +36601,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36751,7 +36751,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36901,7 +36901,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37211,7 +37211,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>5.007272332541864e+17</v>
+        <v>1.502181699762559e+18</v>
       </c>
       <c r="AE244" t="n">
         <v>4</v>
@@ -37361,7 +37361,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>4.002523607919976e+17</v>
+        <v>1.200757082375993e+18</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE4" t="n">
         <v>7</v>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE8" t="n">
         <v>3</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE14" t="n">
         <v>11</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE19" t="n">
         <v>4</v>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.500946352969991e+18</v>
+        <v>4.502839058909974e+18</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE25" t="n">
         <v>4</v>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.204463122796743e+18</v>
+        <v>3.61338936839023e+18</v>
       </c>
       <c r="AE26" t="n">
         <v>2</v>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.601009443211037e+18</v>
+        <v>4.803028329633112e+18</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12295,7 +12295,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12745,7 +12745,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14395,7 +14395,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14695,7 +14695,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14845,7 +14845,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14995,7 +14995,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15595,7 +15595,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16045,7 +16045,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16645,7 +16645,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17095,7 +17095,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17395,7 +17395,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17695,7 +17695,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17845,7 +17845,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18445,7 +18445,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18595,7 +18595,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18745,7 +18745,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18895,7 +18895,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19045,7 +19045,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19345,7 +19345,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19495,7 +19495,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19645,7 +19645,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19795,7 +19795,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20095,7 +20095,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20545,7 +20545,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20695,7 +20695,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20845,7 +20845,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20995,7 +20995,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21145,7 +21145,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21295,7 +21295,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21445,7 +21445,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21745,7 +21745,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22195,7 +22195,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22495,7 +22495,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22645,7 +22645,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22795,7 +22795,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23095,7 +23095,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23245,7 +23245,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23395,7 +23395,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23545,7 +23545,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23695,7 +23695,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23845,7 +23845,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23995,7 +23995,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24295,7 +24295,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24595,7 +24595,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24745,7 +24745,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24895,7 +24895,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25045,7 +25045,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25195,7 +25195,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25345,7 +25345,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25495,7 +25495,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25795,7 +25795,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26395,7 +26395,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26695,7 +26695,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26845,7 +26845,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26995,7 +26995,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27145,7 +27145,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27445,7 +27445,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27595,7 +27595,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27745,7 +27745,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27895,7 +27895,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28045,7 +28045,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28195,7 +28195,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28495,7 +28495,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28795,7 +28795,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28945,7 +28945,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29095,7 +29095,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29245,7 +29245,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29395,7 +29395,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29545,7 +29545,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29695,7 +29695,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29845,7 +29845,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29995,7 +29995,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30145,7 +30145,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30295,7 +30295,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30445,7 +30445,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30595,7 +30595,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30745,7 +30745,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30895,7 +30895,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31045,7 +31045,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31345,7 +31345,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31495,7 +31495,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE206" t="n">
         <v>3</v>
@@ -31645,7 +31645,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31795,7 +31795,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31945,7 +31945,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE210" t="n">
         <v>3</v>
@@ -32245,7 +32245,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32395,7 +32395,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32545,7 +32545,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32695,7 +32695,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32845,7 +32845,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32995,7 +32995,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33145,7 +33145,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE217" t="n">
         <v>229</v>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33445,7 +33445,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33595,7 +33595,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33745,7 +33745,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33895,7 +33895,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34045,7 +34045,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34195,7 +34195,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34345,7 +34345,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34495,7 +34495,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34645,7 +34645,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34795,7 +34795,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34945,7 +34945,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35245,7 +35245,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35395,7 +35395,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35545,7 +35545,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35695,7 +35695,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35845,7 +35845,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36001,7 +36001,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>1.500961604164961e+18</v>
+        <v>4.502884812494883e+18</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36151,7 +36151,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36301,7 +36301,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36451,7 +36451,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36601,7 +36601,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36751,7 +36751,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36901,7 +36901,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37211,7 +37211,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>1.502181699762559e+18</v>
+        <v>4.506545099287677e+18</v>
       </c>
       <c r="AE244" t="n">
         <v>4</v>
@@ -37361,7 +37361,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>1.200757082375993e+18</v>
+        <v>3.602271247127979e+18</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE4" t="n">
         <v>7</v>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>4.506545099287677e+18</v>
+        <v>1.351963529786303e+19</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE8" t="n">
         <v>3</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>4.506545099287677e+18</v>
+        <v>1.351963529786303e+19</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE14" t="n">
         <v>11</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE19" t="n">
         <v>4</v>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>4.502839058909974e+18</v>
+        <v>1.350851717672992e+19</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE25" t="n">
         <v>4</v>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>3.61338936839023e+18</v>
+        <v>1.084016810517069e+19</v>
       </c>
       <c r="AE26" t="n">
         <v>2</v>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>4.803028329633112e+18</v>
+        <v>1.440908498889934e+19</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12295,7 +12295,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12745,7 +12745,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14395,7 +14395,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14695,7 +14695,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14845,7 +14845,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14995,7 +14995,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15595,7 +15595,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16045,7 +16045,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16645,7 +16645,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17095,7 +17095,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17395,7 +17395,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17695,7 +17695,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17845,7 +17845,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18445,7 +18445,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18595,7 +18595,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18745,7 +18745,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18895,7 +18895,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19045,7 +19045,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19345,7 +19345,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19495,7 +19495,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19645,7 +19645,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19795,7 +19795,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20095,7 +20095,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20545,7 +20545,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20695,7 +20695,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20845,7 +20845,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20995,7 +20995,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21145,7 +21145,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21295,7 +21295,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21445,7 +21445,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21745,7 +21745,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22195,7 +22195,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22495,7 +22495,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22645,7 +22645,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22795,7 +22795,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23095,7 +23095,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23245,7 +23245,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23395,7 +23395,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23545,7 +23545,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23695,7 +23695,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23845,7 +23845,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23995,7 +23995,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24295,7 +24295,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24595,7 +24595,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24745,7 +24745,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24895,7 +24895,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25045,7 +25045,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25195,7 +25195,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25345,7 +25345,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25495,7 +25495,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25795,7 +25795,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26395,7 +26395,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26695,7 +26695,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26845,7 +26845,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26995,7 +26995,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27145,7 +27145,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27445,7 +27445,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27595,7 +27595,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27745,7 +27745,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27895,7 +27895,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28045,7 +28045,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28195,7 +28195,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28495,7 +28495,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28795,7 +28795,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28945,7 +28945,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29095,7 +29095,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29245,7 +29245,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29395,7 +29395,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29545,7 +29545,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29695,7 +29695,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29845,7 +29845,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29995,7 +29995,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30145,7 +30145,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30295,7 +30295,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30445,7 +30445,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30595,7 +30595,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30745,7 +30745,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30895,7 +30895,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31045,7 +31045,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31345,7 +31345,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31495,7 +31495,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE206" t="n">
         <v>3</v>
@@ -31645,7 +31645,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31795,7 +31795,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31945,7 +31945,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE210" t="n">
         <v>3</v>
@@ -32245,7 +32245,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32395,7 +32395,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32545,7 +32545,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32695,7 +32695,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32845,7 +32845,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32995,7 +32995,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33145,7 +33145,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE217" t="n">
         <v>229</v>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33445,7 +33445,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33595,7 +33595,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33745,7 +33745,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33895,7 +33895,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34045,7 +34045,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34195,7 +34195,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34345,7 +34345,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34495,7 +34495,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34645,7 +34645,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34795,7 +34795,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34945,7 +34945,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35245,7 +35245,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35395,7 +35395,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35545,7 +35545,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35695,7 +35695,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35845,7 +35845,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36001,7 +36001,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>4.502884812494883e+18</v>
+        <v>1.350865443748465e+19</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36151,7 +36151,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36301,7 +36301,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36451,7 +36451,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36601,7 +36601,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36751,7 +36751,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36901,7 +36901,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37211,7 +37211,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>4.506545099287677e+18</v>
+        <v>1.351963529786303e+19</v>
       </c>
       <c r="AE244" t="n">
         <v>4</v>
@@ -37361,7 +37361,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>3.602271247127979e+18</v>
+        <v>1.080681374138394e+19</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE4" t="n">
         <v>7</v>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.351963529786303e+19</v>
+        <v>4.05589058935891e+19</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE8" t="n">
         <v>3</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.351963529786303e+19</v>
+        <v>4.05589058935891e+19</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE14" t="n">
         <v>11</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE17" t="n">
         <v>2</v>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE18" t="n">
         <v>3</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE19" t="n">
         <v>4</v>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1.350851717672992e+19</v>
+        <v>4.052555153018977e+19</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4175,7 +4175,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE25" t="n">
         <v>4</v>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1.084016810517069e+19</v>
+        <v>3.252050431551207e+19</v>
       </c>
       <c r="AE26" t="n">
         <v>2</v>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>1.440908498889934e+19</v>
+        <v>4.322725496669801e+19</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7795,7 +7795,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10495,7 +10495,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12295,7 +12295,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12745,7 +12745,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14095,7 +14095,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14245,7 +14245,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14395,7 +14395,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14695,7 +14695,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14845,7 +14845,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -14995,7 +14995,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15595,7 +15595,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15895,7 +15895,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16045,7 +16045,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16345,7 +16345,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16645,7 +16645,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17095,7 +17095,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17245,7 +17245,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17395,7 +17395,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17695,7 +17695,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17845,7 +17845,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -17995,7 +17995,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18295,7 +18295,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18445,7 +18445,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18595,7 +18595,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18745,7 +18745,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18895,7 +18895,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19045,7 +19045,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19195,7 +19195,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19345,7 +19345,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19495,7 +19495,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19645,7 +19645,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19795,7 +19795,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19945,7 +19945,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20095,7 +20095,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20545,7 +20545,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20695,7 +20695,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20845,7 +20845,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -20995,7 +20995,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21145,7 +21145,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21295,7 +21295,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21445,7 +21445,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21745,7 +21745,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21895,7 +21895,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22195,7 +22195,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22495,7 +22495,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22645,7 +22645,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22795,7 +22795,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22945,7 +22945,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23095,7 +23095,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23245,7 +23245,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23395,7 +23395,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23545,7 +23545,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23695,7 +23695,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23845,7 +23845,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -23995,7 +23995,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24295,7 +24295,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24595,7 +24595,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24745,7 +24745,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24895,7 +24895,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25045,7 +25045,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25195,7 +25195,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25345,7 +25345,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25495,7 +25495,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25645,7 +25645,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25795,7 +25795,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26245,7 +26245,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26395,7 +26395,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26545,7 +26545,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26695,7 +26695,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26845,7 +26845,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -26995,7 +26995,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27145,7 +27145,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27445,7 +27445,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27595,7 +27595,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27745,7 +27745,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27895,7 +27895,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28045,7 +28045,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28195,7 +28195,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28345,7 +28345,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28495,7 +28495,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28795,7 +28795,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28945,7 +28945,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29095,7 +29095,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29245,7 +29245,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29395,7 +29395,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29545,7 +29545,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29695,7 +29695,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29845,7 +29845,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -29995,7 +29995,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30145,7 +30145,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30295,7 +30295,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30445,7 +30445,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30595,7 +30595,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30745,7 +30745,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30895,7 +30895,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31045,7 +31045,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31345,7 +31345,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31495,7 +31495,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE206" t="n">
         <v>3</v>
@@ -31645,7 +31645,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE207" t="n">
         <v>2</v>
@@ -31795,7 +31795,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31945,7 +31945,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32095,7 +32095,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE210" t="n">
         <v>3</v>
@@ -32245,7 +32245,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE211" t="n">
         <v>2</v>
@@ -32395,7 +32395,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32545,7 +32545,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32695,7 +32695,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32845,7 +32845,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -32995,7 +32995,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33145,7 +33145,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE217" t="n">
         <v>229</v>
@@ -33295,7 +33295,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE218" t="n">
         <v>2</v>
@@ -33445,7 +33445,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33595,7 +33595,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33745,7 +33745,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33895,7 +33895,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34045,7 +34045,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34195,7 +34195,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34345,7 +34345,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34495,7 +34495,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34645,7 +34645,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34795,7 +34795,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34945,7 +34945,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35245,7 +35245,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35395,7 +35395,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35545,7 +35545,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35695,7 +35695,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35845,7 +35845,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36001,7 +36001,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>1.350865443748465e+19</v>
+        <v>4.052596331245395e+19</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36151,7 +36151,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36301,7 +36301,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36451,7 +36451,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36601,7 +36601,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36751,7 +36751,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36901,7 +36901,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37211,7 +37211,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>1.351963529786303e+19</v>
+        <v>4.05589058935891e+19</v>
       </c>
       <c r="AE244" t="n">
         <v>4</v>
@@ -37361,7 +37361,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>1.080681374138394e+19</v>
+        <v>3.242044122415181e+19</v>
       </c>
       <c r="AE245" t="n">
         <v>2</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE4" t="n">
         <v>7</v>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE8" t="n">
         <v>3</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>20415</v>
+        <v>61245</v>
       </c>
       <c r="AE11" t="n">
         <v>4</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE12" t="n">
         <v>9</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE14" t="n">
         <v>7</v>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE15" t="n">
         <v>11</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.215766545905693e+20</v>
+        <v>3.647299637717079e+20</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE25" t="n">
         <v>2</v>
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>9.756151294653622e+19</v>
+        <v>2.926845388396086e+20</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.29681764900094e+20</v>
+        <v>3.890452947002821e+20</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9615,7 +9615,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9765,7 +9765,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9915,7 +9915,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10815,7 +10815,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11115,7 +11115,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11715,7 +11715,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11865,7 +11865,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12015,7 +12015,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12165,7 +12165,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12615,7 +12615,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12915,7 +12915,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13215,7 +13215,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13365,7 +13365,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13515,7 +13515,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13665,7 +13665,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13815,7 +13815,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13965,7 +13965,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14265,7 +14265,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14565,7 +14565,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14865,7 +14865,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15015,7 +15015,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15315,7 +15315,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15465,7 +15465,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15615,7 +15615,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15765,7 +15765,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15915,7 +15915,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16215,7 +16215,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16365,7 +16365,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16515,7 +16515,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16965,7 +16965,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17115,7 +17115,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17265,7 +17265,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17415,7 +17415,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17565,7 +17565,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17715,7 +17715,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18165,7 +18165,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18315,7 +18315,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18465,7 +18465,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18615,7 +18615,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18765,7 +18765,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18915,7 +18915,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19065,7 +19065,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19215,7 +19215,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19365,7 +19365,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19515,7 +19515,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19665,7 +19665,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19815,7 +19815,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19965,7 +19965,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20115,7 +20115,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20415,7 +20415,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20565,7 +20565,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20715,7 +20715,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21015,7 +21015,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21165,7 +21165,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21315,7 +21315,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21465,7 +21465,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21615,7 +21615,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21765,7 +21765,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21915,7 +21915,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22065,7 +22065,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22215,7 +22215,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22365,7 +22365,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22515,7 +22515,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22665,7 +22665,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22815,7 +22815,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22965,7 +22965,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23115,7 +23115,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23415,7 +23415,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23565,7 +23565,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23715,7 +23715,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23865,7 +23865,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24015,7 +24015,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24165,7 +24165,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24315,7 +24315,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24465,7 +24465,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24615,7 +24615,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24765,7 +24765,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24915,7 +24915,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25065,7 +25065,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25215,7 +25215,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25365,7 +25365,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25515,7 +25515,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25665,7 +25665,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25815,7 +25815,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25965,7 +25965,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26115,7 +26115,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26265,7 +26265,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26415,7 +26415,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26565,7 +26565,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26715,7 +26715,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26865,7 +26865,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27015,7 +27015,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27315,7 +27315,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27465,7 +27465,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27615,7 +27615,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27765,7 +27765,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27915,7 +27915,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28215,7 +28215,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28365,7 +28365,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28515,7 +28515,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28665,7 +28665,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28815,7 +28815,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28965,7 +28965,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29115,7 +29115,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29265,7 +29265,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29415,7 +29415,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29565,7 +29565,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29715,7 +29715,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29865,7 +29865,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -30015,7 +30015,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30165,7 +30165,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30315,7 +30315,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30465,7 +30465,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30615,7 +30615,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30765,7 +30765,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30915,7 +30915,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31065,7 +31065,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31215,7 +31215,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31365,7 +31365,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31515,7 +31515,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -31665,7 +31665,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE207" t="n">
         <v>3</v>
@@ -31815,7 +31815,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31965,7 +31965,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32115,7 +32115,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32265,7 +32265,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32565,7 +32565,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32715,7 +32715,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32865,7 +32865,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -33015,7 +33015,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33165,7 +33165,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33315,7 +33315,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE218" t="n">
         <v>229</v>
@@ -33465,7 +33465,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33615,7 +33615,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33765,7 +33765,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33915,7 +33915,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34065,7 +34065,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34215,7 +34215,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34365,7 +34365,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34665,7 +34665,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34815,7 +34815,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34965,7 +34965,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35115,7 +35115,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35265,7 +35265,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35415,7 +35415,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35565,7 +35565,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35715,7 +35715,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35865,7 +35865,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36015,7 +36015,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36171,7 +36171,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>1.215778899373619e+20</v>
+        <v>3.647336698120856e+20</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36321,7 +36321,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36471,7 +36471,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36621,7 +36621,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36771,7 +36771,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36921,7 +36921,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37071,7 +37071,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37221,7 +37221,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37381,7 +37381,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>1.216767176807673e+20</v>
+        <v>3.650301530423019e+20</v>
       </c>
       <c r="AE245" t="n">
         <v>4</v>
@@ -37531,7 +37531,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>9.726132367245543e+19</v>
+        <v>2.917839710173663e+20</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE4" t="n">
         <v>7</v>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE8" t="n">
         <v>3</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>61245</v>
+        <v>183735</v>
       </c>
       <c r="AE11" t="n">
         <v>4</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE12" t="n">
         <v>9</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE14" t="n">
         <v>7</v>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE15" t="n">
         <v>11</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>3.647299637717079e+20</v>
+        <v>1.094189891315124e+21</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE25" t="n">
         <v>2</v>
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>2.926845388396086e+20</v>
+        <v>8.780536165188259e+20</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>3.890452947002821e+20</v>
+        <v>1.167135884100846e+21</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9615,7 +9615,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9765,7 +9765,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9915,7 +9915,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10815,7 +10815,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11115,7 +11115,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11715,7 +11715,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11865,7 +11865,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12015,7 +12015,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12165,7 +12165,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12615,7 +12615,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12915,7 +12915,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13215,7 +13215,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13365,7 +13365,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13515,7 +13515,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13665,7 +13665,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13815,7 +13815,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13965,7 +13965,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14265,7 +14265,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14565,7 +14565,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14865,7 +14865,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15015,7 +15015,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15315,7 +15315,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15465,7 +15465,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15615,7 +15615,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15765,7 +15765,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15915,7 +15915,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16215,7 +16215,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16365,7 +16365,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16515,7 +16515,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16965,7 +16965,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17115,7 +17115,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17265,7 +17265,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17415,7 +17415,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17565,7 +17565,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17715,7 +17715,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18165,7 +18165,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18315,7 +18315,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18465,7 +18465,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18615,7 +18615,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18765,7 +18765,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18915,7 +18915,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19065,7 +19065,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19215,7 +19215,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19365,7 +19365,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19515,7 +19515,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19665,7 +19665,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19815,7 +19815,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19965,7 +19965,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20115,7 +20115,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20415,7 +20415,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20565,7 +20565,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20715,7 +20715,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21015,7 +21015,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21165,7 +21165,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21315,7 +21315,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21465,7 +21465,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21615,7 +21615,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21765,7 +21765,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21915,7 +21915,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22065,7 +22065,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22215,7 +22215,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22365,7 +22365,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22515,7 +22515,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22665,7 +22665,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22815,7 +22815,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22965,7 +22965,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23115,7 +23115,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23415,7 +23415,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23565,7 +23565,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23715,7 +23715,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23865,7 +23865,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24015,7 +24015,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24165,7 +24165,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24315,7 +24315,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24465,7 +24465,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24615,7 +24615,7 @@
         </is>
       </c>
       <c r="AD160" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE160" t="n">
         <v>2</v>
@@ -24765,7 +24765,7 @@
         </is>
       </c>
       <c r="AD161" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE161" t="n">
         <v>2</v>
@@ -24915,7 +24915,7 @@
         </is>
       </c>
       <c r="AD162" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE162" t="n">
         <v>2</v>
@@ -25065,7 +25065,7 @@
         </is>
       </c>
       <c r="AD163" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE163" t="n">
         <v>2</v>
@@ -25215,7 +25215,7 @@
         </is>
       </c>
       <c r="AD164" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE164" t="n">
         <v>2</v>
@@ -25365,7 +25365,7 @@
         </is>
       </c>
       <c r="AD165" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE165" t="n">
         <v>2</v>
@@ -25515,7 +25515,7 @@
         </is>
       </c>
       <c r="AD166" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE166" t="n">
         <v>2</v>
@@ -25665,7 +25665,7 @@
         </is>
       </c>
       <c r="AD167" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE167" t="n">
         <v>2</v>
@@ -25815,7 +25815,7 @@
         </is>
       </c>
       <c r="AD168" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE168" t="n">
         <v>2</v>
@@ -25965,7 +25965,7 @@
         </is>
       </c>
       <c r="AD169" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE169" t="n">
         <v>2</v>
@@ -26115,7 +26115,7 @@
         </is>
       </c>
       <c r="AD170" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE170" t="n">
         <v>2</v>
@@ -26265,7 +26265,7 @@
         </is>
       </c>
       <c r="AD171" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE171" t="n">
         <v>2</v>
@@ -26415,7 +26415,7 @@
         </is>
       </c>
       <c r="AD172" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE172" t="n">
         <v>2</v>
@@ -26565,7 +26565,7 @@
         </is>
       </c>
       <c r="AD173" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE173" t="n">
         <v>2</v>
@@ -26715,7 +26715,7 @@
         </is>
       </c>
       <c r="AD174" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE174" t="n">
         <v>2</v>
@@ -26865,7 +26865,7 @@
         </is>
       </c>
       <c r="AD175" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE175" t="n">
         <v>2</v>
@@ -27015,7 +27015,7 @@
         </is>
       </c>
       <c r="AD176" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE176" t="n">
         <v>2</v>
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="AD177" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE177" t="n">
         <v>2</v>
@@ -27315,7 +27315,7 @@
         </is>
       </c>
       <c r="AD178" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE178" t="n">
         <v>2</v>
@@ -27465,7 +27465,7 @@
         </is>
       </c>
       <c r="AD179" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE179" t="n">
         <v>2</v>
@@ -27615,7 +27615,7 @@
         </is>
       </c>
       <c r="AD180" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE180" t="n">
         <v>2</v>
@@ -27765,7 +27765,7 @@
         </is>
       </c>
       <c r="AD181" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE181" t="n">
         <v>2</v>
@@ -27915,7 +27915,7 @@
         </is>
       </c>
       <c r="AD182" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE182" t="n">
         <v>2</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="AD183" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE183" t="n">
         <v>2</v>
@@ -28215,7 +28215,7 @@
         </is>
       </c>
       <c r="AD184" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE184" t="n">
         <v>2</v>
@@ -28365,7 +28365,7 @@
         </is>
       </c>
       <c r="AD185" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE185" t="n">
         <v>2</v>
@@ -28515,7 +28515,7 @@
         </is>
       </c>
       <c r="AD186" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE186" t="n">
         <v>2</v>
@@ -28665,7 +28665,7 @@
         </is>
       </c>
       <c r="AD187" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE187" t="n">
         <v>2</v>
@@ -28815,7 +28815,7 @@
         </is>
       </c>
       <c r="AD188" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE188" t="n">
         <v>2</v>
@@ -28965,7 +28965,7 @@
         </is>
       </c>
       <c r="AD189" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE189" t="n">
         <v>2</v>
@@ -29115,7 +29115,7 @@
         </is>
       </c>
       <c r="AD190" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE190" t="n">
         <v>2</v>
@@ -29265,7 +29265,7 @@
         </is>
       </c>
       <c r="AD191" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE191" t="n">
         <v>2</v>
@@ -29415,7 +29415,7 @@
         </is>
       </c>
       <c r="AD192" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE192" t="n">
         <v>2</v>
@@ -29565,7 +29565,7 @@
         </is>
       </c>
       <c r="AD193" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE193" t="n">
         <v>2</v>
@@ -29715,7 +29715,7 @@
         </is>
       </c>
       <c r="AD194" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE194" t="n">
         <v>2</v>
@@ -29865,7 +29865,7 @@
         </is>
       </c>
       <c r="AD195" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE195" t="n">
         <v>2</v>
@@ -30015,7 +30015,7 @@
         </is>
       </c>
       <c r="AD196" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE196" t="n">
         <v>2</v>
@@ -30165,7 +30165,7 @@
         </is>
       </c>
       <c r="AD197" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE197" t="n">
         <v>2</v>
@@ -30315,7 +30315,7 @@
         </is>
       </c>
       <c r="AD198" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE198" t="n">
         <v>2</v>
@@ -30465,7 +30465,7 @@
         </is>
       </c>
       <c r="AD199" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE199" t="n">
         <v>2</v>
@@ -30615,7 +30615,7 @@
         </is>
       </c>
       <c r="AD200" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE200" t="n">
         <v>2</v>
@@ -30765,7 +30765,7 @@
         </is>
       </c>
       <c r="AD201" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE201" t="n">
         <v>2</v>
@@ -30915,7 +30915,7 @@
         </is>
       </c>
       <c r="AD202" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE202" t="n">
         <v>2</v>
@@ -31065,7 +31065,7 @@
         </is>
       </c>
       <c r="AD203" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE203" t="n">
         <v>2</v>
@@ -31215,7 +31215,7 @@
         </is>
       </c>
       <c r="AD204" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE204" t="n">
         <v>2</v>
@@ -31365,7 +31365,7 @@
         </is>
       </c>
       <c r="AD205" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE205" t="n">
         <v>2</v>
@@ -31515,7 +31515,7 @@
         </is>
       </c>
       <c r="AD206" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE206" t="n">
         <v>2</v>
@@ -31665,7 +31665,7 @@
         </is>
       </c>
       <c r="AD207" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE207" t="n">
         <v>3</v>
@@ -31815,7 +31815,7 @@
         </is>
       </c>
       <c r="AD208" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE208" t="n">
         <v>2</v>
@@ -31965,7 +31965,7 @@
         </is>
       </c>
       <c r="AD209" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE209" t="n">
         <v>2</v>
@@ -32115,7 +32115,7 @@
         </is>
       </c>
       <c r="AD210" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE210" t="n">
         <v>2</v>
@@ -32265,7 +32265,7 @@
         </is>
       </c>
       <c r="AD211" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE211" t="n">
         <v>3</v>
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="AD212" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE212" t="n">
         <v>2</v>
@@ -32565,7 +32565,7 @@
         </is>
       </c>
       <c r="AD213" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE213" t="n">
         <v>2</v>
@@ -32715,7 +32715,7 @@
         </is>
       </c>
       <c r="AD214" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE214" t="n">
         <v>2</v>
@@ -32865,7 +32865,7 @@
         </is>
       </c>
       <c r="AD215" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE215" t="n">
         <v>2</v>
@@ -33015,7 +33015,7 @@
         </is>
       </c>
       <c r="AD216" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE216" t="n">
         <v>2</v>
@@ -33165,7 +33165,7 @@
         </is>
       </c>
       <c r="AD217" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE217" t="n">
         <v>2</v>
@@ -33315,7 +33315,7 @@
         </is>
       </c>
       <c r="AD218" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE218" t="n">
         <v>229</v>
@@ -33465,7 +33465,7 @@
         </is>
       </c>
       <c r="AD219" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE219" t="n">
         <v>2</v>
@@ -33615,7 +33615,7 @@
         </is>
       </c>
       <c r="AD220" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE220" t="n">
         <v>2</v>
@@ -33765,7 +33765,7 @@
         </is>
       </c>
       <c r="AD221" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE221" t="n">
         <v>2</v>
@@ -33915,7 +33915,7 @@
         </is>
       </c>
       <c r="AD222" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE222" t="n">
         <v>2</v>
@@ -34065,7 +34065,7 @@
         </is>
       </c>
       <c r="AD223" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE223" t="n">
         <v>2</v>
@@ -34215,7 +34215,7 @@
         </is>
       </c>
       <c r="AD224" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE224" t="n">
         <v>2</v>
@@ -34365,7 +34365,7 @@
         </is>
       </c>
       <c r="AD225" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE225" t="n">
         <v>2</v>
@@ -34515,7 +34515,7 @@
         </is>
       </c>
       <c r="AD226" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE226" t="n">
         <v>2</v>
@@ -34665,7 +34665,7 @@
         </is>
       </c>
       <c r="AD227" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE227" t="n">
         <v>2</v>
@@ -34815,7 +34815,7 @@
         </is>
       </c>
       <c r="AD228" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE228" t="n">
         <v>2</v>
@@ -34965,7 +34965,7 @@
         </is>
       </c>
       <c r="AD229" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE229" t="n">
         <v>2</v>
@@ -35115,7 +35115,7 @@
         </is>
       </c>
       <c r="AD230" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE230" t="n">
         <v>2</v>
@@ -35265,7 +35265,7 @@
         </is>
       </c>
       <c r="AD231" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE231" t="n">
         <v>2</v>
@@ -35415,7 +35415,7 @@
         </is>
       </c>
       <c r="AD232" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE232" t="n">
         <v>2</v>
@@ -35565,7 +35565,7 @@
         </is>
       </c>
       <c r="AD233" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE233" t="n">
         <v>2</v>
@@ -35715,7 +35715,7 @@
         </is>
       </c>
       <c r="AD234" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE234" t="n">
         <v>2</v>
@@ -35865,7 +35865,7 @@
         </is>
       </c>
       <c r="AD235" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE235" t="n">
         <v>2</v>
@@ -36015,7 +36015,7 @@
         </is>
       </c>
       <c r="AD236" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE236" t="n">
         <v>2</v>
@@ -36171,7 +36171,7 @@
         </is>
       </c>
       <c r="AD237" t="n">
-        <v>3.647336698120856e+20</v>
+        <v>1.094201009436257e+21</v>
       </c>
       <c r="AE237" t="n">
         <v>2</v>
@@ -36321,7 +36321,7 @@
         </is>
       </c>
       <c r="AD238" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE238" t="n">
         <v>2</v>
@@ -36471,7 +36471,7 @@
         </is>
       </c>
       <c r="AD239" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE239" t="n">
         <v>2</v>
@@ -36621,7 +36621,7 @@
         </is>
       </c>
       <c r="AD240" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE240" t="n">
         <v>2</v>
@@ -36771,7 +36771,7 @@
         </is>
       </c>
       <c r="AD241" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE241" t="n">
         <v>2</v>
@@ -36921,7 +36921,7 @@
         </is>
       </c>
       <c r="AD242" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE242" t="n">
         <v>2</v>
@@ -37071,7 +37071,7 @@
         </is>
       </c>
       <c r="AD243" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE243" t="n">
         <v>2</v>
@@ -37221,7 +37221,7 @@
         </is>
       </c>
       <c r="AD244" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE244" t="n">
         <v>2</v>
@@ -37381,7 +37381,7 @@
         </is>
       </c>
       <c r="AD245" t="n">
-        <v>3.650301530423019e+20</v>
+        <v>1.095090459126906e+21</v>
       </c>
       <c r="AE245" t="n">
         <v>4</v>
@@ -37531,7 +37531,7 @@
         </is>
       </c>
       <c r="AD246" t="n">
-        <v>2.917839710173663e+20</v>
+        <v>8.753519130520989e+20</v>
       </c>
       <c r="AE246" t="n">
         <v>2</v>

--- a/output/contacts_shared.xlsx
+++ b/output/contacts_shared.xlsx
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE4" t="n">
         <v>7</v>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE8" t="n">
         <v>3</v>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE9" t="n">
         <v>3</v>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>1.095090459126906e+21</v>
+        <v>3.285271377380717e+21</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>183735</v>
+        <v>551205</v>
       </c>
       <c r="AE11" t="n">
         <v>4</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE12" t="n">
         <v>9</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE14" t="n">
         <v>7</v>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE15" t="n">
         <v>11</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE18" t="n">
         <v>2</v>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE19" t="n">
         <v>3</v>
@@ -3587,7 +3587,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>1.094189891315124e+21</v>
+        <v>3.282569673945371e+21</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="AD25" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE25" t="n">
         <v>2</v>
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="AD27" t="n">
-        <v>8.780536165188259e+20</v>
+        <v>2.634160849556478e+21</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="AD28" t="n">
-        <v>1.167135884100846e+21</v>
+        <v>3.501407652302539e+21</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="AD29" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="AD30" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="AD31" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE31" t="n">
         <v>2</v>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="AD32" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE32" t="n">
         <v>2</v>
@@ -5565,7 +5565,7 @@
         </is>
       </c>
       <c r="AD33" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE33" t="n">
         <v>2</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="AD34" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE34" t="n">
         <v>2</v>
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="AD35" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE35" t="n">
         <v>2</v>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="AD36" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE36" t="n">
         <v>2</v>
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="AD37" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE37" t="n">
         <v>2</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="AD38" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE38" t="n">
         <v>2</v>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="AD39" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE39" t="n">
         <v>2</v>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="AD40" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE40" t="n">
         <v>2</v>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="AD41" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE41" t="n">
         <v>2</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="AD42" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE42" t="n">
         <v>2</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="AD43" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE43" t="n">
         <v>2</v>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="AD44" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE44" t="n">
         <v>2</v>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="AD45" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE45" t="n">
         <v>2</v>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="AD46" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE46" t="n">
         <v>2</v>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="AD47" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE47" t="n">
         <v>2</v>
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="AD48" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE48" t="n">
         <v>2</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="AD49" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE49" t="n">
         <v>2</v>
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="AD50" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE50" t="n">
         <v>2</v>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="AD51" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE51" t="n">
         <v>2</v>
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="AD52" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE52" t="n">
         <v>2</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="AD53" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE53" t="n">
         <v>2</v>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="AD54" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE54" t="n">
         <v>2</v>
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="AD55" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE55" t="n">
         <v>2</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="AD56" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE56" t="n">
         <v>2</v>
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="AD57" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE57" t="n">
         <v>2</v>
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="AD58" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE58" t="n">
         <v>2</v>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="AD59" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE59" t="n">
         <v>2</v>
@@ -9615,7 +9615,7 @@
         </is>
       </c>
       <c r="AD60" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE60" t="n">
         <v>2</v>
@@ -9765,7 +9765,7 @@
         </is>
       </c>
       <c r="AD61" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE61" t="n">
         <v>2</v>
@@ -9915,7 +9915,7 @@
         </is>
       </c>
       <c r="AD62" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE62" t="n">
         <v>2</v>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="AD63" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE63" t="n">
         <v>2</v>
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="AD64" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE64" t="n">
         <v>2</v>
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="AD65" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE65" t="n">
         <v>2</v>
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="AD66" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE66" t="n">
         <v>2</v>
@@ -10665,7 +10665,7 @@
         </is>
       </c>
       <c r="AD67" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE67" t="n">
         <v>2</v>
@@ -10815,7 +10815,7 @@
         </is>
       </c>
       <c r="AD68" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE68" t="n">
         <v>2</v>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="AD69" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE69" t="n">
         <v>2</v>
@@ -11115,7 +11115,7 @@
         </is>
       </c>
       <c r="AD70" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE70" t="n">
         <v>2</v>
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="AD71" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE71" t="n">
         <v>2</v>
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="AD72" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE72" t="n">
         <v>2</v>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="AD73" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE73" t="n">
         <v>2</v>
@@ -11715,7 +11715,7 @@
         </is>
       </c>
       <c r="AD74" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE74" t="n">
         <v>2</v>
@@ -11865,7 +11865,7 @@
         </is>
       </c>
       <c r="AD75" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE75" t="n">
         <v>2</v>
@@ -12015,7 +12015,7 @@
         </is>
       </c>
       <c r="AD76" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE76" t="n">
         <v>2</v>
@@ -12165,7 +12165,7 @@
         </is>
       </c>
       <c r="AD77" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE77" t="n">
         <v>2</v>
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="AD78" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE78" t="n">
         <v>2</v>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="AD79" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE79" t="n">
         <v>2</v>
@@ -12615,7 +12615,7 @@
         </is>
       </c>
       <c r="AD80" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE80" t="n">
         <v>2</v>
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="AD81" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE81" t="n">
         <v>2</v>
@@ -12915,7 +12915,7 @@
         </is>
       </c>
       <c r="AD82" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE82" t="n">
         <v>2</v>
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="AD83" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE83" t="n">
         <v>2</v>
@@ -13215,7 +13215,7 @@
         </is>
       </c>
       <c r="AD84" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE84" t="n">
         <v>2</v>
@@ -13365,7 +13365,7 @@
         </is>
       </c>
       <c r="AD85" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE85" t="n">
         <v>2</v>
@@ -13515,7 +13515,7 @@
         </is>
       </c>
       <c r="AD86" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE86" t="n">
         <v>2</v>
@@ -13665,7 +13665,7 @@
         </is>
       </c>
       <c r="AD87" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE87" t="n">
         <v>2</v>
@@ -13815,7 +13815,7 @@
         </is>
       </c>
       <c r="AD88" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE88" t="n">
         <v>2</v>
@@ -13965,7 +13965,7 @@
         </is>
       </c>
       <c r="AD89" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE89" t="n">
         <v>2</v>
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="AD90" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE90" t="n">
         <v>2</v>
@@ -14265,7 +14265,7 @@
         </is>
       </c>
       <c r="AD91" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE91" t="n">
         <v>2</v>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="AD92" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE92" t="n">
         <v>2</v>
@@ -14565,7 +14565,7 @@
         </is>
       </c>
       <c r="AD93" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE93" t="n">
         <v>2</v>
@@ -14715,7 +14715,7 @@
         </is>
       </c>
       <c r="AD94" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE94" t="n">
         <v>2</v>
@@ -14865,7 +14865,7 @@
         </is>
       </c>
       <c r="AD95" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE95" t="n">
         <v>2</v>
@@ -15015,7 +15015,7 @@
         </is>
       </c>
       <c r="AD96" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE96" t="n">
         <v>2</v>
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="AD97" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE97" t="n">
         <v>2</v>
@@ -15315,7 +15315,7 @@
         </is>
       </c>
       <c r="AD98" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE98" t="n">
         <v>2</v>
@@ -15465,7 +15465,7 @@
         </is>
       </c>
       <c r="AD99" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE99" t="n">
         <v>2</v>
@@ -15615,7 +15615,7 @@
         </is>
       </c>
       <c r="AD100" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE100" t="n">
         <v>2</v>
@@ -15765,7 +15765,7 @@
         </is>
       </c>
       <c r="AD101" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE101" t="n">
         <v>2</v>
@@ -15915,7 +15915,7 @@
         </is>
       </c>
       <c r="AD102" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE102" t="n">
         <v>2</v>
@@ -16065,7 +16065,7 @@
         </is>
       </c>
       <c r="AD103" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE103" t="n">
         <v>2</v>
@@ -16215,7 +16215,7 @@
         </is>
       </c>
       <c r="AD104" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE104" t="n">
         <v>2</v>
@@ -16365,7 +16365,7 @@
         </is>
       </c>
       <c r="AD105" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE105" t="n">
         <v>2</v>
@@ -16515,7 +16515,7 @@
         </is>
       </c>
       <c r="AD106" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE106" t="n">
         <v>2</v>
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="AD107" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE107" t="n">
         <v>2</v>
@@ -16815,7 +16815,7 @@
         </is>
       </c>
       <c r="AD108" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE108" t="n">
         <v>2</v>
@@ -16965,7 +16965,7 @@
         </is>
       </c>
       <c r="AD109" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE109" t="n">
         <v>2</v>
@@ -17115,7 +17115,7 @@
         </is>
       </c>
       <c r="AD110" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE110" t="n">
         <v>2</v>
@@ -17265,7 +17265,7 @@
         </is>
       </c>
       <c r="AD111" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE111" t="n">
         <v>2</v>
@@ -17415,7 +17415,7 @@
         </is>
       </c>
       <c r="AD112" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE112" t="n">
         <v>2</v>
@@ -17565,7 +17565,7 @@
         </is>
       </c>
       <c r="AD113" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE113" t="n">
         <v>2</v>
@@ -17715,7 +17715,7 @@
         </is>
       </c>
       <c r="AD114" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE114" t="n">
         <v>2</v>
@@ -17865,7 +17865,7 @@
         </is>
       </c>
       <c r="AD115" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE115" t="n">
         <v>2</v>
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="AD116" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE116" t="n">
         <v>2</v>
@@ -18165,7 +18165,7 @@
         </is>
       </c>
       <c r="AD117" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE117" t="n">
         <v>2</v>
@@ -18315,7 +18315,7 @@
         </is>
       </c>
       <c r="AD118" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE118" t="n">
         <v>2</v>
@@ -18465,7 +18465,7 @@
         </is>
       </c>
       <c r="AD119" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE119" t="n">
         <v>2</v>
@@ -18615,7 +18615,7 @@
         </is>
       </c>
       <c r="AD120" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE120" t="n">
         <v>2</v>
@@ -18765,7 +18765,7 @@
         </is>
       </c>
       <c r="AD121" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE121" t="n">
         <v>2</v>
@@ -18915,7 +18915,7 @@
         </is>
       </c>
       <c r="AD122" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE122" t="n">
         <v>2</v>
@@ -19065,7 +19065,7 @@
         </is>
       </c>
       <c r="AD123" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE123" t="n">
         <v>2</v>
@@ -19215,7 +19215,7 @@
         </is>
       </c>
       <c r="AD124" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE124" t="n">
         <v>2</v>
@@ -19365,7 +19365,7 @@
         </is>
       </c>
       <c r="AD125" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE125" t="n">
         <v>2</v>
@@ -19515,7 +19515,7 @@
         </is>
       </c>
       <c r="AD126" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE126" t="n">
         <v>2</v>
@@ -19665,7 +19665,7 @@
         </is>
       </c>
       <c r="AD127" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE127" t="n">
         <v>2</v>
@@ -19815,7 +19815,7 @@
         </is>
       </c>
       <c r="AD128" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE128" t="n">
         <v>2</v>
@@ -19965,7 +19965,7 @@
         </is>
       </c>
       <c r="AD129" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE129" t="n">
         <v>2</v>
@@ -20115,7 +20115,7 @@
         </is>
       </c>
       <c r="AD130" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE130" t="n">
         <v>2</v>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AD131" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE131" t="n">
         <v>2</v>
@@ -20415,7 +20415,7 @@
         </is>
       </c>
       <c r="AD132" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE132" t="n">
         <v>2</v>
@@ -20565,7 +20565,7 @@
         </is>
       </c>
       <c r="AD133" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE133" t="n">
         <v>2</v>
@@ -20715,7 +20715,7 @@
         </is>
       </c>
       <c r="AD134" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE134" t="n">
         <v>2</v>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="AD135" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE135" t="n">
         <v>2</v>
@@ -21015,7 +21015,7 @@
         </is>
       </c>
       <c r="AD136" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE136" t="n">
         <v>2</v>
@@ -21165,7 +21165,7 @@
         </is>
       </c>
       <c r="AD137" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE137" t="n">
         <v>2</v>
@@ -21315,7 +21315,7 @@
         </is>
       </c>
       <c r="AD138" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE138" t="n">
         <v>2</v>
@@ -21465,7 +21465,7 @@
         </is>
       </c>
       <c r="AD139" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE139" t="n">
         <v>2</v>
@@ -21615,7 +21615,7 @@
         </is>
       </c>
       <c r="AD140" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE140" t="n">
         <v>2</v>
@@ -21765,7 +21765,7 @@
         </is>
       </c>
       <c r="AD141" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE141" t="n">
         <v>2</v>
@@ -21915,7 +21915,7 @@
         </is>
       </c>
       <c r="AD142" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE142" t="n">
         <v>2</v>
@@ -22065,7 +22065,7 @@
         </is>
       </c>
       <c r="AD143" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE143" t="n">
         <v>2</v>
@@ -22215,7 +22215,7 @@
         </is>
       </c>
       <c r="AD144" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE144" t="n">
         <v>2</v>
@@ -22365,7 +22365,7 @@
         </is>
       </c>
       <c r="AD145" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE145" t="n">
         <v>2</v>
@@ -22515,7 +22515,7 @@
         </is>
       </c>
       <c r="AD146" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE146" t="n">
         <v>2</v>
@@ -22665,7 +22665,7 @@
         </is>
       </c>
       <c r="AD147" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE147" t="n">
         <v>2</v>
@@ -22815,7 +22815,7 @@
         </is>
       </c>
       <c r="AD148" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE148" t="n">
         <v>2</v>
@@ -22965,7 +22965,7 @@
         </is>
       </c>
       <c r="AD149" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE149" t="n">
         <v>2</v>
@@ -23115,7 +23115,7 @@
         </is>
       </c>
       <c r="AD150" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE150" t="n">
         <v>2</v>
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="AD151" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE151" t="n">
         <v>2</v>
@@ -23415,7 +23415,7 @@
         </is>
       </c>
       <c r="AD152" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE152" t="n">
         <v>2</v>
@@ -23565,7 +23565,7 @@
         </is>
       </c>
       <c r="AD153" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE153" t="n">
         <v>2</v>
@@ -23715,7 +23715,7 @@
         </is>
       </c>
       <c r="AD154" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE154" t="n">
         <v>2</v>
@@ -23865,7 +23865,7 @@
         </is>
       </c>
       <c r="AD155" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE155" t="n">
         <v>2</v>
@@ -24015,7 +24015,7 @@
         </is>
       </c>
       <c r="AD156" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE156" t="n">
         <v>2</v>
@@ -24165,7 +24165,7 @@
         </is>
       </c>
       <c r="AD157" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE157" t="n">
         <v>2</v>
@@ -24315,7 +24315,7 @@
         </is>
       </c>
       <c r="AD158" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE158" t="n">
         <v>2</v>
@@ -24465,7 +24465,7 @@
         </is>
       </c>
       <c r="AD159" t="n">
-        <v>8.753519130520989e+20</v>
+        <v>2.626055739156296e+21</v>
       </c>
       <c r="AE159" t="n">
         <v>2</v>
@@ -24615,7 +24615,7 @@
    